--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="756">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">EQUI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73039221763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76171112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75835585594177</t>
+    <t xml:space="preserve">1.73039186000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76171135902405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7583554983139</t>
   </si>
   <si>
     <t xml:space="preserve">1.75499987602234</t>
@@ -59,112 +59,112 @@
     <t xml:space="preserve">1.74493300914764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71361374855042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71808779239655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7337474822998</t>
+    <t xml:space="preserve">1.71361362934113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71808791160583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374772071838</t>
   </si>
   <si>
     <t xml:space="preserve">1.72032511234283</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70130968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70019137859344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69795393943787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68005728721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68900561332703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69571685791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69683587551117</t>
+    <t xml:space="preserve">1.7013099193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70019090175629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69795405864716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68005704879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68900573253632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69571709632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69683575630188</t>
   </si>
   <si>
     <t xml:space="preserve">1.69124293327332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70242846012115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68229448795319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68565011024475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66775345802307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69012415409088</t>
+    <t xml:space="preserve">1.70242810249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6822943687439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68564999103546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66775333881378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69012427330017</t>
   </si>
   <si>
     <t xml:space="preserve">1.71696937084198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73262917995453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72256183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72144377231598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71473264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71585094928741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74717032909393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7505259513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73934018611908</t>
+    <t xml:space="preserve">1.73262929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72256195545197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72144365310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71473217010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71585083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74717044830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75052583217621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73934042453766</t>
   </si>
   <si>
     <t xml:space="preserve">1.708580493927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71137678623199</t>
+    <t xml:space="preserve">1.71137654781342</t>
   </si>
   <si>
     <t xml:space="preserve">1.74213671684265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74772918224335</t>
+    <t xml:space="preserve">1.74772930145264</t>
   </si>
   <si>
     <t xml:space="preserve">1.73095142841339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72815465927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71417319774628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79526782035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7673043012619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77289664745331</t>
+    <t xml:space="preserve">1.72815477848053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71417307853699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7952675819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76730418205261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7728967666626</t>
   </si>
   <si>
     <t xml:space="preserve">1.78967487812042</t>
@@ -173,157 +173,157 @@
     <t xml:space="preserve">1.77569317817688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78408205509186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78687846660614</t>
+    <t xml:space="preserve">1.78408229351044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78687858581543</t>
   </si>
   <si>
     <t xml:space="preserve">1.84560215473175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82323122024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81763887405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78128588199615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84280610084534</t>
+    <t xml:space="preserve">1.82323145866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81763851642609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78128600120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84280586242676</t>
   </si>
   <si>
     <t xml:space="preserve">1.8344167470932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86517691612244</t>
+    <t xml:space="preserve">1.86517703533173</t>
   </si>
   <si>
     <t xml:space="preserve">1.87076961994171</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85119521617889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86238050460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85958397388458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8567875623703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84000968933105</t>
+    <t xml:space="preserve">1.85119497776031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86238026618958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85958433151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678791999817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84000945091248</t>
   </si>
   <si>
     <t xml:space="preserve">1.89034426212311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93820083141327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92025458812714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92922818660736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89333534240723</t>
+    <t xml:space="preserve">1.93820071220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92025470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9292277097702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89333522319794</t>
   </si>
   <si>
     <t xml:space="preserve">1.86641561985016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87837994098663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90829050540924</t>
+    <t xml:space="preserve">1.8783802986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90829038619995</t>
   </si>
   <si>
     <t xml:space="preserve">1.92324566841125</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92623686790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91128122806549</t>
+    <t xml:space="preserve">1.92623674869537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91128146648407</t>
   </si>
   <si>
     <t xml:space="preserve">1.93221890926361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85445141792297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81257688999176</t>
+    <t xml:space="preserve">1.85445153713226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8125764131546</t>
   </si>
   <si>
     <t xml:space="preserve">1.84248721599579</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84547865390778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753217220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86940693855286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83052325248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86342489719391</t>
+    <t xml:space="preserve">1.84547829627991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753229141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8694064617157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83052313327789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86342465877533</t>
   </si>
   <si>
     <t xml:space="preserve">1.88137090206146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88436198234558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89632666110992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91726350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8993171453476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529918670654</t>
+    <t xml:space="preserve">1.88436233997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89632654190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91726362705231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89931750297546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9052996635437</t>
   </si>
   <si>
     <t xml:space="preserve">1.96212947368622</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94119203090668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93520975112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94418287277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8873530626297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90230846405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91427254676819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85744249820709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9471743106842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96512055397034</t>
+    <t xml:space="preserve">1.94119191169739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93520998954773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94418299198151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88735294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90230822563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9142724275589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85744261741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94717395305634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96512043476105</t>
   </si>
   <si>
     <t xml:space="preserve">2.00400400161743</t>
@@ -332,49 +332,49 @@
     <t xml:space="preserve">2.0129771232605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9740936756134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01596832275391</t>
+    <t xml:space="preserve">1.97409391403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01596808433533</t>
   </si>
   <si>
     <t xml:space="preserve">2.05784320831299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0608344078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03391432762146</t>
+    <t xml:space="preserve">2.06083369255066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03391480445862</t>
   </si>
   <si>
     <t xml:space="preserve">2.00998592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97708439826965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913851261139</t>
+    <t xml:space="preserve">1.97708463668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913815498352</t>
   </si>
   <si>
     <t xml:space="preserve">2.00699520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06382489204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05186104774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99503111839294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99802207946777</t>
+    <t xml:space="preserve">2.06382536888123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05186128616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99503135681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9980217218399</t>
   </si>
   <si>
     <t xml:space="preserve">1.95614719390869</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97110259532928</t>
+    <t xml:space="preserve">1.97110223770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.13261961936951</t>
@@ -383,46 +383,46 @@
     <t xml:space="preserve">2.12065505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03989696502686</t>
+    <t xml:space="preserve">2.0398964881897</t>
   </si>
   <si>
     <t xml:space="preserve">2.04587888717651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02494144439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904883861542</t>
+    <t xml:space="preserve">2.02494120597839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904919624329</t>
   </si>
   <si>
     <t xml:space="preserve">1.98007571697235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99203956127167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95315611362457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87239789962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86043357849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83650529384613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87538909912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08081126213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95236563682556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94594359397888</t>
+    <t xml:space="preserve">1.99203991889954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95315623283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8723977804184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86043381690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83650541305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8753889799118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08081078529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95236575603485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9459433555603</t>
   </si>
   <si>
     <t xml:space="preserve">1.9395215511322</t>
@@ -431,49 +431,49 @@
     <t xml:space="preserve">1.9266768693924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86887681484222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83676540851593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83034241199493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80465400218964</t>
+    <t xml:space="preserve">1.86887669563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83676505088806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83034300804138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80465424060822</t>
   </si>
   <si>
     <t xml:space="preserve">1.79180955886841</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77896499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7725430727005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69547533988953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73400914669037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68905341625214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65051960945129</t>
+    <t xml:space="preserve">1.77896511554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77254259586334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69547557830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73400938510895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68905329704285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65051972866058</t>
   </si>
   <si>
     <t xml:space="preserve">1.66978669166565</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7083203792572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72116458415985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67620897293091</t>
+    <t xml:space="preserve">1.70831990242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72116494178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67620885372162</t>
   </si>
   <si>
     <t xml:space="preserve">1.71474242210388</t>
@@ -488,34 +488,34 @@
     <t xml:space="preserve">1.7275869846344</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74685382843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74043154716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75327599048615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75969803333282</t>
+    <t xml:space="preserve">1.74685370922089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74043118953705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75327587127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75969815254211</t>
   </si>
   <si>
     <t xml:space="preserve">1.70189797878265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68263113498688</t>
+    <t xml:space="preserve">1.68263125419617</t>
   </si>
   <si>
     <t xml:space="preserve">1.65694200992584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63767540454865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6119863986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60556387901306</t>
+    <t xml:space="preserve">1.63767552375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61198604106903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60556399822235</t>
   </si>
   <si>
     <t xml:space="preserve">1.59914183616638</t>
@@ -524,172 +524,172 @@
     <t xml:space="preserve">1.61840856075287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59271967411041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62483048439026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81749856472015</t>
+    <t xml:space="preserve">1.59271919727325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62483084201813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81749868392944</t>
   </si>
   <si>
     <t xml:space="preserve">1.86245429515839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85603213310242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84960961341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82392072677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78538703918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81107640266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79823160171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125324249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5156524181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4000518321991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58629751205444</t>
+    <t xml:space="preserve">1.85603189468384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84960997104645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82392060756683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78538739681244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81107604503632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79823172092438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125312328339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51565229892731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40005195140839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58629739284515</t>
   </si>
   <si>
     <t xml:space="preserve">1.54134154319763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41931867599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43858528137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35509610176086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33582937717438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36151814460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36794078350067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3165625333786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32940685749054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32298481464386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37436282634735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38720726966858</t>
+    <t xml:space="preserve">1.41931879520416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43858563899994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35509598255157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33582925796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36151826381683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36794066429138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31656241416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32940697669983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32298457622528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37436294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38720762729645</t>
   </si>
   <si>
     <t xml:space="preserve">1.34867370128632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38078534603119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47069668769836</t>
+    <t xml:space="preserve">1.38078498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47069656848907</t>
   </si>
   <si>
     <t xml:space="preserve">1.42574083805084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4321631193161</t>
+    <t xml:space="preserve">1.43216335773468</t>
   </si>
   <si>
     <t xml:space="preserve">1.49638569355011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45785200595856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4128965139389</t>
+    <t xml:space="preserve">1.45785212516785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41289639472961</t>
   </si>
   <si>
     <t xml:space="preserve">1.45142996311188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47711896896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48354125022888</t>
+    <t xml:space="preserve">1.47711873054504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48354113101959</t>
   </si>
   <si>
     <t xml:space="preserve">1.46427440643311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57345294952393</t>
+    <t xml:space="preserve">1.57345271110535</t>
   </si>
   <si>
     <t xml:space="preserve">1.44500756263733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48996317386627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55418610572815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76612019538879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90653836727142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85167407989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70079708099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68708074092865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65279054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68022298812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65964877605438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64593255519867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61164224147797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69393920898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67336487770081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70765507221222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66650652885437</t>
+    <t xml:space="preserve">1.48996353149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55418634414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76612055301666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90653872489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85167419910431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70079672336578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68708086013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65279066562653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68022274971008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65964889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64593267440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61164212226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69393885135651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67336463928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70765495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66650664806366</t>
   </si>
   <si>
     <t xml:space="preserve">1.7145129442215</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">1.72822916507721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74194550514221</t>
+    <t xml:space="preserve">1.74194526672363</t>
   </si>
   <si>
     <t xml:space="preserve">1.63221669197083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59792613983154</t>
+    <t xml:space="preserve">1.59792625904083</t>
   </si>
   <si>
     <t xml:space="preserve">1.56363594532013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55677771568298</t>
+    <t xml:space="preserve">1.55677783489227</t>
   </si>
   <si>
     <t xml:space="preserve">1.5704939365387</t>
@@ -719,37 +719,37 @@
     <t xml:space="preserve">1.58421015739441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5910679101944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57735204696655</t>
+    <t xml:space="preserve">1.59106814861298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57735180854797</t>
   </si>
   <si>
     <t xml:space="preserve">1.61850023269653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62535810470581</t>
+    <t xml:space="preserve">1.6253582239151</t>
   </si>
   <si>
     <t xml:space="preserve">1.6047842502594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53620362281799</t>
+    <t xml:space="preserve">1.53620398044586</t>
   </si>
   <si>
     <t xml:space="preserve">1.54991984367371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6390745639801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54306173324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52934563159943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52248752117157</t>
+    <t xml:space="preserve">1.63907468318939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54306185245514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52934587001801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52248764038086</t>
   </si>
   <si>
     <t xml:space="preserve">1.51562964916229</t>
@@ -758,109 +758,109 @@
     <t xml:space="preserve">1.50877165794373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50191342830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4813392162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48819732666016</t>
+    <t xml:space="preserve">1.50191354751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48133957386017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48819744586945</t>
   </si>
   <si>
     <t xml:space="preserve">1.46762323379517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45390689373016</t>
+    <t xml:space="preserve">1.45390701293945</t>
   </si>
   <si>
     <t xml:space="preserve">1.39904260635376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36475241184235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37846863269806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37161040306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35789442062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35446548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72137117385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78309369087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8173840045929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79680967330933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78995180130005</t>
+    <t xml:space="preserve">1.36475253105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37846851348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3716105222702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35789430141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35446524620056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72137093544006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7830935716629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81738388538361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79680979251862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78995168209076</t>
   </si>
   <si>
     <t xml:space="preserve">1.77623546123505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81052553653717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83109998703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8379579782486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80366778373718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84481608867645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8722482919693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89968049526215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91339671611786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92711269855499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94082880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96140313148499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97511887550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94768679141998</t>
+    <t xml:space="preserve">1.81052577495575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83109986782074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83795833587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80366766452789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84481620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87224805355072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89968061447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91339659690857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92711305618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94082903862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96140265464783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97511911392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94768691062927</t>
   </si>
   <si>
     <t xml:space="preserve">1.92025446891785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88596415519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95454430580139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93397092819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96826088428497</t>
+    <t xml:space="preserve">1.88596439361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95454478263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93397045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96826100349426</t>
   </si>
   <si>
     <t xml:space="preserve">2.01626753807068</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">2.0505576133728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04369926452637</t>
+    <t xml:space="preserve">2.04369974136353</t>
   </si>
   <si>
     <t xml:space="preserve">2.06427383422852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03684139251709</t>
+    <t xml:space="preserve">2.03684163093567</t>
   </si>
   <si>
     <t xml:space="preserve">2.02998375892639</t>
@@ -884,55 +884,55 @@
     <t xml:space="preserve">2.05741572380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113194465637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07798981666565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08484768867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0990309715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10612201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13448691368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09193897247314</t>
+    <t xml:space="preserve">2.07113170623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07798957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08484792709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09903073310852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10612177848816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13448715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09193921089172</t>
   </si>
   <si>
     <t xml:space="preserve">2.14157843589783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1132128238678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12030458450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12739586830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16285228729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17703533172607</t>
+    <t xml:space="preserve">2.11321330070496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12030482292175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12739562988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1628520488739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1770350933075</t>
   </si>
   <si>
     <t xml:space="preserve">2.22667455673218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20540046691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25503993034363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26213121414185</t>
+    <t xml:space="preserve">2.20540070533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25503945350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26213073730469</t>
   </si>
   <si>
     <t xml:space="preserve">2.24794840812683</t>
@@ -944,34 +944,34 @@
     <t xml:space="preserve">2.19830894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2337658405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24085664749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21249127388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28340482711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26922202110291</t>
+    <t xml:space="preserve">2.23376607894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24085688591003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21249151229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28340458869934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26922225952148</t>
   </si>
   <si>
     <t xml:space="preserve">2.29049611091614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29758763313293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31177020072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31886124610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32595252990723</t>
+    <t xml:space="preserve">2.29758739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176996231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31886148452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32595276832581</t>
   </si>
   <si>
     <t xml:space="preserve">2.3330442905426</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">2.30467891693115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36850070953369</t>
+    <t xml:space="preserve">2.36850047111511</t>
   </si>
   <si>
     <t xml:space="preserve">2.38977456092834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37559199333191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38268303871155</t>
+    <t xml:space="preserve">2.37559151649475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38268327713013</t>
   </si>
   <si>
     <t xml:space="preserve">2.39686608314514</t>
@@ -998,22 +998,22 @@
     <t xml:space="preserve">2.40395712852478</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44650506973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43232226371765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49614453315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51032733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58124041557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55287480354309</t>
+    <t xml:space="preserve">2.44650530815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43232274055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49614429473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51032710075378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58124017715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55287504196167</t>
   </si>
   <si>
     <t xml:space="preserve">2.55996608734131</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">2.60960555076599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63797068595886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58833169937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59542298316956</t>
+    <t xml:space="preserve">2.63797116279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58833146095276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59542274475098</t>
   </si>
   <si>
     <t xml:space="preserve">2.61669707298279</t>
@@ -1046,70 +1046,70 @@
     <t xml:space="preserve">2.65924477577209</t>
   </si>
   <si>
+    <t xml:space="preserve">2.7017924785614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6947009563446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72306656837463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.715975522995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68761014938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7088840007782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68051838874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73092246055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907521247864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76733493804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8110294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86200666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84015965461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81831192970276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80374717712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83287715911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78189969062805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72363972663879</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.70179271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69470143318176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72306656837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71597504615784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68760991096497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70888376235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68051862716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73092246055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907497406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76733469963074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8110294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8620069026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84015941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81831192970276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80374717712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83287715911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78189969062805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72363996505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70179295539856</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.75277018547058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6945104598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71635794639587</t>
+    <t xml:space="preserve">2.69451022148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71635770797729</t>
   </si>
   <si>
     <t xml:space="preserve">2.74548745155334</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">2.73820495605469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77461719512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82559466362</t>
+    <t xml:space="preserve">2.77461743354797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82559442520142</t>
   </si>
   <si>
     <t xml:space="preserve">2.78918218612671</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">2.76005220413208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62896823883057</t>
+    <t xml:space="preserve">2.62896800041199</t>
   </si>
   <si>
     <t xml:space="preserve">2.62168550491333</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">2.86928939819336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61440324783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55614376068115</t>
+    <t xml:space="preserve">2.61440348625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55614352226257</t>
   </si>
   <si>
     <t xml:space="preserve">2.5342960357666</t>
@@ -1157,25 +1157,25 @@
     <t xml:space="preserve">2.43962407112122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31582260131836</t>
+    <t xml:space="preserve">2.3158221244812</t>
   </si>
   <si>
     <t xml:space="preserve">2.22843289375305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27212738990784</t>
+    <t xml:space="preserve">2.27212762832642</t>
   </si>
   <si>
     <t xml:space="preserve">2.40321183204651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41049432754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54886054992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65809774398804</t>
+    <t xml:space="preserve">2.41049408912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54886102676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65809798240662</t>
   </si>
   <si>
     <t xml:space="preserve">2.54157853126526</t>
@@ -1184,46 +1184,46 @@
     <t xml:space="preserve">2.67266297340393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88385438919067</t>
+    <t xml:space="preserve">2.88385391235352</t>
   </si>
   <si>
     <t xml:space="preserve">2.89841914176941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95667886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94211387634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97124361991882</t>
+    <t xml:space="preserve">2.95667862892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94211411476135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97124338150024</t>
   </si>
   <si>
     <t xml:space="preserve">2.94939637184143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91298389434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85472464561462</t>
+    <t xml:space="preserve">2.91298413276672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85472440719604</t>
   </si>
   <si>
     <t xml:space="preserve">2.97852635383606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96396136283875</t>
+    <t xml:space="preserve">2.96396160125732</t>
   </si>
   <si>
     <t xml:space="preserve">2.89113664627075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90570163726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92754888534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05783271789551</t>
+    <t xml:space="preserve">2.90570139884949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92754912376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05783224105835</t>
   </si>
   <si>
     <t xml:space="preserve">3.02717757225037</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">3.05016875267029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01951360702515</t>
+    <t xml:space="preserve">3.01951384544373</t>
   </si>
   <si>
     <t xml:space="preserve">2.98885893821716</t>
@@ -1253,13 +1253,13 @@
     <t xml:space="preserve">2.66698169708252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68230891227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67464566230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68997311592102</t>
+    <t xml:space="preserve">2.6823091506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67464542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68997287750244</t>
   </si>
   <si>
     <t xml:space="preserve">2.720627784729</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">2.65165424346924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64399075508118</t>
+    <t xml:space="preserve">2.64399027824402</t>
   </si>
   <si>
     <t xml:space="preserve">2.62099933624268</t>
@@ -1298,16 +1298,16 @@
     <t xml:space="preserve">2.56735301017761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53669834136963</t>
+    <t xml:space="preserve">2.53669786453247</t>
   </si>
   <si>
     <t xml:space="preserve">2.52137064933777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55968928337097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52903413772583</t>
+    <t xml:space="preserve">2.55968952178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52903437614441</t>
   </si>
   <si>
     <t xml:space="preserve">2.55202555656433</t>
@@ -1322,16 +1322,16 @@
     <t xml:space="preserve">2.46772456169128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49837923049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4370698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45239686965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49071574211121</t>
+    <t xml:space="preserve">2.49837946891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43706941604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.452397108078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49071598052979</t>
   </si>
   <si>
     <t xml:space="preserve">2.50604295730591</t>
@@ -1340,10 +1340,10 @@
     <t xml:space="preserve">2.47538805007935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46006107330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48305177688599</t>
+    <t xml:space="preserve">2.46006059646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48305201530457</t>
   </si>
   <si>
     <t xml:space="preserve">2.71296429634094</t>
@@ -1364,64 +1364,61 @@
     <t xml:space="preserve">2.81259298324585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85091137886047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86623907089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89019060134888</t>
+    <t xml:space="preserve">2.85091161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86623859405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89019083976746</t>
   </si>
   <si>
     <t xml:space="preserve">2.89817500114441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92212677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91414260864258</t>
+    <t xml:space="preserve">2.92212653160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91414284706116</t>
   </si>
   <si>
     <t xml:space="preserve">2.8822066783905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95406270027161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9620463848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97003030776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94607830047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87422299385071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86623883247375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9061586856842</t>
+    <t xml:space="preserve">2.95406246185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96204662322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97003054618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94607853889465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87422275543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90615892410278</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809461593628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93011069297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9939820766449</t>
+    <t xml:space="preserve">2.93011045455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99398231506348</t>
   </si>
   <si>
     <t xml:space="preserve">3.00196623802185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97801446914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06583762168884</t>
+    <t xml:space="preserve">2.97801423072815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06583786010742</t>
   </si>
   <si>
     <t xml:space="preserve">3.08978962898254</t>
@@ -1430,19 +1427,19 @@
     <t xml:space="preserve">3.08180546760559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01793432235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04986977577209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9859983921051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02591776847839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03390216827393</t>
+    <t xml:space="preserve">3.0179340839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04986953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98599791526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02591800689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03390192985535</t>
   </si>
   <si>
     <t xml:space="preserve">3.11374139785767</t>
@@ -1451,10 +1448,10 @@
     <t xml:space="preserve">3.0738217830658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04188585281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12172555923462</t>
+    <t xml:space="preserve">3.04188561439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1217257976532</t>
   </si>
   <si>
     <t xml:space="preserve">3.12970972061157</t>
@@ -1463,13 +1460,13 @@
     <t xml:space="preserve">3.09777355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15366125106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10575771331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05785369873047</t>
+    <t xml:space="preserve">3.15366148948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10575747489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05785393714905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24148488044739</t>
@@ -1481,49 +1478,49 @@
     <t xml:space="preserve">3.16164517402649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14567732810974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13769340515137</t>
+    <t xml:space="preserve">3.14567708969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13769316673279</t>
   </si>
   <si>
     <t xml:space="preserve">3.17761301994324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1944260597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21123862266541</t>
+    <t xml:space="preserve">3.19442582130432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21123838424683</t>
   </si>
   <si>
     <t xml:space="preserve">3.18601942062378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14398765563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15239381790161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16920685768127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11876845359802</t>
+    <t xml:space="preserve">3.14398741722107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15239405632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1692066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1187686920166</t>
   </si>
   <si>
     <t xml:space="preserve">3.11036205291748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12717461585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13558125495911</t>
+    <t xml:space="preserve">3.12717509269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13558101654053</t>
   </si>
   <si>
     <t xml:space="preserve">3.0935492515564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10195589065552</t>
+    <t xml:space="preserve">3.10195565223694</t>
   </si>
   <si>
     <t xml:space="preserve">3.08514285087585</t>
@@ -1532,10 +1529,10 @@
     <t xml:space="preserve">3.16080045700073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07673668861389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06833004951477</t>
+    <t xml:space="preserve">3.07673621177673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06833028793335</t>
   </si>
   <si>
     <t xml:space="preserve">3.05151748657227</t>
@@ -1547,7 +1544,7 @@
     <t xml:space="preserve">3.0347044467926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05992364883423</t>
+    <t xml:space="preserve">3.05992388725281</t>
   </si>
   <si>
     <t xml:space="preserve">3.02629804611206</t>
@@ -1559,7 +1556,7 @@
     <t xml:space="preserve">2.97585988044739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00107884407043</t>
+    <t xml:space="preserve">3.00107908248901</t>
   </si>
   <si>
     <t xml:space="preserve">3.01789164543152</t>
@@ -1574,28 +1571,28 @@
     <t xml:space="preserve">2.88338971138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90860867500305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8665771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85817050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87498331069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83295106887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91701531410217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93382811546326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89179611206055</t>
+    <t xml:space="preserve">2.90860891342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86657691001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85817074775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87498354911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83295130729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91701507568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93382787704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89179635047913</t>
   </si>
   <si>
     <t xml:space="preserve">2.98426628112793</t>
@@ -1604,13 +1601,13 @@
     <t xml:space="preserve">2.92542171478271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95904731750488</t>
+    <t xml:space="preserve">2.9590470790863</t>
   </si>
   <si>
     <t xml:space="preserve">2.96745347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99267244338989</t>
+    <t xml:space="preserve">2.99267268180847</t>
   </si>
   <si>
     <t xml:space="preserve">3.08550214767456</t>
@@ -1622,19 +1619,19 @@
     <t xml:space="preserve">3.09426784515381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11179876327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12933015823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13809585571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15562701225281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19945549964905</t>
+    <t xml:space="preserve">3.11179900169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12933039665222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13809561729431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15562725067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19945526123047</t>
   </si>
   <si>
     <t xml:space="preserve">3.20822095870972</t>
@@ -1643,13 +1640,13 @@
     <t xml:space="preserve">3.22575235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24328374862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23451781272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25204920768738</t>
+    <t xml:space="preserve">3.24328351020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23451805114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25204944610596</t>
   </si>
   <si>
     <t xml:space="preserve">3.1906898021698</t>
@@ -1661,7 +1658,7 @@
     <t xml:space="preserve">3.18192410469055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17315816879272</t>
+    <t xml:space="preserve">3.1731584072113</t>
   </si>
   <si>
     <t xml:space="preserve">3.21698665618896</t>
@@ -1670,37 +1667,37 @@
     <t xml:space="preserve">3.26958036422729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27834606170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29587721824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3221743106842</t>
+    <t xml:space="preserve">3.27834582328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29587745666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32217407226562</t>
   </si>
   <si>
     <t xml:space="preserve">3.31340861320496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33970546722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43612742424011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39229893684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44489312171936</t>
+    <t xml:space="preserve">3.33970522880554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43612766265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39229917526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44489288330078</t>
   </si>
   <si>
     <t xml:space="preserve">3.45365858078003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41859602928162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48872137069702</t>
+    <t xml:space="preserve">3.4185962677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48872113227844</t>
   </si>
   <si>
     <t xml:space="preserve">3.51501822471619</t>
@@ -1712,49 +1709,49 @@
     <t xml:space="preserve">3.37476801872253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3835334777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47118973731995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40983033180237</t>
+    <t xml:space="preserve">3.38353323936462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47118997573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40983057022095</t>
   </si>
   <si>
     <t xml:space="preserve">3.46242427825928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50625252723694</t>
+    <t xml:space="preserve">3.50625228881836</t>
   </si>
   <si>
     <t xml:space="preserve">3.52378368377686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49748682975769</t>
+    <t xml:space="preserve">3.49748706817627</t>
   </si>
   <si>
     <t xml:space="preserve">3.54131484031677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5325493812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55884623527527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5939085483551</t>
+    <t xml:space="preserve">3.53254961967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55884647369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59390878677368</t>
   </si>
   <si>
     <t xml:space="preserve">3.66403365135193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61144018173218</t>
+    <t xml:space="preserve">3.6114399433136</t>
   </si>
   <si>
     <t xml:space="preserve">3.60267448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55008101463318</t>
+    <t xml:space="preserve">3.5500807762146</t>
   </si>
   <si>
     <t xml:space="preserve">3.57637739181519</t>
@@ -1763,7 +1760,7 @@
     <t xml:space="preserve">3.58559513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60402989387512</t>
+    <t xml:space="preserve">3.6040301322937</t>
   </si>
   <si>
     <t xml:space="preserve">3.57637763023376</t>
@@ -1781,7 +1778,7 @@
     <t xml:space="preserve">3.52107262611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55794262886047</t>
+    <t xml:space="preserve">3.55794239044189</t>
   </si>
   <si>
     <t xml:space="preserve">3.56716012954712</t>
@@ -1796,13 +1793,13 @@
     <t xml:space="preserve">3.42889809608459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51185536384583</t>
+    <t xml:space="preserve">3.51185512542725</t>
   </si>
   <si>
     <t xml:space="preserve">3.47498536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53029012680054</t>
+    <t xml:space="preserve">3.53029036521912</t>
   </si>
   <si>
     <t xml:space="preserve">3.49342036247253</t>
@@ -1811,16 +1808,16 @@
     <t xml:space="preserve">3.54872512817383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65011715888977</t>
+    <t xml:space="preserve">3.65011739730835</t>
   </si>
   <si>
     <t xml:space="preserve">3.6408998966217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63168263435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44733309745789</t>
+    <t xml:space="preserve">3.63168239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44733285903931</t>
   </si>
   <si>
     <t xml:space="preserve">3.50263786315918</t>
@@ -1829,7 +1826,7 @@
     <t xml:space="preserve">3.67776989936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463966369629</t>
+    <t xml:space="preserve">3.71463990211487</t>
   </si>
   <si>
     <t xml:space="preserve">3.78837943077087</t>
@@ -1838,10 +1835,10 @@
     <t xml:space="preserve">3.75150966644287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.659334897995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77916169166565</t>
+    <t xml:space="preserve">3.65933465957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77916193008423</t>
   </si>
   <si>
     <t xml:space="preserve">3.80681443214417</t>
@@ -1853,7 +1850,7 @@
     <t xml:space="preserve">3.84368419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76994466781616</t>
+    <t xml:space="preserve">3.76994442939758</t>
   </si>
   <si>
     <t xml:space="preserve">3.81603169441223</t>
@@ -1868,7 +1865,7 @@
     <t xml:space="preserve">3.91742372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90820622444153</t>
+    <t xml:space="preserve">3.90820646286011</t>
   </si>
   <si>
     <t xml:space="preserve">3.89898896217346</t>
@@ -1877,7 +1874,7 @@
     <t xml:space="preserve">3.88055419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93585896492004</t>
+    <t xml:space="preserve">3.93585848808289</t>
   </si>
   <si>
     <t xml:space="preserve">3.94507646560669</t>
@@ -1889,7 +1886,7 @@
     <t xml:space="preserve">3.86211895942688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83446645736694</t>
+    <t xml:space="preserve">3.83446669578552</t>
   </si>
   <si>
     <t xml:space="preserve">3.83412289619446</t>
@@ -35997,7 +35994,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1284" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36049,7 +36046,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1286" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36075,7 +36072,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1287" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36153,7 +36150,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36257,7 +36254,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1294" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36335,7 +36332,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1297" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36413,7 +36410,7 @@
         <v>3.75</v>
       </c>
       <c r="G1300" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36439,7 +36436,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1301" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36465,7 +36462,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1302" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36491,7 +36488,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1303" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36517,7 +36514,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1304" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36543,7 +36540,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1305" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36569,7 +36566,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1306" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36595,7 +36592,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1307" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36621,7 +36618,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36673,7 +36670,7 @@
         <v>3.75</v>
       </c>
       <c r="G1310" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36699,7 +36696,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36725,7 +36722,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1312" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36751,7 +36748,7 @@
         <v>3.75</v>
       </c>
       <c r="G1313" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36777,7 +36774,7 @@
         <v>3.75</v>
       </c>
       <c r="G1314" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36881,7 +36878,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36907,7 +36904,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36933,7 +36930,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36959,7 +36956,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1321" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36985,7 +36982,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1322" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37011,7 +37008,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1323" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37037,7 +37034,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1324" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37063,7 +37060,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1325" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37089,7 +37086,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1326" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37115,7 +37112,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1327" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37141,7 +37138,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1328" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37167,7 +37164,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1329" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37193,7 +37190,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37219,7 +37216,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1331" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37245,7 +37242,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1332" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37271,7 +37268,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1333" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37297,7 +37294,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1334" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37323,7 +37320,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37349,7 +37346,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1336" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37375,7 +37372,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1337" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37401,7 +37398,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1338" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37427,7 +37424,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37453,7 +37450,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1340" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37479,7 +37476,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1341" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37505,7 +37502,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1342" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37531,7 +37528,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1343" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37557,7 +37554,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37583,7 +37580,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1345" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37609,7 +37606,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1346" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37635,7 +37632,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37687,7 +37684,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37713,7 +37710,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1350" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37739,7 +37736,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1351" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37765,7 +37762,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1352" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37791,7 +37788,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1353" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37817,7 +37814,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37843,7 +37840,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1355" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37869,7 +37866,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1356" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37895,7 +37892,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1357" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37921,7 +37918,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1358" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37947,7 +37944,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1359" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37973,7 +37970,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1360" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37999,7 +37996,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1361" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38025,7 +38022,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1362" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38051,7 +38048,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1363" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38077,7 +38074,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1364" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38103,7 +38100,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1365" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38129,7 +38126,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1366" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38155,7 +38152,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38181,7 +38178,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1368" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38207,7 +38204,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38233,7 +38230,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1370" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38259,7 +38256,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1371" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38285,7 +38282,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38311,7 +38308,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1373" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38337,7 +38334,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1374" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38363,7 +38360,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1375" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38389,7 +38386,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38415,7 +38412,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1377" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38441,7 +38438,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1378" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38467,7 +38464,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1379" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38493,7 +38490,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1380" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38519,7 +38516,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38545,7 +38542,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1382" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38571,7 +38568,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38597,7 +38594,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1384" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38623,7 +38620,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1385" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38649,7 +38646,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1386" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38675,7 +38672,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38701,7 +38698,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1388" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38727,7 +38724,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38753,7 +38750,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1390" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38779,7 +38776,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38805,7 +38802,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1392" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38831,7 +38828,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1393" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38857,7 +38854,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38883,7 +38880,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1395" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38909,7 +38906,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1396" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38935,7 +38932,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1397" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38961,7 +38958,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1398" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38987,7 +38984,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1399" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39013,7 +39010,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1400" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39039,7 +39036,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1401" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39065,7 +39062,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1402" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39091,7 +39088,7 @@
         <v>3.75</v>
       </c>
       <c r="G1403" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39117,7 +39114,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39143,7 +39140,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1405" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39169,7 +39166,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1406" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39195,7 +39192,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1407" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39221,7 +39218,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1408" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39247,7 +39244,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1409" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39273,7 +39270,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1410" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39299,7 +39296,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1411" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39325,7 +39322,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1412" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39351,7 +39348,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1413" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39377,7 +39374,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1414" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39403,7 +39400,7 @@
         <v>3.75</v>
       </c>
       <c r="G1415" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39429,7 +39426,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39455,7 +39452,7 @@
         <v>3.75</v>
       </c>
       <c r="G1417" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39481,7 +39478,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1418" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39507,7 +39504,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39533,7 +39530,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1420" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39559,7 +39556,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1421" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39585,7 +39582,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1422" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39611,7 +39608,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39637,7 +39634,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1424" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39663,7 +39660,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1425" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39689,7 +39686,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1426" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39715,7 +39712,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1427" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39741,7 +39738,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1428" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39767,7 +39764,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39793,7 +39790,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1430" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39819,7 +39816,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39845,7 +39842,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39871,7 +39868,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1433" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39897,7 +39894,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39923,7 +39920,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1435" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39949,7 +39946,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1436" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39975,7 +39972,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1437" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40001,7 +39998,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1438" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40027,7 +40024,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1439" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40053,7 +40050,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40079,7 +40076,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1441" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40105,7 +40102,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40131,7 +40128,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1443" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40157,7 +40154,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1444" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40183,7 +40180,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1445" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40209,7 +40206,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1446" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40235,7 +40232,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1447" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40261,7 +40258,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1448" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40287,7 +40284,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1449" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40313,7 +40310,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1450" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40339,7 +40336,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1451" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40365,7 +40362,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1452" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40391,7 +40388,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40417,7 +40414,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40443,7 +40440,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40469,7 +40466,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40495,7 +40492,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1457" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40521,7 +40518,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40547,7 +40544,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1459" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40573,7 +40570,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1460" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40599,7 +40596,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40625,7 +40622,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1462" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40651,7 +40648,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40677,7 +40674,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1464" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40703,7 +40700,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40729,7 +40726,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1466" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40755,7 +40752,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1467" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40781,7 +40778,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1468" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40807,7 +40804,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1469" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40833,7 +40830,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1470" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40859,7 +40856,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1471" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40885,7 +40882,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1472" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40911,7 +40908,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1473" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40937,7 +40934,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40963,7 +40960,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1475" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40989,7 +40986,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1476" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41015,7 +41012,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1477" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41041,7 +41038,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1478" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41067,7 +41064,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1479" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41093,7 +41090,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41119,7 +41116,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41145,7 +41142,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1482" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41171,7 +41168,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1483" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41197,7 +41194,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1484" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41223,7 +41220,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1485" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41249,7 +41246,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1486" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41275,7 +41272,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1487" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41301,7 +41298,7 @@
         <v>3.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41327,7 +41324,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1489" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41353,7 +41350,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41379,7 +41376,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1491" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41405,7 +41402,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1492" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41431,7 +41428,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41457,7 +41454,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1494" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41483,7 +41480,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1495" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41509,7 +41506,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1496" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41535,7 +41532,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1497" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41561,7 +41558,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1498" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41587,7 +41584,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1499" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41613,7 +41610,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1500" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41639,7 +41636,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1501" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41665,7 +41662,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41691,7 +41688,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1503" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41717,7 +41714,7 @@
         <v>3.5</v>
       </c>
       <c r="G1504" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41743,7 +41740,7 @@
         <v>3.5</v>
       </c>
       <c r="G1505" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41769,7 +41766,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1506" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41795,7 +41792,7 @@
         <v>3.5</v>
       </c>
       <c r="G1507" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41821,7 +41818,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1508" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41847,7 +41844,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1509" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41873,7 +41870,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1510" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41899,7 +41896,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1511" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41925,7 +41922,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1512" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41951,7 +41948,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41977,7 +41974,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42003,7 +42000,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42029,7 +42026,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42055,7 +42052,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1517" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42081,7 +42078,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1518" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42107,7 +42104,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1519" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42133,7 +42130,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1520" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42159,7 +42156,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42185,7 +42182,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42211,7 +42208,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1523" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42237,7 +42234,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1524" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42263,7 +42260,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1525" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42289,7 +42286,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1526" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42315,7 +42312,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1527" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42341,7 +42338,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1528" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42367,7 +42364,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1529" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42393,7 +42390,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1530" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42419,7 +42416,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1531" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42445,7 +42442,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1532" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42471,7 +42468,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1533" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42497,7 +42494,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1534" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42523,7 +42520,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1535" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42549,7 +42546,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1536" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42575,7 +42572,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1537" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42601,7 +42598,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1538" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42627,7 +42624,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1539" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42653,7 +42650,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1540" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42679,7 +42676,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1541" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42705,7 +42702,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42731,7 +42728,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1543" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42757,7 +42754,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1544" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42783,7 +42780,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1545" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42809,7 +42806,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1546" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42835,7 +42832,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1547" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42861,7 +42858,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1548" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42887,7 +42884,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1549" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42913,7 +42910,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1550" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42939,7 +42936,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1551" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42965,7 +42962,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1552" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42991,7 +42988,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1553" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43017,7 +43014,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1554" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43043,7 +43040,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1555" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43069,7 +43066,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1556" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43095,7 +43092,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1557" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43121,7 +43118,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1558" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43147,7 +43144,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1559" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43173,7 +43170,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1560" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43199,7 +43196,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43225,7 +43222,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1562" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43251,7 +43248,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1563" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43277,7 +43274,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1564" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43303,7 +43300,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1565" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43329,7 +43326,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1566" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43355,7 +43352,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1567" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43381,7 +43378,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1568" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43407,7 +43404,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1569" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43433,7 +43430,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1570" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43459,7 +43456,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1571" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43485,7 +43482,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1572" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43511,7 +43508,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1573" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43537,7 +43534,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1574" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43563,7 +43560,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1575" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43589,7 +43586,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1576" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43615,7 +43612,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1577" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43641,7 +43638,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1578" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43667,7 +43664,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1579" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43693,7 +43690,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1580" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43719,7 +43716,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1581" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43745,7 +43742,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1582" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43771,7 +43768,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1583" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43797,7 +43794,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1584" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43823,7 +43820,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1585" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43849,7 +43846,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1586" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43875,7 +43872,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1587" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43901,7 +43898,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1588" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43927,7 +43924,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1589" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43953,7 +43950,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1590" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43979,7 +43976,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1591" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44005,7 +44002,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1592" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44031,7 +44028,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1593" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44057,7 +44054,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1594" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44083,7 +44080,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1595" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44109,7 +44106,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1596" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44135,7 +44132,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1597" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44161,7 +44158,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1598" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44187,7 +44184,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1599" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44213,7 +44210,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1600" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44239,7 +44236,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44265,7 +44262,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1602" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44291,7 +44288,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44317,7 +44314,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44343,7 +44340,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1605" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44369,7 +44366,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1606" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44395,7 +44392,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1607" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44421,7 +44418,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44447,7 +44444,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1609" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44473,7 +44470,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1610" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44499,7 +44496,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44525,7 +44522,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1612" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44551,7 +44548,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1613" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44577,7 +44574,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44603,7 +44600,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1615" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44629,7 +44626,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1616" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44655,7 +44652,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1617" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44681,7 +44678,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1618" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44707,7 +44704,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1619" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44733,7 +44730,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1620" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44759,7 +44756,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1621" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44785,7 +44782,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1622" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44811,7 +44808,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1623" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44837,7 +44834,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44863,7 +44860,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44889,7 +44886,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44915,7 +44912,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1627" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44941,7 +44938,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1628" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44967,7 +44964,7 @@
         <v>4</v>
       </c>
       <c r="G1629" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44993,7 +44990,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1630" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45019,7 +45016,7 @@
         <v>4</v>
       </c>
       <c r="G1631" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45045,7 +45042,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1632" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45071,7 +45068,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45097,7 +45094,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1634" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45123,7 +45120,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45149,7 +45146,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45175,7 +45172,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1637" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45201,7 +45198,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1638" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45227,7 +45224,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1639" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45253,7 +45250,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1640" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45279,7 +45276,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45305,7 +45302,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1642" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45331,7 +45328,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1643" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45357,7 +45354,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1644" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45383,7 +45380,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1645" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45409,7 +45406,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45435,7 +45432,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1647" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45461,7 +45458,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1648" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45487,7 +45484,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1649" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45513,7 +45510,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1650" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45539,7 +45536,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45565,7 +45562,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1652" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45591,7 +45588,7 @@
         <v>4</v>
       </c>
       <c r="G1653" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45617,7 +45614,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1654" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45643,7 +45640,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1655" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45669,7 +45666,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1656" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45695,7 +45692,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1657" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45721,7 +45718,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1658" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45747,7 +45744,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45773,7 +45770,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45799,7 +45796,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1661" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45825,7 +45822,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1662" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45851,7 +45848,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45877,7 +45874,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1664" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45903,7 +45900,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45929,7 +45926,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1666" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45955,7 +45952,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1667" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45981,7 +45978,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1668" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46007,7 +46004,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1669" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46033,7 +46030,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46059,7 +46056,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1671" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46085,7 +46082,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1672" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46111,7 +46108,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46137,7 +46134,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1674" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46163,7 +46160,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1675" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46189,7 +46186,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1676" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46215,7 +46212,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1677" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46241,7 +46238,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1678" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46267,7 +46264,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1679" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46293,7 +46290,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1680" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46319,7 +46316,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1681" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46345,7 +46342,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1682" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46371,7 +46368,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1683" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46397,7 +46394,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1684" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46423,7 +46420,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1685" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46449,7 +46446,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1686" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46475,7 +46472,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46501,7 +46498,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1688" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46527,7 +46524,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1689" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46553,7 +46550,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1690" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46579,7 +46576,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1691" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46605,7 +46602,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1692" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46631,7 +46628,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1693" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46657,7 +46654,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1694" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46683,7 +46680,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1695" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46709,7 +46706,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1696" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46735,7 +46732,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1697" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46761,7 +46758,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46787,7 +46784,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1699" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46813,7 +46810,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1700" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46839,7 +46836,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1701" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46865,7 +46862,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1702" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46891,7 +46888,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1703" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46917,7 +46914,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1704" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46943,7 +46940,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46969,7 +46966,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46995,7 +46992,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47021,7 +47018,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1708" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47047,7 +47044,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1709" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47073,7 +47070,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1710" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47099,7 +47096,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47125,7 +47122,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1712" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47151,7 +47148,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1713" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47177,7 +47174,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47203,7 +47200,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1715" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47229,7 +47226,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1716" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47255,7 +47252,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47281,7 +47278,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1718" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47307,7 +47304,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47333,7 +47330,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1720" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47359,7 +47356,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47385,7 +47382,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1722" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47411,7 +47408,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1723" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47437,7 +47434,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1724" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47463,7 +47460,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1725" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47489,7 +47486,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47515,7 +47512,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1727" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47541,7 +47538,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1728" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47567,7 +47564,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1729" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47593,7 +47590,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1730" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47619,7 +47616,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1731" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47645,7 +47642,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1732" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47671,7 +47668,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1733" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47697,7 +47694,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1734" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47723,7 +47720,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1735" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47749,7 +47746,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1736" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47775,7 +47772,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1737" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47801,7 +47798,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1738" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47827,7 +47824,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1739" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47853,7 +47850,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1740" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47879,7 +47876,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1741" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47905,7 +47902,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47931,7 +47928,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1743" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47957,7 +47954,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1744" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47983,7 +47980,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1745" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48009,7 +48006,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1746" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48035,7 +48032,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1747" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48061,7 +48058,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1748" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48087,7 +48084,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1749" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48113,7 +48110,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1750" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48139,7 +48136,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1751" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48165,7 +48162,7 @@
         <v>4.25</v>
       </c>
       <c r="G1752" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48191,7 +48188,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1753" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48217,7 +48214,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1754" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48243,7 +48240,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48269,7 +48266,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1756" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48295,7 +48292,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1757" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48321,7 +48318,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1758" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48347,7 +48344,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1759" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48373,7 +48370,7 @@
         <v>4.25</v>
       </c>
       <c r="G1760" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48399,7 +48396,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48425,7 +48422,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1762" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48451,7 +48448,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1763" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48477,7 +48474,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48503,7 +48500,7 @@
         <v>4.25</v>
       </c>
       <c r="G1765" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48529,7 +48526,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1766" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48555,7 +48552,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48581,7 +48578,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1768" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48607,7 +48604,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48633,7 +48630,7 @@
         <v>4.25</v>
       </c>
       <c r="G1770" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48659,7 +48656,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1771" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48685,7 +48682,7 @@
         <v>4.25</v>
       </c>
       <c r="G1772" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48711,7 +48708,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1773" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48737,7 +48734,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1774" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48763,7 +48760,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1775" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48789,7 +48786,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1776" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48815,7 +48812,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1777" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48841,7 +48838,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1778" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48867,7 +48864,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48893,7 +48890,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1780" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48919,7 +48916,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1781" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48945,7 +48942,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1782" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48971,7 +48968,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1783" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48997,7 +48994,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1784" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49023,7 +49020,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1785" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49049,7 +49046,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1786" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49075,7 +49072,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1787" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49101,7 +49098,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1788" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49127,7 +49124,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1789" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49153,7 +49150,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1790" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49179,7 +49176,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1791" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49205,7 +49202,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1792" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49231,7 +49228,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1793" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49257,7 +49254,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1794" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49283,7 +49280,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49309,7 +49306,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49335,7 +49332,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49361,7 +49358,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49387,7 +49384,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1799" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49413,7 +49410,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1800" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49439,7 +49436,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1801" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49465,7 +49462,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1802" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49491,7 +49488,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49517,7 +49514,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1804" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49543,7 +49540,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1805" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49569,7 +49566,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1806" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49595,7 +49592,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49621,7 +49618,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1808" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49647,7 +49644,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1809" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49673,7 +49670,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1810" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49699,7 +49696,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1811" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49725,7 +49722,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1812" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49751,7 +49748,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1813" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49777,7 +49774,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1814" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49803,7 +49800,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1815" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49829,7 +49826,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1816" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49855,7 +49852,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1817" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49881,7 +49878,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49907,7 +49904,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1819" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49933,7 +49930,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1820" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49959,7 +49956,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1821" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49985,7 +49982,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1822" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50011,7 +50008,7 @@
         <v>4.25</v>
       </c>
       <c r="G1823" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50037,7 +50034,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1824" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50063,7 +50060,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50089,7 +50086,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1826" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50115,7 +50112,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50141,7 +50138,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1828" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50167,7 +50164,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1829" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50193,7 +50190,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1830" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50219,7 +50216,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1831" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50245,7 +50242,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50271,7 +50268,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1833" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50297,7 +50294,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50323,7 +50320,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50349,7 +50346,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1836" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50375,7 +50372,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1837" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50401,7 +50398,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1838" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50427,7 +50424,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1839" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50453,7 +50450,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1840" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50479,7 +50476,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1841" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50505,7 +50502,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1842" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50531,7 +50528,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1843" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50557,7 +50554,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1844" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50583,7 +50580,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1845" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50609,7 +50606,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1846" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50635,7 +50632,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1847" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50661,7 +50658,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50687,7 +50684,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1849" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50713,7 +50710,7 @@
         <v>4.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50739,7 +50736,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1851" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50765,7 +50762,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50791,7 +50788,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1853" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50817,7 +50814,7 @@
         <v>4.25</v>
       </c>
       <c r="G1854" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50843,7 +50840,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1855" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50869,7 +50866,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1856" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50895,7 +50892,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1857" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50921,7 +50918,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1858" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50947,7 +50944,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50973,7 +50970,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1860" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50999,7 +50996,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1861" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51025,7 +51022,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51051,7 +51048,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1863" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51077,7 +51074,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1864" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51103,7 +51100,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1865" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51129,7 +51126,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1866" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51155,7 +51152,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1867" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51181,7 +51178,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1868" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51207,7 +51204,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1869" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51233,7 +51230,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1870" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51259,7 +51256,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1871" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51285,7 +51282,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1872" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51311,7 +51308,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1873" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51337,7 +51334,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1874" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51363,7 +51360,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1875" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51389,7 +51386,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1876" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51415,7 +51412,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1877" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51441,7 +51438,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1878" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51467,7 +51464,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1879" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51493,7 +51490,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1880" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51519,7 +51516,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1881" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51545,7 +51542,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1882" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51571,7 +51568,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1883" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51597,7 +51594,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1884" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51623,7 +51620,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1885" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51649,7 +51646,7 @@
         <v>4.25</v>
       </c>
       <c r="G1886" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51675,7 +51672,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51701,7 +51698,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1888" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51727,7 +51724,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51753,7 +51750,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1890" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51779,7 +51776,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1891" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51805,7 +51802,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1892" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51831,7 +51828,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1893" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51857,7 +51854,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1894" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51883,7 +51880,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1895" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51909,7 +51906,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51935,7 +51932,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1897" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51961,7 +51958,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1898" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51987,7 +51984,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1899" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52013,7 +52010,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1900" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52039,7 +52036,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52065,7 +52062,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1902" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52091,7 +52088,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1903" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52117,7 +52114,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1904" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52143,7 +52140,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1905" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52169,7 +52166,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52195,7 +52192,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52221,7 +52218,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1908" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52247,7 +52244,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1909" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52273,7 +52270,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1910" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52299,7 +52296,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1911" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52325,7 +52322,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52351,7 +52348,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1913" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52377,7 +52374,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1914" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52403,7 +52400,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1915" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52429,7 +52426,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1916" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52455,7 +52452,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1917" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52481,7 +52478,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1918" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52507,7 +52504,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1919" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52533,7 +52530,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1920" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52559,7 +52556,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1921" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52585,7 +52582,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1922" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52611,7 +52608,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G1923" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52637,7 +52634,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1924" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52663,7 +52660,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1925" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52689,7 +52686,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1926" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52715,7 +52712,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1927" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52741,7 +52738,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1928" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52767,7 +52764,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1929" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52793,7 +52790,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52819,7 +52816,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G1931" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52845,7 +52842,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1932" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52871,7 +52868,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1933" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52897,7 +52894,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1934" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52923,7 +52920,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1935" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52949,7 +52946,7 @@
         <v>4.5</v>
       </c>
       <c r="G1936" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52975,7 +52972,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1937" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53001,7 +52998,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1938" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53027,7 +53024,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1939" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53053,7 +53050,7 @@
         <v>4.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53079,7 +53076,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1941" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53105,7 +53102,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1942" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53131,7 +53128,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1943" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53157,7 +53154,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53183,7 +53180,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1945" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53209,7 +53206,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1946" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53235,7 +53232,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53261,7 +53258,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1948" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53287,7 +53284,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1949" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53313,7 +53310,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1950" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53339,7 +53336,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1951" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53365,7 +53362,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1952" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53391,7 +53388,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1953" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53417,7 +53414,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53443,7 +53440,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1955" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53469,7 +53466,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1956" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53495,7 +53492,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53521,7 +53518,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1958" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53547,7 +53544,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53573,7 +53570,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53599,7 +53596,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1961" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53625,7 +53622,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1962" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53651,7 +53648,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53677,7 +53674,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53703,7 +53700,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G1965" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53729,7 +53726,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1966" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53755,7 +53752,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1967" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53781,7 +53778,7 @@
         <v>5</v>
       </c>
       <c r="G1968" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53807,7 +53804,7 @@
         <v>5</v>
       </c>
       <c r="G1969" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53833,7 +53830,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1970" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53859,7 +53856,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1971" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53885,7 +53882,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G1972" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53911,7 +53908,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1973" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53937,7 +53934,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53963,7 +53960,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53989,7 +53986,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1976" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54015,7 +54012,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1977" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54041,7 +54038,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1978" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54067,7 +54064,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1979" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54093,7 +54090,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54119,7 +54116,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1981" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54145,7 +54142,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1982" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54171,7 +54168,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1983" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54197,7 +54194,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1984" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54223,7 +54220,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1985" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54249,7 +54246,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1986" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54275,7 +54272,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1987" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54301,7 +54298,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54327,7 +54324,7 @@
         <v>5.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54353,7 +54350,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1990" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54379,7 +54376,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1991" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54405,7 +54402,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54431,7 +54428,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1993" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54457,7 +54454,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1994" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54483,7 +54480,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1995" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54509,7 +54506,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1996" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54535,7 +54532,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1997" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54561,7 +54558,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1998" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54587,7 +54584,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54613,7 +54610,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2000" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54639,7 +54636,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2001" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54665,7 +54662,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G2002" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54691,7 +54688,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54717,7 +54714,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54743,7 +54740,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2005" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54769,7 +54766,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2006" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54795,7 +54792,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2007" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54821,7 +54818,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2008" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54829,7 +54826,7 @@
     </row>
     <row r="2009">
       <c r="A2009" s="1" t="n">
-        <v>45951.6493055556</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2009" t="n">
         <v>31551</v>
@@ -54847,9 +54844,35 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2009" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2009" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" s="1" t="n">
+        <v>45952.6494444444</v>
+      </c>
+      <c r="B2010" t="n">
+        <v>194531</v>
+      </c>
+      <c r="C2010" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="D2010" t="n">
+        <v>5.57999992370605</v>
+      </c>
+      <c r="E2010" t="n">
+        <v>5.6100001335144</v>
+      </c>
+      <c r="F2010" t="n">
+        <v>5.65999984741211</v>
+      </c>
+      <c r="G2010" t="s">
+        <v>748</v>
+      </c>
+      <c r="H2010" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66104185581207</t>
+    <t xml:space="preserve">1.66104221343994</t>
   </si>
   <si>
     <t xml:space="preserve">EQUI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73039221763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76171112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75835585594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75500023365021</t>
+    <t xml:space="preserve">1.7303923368454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76171135902405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75835561752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75499999523163</t>
   </si>
   <si>
     <t xml:space="preserve">1.74493312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71361339092255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71808779239655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73374760150909</t>
+    <t xml:space="preserve">1.71361351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71808815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374736309052</t>
   </si>
   <si>
     <t xml:space="preserve">1.72032499313354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7013099193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70019114017487</t>
+    <t xml:space="preserve">1.70130968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70019137859344</t>
   </si>
   <si>
     <t xml:space="preserve">1.69795417785645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68005740642548</t>
+    <t xml:space="preserve">1.6800571680069</t>
   </si>
   <si>
     <t xml:space="preserve">1.68900585174561</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">1.69571709632874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69683563709259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69124281406403</t>
+    <t xml:space="preserve">1.69683539867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69124293327332</t>
   </si>
   <si>
     <t xml:space="preserve">1.70242834091187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6822943687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66775357723236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69012463092804</t>
+    <t xml:space="preserve">1.68229413032532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68565022945404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6677531003952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69012403488159</t>
   </si>
   <si>
     <t xml:space="preserve">1.71696925163269</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">1.72256219387054</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7214435338974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71473240852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71585071086884</t>
+    <t xml:space="preserve">1.72144377231598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7147319316864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7158510684967</t>
   </si>
   <si>
     <t xml:space="preserve">1.74717009067535</t>
@@ -134,115 +134,115 @@
     <t xml:space="preserve">1.75052583217621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7393399477005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70858061313629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71137714385986</t>
+    <t xml:space="preserve">1.73934042453766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70858037471771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71137690544128</t>
   </si>
   <si>
     <t xml:space="preserve">1.74213683605194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74772965908051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73095107078552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72815454006195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71417319774628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79526782035828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7673043012619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77289688587189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78967499732971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7756929397583</t>
+    <t xml:space="preserve">1.74772942066193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73095142841339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7281551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71417307853699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79526793956757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76730418205261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77289640903473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78967523574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77569317817688</t>
   </si>
   <si>
     <t xml:space="preserve">1.78408229351044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78687822818756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84560227394104</t>
+    <t xml:space="preserve">1.78687882423401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84560239315033</t>
   </si>
   <si>
     <t xml:space="preserve">1.82323122024536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81763851642609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78128576278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84280574321747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83441686630249</t>
+    <t xml:space="preserve">1.81763887405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78128588199615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84280622005463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83441698551178</t>
   </si>
   <si>
     <t xml:space="preserve">1.86517703533173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87076950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85119497776031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86238050460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85958397388458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678744316101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84000968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89034450054169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93820095062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92025470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92922794818878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89333522319794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86641597747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87838041782379</t>
+    <t xml:space="preserve">1.87076985836029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85119521617889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86238062381744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85958421230316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678780078888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84000957012177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89034426212311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93820083141327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.920254945755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92922806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89333510398865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86641585826874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87838017940521</t>
   </si>
   <si>
     <t xml:space="preserve">1.90829062461853</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92324566841125</t>
+    <t xml:space="preserve">1.92324554920197</t>
   </si>
   <si>
     <t xml:space="preserve">1.92623686790466</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">1.91128170490265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93221867084503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85445141792297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81257677078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8424870967865</t>
+    <t xml:space="preserve">1.9322190284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85445117950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81257665157318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84248733520508</t>
   </si>
   <si>
     <t xml:space="preserve">1.8454784154892</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">1.82753217220306</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86940717697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83052325248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86342465877533</t>
+    <t xml:space="preserve">1.86940670013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83052349090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86342477798462</t>
   </si>
   <si>
     <t xml:space="preserve">1.88137102127075</t>
@@ -284,52 +284,52 @@
     <t xml:space="preserve">1.88436210155487</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89632642269135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91726362705231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89931726455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529918670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9621297121048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94119215011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93520975112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94418299198151</t>
+    <t xml:space="preserve">1.89632594585419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91726350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89931738376617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90529942512512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96212935447693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94119191169739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93520963191986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94418323040009</t>
   </si>
   <si>
     <t xml:space="preserve">1.88735294342041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90230870246887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91427266597748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85744249820709</t>
+    <t xml:space="preserve">1.90230846405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91427278518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85744285583496</t>
   </si>
   <si>
     <t xml:space="preserve">1.94717442989349</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96512019634247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00400400161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01297688484192</t>
+    <t xml:space="preserve">1.96512043476105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00400376319885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01297736167908</t>
   </si>
   <si>
     <t xml:space="preserve">1.9740936756134</t>
@@ -347,70 +347,70 @@
     <t xml:space="preserve">2.03391480445862</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00998616218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97708439826965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9591383934021</t>
+    <t xml:space="preserve">2.00998640060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97708451747894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913827419281</t>
   </si>
   <si>
     <t xml:space="preserve">2.00699496269226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06382513046265</t>
+    <t xml:space="preserve">2.06382489204407</t>
   </si>
   <si>
     <t xml:space="preserve">2.05186104774475</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99503099918365</t>
+    <t xml:space="preserve">1.99503111839294</t>
   </si>
   <si>
     <t xml:space="preserve">1.99802196025848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95614719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97110247612</t>
+    <t xml:space="preserve">1.95614731311798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97110295295715</t>
   </si>
   <si>
     <t xml:space="preserve">2.13261914253235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12065505981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03989696502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04587864875793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02494168281555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904871940613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98007595539093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99203991889954</t>
+    <t xml:space="preserve">2.12065482139587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03989672660828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04587888717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02494144439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904883861542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98007571697235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99204015731812</t>
   </si>
   <si>
     <t xml:space="preserve">1.95315623283386</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87239789962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86043381690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83650529384613</t>
+    <t xml:space="preserve">1.87239801883698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8604336977005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83650493621826</t>
   </si>
   <si>
     <t xml:space="preserve">1.87538886070251</t>
@@ -419,97 +419,97 @@
     <t xml:space="preserve">2.08081078529358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95236599445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94594347476959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93952131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9266768693924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86887657642365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83676528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83034324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80465388298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79180943965912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77896499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7725430727005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6954756975174</t>
+    <t xml:space="preserve">1.95236587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94594359397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93952119350433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92667698860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86887681484222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83676540851593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83034288883209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80465364456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79180932044983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77896511554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77254283428192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69547581672668</t>
   </si>
   <si>
     <t xml:space="preserve">1.73400950431824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68905329704285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65051996707916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978669166565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70832014083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72116482257843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67620849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71474242210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6633642911911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64409756660461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72758686542511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7468535900116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74043142795563</t>
+    <t xml:space="preserve">1.68905353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65051972866058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7083203792572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72116470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67620897293091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71474206447601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66336441040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64409744739532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7275869846344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74685370922089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74043130874634</t>
   </si>
   <si>
     <t xml:space="preserve">1.75327587127686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75969815254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70189785957336</t>
+    <t xml:space="preserve">1.7596982717514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70189797878265</t>
   </si>
   <si>
     <t xml:space="preserve">1.68263125419617</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65694224834442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63767540454865</t>
+    <t xml:space="preserve">1.65694200992584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63767528533936</t>
   </si>
   <si>
     <t xml:space="preserve">1.61198627948761</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">1.60556399822235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59914195537567</t>
+    <t xml:space="preserve">1.59914183616638</t>
   </si>
   <si>
     <t xml:space="preserve">1.61840844154358</t>
@@ -527,67 +527,67 @@
     <t xml:space="preserve">1.59271967411041</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62483048439026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81749844551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86245453357697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85603225231171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84960985183716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82392084598541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78538727760315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81107604503632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79823136329651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125312328339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5156524181366</t>
+    <t xml:space="preserve">1.62483084201813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81749868392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86245429515839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85603201389313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84961009025574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82392072677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78538715839386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8110762834549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7982314825058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125324249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51565229892731</t>
   </si>
   <si>
     <t xml:space="preserve">1.40005207061768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58629727363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54134154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41931867599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43858551979065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35509598255157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33582925796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36151826381683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36794066429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3165625333786</t>
+    <t xml:space="preserve">1.58629739284515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54134178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41931855678558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43858528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35509610176086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3358291387558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36151814460754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36794078350067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31656241416931</t>
   </si>
   <si>
     <t xml:space="preserve">1.32940697669983</t>
@@ -596,91 +596,91 @@
     <t xml:space="preserve">1.32298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37436270713806</t>
+    <t xml:space="preserve">1.37436294555664</t>
   </si>
   <si>
     <t xml:space="preserve">1.38720750808716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34867370128632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3807852268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47069680690765</t>
+    <t xml:space="preserve">1.3486739397049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38078510761261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47069668769836</t>
   </si>
   <si>
     <t xml:space="preserve">1.42574083805084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43216335773468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49638569355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45785236358643</t>
+    <t xml:space="preserve">1.4321631193161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4963858127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45785212516785</t>
   </si>
   <si>
     <t xml:space="preserve">1.41289627552032</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45143020153046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47711896896362</t>
+    <t xml:space="preserve">1.45142996311188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47711884975433</t>
   </si>
   <si>
     <t xml:space="preserve">1.48354113101959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46427440643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57345294952393</t>
+    <t xml:space="preserve">1.46427428722382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57345271110535</t>
   </si>
   <si>
     <t xml:space="preserve">1.44500756263733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48996329307556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55418586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76612055301666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90653848648071</t>
+    <t xml:space="preserve">1.48996353149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55418598651886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76612067222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90653860569</t>
   </si>
   <si>
     <t xml:space="preserve">1.85167443752289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70079708099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68708086013794</t>
+    <t xml:space="preserve">1.70079720020294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68708097934723</t>
   </si>
   <si>
     <t xml:space="preserve">1.65279066562653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68022286891937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65964841842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64593255519867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61164224147797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69393885135651</t>
+    <t xml:space="preserve">1.68022274971008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65964865684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64593279361725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61164212226868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69393908977509</t>
   </si>
   <si>
     <t xml:space="preserve">1.67336487770081</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">1.70765507221222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66650676727295</t>
+    <t xml:space="preserve">1.66650652885437</t>
   </si>
   <si>
     <t xml:space="preserve">1.71451306343079</t>
@@ -701,52 +701,52 @@
     <t xml:space="preserve">1.74194538593292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63221633434296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59792625904083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56363594532013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55677807331085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57049417495728</t>
+    <t xml:space="preserve">1.63221645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59792637825012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56363582611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55677783489227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5704939365387</t>
   </si>
   <si>
     <t xml:space="preserve">1.58421003818512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59106802940369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57735216617584</t>
+    <t xml:space="preserve">1.59106814861298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57735192775726</t>
   </si>
   <si>
     <t xml:space="preserve">1.61850023269653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62535834312439</t>
+    <t xml:space="preserve">1.62535810470581</t>
   </si>
   <si>
     <t xml:space="preserve">1.60478413105011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53620386123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54992008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63907444477081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54306173324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52934587001801</t>
+    <t xml:space="preserve">1.53620362281799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54991984367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6390745639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54306161403656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52934563159943</t>
   </si>
   <si>
     <t xml:space="preserve">1.52248764038086</t>
@@ -755,124 +755,124 @@
     <t xml:space="preserve">1.515629529953</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50877153873444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50191354751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48133945465088</t>
+    <t xml:space="preserve">1.50877141952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50191342830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48133933544159</t>
   </si>
   <si>
     <t xml:space="preserve">1.48819732666016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46762311458588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45390701293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39904260635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36475241184235</t>
+    <t xml:space="preserve">1.46762323379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45390689373016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39904272556305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36475253105164</t>
   </si>
   <si>
     <t xml:space="preserve">1.37846851348877</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3716105222702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35789453983307</t>
+    <t xml:space="preserve">1.37161040306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3578941822052</t>
   </si>
   <si>
     <t xml:space="preserve">1.35446536540985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72137105464935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7830935716629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81738388538361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79680979251862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78995132446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77623558044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81052589416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83109998703003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83795821666718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80366766452789</t>
+    <t xml:space="preserve">1.72137117385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78309345245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8173840045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79680991172791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78995168209076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77623546123505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81052601337433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83109962940216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8379579782486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80366790294647</t>
   </si>
   <si>
     <t xml:space="preserve">1.84481620788574</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87224817276001</t>
+    <t xml:space="preserve">1.8722482919693</t>
   </si>
   <si>
     <t xml:space="preserve">1.89968061447144</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91339659690857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9271125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94082880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96140289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97511911392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94768691062927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92025423049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88596439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95454525947571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93397045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96826124191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01626706123352</t>
+    <t xml:space="preserve">1.91339647769928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92711234092712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94082903862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9614030122757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9751193523407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94768679141998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92025446891785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88596451282501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95454478263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93397068977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96826088428497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0162672996521</t>
   </si>
   <si>
     <t xml:space="preserve">2.05055785179138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04369974136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06427383422852</t>
+    <t xml:space="preserve">2.04369926452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06427359580994</t>
   </si>
   <si>
     <t xml:space="preserve">2.03684163093567</t>
@@ -884,40 +884,40 @@
     <t xml:space="preserve">2.05741572380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113170623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07799005508423</t>
+    <t xml:space="preserve">2.07113146781921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07798981666565</t>
   </si>
   <si>
     <t xml:space="preserve">2.08484792709351</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09903073310852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10612177848816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13448715209961</t>
+    <t xml:space="preserve">2.09903025627136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10612201690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13448691368103</t>
   </si>
   <si>
     <t xml:space="preserve">2.09193921089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14157843589783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11321330070496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12030458450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12739610671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16285228729248</t>
+    <t xml:space="preserve">2.14157819747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1132128238678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12030482292175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12739586830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16285252571106</t>
   </si>
   <si>
     <t xml:space="preserve">2.1770350933075</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">2.25503969192505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26213073730469</t>
+    <t xml:space="preserve">2.26213121414185</t>
   </si>
   <si>
     <t xml:space="preserve">2.24794816970825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21958327293396</t>
+    <t xml:space="preserve">2.2195827960968</t>
   </si>
   <si>
     <t xml:space="preserve">2.19830894470215</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2337658405304</t>
+    <t xml:space="preserve">2.23376560211182</t>
   </si>
   <si>
     <t xml:space="preserve">2.24085712432861</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">2.26922225952148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29049587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29758715629578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31177020072937</t>
+    <t xml:space="preserve">2.29049634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29758739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176996231079</t>
   </si>
   <si>
     <t xml:space="preserve">2.31886148452759</t>
@@ -974,52 +974,52 @@
     <t xml:space="preserve">2.32595276832581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3330442905426</t>
+    <t xml:space="preserve">2.33304405212402</t>
   </si>
   <si>
     <t xml:space="preserve">2.30467867851257</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36850047111511</t>
+    <t xml:space="preserve">2.36850070953369</t>
   </si>
   <si>
     <t xml:space="preserve">2.38977456092834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37559175491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38268280029297</t>
+    <t xml:space="preserve">2.37559199333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38268327713013</t>
   </si>
   <si>
     <t xml:space="preserve">2.39686608314514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40395736694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44650506973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43232274055481</t>
+    <t xml:space="preserve">2.40395712852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44650530815125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43232250213623</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614453315735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51032757759094</t>
+    <t xml:space="preserve">2.51032710075378</t>
   </si>
   <si>
     <t xml:space="preserve">2.58124017715454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55287480354309</t>
+    <t xml:space="preserve">2.55287504196167</t>
   </si>
   <si>
     <t xml:space="preserve">2.55996608734131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63087964057922</t>
+    <t xml:space="preserve">2.63087940216064</t>
   </si>
   <si>
     <t xml:space="preserve">2.62378811836243</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">2.60960578918457</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63797092437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58833146095276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59542298316956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61669683456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6521532535553</t>
+    <t xml:space="preserve">2.63797044754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58833169937134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59542274475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61669707298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65215349197388</t>
   </si>
   <si>
     <t xml:space="preserve">2.65924453735352</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">2.70179271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69470167160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72306680679321</t>
+    <t xml:space="preserve">2.69470119476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72306656837463</t>
   </si>
   <si>
     <t xml:space="preserve">2.71597528457642</t>
@@ -1064,94 +1064,94 @@
     <t xml:space="preserve">2.7088840007782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68051862716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73092269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907473564148</t>
+    <t xml:space="preserve">2.68051886558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73092222213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907521247864</t>
   </si>
   <si>
     <t xml:space="preserve">2.76733493804932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8110294342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86200714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84015941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81831169128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8037474155426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83287692070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78189969062805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72363996505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75277018547058</t>
+    <t xml:space="preserve">2.81102967262268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8620069026947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84015965461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81831192970276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80374717712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83287668228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78189992904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72364020347595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.752769947052</t>
   </si>
   <si>
     <t xml:space="preserve">2.69451022148132</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71635746955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74548768997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73820519447327</t>
+    <t xml:space="preserve">2.71635770797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74548745155334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73820471763611</t>
   </si>
   <si>
     <t xml:space="preserve">2.77461743354797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82559442520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78918242454529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79646468162537</t>
+    <t xml:space="preserve">2.82559466362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78918218612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79646444320679</t>
   </si>
   <si>
     <t xml:space="preserve">2.76005244255066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62896823883057</t>
+    <t xml:space="preserve">2.62896800041199</t>
   </si>
   <si>
     <t xml:space="preserve">2.62168550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66538071632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86928939819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61440300941467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55614376068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5342960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43962407112122</t>
+    <t xml:space="preserve">2.66538047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86928915977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61440348625183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55614352226257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53429627418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43962430953979</t>
   </si>
   <si>
     <t xml:space="preserve">2.31582236289978</t>
@@ -1160,40 +1160,40 @@
     <t xml:space="preserve">2.22843265533447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27212738990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40321183204651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41049432754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5488612651825</t>
+    <t xml:space="preserve">2.27212715148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40321159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41049408912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54886102676392</t>
   </si>
   <si>
     <t xml:space="preserve">2.65809798240662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54157876968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67266273498535</t>
+    <t xml:space="preserve">2.54157853126526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67266297340393</t>
   </si>
   <si>
     <t xml:space="preserve">2.88385415077209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89841914176941</t>
+    <t xml:space="preserve">2.89841890335083</t>
   </si>
   <si>
     <t xml:space="preserve">2.95667862892151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94211363792419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97124409675598</t>
+    <t xml:space="preserve">2.94211387634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97124361991882</t>
   </si>
   <si>
     <t xml:space="preserve">2.94939637184143</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">2.91298413276672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85472440719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97852659225464</t>
+    <t xml:space="preserve">2.85472464561462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97852611541748</t>
   </si>
   <si>
     <t xml:space="preserve">2.96396136283875</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">2.90570139884949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92754888534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05783224105835</t>
+    <t xml:space="preserve">2.92754912376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05783247947693</t>
   </si>
   <si>
     <t xml:space="preserve">3.02717757225037</t>
@@ -1232,49 +1232,49 @@
     <t xml:space="preserve">3.01951384544373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98885869979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95054030418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88923048973083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91222143173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77427387237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66698169708252</t>
+    <t xml:space="preserve">2.98885917663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95054006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88923025131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91222167015076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77427411079407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6669819355011</t>
   </si>
   <si>
     <t xml:space="preserve">2.68230938911438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67464566230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68997311592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72062754631042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69763660430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72829127311707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7053005695343</t>
+    <t xml:space="preserve">2.67464542388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68997287750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.720627784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69763684272766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72829151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70530033111572</t>
   </si>
   <si>
     <t xml:space="preserve">2.63632678985596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65165448188782</t>
+    <t xml:space="preserve">2.65165424346924</t>
   </si>
   <si>
     <t xml:space="preserve">2.6439905166626</t>
@@ -1286,16 +1286,16 @@
     <t xml:space="preserve">2.59034442901611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65931797027588</t>
+    <t xml:space="preserve">2.65931820869446</t>
   </si>
   <si>
     <t xml:space="preserve">2.61333560943604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56735301017761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53669810295105</t>
+    <t xml:space="preserve">2.56735324859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53669786453247</t>
   </si>
   <si>
     <t xml:space="preserve">2.52137064933777</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.52903437614441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55202579498291</t>
+    <t xml:space="preserve">2.55202555656433</t>
   </si>
   <si>
     <t xml:space="preserve">2.54436182975769</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">2.59800815582275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46772456169128</t>
+    <t xml:space="preserve">2.46772432327271</t>
   </si>
   <si>
     <t xml:space="preserve">2.49837946891785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43706965446472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.452397108078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49071550369263</t>
+    <t xml:space="preserve">2.43706941604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45239686965942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49071574211121</t>
   </si>
   <si>
     <t xml:space="preserve">2.50604319572449</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">2.47538805007935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46006083488464</t>
+    <t xml:space="preserve">2.46006059646606</t>
   </si>
   <si>
     <t xml:space="preserve">2.48305201530457</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">2.78960156440735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80492925643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82025647163391</t>
+    <t xml:space="preserve">2.80492901802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82025671005249</t>
   </si>
   <si>
     <t xml:space="preserve">2.82792019844055</t>
@@ -1361,10 +1361,10 @@
     <t xml:space="preserve">2.81259274482727</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85091114044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86623883247375</t>
+    <t xml:space="preserve">2.85091161727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86623907089233</t>
   </si>
   <si>
     <t xml:space="preserve">2.89019060134888</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">2.89817476272583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92212677001953</t>
+    <t xml:space="preserve">2.92212653160095</t>
   </si>
   <si>
     <t xml:space="preserve">2.91414260864258</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">2.95406246185303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9620463848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97003054618835</t>
+    <t xml:space="preserve">2.96204614639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97003030776978</t>
   </si>
   <si>
     <t xml:space="preserve">2.94607853889465</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">2.87422275543213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90615892410278</t>
+    <t xml:space="preserve">2.9061586856842</t>
   </si>
   <si>
     <t xml:space="preserve">2.93809461593628</t>
@@ -1406,10 +1406,10 @@
     <t xml:space="preserve">2.93011069297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99398231506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00196623802185</t>
+    <t xml:space="preserve">2.9939820766449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00196599960327</t>
   </si>
   <si>
     <t xml:space="preserve">2.97801423072815</t>
@@ -1418,10 +1418,10 @@
     <t xml:space="preserve">3.06583762168884</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08978939056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08180546760559</t>
+    <t xml:space="preserve">3.08978962898254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08180570602417</t>
   </si>
   <si>
     <t xml:space="preserve">3.0179340839386</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">3.04987001419067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9859983921051</t>
+    <t xml:space="preserve">2.98599815368652</t>
   </si>
   <si>
     <t xml:space="preserve">3.02591800689697</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">3.03390216827393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11374139785767</t>
+    <t xml:space="preserve">3.11374163627625</t>
   </si>
   <si>
     <t xml:space="preserve">3.0738217830658</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">3.12172555923462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12970924377441</t>
+    <t xml:space="preserve">3.12970972061157</t>
   </si>
   <si>
     <t xml:space="preserve">3.09777355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15366125106812</t>
+    <t xml:space="preserve">3.15366148948669</t>
   </si>
   <si>
     <t xml:space="preserve">3.10575747489929</t>
@@ -1484,28 +1484,28 @@
     <t xml:space="preserve">3.17761301994324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19442582130432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21123886108398</t>
+    <t xml:space="preserve">3.1944260597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21123862266541</t>
   </si>
   <si>
     <t xml:space="preserve">3.18601965904236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14398765563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15239405632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16920685768127</t>
+    <t xml:space="preserve">3.14398741722107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15239381790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1692066192627</t>
   </si>
   <si>
     <t xml:space="preserve">3.11876845359802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11036205291748</t>
+    <t xml:space="preserve">3.1103618144989</t>
   </si>
   <si>
     <t xml:space="preserve">3.12717485427856</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">3.13558101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09354948997498</t>
+    <t xml:space="preserve">3.0935492515564</t>
   </si>
   <si>
     <t xml:space="preserve">3.10195565223694</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">3.08514285087585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16080021858215</t>
+    <t xml:space="preserve">3.16079998016357</t>
   </si>
   <si>
     <t xml:space="preserve">3.07673645019531</t>
@@ -1532,22 +1532,22 @@
     <t xml:space="preserve">3.06833004951477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05151748657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04311060905457</t>
+    <t xml:space="preserve">3.05151724815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04311084747314</t>
   </si>
   <si>
     <t xml:space="preserve">3.0347044467926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05992364883423</t>
+    <t xml:space="preserve">3.05992388725281</t>
   </si>
   <si>
     <t xml:space="preserve">3.02629804611206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00948524475098</t>
+    <t xml:space="preserve">3.00948548316956</t>
   </si>
   <si>
     <t xml:space="preserve">2.97585988044739</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">3.00107884407043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01789140701294</t>
+    <t xml:space="preserve">3.0178918838501</t>
   </si>
   <si>
     <t xml:space="preserve">2.95064067840576</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">2.88338971138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90860867500305</t>
+    <t xml:space="preserve">2.90860915184021</t>
   </si>
   <si>
     <t xml:space="preserve">2.8665771484375</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">2.85817074775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87498354911804</t>
+    <t xml:space="preserve">2.87498331069946</t>
   </si>
   <si>
     <t xml:space="preserve">2.83295130729675</t>
@@ -1586,16 +1586,16 @@
     <t xml:space="preserve">2.91701531410217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93382811546326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89179635047913</t>
+    <t xml:space="preserve">2.93382787704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89179587364197</t>
   </si>
   <si>
     <t xml:space="preserve">2.98426604270935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92542147636414</t>
+    <t xml:space="preserve">2.92542171478271</t>
   </si>
   <si>
     <t xml:space="preserve">2.9590470790863</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">3.09426784515381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11179876327515</t>
+    <t xml:space="preserve">3.11179900169373</t>
   </si>
   <si>
     <t xml:space="preserve">3.12933015823364</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">3.22575235366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24328374862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23451781272888</t>
+    <t xml:space="preserve">3.24328327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23451805114746</t>
   </si>
   <si>
     <t xml:space="preserve">3.25204920768738</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">3.18192410469055</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17315816879272</t>
+    <t xml:space="preserve">3.1731584072113</t>
   </si>
   <si>
     <t xml:space="preserve">3.21698665618896</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">3.26958036422729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27834606170654</t>
+    <t xml:space="preserve">3.27834582328796</t>
   </si>
   <si>
     <t xml:space="preserve">3.29587721824646</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">3.3221743106842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31340861320496</t>
+    <t xml:space="preserve">3.31340837478638</t>
   </si>
   <si>
     <t xml:space="preserve">3.33970546722412</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">3.43612742424011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39229893684387</t>
+    <t xml:space="preserve">3.39229917526245</t>
   </si>
   <si>
     <t xml:space="preserve">3.44489312171936</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">3.41859602928162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48872137069702</t>
+    <t xml:space="preserve">3.48872089385986</t>
   </si>
   <si>
     <t xml:space="preserve">3.51501822471619</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">3.4010648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37476801872253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3835334777832</t>
+    <t xml:space="preserve">3.37476778030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38353323936462</t>
   </si>
   <si>
     <t xml:space="preserve">3.47118973731995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40983033180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46242427825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50625252723694</t>
+    <t xml:space="preserve">3.40983057022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46242451667786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50625228881836</t>
   </si>
   <si>
     <t xml:space="preserve">3.52378368377686</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">3.54131484031677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5325493812561</t>
+    <t xml:space="preserve">3.53254961967468</t>
   </si>
   <si>
     <t xml:space="preserve">3.55884623527527</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">3.66403365135193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61144018173218</t>
+    <t xml:space="preserve">3.61143970489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.60267448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55008101463318</t>
+    <t xml:space="preserve">3.5500807762146</t>
   </si>
   <si>
     <t xml:space="preserve">3.57637739181519</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">3.58559513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60402989387512</t>
+    <t xml:space="preserve">3.6040301322937</t>
   </si>
   <si>
     <t xml:space="preserve">3.57637763023376</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">3.52107262611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55794262886047</t>
+    <t xml:space="preserve">3.55794239044189</t>
   </si>
   <si>
     <t xml:space="preserve">3.56716012954712</t>
@@ -1790,13 +1790,13 @@
     <t xml:space="preserve">3.42889809608459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51185536384583</t>
+    <t xml:space="preserve">3.51185512542725</t>
   </si>
   <si>
     <t xml:space="preserve">3.47498536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53029012680054</t>
+    <t xml:space="preserve">3.53029036521912</t>
   </si>
   <si>
     <t xml:space="preserve">3.49342036247253</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">3.54872512817383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65011715888977</t>
+    <t xml:space="preserve">3.65011739730835</t>
   </si>
   <si>
     <t xml:space="preserve">3.6408998966217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63168263435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44733309745789</t>
+    <t xml:space="preserve">3.63168239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44733285903931</t>
   </si>
   <si>
     <t xml:space="preserve">3.50263786315918</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">3.67776989936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463966369629</t>
+    <t xml:space="preserve">3.71463990211487</t>
   </si>
   <si>
     <t xml:space="preserve">3.78837943077087</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">3.75150966644287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.659334897995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77916169166565</t>
+    <t xml:space="preserve">3.65933465957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77916193008423</t>
   </si>
   <si>
     <t xml:space="preserve">3.80681443214417</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">3.84368419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76994466781616</t>
+    <t xml:space="preserve">3.76994442939758</t>
   </si>
   <si>
     <t xml:space="preserve">3.81603169441223</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">3.91742372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90820622444153</t>
+    <t xml:space="preserve">3.90820646286011</t>
   </si>
   <si>
     <t xml:space="preserve">3.89898896217346</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">3.88055419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93585896492004</t>
+    <t xml:space="preserve">3.93585848808289</t>
   </si>
   <si>
     <t xml:space="preserve">3.94507646560669</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">3.86211895942688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83446645736694</t>
+    <t xml:space="preserve">3.83446669578552</t>
   </si>
   <si>
     <t xml:space="preserve">3.83412289619446</t>
@@ -54956,7 +54956,7 @@
     </row>
     <row r="2014">
       <c r="A2014" s="1" t="n">
-        <v>45958.6913078704</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2014" t="n">
         <v>36937</v>
@@ -54977,6 +54977,32 @@
         <v>748</v>
       </c>
       <c r="H2014" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" s="1" t="n">
+        <v>45959.6910763889</v>
+      </c>
+      <c r="B2015" t="n">
+        <v>41091</v>
+      </c>
+      <c r="C2015" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="D2015" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="E2015" t="n">
+        <v>5.73000001907349</v>
+      </c>
+      <c r="F2015" t="n">
+        <v>5.73000001907349</v>
+      </c>
+      <c r="G2015" t="s">
+        <v>748</v>
+      </c>
+      <c r="H2015" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66104197502136</t>
+    <t xml:space="preserve">1.66104221343994</t>
   </si>
   <si>
     <t xml:space="preserve">EQUI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73039221763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76171135902405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75835561752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75499999523163</t>
+    <t xml:space="preserve">1.73039209842682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76171112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75835585594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75499975681305</t>
   </si>
   <si>
     <t xml:space="preserve">1.74493300914764</t>
@@ -62,199 +62,199 @@
     <t xml:space="preserve">1.71361362934113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71808815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73374736309052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72032475471497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70130980014801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70019137859344</t>
+    <t xml:space="preserve">1.71808803081512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374772071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72032511234283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7013099193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70019114017487</t>
   </si>
   <si>
     <t xml:space="preserve">1.69795405864716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68005740642548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68900537490845</t>
+    <t xml:space="preserve">1.68005728721619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68900561332703</t>
   </si>
   <si>
     <t xml:space="preserve">1.69571709632874</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6968355178833</t>
+    <t xml:space="preserve">1.69683539867401</t>
   </si>
   <si>
     <t xml:space="preserve">1.69124293327332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.702427983284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6822943687439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68564987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66775321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69012427330017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71696949005127</t>
+    <t xml:space="preserve">1.70242822170258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68229424953461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68565011024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66775369644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69012439250946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71696937084198</t>
   </si>
   <si>
     <t xml:space="preserve">1.73262906074524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72256207466125</t>
+    <t xml:space="preserve">1.72256219387054</t>
   </si>
   <si>
     <t xml:space="preserve">1.72144401073456</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71473217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71585083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74717044830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75052559375763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73934042453766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70858013629913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71137666702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74213671684265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74772953987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73095142841339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72815477848053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7141729593277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7952675819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76730394363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77289700508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78967487812042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7756929397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78408241271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78687834739685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84560215473175</t>
+    <t xml:space="preserve">1.71473264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71585094928741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74717020988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75052571296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73934018611908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.708580493927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71137642860413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74213695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74772942066193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7309513092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72815465927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71417343616486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79526770114899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76730406284332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7728967666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.789675116539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77569317817688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78408229351044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78687870502472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84560227394104</t>
   </si>
   <si>
     <t xml:space="preserve">1.82323122024536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81763875484467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78128576278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84280598163605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83441686630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86517679691315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87076961994171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85119485855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86238026618958</t>
+    <t xml:space="preserve">1.81763863563538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78128600120544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84280610084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83441662788391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86517691612244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.870769739151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8511950969696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86238050460815</t>
   </si>
   <si>
     <t xml:space="preserve">1.85958433151245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85678791999817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84000980854034</t>
+    <t xml:space="preserve">1.85678768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84000968933105</t>
   </si>
   <si>
     <t xml:space="preserve">1.89034414291382</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93820106983185</t>
+    <t xml:space="preserve">1.93820095062256</t>
   </si>
   <si>
     <t xml:space="preserve">1.92025482654572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92922794818878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89333522319794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86641573905945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87837994098663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90829062461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92324554920197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92623710632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91128146648407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93221867084503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8544510602951</t>
+    <t xml:space="preserve">1.9292277097702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89333546161652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86641561985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87838006019592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90829050540924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92324566841125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92623662948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91128134727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93221890926361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85445141792297</t>
   </si>
   <si>
     <t xml:space="preserve">1.81257677078247</t>
@@ -263,73 +263,76 @@
     <t xml:space="preserve">1.84248733520508</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84547817707062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753205299377</t>
+    <t xml:space="preserve">1.84547829627991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753229141235</t>
   </si>
   <si>
     <t xml:space="preserve">1.86940681934357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83052337169647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86342465877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88137078285217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88436198234558</t>
+    <t xml:space="preserve">1.83052277565002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86342477798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88137090206146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88436210155487</t>
   </si>
   <si>
     <t xml:space="preserve">1.89632630348206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9172637462616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89931726455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90529906749725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96212959289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9411917924881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93520998954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9441831111908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88735282421112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.902308344841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9142724275589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85744285583496</t>
+    <t xml:space="preserve">1.91726338863373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89931738376617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89034390449524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90529954433441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96212947368622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94119191169739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93520987033844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94418323040009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88735342025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90230846405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91427278518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8574423789978</t>
   </si>
   <si>
     <t xml:space="preserve">1.94717419147491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96512019634247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00400424003601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01297760009766</t>
+    <t xml:space="preserve">1.96512007713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00400400161743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01297736167908</t>
   </si>
   <si>
     <t xml:space="preserve">1.97409355640411</t>
@@ -338,43 +341,43 @@
     <t xml:space="preserve">2.01596832275391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06083416938782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0339150428772</t>
+    <t xml:space="preserve">2.05784344673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06083393096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03391432762146</t>
   </si>
   <si>
     <t xml:space="preserve">2.00998592376709</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97708427906036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913851261139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00699496269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06382489204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05186104774475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99503099918365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99802184104919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95614731311798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97110247612</t>
+    <t xml:space="preserve">1.9770849943161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913803577423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00699520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06382536888123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05186057090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99503087997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99802196025848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95614719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97110259532928</t>
   </si>
   <si>
     <t xml:space="preserve">2.13261938095093</t>
@@ -386,13 +389,13 @@
     <t xml:space="preserve">2.03989672660828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04587888717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02494144439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904919624329</t>
+    <t xml:space="preserve">2.04587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02494096755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.989049077034</t>
   </si>
   <si>
     <t xml:space="preserve">1.98007559776306</t>
@@ -401,25 +404,25 @@
     <t xml:space="preserve">1.99203991889954</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95315647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87239742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8604336977005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83650505542755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87538909912109</t>
+    <t xml:space="preserve">1.95315623283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87239789962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86043345928192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83650529384613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8753889799118</t>
   </si>
   <si>
     <t xml:space="preserve">2.08081102371216</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95236587524414</t>
+    <t xml:space="preserve">1.95236575603485</t>
   </si>
   <si>
     <t xml:space="preserve">1.94594347476959</t>
@@ -428,25 +431,25 @@
     <t xml:space="preserve">1.93952131271362</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92667698860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86887669563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83676517009735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83034312725067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80465412139893</t>
+    <t xml:space="preserve">1.92667710781097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86887657642365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83676493167877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83034288883209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80465400218964</t>
   </si>
   <si>
     <t xml:space="preserve">1.79180943965912</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7789648771286</t>
+    <t xml:space="preserve">1.77896475791931</t>
   </si>
   <si>
     <t xml:space="preserve">1.77254247665405</t>
@@ -455,52 +458,52 @@
     <t xml:space="preserve">1.69547581672668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73400962352753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68905341625214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65051972866058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66978693008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70832014083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72116470336914</t>
+    <t xml:space="preserve">1.73400938510895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68905365467072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65051984786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66978669166565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70832026004791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72116494178772</t>
   </si>
   <si>
     <t xml:space="preserve">1.67620885372162</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71474242210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66336464881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6440976858139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72758662700653</t>
+    <t xml:space="preserve">1.71474254131317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66336452960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64409744739532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72758710384369</t>
   </si>
   <si>
     <t xml:space="preserve">1.74685382843018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74043166637421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75327599048615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7596982717514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70189785957336</t>
+    <t xml:space="preserve">1.74043154716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75327575206757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75969803333282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70189797878265</t>
   </si>
   <si>
     <t xml:space="preserve">1.68263077735901</t>
@@ -509,76 +512,76 @@
     <t xml:space="preserve">1.65694212913513</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63767516613007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6119863986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60556423664093</t>
+    <t xml:space="preserve">1.63767552375793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61198616027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60556399822235</t>
   </si>
   <si>
     <t xml:space="preserve">1.59914195537567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61840867996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59271967411041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62483108043671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81749844551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8624541759491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85603213310242</t>
+    <t xml:space="preserve">1.61840856075287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59271943569183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62483084201813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81749868392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86245405673981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856032371521</t>
   </si>
   <si>
     <t xml:space="preserve">1.84960985183716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8239209651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78538739681244</t>
+    <t xml:space="preserve">1.82392060756683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78538703918457</t>
   </si>
   <si>
     <t xml:space="preserve">1.81107640266418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79823172092438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63125312328339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51565265655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40005171298981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58629739284515</t>
+    <t xml:space="preserve">1.79823160171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63125324249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51565253734589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4000518321991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58629703521729</t>
   </si>
   <si>
     <t xml:space="preserve">1.54134154319763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41931879520416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43858551979065</t>
+    <t xml:space="preserve">1.41931867599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43858540058136</t>
   </si>
   <si>
     <t xml:space="preserve">1.35509610176086</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33582925796509</t>
+    <t xml:space="preserve">1.3358291387558</t>
   </si>
   <si>
     <t xml:space="preserve">1.36151826381683</t>
@@ -599,16 +602,16 @@
     <t xml:space="preserve">1.37436306476593</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38720738887787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34867382049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38078510761261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47069656848907</t>
+    <t xml:space="preserve">1.38720726966858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34867370128632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38078498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47069668769836</t>
   </si>
   <si>
     <t xml:space="preserve">1.42574083805084</t>
@@ -617,7 +620,7 @@
     <t xml:space="preserve">1.4321631193161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49638545513153</t>
+    <t xml:space="preserve">1.49638569355011</t>
   </si>
   <si>
     <t xml:space="preserve">1.45785212516785</t>
@@ -626,37 +629,37 @@
     <t xml:space="preserve">1.4128965139389</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45142984390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47711896896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48354113101959</t>
+    <t xml:space="preserve">1.45143008232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47711884975433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48354125022888</t>
   </si>
   <si>
     <t xml:space="preserve">1.46427440643311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57345271110535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4450079202652</t>
+    <t xml:space="preserve">1.57345283031464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44500768184662</t>
   </si>
   <si>
     <t xml:space="preserve">1.48996353149414</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55418610572815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76612055301666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90653860569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85167419910431</t>
+    <t xml:space="preserve">1.55418586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76612067222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90653884410858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85167443752289</t>
   </si>
   <si>
     <t xml:space="preserve">1.70079708099365</t>
@@ -668,13 +671,13 @@
     <t xml:space="preserve">1.65279078483582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68022274971008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65964877605438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64593243598938</t>
+    <t xml:space="preserve">1.68022298812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65964865684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64593267440796</t>
   </si>
   <si>
     <t xml:space="preserve">1.61164212226868</t>
@@ -686,43 +689,43 @@
     <t xml:space="preserve">1.67336463928223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70765495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66650700569153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71451306343079</t>
+    <t xml:space="preserve">1.70765483379364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66650676727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71451330184937</t>
   </si>
   <si>
     <t xml:space="preserve">1.72822904586792</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74194514751434</t>
+    <t xml:space="preserve">1.74194526672363</t>
   </si>
   <si>
     <t xml:space="preserve">1.63221645355225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59792613983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56363606452942</t>
+    <t xml:space="preserve">1.59792625904083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56363570690155</t>
   </si>
   <si>
     <t xml:space="preserve">1.55677783489227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57049369812012</t>
+    <t xml:space="preserve">1.5704939365387</t>
   </si>
   <si>
     <t xml:space="preserve">1.58421015739441</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59106826782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57735192775726</t>
+    <t xml:space="preserve">1.59106802940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57735216617584</t>
   </si>
   <si>
     <t xml:space="preserve">1.61850011348724</t>
@@ -737,28 +740,28 @@
     <t xml:space="preserve">1.53620386123657</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54991984367371</t>
+    <t xml:space="preserve">1.549919962883</t>
   </si>
   <si>
     <t xml:space="preserve">1.6390745639801</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54306185245514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52934587001801</t>
+    <t xml:space="preserve">1.54306173324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52934575080872</t>
   </si>
   <si>
     <t xml:space="preserve">1.52248752117157</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51562929153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50877141952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50191342830658</t>
+    <t xml:space="preserve">1.515629529953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50877153873444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50191354751587</t>
   </si>
   <si>
     <t xml:space="preserve">1.48133945465088</t>
@@ -773,25 +776,25 @@
     <t xml:space="preserve">1.45390701293945</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39904248714447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36475241184235</t>
+    <t xml:space="preserve">1.39904260635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36475229263306</t>
   </si>
   <si>
     <t xml:space="preserve">1.37846839427948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3716105222702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35789430141449</t>
+    <t xml:space="preserve">1.37161028385162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35789442062378</t>
   </si>
   <si>
     <t xml:space="preserve">1.35446536540985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72137093544006</t>
+    <t xml:space="preserve">1.72137105464935</t>
   </si>
   <si>
     <t xml:space="preserve">1.7830935716629</t>
@@ -800,79 +803,79 @@
     <t xml:space="preserve">1.81738376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79680991172791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78995168209076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77623546123505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81052613258362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83109998703003</t>
+    <t xml:space="preserve">1.79680967330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78995132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77623534202576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81052589416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83110010623932</t>
   </si>
   <si>
     <t xml:space="preserve">1.83795809745789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80366790294647</t>
+    <t xml:space="preserve">1.80366814136505</t>
   </si>
   <si>
     <t xml:space="preserve">1.84481608867645</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87224817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89968085289001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91339683532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92711293697357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94082880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96140289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97511875629425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94768702983856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88596415519714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95454490184784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93397068977356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96826088428497</t>
+    <t xml:space="preserve">1.8722482919693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89968073368073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91339671611786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92711269855499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94082868099213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96140313148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97511887550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94768691062927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88596427440643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95454502105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93397080898285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96826100349426</t>
   </si>
   <si>
     <t xml:space="preserve">2.0162672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0505576133728</t>
+    <t xml:space="preserve">2.05055785179138</t>
   </si>
   <si>
     <t xml:space="preserve">2.04369950294495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06427383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03684139251709</t>
+    <t xml:space="preserve">2.06427407264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03684163093567</t>
   </si>
   <si>
     <t xml:space="preserve">2.02998352050781</t>
@@ -881,10 +884,10 @@
     <t xml:space="preserve">2.05741572380066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113194465637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07798957824707</t>
+    <t xml:space="preserve">2.07113170623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07798981666565</t>
   </si>
   <si>
     <t xml:space="preserve">2.08484792709351</t>
@@ -893,7 +896,7 @@
     <t xml:space="preserve">2.09903049468994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10612177848816</t>
+    <t xml:space="preserve">2.10612201690674</t>
   </si>
   <si>
     <t xml:space="preserve">2.13448715209961</t>
@@ -902,10 +905,10 @@
     <t xml:space="preserve">2.09193921089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14157867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11321306228638</t>
+    <t xml:space="preserve">2.14157843589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11321353912354</t>
   </si>
   <si>
     <t xml:space="preserve">2.12030434608459</t>
@@ -920,13 +923,13 @@
     <t xml:space="preserve">2.1770350933075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2266743183136</t>
+    <t xml:space="preserve">2.22667455673218</t>
   </si>
   <si>
     <t xml:space="preserve">2.20540022850037</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25503945350647</t>
+    <t xml:space="preserve">2.25503969192505</t>
   </si>
   <si>
     <t xml:space="preserve">2.26213097572327</t>
@@ -938,19 +941,19 @@
     <t xml:space="preserve">2.2195827960968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19830894470215</t>
+    <t xml:space="preserve">2.19830918312073</t>
   </si>
   <si>
     <t xml:space="preserve">2.2337658405304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24085688591003</t>
+    <t xml:space="preserve">2.24085664749146</t>
   </si>
   <si>
     <t xml:space="preserve">2.21249151229858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28340530395508</t>
+    <t xml:space="preserve">2.28340482711792</t>
   </si>
   <si>
     <t xml:space="preserve">2.26922225952148</t>
@@ -959,34 +962,34 @@
     <t xml:space="preserve">2.29049634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29758739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31177020072937</t>
+    <t xml:space="preserve">2.29758763313293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31176996231079</t>
   </si>
   <si>
     <t xml:space="preserve">2.31886124610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32595252990723</t>
+    <t xml:space="preserve">2.32595276832581</t>
   </si>
   <si>
     <t xml:space="preserve">2.33304405212402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30467867851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36850023269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38977456092834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37559175491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38268351554871</t>
+    <t xml:space="preserve">2.30467915534973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36850047111511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38977432250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37559199333191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38268327713013</t>
   </si>
   <si>
     <t xml:space="preserve">2.39686608314514</t>
@@ -998,19 +1001,19 @@
     <t xml:space="preserve">2.44650530815125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43232274055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49614429473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51032710075378</t>
+    <t xml:space="preserve">2.43232250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49614453315735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51032733917236</t>
   </si>
   <si>
     <t xml:space="preserve">2.58124017715454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55287528038025</t>
+    <t xml:space="preserve">2.55287480354309</t>
   </si>
   <si>
     <t xml:space="preserve">2.55996632575989</t>
@@ -1025,22 +1028,22 @@
     <t xml:space="preserve">2.60960555076599</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63797044754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58833122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59542274475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61669707298279</t>
+    <t xml:space="preserve">2.63797068595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58833146095276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59542298316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61669659614563</t>
   </si>
   <si>
     <t xml:space="preserve">2.65215349197388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65924477577209</t>
+    <t xml:space="preserve">2.65924453735352</t>
   </si>
   <si>
     <t xml:space="preserve">2.70179271697998</t>
@@ -1052,7 +1055,7 @@
     <t xml:space="preserve">2.72306656837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71597528457642</t>
+    <t xml:space="preserve">2.715975522995</t>
   </si>
   <si>
     <t xml:space="preserve">2.68760991096497</t>
@@ -1061,19 +1064,19 @@
     <t xml:space="preserve">2.7088840007782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68051862716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73092269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70907497406006</t>
+    <t xml:space="preserve">2.68051886558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73092246055603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70907521247864</t>
   </si>
   <si>
     <t xml:space="preserve">2.76733469963074</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81102967262268</t>
+    <t xml:space="preserve">2.8110294342041</t>
   </si>
   <si>
     <t xml:space="preserve">2.86200666427612</t>
@@ -1082,31 +1085,28 @@
     <t xml:space="preserve">2.84015965461731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81831192970276</t>
+    <t xml:space="preserve">2.81831216812134</t>
   </si>
   <si>
     <t xml:space="preserve">2.80374693870544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83287692070007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78189969062805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72363996505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70179295539856</t>
+    <t xml:space="preserve">2.83287739753723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78190016746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72364020347595</t>
   </si>
   <si>
     <t xml:space="preserve">2.752769947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6945104598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71635746955872</t>
+    <t xml:space="preserve">2.69451022148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71635770797729</t>
   </si>
   <si>
     <t xml:space="preserve">2.74548745155334</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">2.77461743354797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82559490203857</t>
+    <t xml:space="preserve">2.82559442520142</t>
   </si>
   <si>
     <t xml:space="preserve">2.78918218612671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79646444320679</t>
+    <t xml:space="preserve">2.79646468162537</t>
   </si>
   <si>
     <t xml:space="preserve">2.76005220413208</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">2.62896800041199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62168526649475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66538023948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86928939819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61440324783325</t>
+    <t xml:space="preserve">2.62168550491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66538071632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86928915977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61440348625183</t>
   </si>
   <si>
     <t xml:space="preserve">2.55614352226257</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">2.31582236289978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22843241691589</t>
+    <t xml:space="preserve">2.22843265533447</t>
   </si>
   <si>
     <t xml:space="preserve">2.27212738990784</t>
@@ -1172,64 +1172,64 @@
     <t xml:space="preserve">2.54886102676392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6580982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54157853126526</t>
+    <t xml:space="preserve">2.65809798240662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54157876968384</t>
   </si>
   <si>
     <t xml:space="preserve">2.67266297340393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88385438919067</t>
+    <t xml:space="preserve">2.88385391235352</t>
   </si>
   <si>
     <t xml:space="preserve">2.89841914176941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95667886734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94211363792419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97124361991882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94939637184143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91298413276672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85472464561462</t>
+    <t xml:space="preserve">2.95667862892151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94211387634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97124338150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94939684867859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91298389434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85472416877747</t>
   </si>
   <si>
     <t xml:space="preserve">2.97852635383606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96396136283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89113640785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90570139884949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92754912376404</t>
+    <t xml:space="preserve">2.96396160125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89113688468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90570163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92754888534546</t>
   </si>
   <si>
     <t xml:space="preserve">3.05783247947693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717757225037</t>
+    <t xml:space="preserve">3.02717733383179</t>
   </si>
   <si>
     <t xml:space="preserve">3.05016851425171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01951384544373</t>
+    <t xml:space="preserve">3.01951360702515</t>
   </si>
   <si>
     <t xml:space="preserve">2.98885893821716</t>
@@ -1241,16 +1241,16 @@
     <t xml:space="preserve">2.88923025131226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91222167015076</t>
+    <t xml:space="preserve">2.91222143173218</t>
   </si>
   <si>
     <t xml:space="preserve">2.77427411079407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6669819355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68230891227722</t>
+    <t xml:space="preserve">2.66698169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6823091506958</t>
   </si>
   <si>
     <t xml:space="preserve">2.67464566230774</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">2.68997287750244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.720627784729</t>
+    <t xml:space="preserve">2.72062754631042</t>
   </si>
   <si>
     <t xml:space="preserve">2.69763660430908</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">2.70530033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63632702827454</t>
+    <t xml:space="preserve">2.63632678985596</t>
   </si>
   <si>
     <t xml:space="preserve">2.65165424346924</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">2.6439905166626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6209990978241</t>
+    <t xml:space="preserve">2.62099933624268</t>
   </si>
   <si>
     <t xml:space="preserve">2.59034442901611</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">2.61333560943604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56735324859619</t>
+    <t xml:space="preserve">2.56735301017761</t>
   </si>
   <si>
     <t xml:space="preserve">2.53669810295105</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52137041091919</t>
+    <t xml:space="preserve">2.52137064933777</t>
   </si>
   <si>
     <t xml:space="preserve">2.55968928337097</t>
@@ -1307,16 +1307,16 @@
     <t xml:space="preserve">2.52903437614441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55202555656433</t>
+    <t xml:space="preserve">2.55202579498291</t>
   </si>
   <si>
     <t xml:space="preserve">2.54436182975769</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59800791740417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46772456169128</t>
+    <t xml:space="preserve">2.59800815582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46772432327271</t>
   </si>
   <si>
     <t xml:space="preserve">2.49837946891785</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">2.43706965446472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.452397108078</t>
+    <t xml:space="preserve">2.45239686965942</t>
   </si>
   <si>
     <t xml:space="preserve">2.49071574211121</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">2.4753885269165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46006083488464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48305177688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71296405792236</t>
+    <t xml:space="preserve">2.46006059646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48305201530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71296429634094</t>
   </si>
   <si>
     <t xml:space="preserve">2.78960156440735</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">2.82025647163391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82792043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81259298324585</t>
+    <t xml:space="preserve">2.82792019844055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81259274482727</t>
   </si>
   <si>
     <t xml:space="preserve">2.85091137886047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86623883247375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89019060134888</t>
+    <t xml:space="preserve">2.86623907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89019083976746</t>
   </si>
   <si>
     <t xml:space="preserve">2.89817476272583</t>
@@ -1379,19 +1379,19 @@
     <t xml:space="preserve">2.91414260864258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88220691680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95406246185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96204662322998</t>
+    <t xml:space="preserve">2.8822066783905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95406222343445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9620463848114</t>
   </si>
   <si>
     <t xml:space="preserve">2.97003030776978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94607877731323</t>
+    <t xml:space="preserve">2.94607853889465</t>
   </si>
   <si>
     <t xml:space="preserve">2.87422275543213</t>
@@ -1403,13 +1403,13 @@
     <t xml:space="preserve">2.93809461593628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93011045455933</t>
+    <t xml:space="preserve">2.93011069297791</t>
   </si>
   <si>
     <t xml:space="preserve">2.9939820766449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00196623802185</t>
+    <t xml:space="preserve">3.00196576118469</t>
   </si>
   <si>
     <t xml:space="preserve">2.97801423072815</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">3.08180546760559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01793384552002</t>
+    <t xml:space="preserve">3.0179340839386</t>
   </si>
   <si>
     <t xml:space="preserve">3.04986977577209</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">2.98599815368652</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02591776847839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03390169143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11374139785767</t>
+    <t xml:space="preserve">3.02591824531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03390216827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11374187469482</t>
   </si>
   <si>
     <t xml:space="preserve">3.0738217830658</t>
@@ -1448,52 +1448,52 @@
     <t xml:space="preserve">3.04188585281372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12172532081604</t>
+    <t xml:space="preserve">3.12172555923462</t>
   </si>
   <si>
     <t xml:space="preserve">3.12970948219299</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09777355194092</t>
+    <t xml:space="preserve">3.0977737903595</t>
   </si>
   <si>
     <t xml:space="preserve">3.15366125106812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10575771331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05785369873047</t>
+    <t xml:space="preserve">3.10575747489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05785393714905</t>
   </si>
   <si>
     <t xml:space="preserve">3.24148464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16962933540344</t>
+    <t xml:space="preserve">3.16962909698486</t>
   </si>
   <si>
     <t xml:space="preserve">3.16164517402649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14567708969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13769316673279</t>
+    <t xml:space="preserve">3.14567732810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13769364356995</t>
   </si>
   <si>
     <t xml:space="preserve">3.17761325836182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19442582130432</t>
+    <t xml:space="preserve">3.1944260597229</t>
   </si>
   <si>
     <t xml:space="preserve">3.21123862266541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18601942062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14398765563965</t>
+    <t xml:space="preserve">3.18601965904236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14398741722107</t>
   </si>
   <si>
     <t xml:space="preserve">3.15239381790161</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">3.11876845359802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11036205291748</t>
+    <t xml:space="preserve">3.1103618144989</t>
   </si>
   <si>
     <t xml:space="preserve">3.12717485427856</t>
@@ -1514,22 +1514,22 @@
     <t xml:space="preserve">3.13558101654053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09354901313782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10195589065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08514308929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16080069541931</t>
+    <t xml:space="preserve">3.0935492515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10195565223694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08514285087585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16079998016357</t>
   </si>
   <si>
     <t xml:space="preserve">3.07673645019531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06833028793335</t>
+    <t xml:space="preserve">3.06833004951477</t>
   </si>
   <si>
     <t xml:space="preserve">3.05151724815369</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">3.0347044467926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05992364883423</t>
+    <t xml:space="preserve">3.05992388725281</t>
   </si>
   <si>
     <t xml:space="preserve">3.02629804611206</t>
@@ -1550,13 +1550,13 @@
     <t xml:space="preserve">3.00948548316956</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97585964202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00107908248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01789164543152</t>
+    <t xml:space="preserve">2.97585988044739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00107884407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0178918838501</t>
   </si>
   <si>
     <t xml:space="preserve">2.95064067840576</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">2.88338971138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90860891342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86657691001892</t>
+    <t xml:space="preserve">2.90860915184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8665771484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.85817074775696</t>
@@ -1580,19 +1580,19 @@
     <t xml:space="preserve">2.87498331069946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83295106887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91701507568359</t>
+    <t xml:space="preserve">2.83295130729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91701531410217</t>
   </si>
   <si>
     <t xml:space="preserve">2.93382787704468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89179611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98426628112793</t>
+    <t xml:space="preserve">2.89179587364197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98426604270935</t>
   </si>
   <si>
     <t xml:space="preserve">2.92542171478271</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">2.96745347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99267268180847</t>
+    <t xml:space="preserve">2.99267244338989</t>
   </si>
   <si>
     <t xml:space="preserve">3.08550214767456</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">3.11179900169373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12933039665222</t>
+    <t xml:space="preserve">3.12933015823364</t>
   </si>
   <si>
     <t xml:space="preserve">3.13809585571289</t>
@@ -1628,22 +1628,22 @@
     <t xml:space="preserve">3.15562701225281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19945526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2082211971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22575211524963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24328351020813</t>
+    <t xml:space="preserve">3.19945549964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20822095870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22575235366821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24328327178955</t>
   </si>
   <si>
     <t xml:space="preserve">3.23451805114746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25204944610596</t>
+    <t xml:space="preserve">3.25204920768738</t>
   </si>
   <si>
     <t xml:space="preserve">3.1906898021698</t>
@@ -1664,37 +1664,37 @@
     <t xml:space="preserve">3.26958036422729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27834606170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29587745666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32217407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31340861320496</t>
+    <t xml:space="preserve">3.27834582328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29587721824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3221743106842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31340837478638</t>
   </si>
   <si>
     <t xml:space="preserve">3.33970546722412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43612766265869</t>
+    <t xml:space="preserve">3.43612742424011</t>
   </si>
   <si>
     <t xml:space="preserve">3.39229917526245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44489288330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45365881919861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4185962677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48872113227844</t>
+    <t xml:space="preserve">3.44489312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45365858078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41859602928162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48872089385986</t>
   </si>
   <si>
     <t xml:space="preserve">3.51501822471619</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">3.4010648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37476801872253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3835334777832</t>
+    <t xml:space="preserve">3.37476778030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38353323936462</t>
   </si>
   <si>
     <t xml:space="preserve">3.47118973731995</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">3.40983057022095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46242427825928</t>
+    <t xml:space="preserve">3.46242451667786</t>
   </si>
   <si>
     <t xml:space="preserve">3.50625228881836</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">3.52378368377686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49748706817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54131507873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5325493812561</t>
+    <t xml:space="preserve">3.49748682975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54131484031677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53254961967468</t>
   </si>
   <si>
     <t xml:space="preserve">3.55884623527527</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">3.66403365135193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6114399433136</t>
+    <t xml:space="preserve">3.61143970489502</t>
   </si>
   <si>
     <t xml:space="preserve">3.60267448425293</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">3.58559513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60402989387512</t>
+    <t xml:space="preserve">3.6040301322937</t>
   </si>
   <si>
     <t xml:space="preserve">3.57637763023376</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">3.52107262611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55794262886047</t>
+    <t xml:space="preserve">3.55794239044189</t>
   </si>
   <si>
     <t xml:space="preserve">3.56716012954712</t>
@@ -1790,13 +1790,13 @@
     <t xml:space="preserve">3.42889809608459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51185536384583</t>
+    <t xml:space="preserve">3.51185512542725</t>
   </si>
   <si>
     <t xml:space="preserve">3.47498536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53029012680054</t>
+    <t xml:space="preserve">3.53029036521912</t>
   </si>
   <si>
     <t xml:space="preserve">3.49342036247253</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">3.54872512817383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65011715888977</t>
+    <t xml:space="preserve">3.65011739730835</t>
   </si>
   <si>
     <t xml:space="preserve">3.6408998966217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63168263435364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44733309745789</t>
+    <t xml:space="preserve">3.63168239593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44733285903931</t>
   </si>
   <si>
     <t xml:space="preserve">3.50263786315918</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">3.67776989936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463966369629</t>
+    <t xml:space="preserve">3.71463990211487</t>
   </si>
   <si>
     <t xml:space="preserve">3.78837943077087</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">3.75150966644287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.659334897995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77916169166565</t>
+    <t xml:space="preserve">3.65933465957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77916193008423</t>
   </si>
   <si>
     <t xml:space="preserve">3.80681443214417</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">3.84368419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76994466781616</t>
+    <t xml:space="preserve">3.76994442939758</t>
   </si>
   <si>
     <t xml:space="preserve">3.81603169441223</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">3.91742372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90820622444153</t>
+    <t xml:space="preserve">3.90820646286011</t>
   </si>
   <si>
     <t xml:space="preserve">3.89898896217346</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">3.88055419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93585896492004</t>
+    <t xml:space="preserve">3.93585848808289</t>
   </si>
   <si>
     <t xml:space="preserve">3.94507646560669</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">3.86211895942688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83446645736694</t>
+    <t xml:space="preserve">3.83446669578552</t>
   </si>
   <si>
     <t xml:space="preserve">3.83412289619446</t>
@@ -6441,7 +6441,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G147" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6493,7 +6493,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G149" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6649,7 +6649,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G155" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6675,7 +6675,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G156" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6727,7 +6727,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G158" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6753,7 +6753,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G159" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -6935,7 +6935,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G166" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -6987,7 +6987,7 @@
         <v>3.25</v>
       </c>
       <c r="G168" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7013,7 +7013,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G169" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7169,7 +7169,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G175" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7195,7 +7195,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G176" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7247,7 +7247,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G178" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7273,7 +7273,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G179" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7299,7 +7299,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G180" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7325,7 +7325,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G181" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7351,7 +7351,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G182" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7377,7 +7377,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G183" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7403,7 +7403,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G184" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7455,7 +7455,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G186" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7481,7 +7481,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G187" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7507,7 +7507,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G188" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7533,7 +7533,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G189" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7559,7 +7559,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G190" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7611,7 +7611,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G192" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7767,7 +7767,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G198" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7871,7 +7871,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G202" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7897,7 +7897,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G203" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -7949,7 +7949,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G205" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8001,7 +8001,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G207" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8027,7 +8027,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G208" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8053,7 +8053,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G209" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8079,7 +8079,7 @@
         <v>3.25</v>
       </c>
       <c r="G210" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8131,7 +8131,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G212" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8157,7 +8157,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G213" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8183,7 +8183,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G214" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8209,7 +8209,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G215" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8235,7 +8235,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G216" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8261,7 +8261,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G217" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8287,7 +8287,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G218" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8313,7 +8313,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G219" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8339,7 +8339,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G220" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8365,7 +8365,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G221" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8391,7 +8391,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8417,7 +8417,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G223" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8443,7 +8443,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8469,7 +8469,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G225" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8495,7 +8495,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G226" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8521,7 +8521,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G227" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8547,7 +8547,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G228" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8573,7 +8573,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G229" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8599,7 +8599,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G230" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8625,7 +8625,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G231" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8651,7 +8651,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8677,7 +8677,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G233" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8703,7 +8703,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G234" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8729,7 +8729,7 @@
         <v>3.25</v>
       </c>
       <c r="G235" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8755,7 +8755,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8781,7 +8781,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G237" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8807,7 +8807,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G238" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8833,7 +8833,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G239" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8859,7 +8859,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G240" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8885,7 +8885,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G241" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -8911,7 +8911,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G242" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -8937,7 +8937,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G243" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -8963,7 +8963,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G244" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -8989,7 +8989,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G245" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9015,7 +9015,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G246" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9041,7 +9041,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G247" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9067,7 +9067,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G248" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9093,7 +9093,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G249" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9119,7 +9119,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G250" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9145,7 +9145,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G251" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9171,7 +9171,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G252" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9197,7 +9197,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G253" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9223,7 +9223,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G254" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9249,7 +9249,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9275,7 +9275,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G256" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9301,7 +9301,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G257" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9327,7 +9327,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G258" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9353,7 +9353,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G259" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9379,7 +9379,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G260" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9405,7 +9405,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G261" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9431,7 +9431,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G262" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9457,7 +9457,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9483,7 +9483,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9509,7 +9509,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G265" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9535,7 +9535,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G266" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9561,7 +9561,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9587,7 +9587,7 @@
         <v>3.25</v>
       </c>
       <c r="G268" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9613,7 +9613,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G269" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9639,7 +9639,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G270" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9665,7 +9665,7 @@
         <v>3.25</v>
       </c>
       <c r="G271" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9691,7 +9691,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9717,7 +9717,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9795,7 +9795,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G276" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9821,7 +9821,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G277" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -9977,7 +9977,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G283" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10315,7 +10315,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G296" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10341,7 +10341,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G297" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10367,7 +10367,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G298" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10497,7 +10497,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G303" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10549,7 +10549,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G305" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10627,7 +10627,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G308" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10679,7 +10679,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G310" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10705,7 +10705,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10757,7 +10757,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G313" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10809,7 +10809,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G315" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10835,7 +10835,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G316" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10861,7 +10861,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G317" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10887,7 +10887,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G318" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11017,7 +11017,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G323" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11043,7 +11043,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G324" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11069,7 +11069,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G325" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11095,7 +11095,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G326" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11147,7 +11147,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G328" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11199,7 +11199,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G330" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11225,7 +11225,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11277,7 +11277,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11303,7 +11303,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11329,7 +11329,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G335" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11355,7 +11355,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G336" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11407,7 +11407,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G338" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11433,7 +11433,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G339" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11485,7 +11485,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G341" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11537,7 +11537,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G343" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11641,7 +11641,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G347" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11693,7 +11693,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G349" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11745,7 +11745,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G351" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -11771,7 +11771,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G352" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11797,7 +11797,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G353" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11823,7 +11823,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G354" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -11849,7 +11849,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G355" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11901,7 +11901,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G357" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -11927,7 +11927,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G358" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -11979,7 +11979,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G360" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12005,7 +12005,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G361" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12057,7 +12057,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G363" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12083,7 +12083,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G364" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12109,7 +12109,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G365" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12135,7 +12135,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12161,7 +12161,7 @@
         <v>3</v>
       </c>
       <c r="G367" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12187,7 +12187,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G368" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12213,7 +12213,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G369" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12239,7 +12239,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G370" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12265,7 +12265,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G371" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12291,7 +12291,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G372" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12317,7 +12317,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G373" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12343,7 +12343,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G374" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12369,7 +12369,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G375" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12395,7 +12395,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12421,7 +12421,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G377" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12447,7 +12447,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G378" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12473,7 +12473,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G379" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12499,7 +12499,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G380" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12525,7 +12525,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G381" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12551,7 +12551,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G382" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12577,7 +12577,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G383" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12603,7 +12603,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G384" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12629,7 +12629,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G385" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12655,7 +12655,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G386" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12681,7 +12681,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G387" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12707,7 +12707,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G388" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12733,7 +12733,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G389" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12759,7 +12759,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G390" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12785,7 +12785,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G391" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12811,7 +12811,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12837,7 +12837,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G393" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12863,7 +12863,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G394" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12889,7 +12889,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G395" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -12915,7 +12915,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G396" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -12941,7 +12941,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G397" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -12967,7 +12967,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G398" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -12993,7 +12993,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G399" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13019,7 +13019,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G400" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13045,7 +13045,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G401" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13071,7 +13071,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G402" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13097,7 +13097,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G403" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13123,7 +13123,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G404" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13149,7 +13149,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G405" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13175,7 +13175,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G406" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13201,7 +13201,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G407" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13227,7 +13227,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G408" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13253,7 +13253,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13279,7 +13279,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G410" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13305,7 +13305,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G411" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13331,7 +13331,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G412" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13357,7 +13357,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G413" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13383,7 +13383,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G414" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13409,7 +13409,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G415" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13435,7 +13435,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G416" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13461,7 +13461,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G417" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13487,7 +13487,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G418" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13513,7 +13513,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G419" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13539,7 +13539,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G420" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13565,7 +13565,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G421" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13591,7 +13591,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G422" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13617,7 +13617,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G423" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13643,7 +13643,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G424" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13669,7 +13669,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13695,7 +13695,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G426" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13721,7 +13721,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G427" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13747,7 +13747,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G428" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13773,7 +13773,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G429" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13799,7 +13799,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G430" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13825,7 +13825,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G431" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13851,7 +13851,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G432" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13877,7 +13877,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G433" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -13903,7 +13903,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G434" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -13929,7 +13929,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G435" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -13955,7 +13955,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G436" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -13981,7 +13981,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G437" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14007,7 +14007,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G438" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14033,7 +14033,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G439" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14059,7 +14059,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G440" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14085,7 +14085,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G441" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14111,7 +14111,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G442" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14137,7 +14137,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G443" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14163,7 +14163,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G444" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14189,7 +14189,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G445" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14215,7 +14215,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G446" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14241,7 +14241,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G447" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14267,7 +14267,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G448" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14293,7 +14293,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G449" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14319,7 +14319,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G450" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14345,7 +14345,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G451" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14371,7 +14371,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G452" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14397,7 +14397,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G453" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14423,7 +14423,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G454" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14449,7 +14449,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G455" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14475,7 +14475,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G456" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14501,7 +14501,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14527,7 +14527,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G458" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14553,7 +14553,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G459" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14579,7 +14579,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G460" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14605,7 +14605,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G461" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14631,7 +14631,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G462" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14657,7 +14657,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G463" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14683,7 +14683,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G464" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14709,7 +14709,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G465" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14735,7 +14735,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G466" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14761,7 +14761,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G467" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14787,7 +14787,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G468" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14813,7 +14813,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G469" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14839,7 +14839,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G470" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14865,7 +14865,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G471" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14891,7 +14891,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G472" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -14917,7 +14917,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G473" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -14943,7 +14943,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -14969,7 +14969,7 @@
         <v>2.5</v>
       </c>
       <c r="G475" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -14995,7 +14995,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G476" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15021,7 +15021,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G477" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15047,7 +15047,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G478" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15073,7 +15073,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G479" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15099,7 +15099,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G480" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15125,7 +15125,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G481" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15151,7 +15151,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G482" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15177,7 +15177,7 @@
         <v>2.5</v>
       </c>
       <c r="G483" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15203,7 +15203,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G484" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15229,7 +15229,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15255,7 +15255,7 @@
         <v>2.5</v>
       </c>
       <c r="G486" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15281,7 +15281,7 @@
         <v>2.5</v>
       </c>
       <c r="G487" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15307,7 +15307,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G488" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15333,7 +15333,7 @@
         <v>2.5</v>
       </c>
       <c r="G489" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15359,7 +15359,7 @@
         <v>2.5</v>
       </c>
       <c r="G490" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15385,7 +15385,7 @@
         <v>2.5</v>
       </c>
       <c r="G491" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15411,7 +15411,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G492" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15437,7 +15437,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G493" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15463,7 +15463,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G494" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15489,7 +15489,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G495" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15515,7 +15515,7 @@
         <v>2.5</v>
       </c>
       <c r="G496" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15541,7 +15541,7 @@
         <v>2.5</v>
       </c>
       <c r="G497" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15567,7 +15567,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G498" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15593,7 +15593,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G499" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15619,7 +15619,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G500" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15645,7 +15645,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G501" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15671,7 +15671,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G502" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15697,7 +15697,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G503" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15723,7 +15723,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G504" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15749,7 +15749,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G505" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15775,7 +15775,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G506" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15801,7 +15801,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G507" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15827,7 +15827,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G508" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15853,7 +15853,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G509" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15879,7 +15879,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G510" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -15905,7 +15905,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G511" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -15931,7 +15931,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -15957,7 +15957,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G513" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -15983,7 +15983,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G514" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16009,7 +16009,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16035,7 +16035,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G516" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16061,7 +16061,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G517" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16087,7 +16087,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G518" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16113,7 +16113,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16139,7 +16139,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G520" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16165,7 +16165,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G521" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16191,7 +16191,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G522" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16217,7 +16217,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G523" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16243,7 +16243,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G524" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16269,7 +16269,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G525" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16295,7 +16295,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G526" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16321,7 +16321,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G527" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16347,7 +16347,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16373,7 +16373,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G529" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16399,7 +16399,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G530" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16425,7 +16425,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G531" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16451,7 +16451,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G532" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16477,7 +16477,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G533" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16503,7 +16503,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G534" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16529,7 +16529,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G535" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16555,7 +16555,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G536" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16581,7 +16581,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G537" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16607,7 +16607,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16633,7 +16633,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16659,7 +16659,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G540" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16685,7 +16685,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G541" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16711,7 +16711,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G542" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16737,7 +16737,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G543" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16763,7 +16763,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G544" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16789,7 +16789,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G545" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16815,7 +16815,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G546" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16841,7 +16841,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G547" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16867,7 +16867,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G548" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16893,7 +16893,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G549" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -16919,7 +16919,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G550" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -16945,7 +16945,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G551" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -16971,7 +16971,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G552" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -16997,7 +16997,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G553" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17023,7 +17023,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G554" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17049,7 +17049,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G555" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17075,7 +17075,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G556" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17101,7 +17101,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G557" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17127,7 +17127,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G558" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17153,7 +17153,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G559" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17179,7 +17179,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G560" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17205,7 +17205,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G561" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17231,7 +17231,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G562" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17257,7 +17257,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G563" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17283,7 +17283,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G564" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17309,7 +17309,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G565" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17335,7 +17335,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G566" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17361,7 +17361,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G567" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17387,7 +17387,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G568" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17413,7 +17413,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G569" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17439,7 +17439,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G570" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17465,7 +17465,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G571" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17491,7 +17491,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G572" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17517,7 +17517,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G573" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17543,7 +17543,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G574" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17569,7 +17569,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G575" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17595,7 +17595,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G576" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17621,7 +17621,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G577" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17647,7 +17647,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G578" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17673,7 +17673,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G579" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17699,7 +17699,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G580" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17725,7 +17725,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17751,7 +17751,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G582" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17777,7 +17777,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G583" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17803,7 +17803,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G584" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17829,7 +17829,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G585" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17855,7 +17855,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G586" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17881,7 +17881,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G587" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -17907,7 +17907,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G588" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -17933,7 +17933,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G589" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -17959,7 +17959,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G590" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -17985,7 +17985,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G591" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18011,7 +18011,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G592" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18037,7 +18037,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G593" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18063,7 +18063,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G594" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18089,7 +18089,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G595" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18115,7 +18115,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G596" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18141,7 +18141,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G597" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18167,7 +18167,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G598" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18193,7 +18193,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G599" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18219,7 +18219,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G600" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18245,7 +18245,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G601" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18271,7 +18271,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G602" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18297,7 +18297,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18323,7 +18323,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G604" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18349,7 +18349,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G605" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18375,7 +18375,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G606" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18401,7 +18401,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18427,7 +18427,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G608" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18453,7 +18453,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G609" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18479,7 +18479,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G610" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18505,7 +18505,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G611" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18531,7 +18531,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G612" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18557,7 +18557,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18583,7 +18583,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G614" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18609,7 +18609,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G615" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18635,7 +18635,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G616" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18661,7 +18661,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G617" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18687,7 +18687,7 @@
         <v>2.25</v>
       </c>
       <c r="G618" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18713,7 +18713,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G619" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18739,7 +18739,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G620" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18765,7 +18765,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G621" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18791,7 +18791,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G622" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18817,7 +18817,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18843,7 +18843,7 @@
         <v>2.25</v>
       </c>
       <c r="G624" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18869,7 +18869,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18895,7 +18895,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -18921,7 +18921,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G627" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -18947,7 +18947,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G628" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -18973,7 +18973,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G629" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -18999,7 +18999,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G630" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19025,7 +19025,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G631" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19051,7 +19051,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19077,7 +19077,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G633" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19103,7 +19103,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G634" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19129,7 +19129,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G635" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19155,7 +19155,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19181,7 +19181,7 @@
         <v>2.75</v>
       </c>
       <c r="G637" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19207,7 +19207,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G638" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19259,7 +19259,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G640" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19285,7 +19285,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G641" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19311,7 +19311,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G642" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19337,7 +19337,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G643" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -19363,7 +19363,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G644" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -19389,7 +19389,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G645" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -19415,7 +19415,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G646" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -19441,7 +19441,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G647" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -19467,7 +19467,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G648" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -19493,7 +19493,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G649" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -19519,7 +19519,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G650" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -19545,7 +19545,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G651" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -19571,7 +19571,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G652" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -19597,7 +19597,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G653" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -19623,7 +19623,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G654" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -19649,7 +19649,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G655" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -19675,7 +19675,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G656" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -19701,7 +19701,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G657" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -19727,7 +19727,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G658" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -19753,7 +19753,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G659" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19779,7 +19779,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G660" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19805,7 +19805,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G661" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -19831,7 +19831,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G662" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -19857,7 +19857,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G663" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -19883,7 +19883,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G664" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19909,7 +19909,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G665" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -19935,7 +19935,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G666" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -19961,7 +19961,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G667" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -19987,7 +19987,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G668" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20013,7 +20013,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G669" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20039,7 +20039,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G670" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20065,7 +20065,7 @@
         <v>2.5</v>
       </c>
       <c r="G671" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20091,7 +20091,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G672" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20117,7 +20117,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G673" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20143,7 +20143,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G674" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20169,7 +20169,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G675" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20195,7 +20195,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G676" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20221,7 +20221,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G677" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20247,7 +20247,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G678" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20273,7 +20273,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G679" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20299,7 +20299,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G680" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20325,7 +20325,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G681" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -20351,7 +20351,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G682" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -20377,7 +20377,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G683" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -20403,7 +20403,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G684" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -20429,7 +20429,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -20455,7 +20455,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G686" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -20481,7 +20481,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G687" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -20507,7 +20507,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G688" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -20533,7 +20533,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G689" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -20559,7 +20559,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G690" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -20585,7 +20585,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G691" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -20611,7 +20611,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G692" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20637,7 +20637,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G693" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20663,7 +20663,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G694" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -20689,7 +20689,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G695" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -20715,7 +20715,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G696" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20741,7 +20741,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G697" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20767,7 +20767,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G698" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -20793,7 +20793,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G699" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -20819,7 +20819,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G700" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -20845,7 +20845,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G701" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -20871,7 +20871,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G702" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20897,7 +20897,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G703" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20923,7 +20923,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G704" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20949,7 +20949,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G705" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -20975,7 +20975,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G706" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21001,7 +21001,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G707" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21027,7 +21027,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G708" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21053,7 +21053,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G709" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21079,7 +21079,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G710" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21105,7 +21105,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G711" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21131,7 +21131,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G712" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21157,7 +21157,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G713" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21183,7 +21183,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G714" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21209,7 +21209,7 @@
         <v>2.25</v>
       </c>
       <c r="G715" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21235,7 +21235,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G716" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21261,7 +21261,7 @@
         <v>2.25</v>
       </c>
       <c r="G717" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21287,7 +21287,7 @@
         <v>2.25</v>
       </c>
       <c r="G718" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21313,7 +21313,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G719" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21339,7 +21339,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G720" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21365,7 +21365,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G721" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -21391,7 +21391,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G722" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -21417,7 +21417,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G723" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -21443,7 +21443,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G724" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -21469,7 +21469,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G725" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -21495,7 +21495,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G726" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -21521,7 +21521,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G727" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -21547,7 +21547,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G728" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -21573,7 +21573,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G729" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -21599,7 +21599,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G730" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21625,7 +21625,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G731" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21651,7 +21651,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G732" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21677,7 +21677,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G733" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21703,7 +21703,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G734" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -21729,7 +21729,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G735" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -21755,7 +21755,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G736" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -21781,7 +21781,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G737" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -21807,7 +21807,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G738" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -21833,7 +21833,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G739" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -21859,7 +21859,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G740" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -21885,7 +21885,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G741" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -21911,7 +21911,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G742" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -21937,7 +21937,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G743" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21963,7 +21963,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G744" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21989,7 +21989,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G745" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22015,7 +22015,7 @@
         <v>2</v>
       </c>
       <c r="G746" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22041,7 +22041,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G747" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22067,7 +22067,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G748" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22093,7 +22093,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G749" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22119,7 +22119,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G750" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22145,7 +22145,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G751" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22171,7 +22171,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G752" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22197,7 +22197,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G753" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22223,7 +22223,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G754" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22249,7 +22249,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G755" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22275,7 +22275,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G756" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22301,7 +22301,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G757" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22327,7 +22327,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G758" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -22353,7 +22353,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G759" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -22379,7 +22379,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G760" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -22405,7 +22405,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G761" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -22431,7 +22431,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G762" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -22457,7 +22457,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G763" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -22483,7 +22483,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G764" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -22509,7 +22509,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G765" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -22535,7 +22535,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G766" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -22561,7 +22561,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G767" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -22587,7 +22587,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G768" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22613,7 +22613,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G769" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22639,7 +22639,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G770" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22665,7 +22665,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G771" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22691,7 +22691,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G772" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22717,7 +22717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G773" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22743,7 +22743,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G774" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22769,7 +22769,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G775" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22795,7 +22795,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G776" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22821,7 +22821,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G777" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22847,7 +22847,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G778" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22873,7 +22873,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G779" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22899,7 +22899,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G780" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22925,7 +22925,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G781" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22951,7 +22951,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G782" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22977,7 +22977,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G783" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23003,7 +23003,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G784" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23029,7 +23029,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G785" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23055,7 +23055,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G786" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23081,7 +23081,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G787" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23107,7 +23107,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G788" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23133,7 +23133,7 @@
         <v>2.5</v>
       </c>
       <c r="G789" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23159,7 +23159,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G790" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23185,7 +23185,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G791" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23211,7 +23211,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G792" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23237,7 +23237,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G793" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23263,7 +23263,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G794" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23289,7 +23289,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G795" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23315,7 +23315,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G796" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -23341,7 +23341,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G797" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -23367,7 +23367,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G798" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -23393,7 +23393,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G799" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -23419,7 +23419,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G800" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -23445,7 +23445,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G801" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -23471,7 +23471,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G802" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -23497,7 +23497,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G803" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -23523,7 +23523,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G804" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -23549,7 +23549,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G805" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -23575,7 +23575,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G806" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23601,7 +23601,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G807" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23627,7 +23627,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G808" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23653,7 +23653,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G809" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23679,7 +23679,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G810" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23705,7 +23705,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G811" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23731,7 +23731,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G812" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23757,7 +23757,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G813" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23783,7 +23783,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G814" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23809,7 +23809,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G815" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23835,7 +23835,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G816" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23861,7 +23861,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G817" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23887,7 +23887,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G818" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23913,7 +23913,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G819" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23939,7 +23939,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G820" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23991,7 +23991,7 @@
         <v>2.75</v>
       </c>
       <c r="G822" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24069,7 +24069,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G825" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24095,7 +24095,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G826" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24121,7 +24121,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G827" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24147,7 +24147,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G828" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24173,7 +24173,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G829" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24199,7 +24199,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G830" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24225,7 +24225,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G831" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24251,7 +24251,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G832" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24277,7 +24277,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G833" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24303,7 +24303,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G834" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24329,7 +24329,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G835" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -24355,7 +24355,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G836" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24381,7 +24381,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G837" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24407,7 +24407,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G838" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24433,7 +24433,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G839" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24459,7 +24459,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G840" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24485,7 +24485,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G841" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24511,7 +24511,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G842" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24537,7 +24537,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G843" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24563,7 +24563,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G844" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24589,7 +24589,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G845" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24615,7 +24615,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G846" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24641,7 +24641,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G847" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24667,7 +24667,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G848" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24693,7 +24693,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G849" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24719,7 +24719,7 @@
         <v>3</v>
       </c>
       <c r="G850" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24745,7 +24745,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G851" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24771,7 +24771,7 @@
         <v>3</v>
       </c>
       <c r="G852" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24797,7 +24797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G853" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24823,7 +24823,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G854" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24849,7 +24849,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G855" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24875,7 +24875,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G856" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24901,7 +24901,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G857" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24927,7 +24927,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G858" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24953,7 +24953,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G859" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -24979,7 +24979,7 @@
         <v>3</v>
       </c>
       <c r="G860" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25005,7 +25005,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G861" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25031,7 +25031,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25057,7 +25057,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G863" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25083,7 +25083,7 @@
         <v>3</v>
       </c>
       <c r="G864" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25109,7 +25109,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G865" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25135,7 +25135,7 @@
         <v>3</v>
       </c>
       <c r="G866" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25161,7 +25161,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G867" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25187,7 +25187,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G868" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25213,7 +25213,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G869" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25239,7 +25239,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G870" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25265,7 +25265,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G871" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25291,7 +25291,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G872" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25317,7 +25317,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G873" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25343,7 +25343,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G874" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25369,7 +25369,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G875" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25395,7 +25395,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G876" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25421,7 +25421,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G877" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25447,7 +25447,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G878" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25473,7 +25473,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G879" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25499,7 +25499,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G880" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25525,7 +25525,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G881" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25551,7 +25551,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G882" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25577,7 +25577,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G883" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25603,7 +25603,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G884" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25629,7 +25629,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G885" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25655,7 +25655,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G886" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25681,7 +25681,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G887" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25707,7 +25707,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G888" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25733,7 +25733,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G889" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25759,7 +25759,7 @@
         <v>3</v>
       </c>
       <c r="G890" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25785,7 +25785,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G891" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25811,7 +25811,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G892" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25837,7 +25837,7 @@
         <v>3</v>
       </c>
       <c r="G893" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25863,7 +25863,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G894" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25889,7 +25889,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G895" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25915,7 +25915,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G896" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -25941,7 +25941,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G897" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -25967,7 +25967,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G898" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -25993,7 +25993,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G899" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26019,7 +26019,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G900" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26045,7 +26045,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G901" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26071,7 +26071,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G902" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26097,7 +26097,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G903" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26123,7 +26123,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26149,7 +26149,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G905" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26175,7 +26175,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G906" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26201,7 +26201,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G907" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26227,7 +26227,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G908" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26253,7 +26253,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G909" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26279,7 +26279,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G910" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26305,7 +26305,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G911" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26331,7 +26331,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G912" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26357,7 +26357,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G913" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26383,7 +26383,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G914" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26409,7 +26409,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G915" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26435,7 +26435,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G916" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26461,7 +26461,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G917" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26487,7 +26487,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G918" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26513,7 +26513,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G919" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26539,7 +26539,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G920" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26565,7 +26565,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G921" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26591,7 +26591,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G922" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26617,7 +26617,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G923" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26643,7 +26643,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G924" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26669,7 +26669,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G925" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26695,7 +26695,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G926" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26721,7 +26721,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G927" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26747,7 +26747,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G928" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26773,7 +26773,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G929" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26799,7 +26799,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26825,7 +26825,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G931" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26851,7 +26851,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G932" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26877,7 +26877,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G933" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26903,7 +26903,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G934" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26929,7 +26929,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G935" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26955,7 +26955,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G936" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -26981,7 +26981,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G937" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27007,7 +27007,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G938" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27033,7 +27033,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G939" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27059,7 +27059,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G940" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27085,7 +27085,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G941" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27111,7 +27111,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G942" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27137,7 +27137,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27163,7 +27163,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G944" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27189,7 +27189,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G945" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27215,7 +27215,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G946" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27241,7 +27241,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G947" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27267,7 +27267,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G948" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27293,7 +27293,7 @@
         <v>3.25</v>
       </c>
       <c r="G949" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27319,7 +27319,7 @@
         <v>3.25</v>
       </c>
       <c r="G950" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27345,7 +27345,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G951" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27371,7 +27371,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G952" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27397,7 +27397,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G953" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27423,7 +27423,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G954" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27449,7 +27449,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G955" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27475,7 +27475,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G956" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27501,7 +27501,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G957" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27527,7 +27527,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G958" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27553,7 +27553,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G959" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27579,7 +27579,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G960" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27605,7 +27605,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G961" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27631,7 +27631,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G962" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G964" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27709,7 +27709,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G965" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27735,7 +27735,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G966" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27761,7 +27761,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G967" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27787,7 +27787,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G968" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27813,7 +27813,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G969" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27839,7 +27839,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G970" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27865,7 +27865,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G971" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27891,7 +27891,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G972" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G973" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27943,7 +27943,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G974" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G975" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27995,7 +27995,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G976" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28021,7 +28021,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G977" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28047,7 +28047,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G978" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G979" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28099,7 +28099,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G980" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28125,7 +28125,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G981" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28151,7 +28151,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G982" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28177,7 +28177,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G983" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28203,7 +28203,7 @@
         <v>3.75</v>
       </c>
       <c r="G984" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28229,7 +28229,7 @@
         <v>3.75</v>
       </c>
       <c r="G985" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28255,7 +28255,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G986" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28281,7 +28281,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G987" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28307,7 +28307,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G988" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28333,7 +28333,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G989" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28359,7 +28359,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G990" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28385,7 +28385,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G991" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28411,7 +28411,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28437,7 +28437,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G993" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28463,7 +28463,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G994" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28489,7 +28489,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28515,7 +28515,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G996" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28541,7 +28541,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28567,7 +28567,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G998" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28593,7 +28593,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28619,7 +28619,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1000" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28645,7 +28645,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1001" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28671,7 +28671,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1002" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28697,7 +28697,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1003" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28723,7 +28723,7 @@
         <v>3.75</v>
       </c>
       <c r="G1004" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28749,7 +28749,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1005" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28775,7 +28775,7 @@
         <v>3.75</v>
       </c>
       <c r="G1006" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28801,7 +28801,7 @@
         <v>3.75</v>
       </c>
       <c r="G1007" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28827,7 +28827,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1008" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28853,7 +28853,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1009" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28879,7 +28879,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1010" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28905,7 +28905,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1011" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -28931,7 +28931,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1012" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28957,7 +28957,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1013" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28983,7 +28983,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1014" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29009,7 +29009,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1015" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29035,7 +29035,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1016" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29061,7 +29061,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1017" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29087,7 +29087,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1018" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29113,7 +29113,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1019" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29139,7 +29139,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1020" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29191,7 +29191,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1022" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29243,7 +29243,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1024" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29269,7 +29269,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1025" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29295,7 +29295,7 @@
         <v>3.75</v>
       </c>
       <c r="G1026" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29321,7 +29321,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1027" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29347,7 +29347,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1028" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29373,7 +29373,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1029" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1030" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1035" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1036" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29581,7 +29581,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1037" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29685,7 +29685,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1041" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1043" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1045" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1052" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1056" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30153,7 +30153,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1059" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30179,7 +30179,7 @@
         <v>3.75</v>
       </c>
       <c r="G1060" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30231,7 +30231,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1062" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1063" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1065" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30413,7 +30413,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1069" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1070" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30465,7 +30465,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1071" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1076" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30621,7 +30621,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1077" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1079" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31115,7 +31115,7 @@
         <v>3.75</v>
       </c>
       <c r="G1096" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31167,7 +31167,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1098" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31193,7 +31193,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1099" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31219,7 +31219,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1100" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31271,7 +31271,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1102" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31297,7 +31297,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1103" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31323,7 +31323,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1104" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31531,7 +31531,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1112" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31999,7 +31999,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32025,7 +32025,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1131" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -55095,13 +55095,13 @@
     </row>
     <row r="2019">
       <c r="A2019" s="1" t="n">
-        <v>45965.6912615741</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2019" t="n">
         <v>126238</v>
       </c>
       <c r="C2019" t="n">
-        <v>5.80000019073486</v>
+        <v>5.80999994277954</v>
       </c>
       <c r="D2019" t="n">
         <v>5.67000007629395</v>
@@ -55116,6 +55116,32 @@
         <v>758</v>
       </c>
       <c r="H2019" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" s="1" t="n">
+        <v>45966.6912152778</v>
+      </c>
+      <c r="B2020" t="n">
+        <v>42479</v>
+      </c>
+      <c r="C2020" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="D2020" t="n">
+        <v>5.69000005722046</v>
+      </c>
+      <c r="E2020" t="n">
+        <v>5.78999996185303</v>
+      </c>
+      <c r="F2020" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G2020" t="s">
+        <v>755</v>
+      </c>
+      <c r="H2020" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">EQUI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73039174079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76171171665192</t>
+    <t xml:space="preserve">1.73039221763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76171135902405</t>
   </si>
   <si>
     <t xml:space="preserve">1.75835561752319</t>
@@ -56,229 +56,229 @@
     <t xml:space="preserve">1.75500011444092</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74493288993835</t>
+    <t xml:space="preserve">1.74493312835693</t>
   </si>
   <si>
     <t xml:space="preserve">1.71361362934113</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71808779239655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7337474822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72032499313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70131015777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70019125938416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69795429706573</t>
+    <t xml:space="preserve">1.71808791160583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73374783992767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72032511234283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7013099193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70019137859344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69795441627502</t>
   </si>
   <si>
     <t xml:space="preserve">1.68005728721619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68900573253632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69571709632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69683527946472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69124281406403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70242810249329</t>
+    <t xml:space="preserve">1.6890059709549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69571721553802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69683539867401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69124293327332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70242822170258</t>
   </si>
   <si>
     <t xml:space="preserve">1.6822943687439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68564999103546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66775333881378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69012439250946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7169691324234</t>
+    <t xml:space="preserve">1.68565034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66775345802307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69012415409088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71696960926056</t>
   </si>
   <si>
     <t xml:space="preserve">1.73262906074524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72256207466125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7214435338974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71473228931427</t>
+    <t xml:space="preserve">1.72256219387054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72144401073456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71473264694214</t>
   </si>
   <si>
     <t xml:space="preserve">1.71585083007812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74717032909393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7505259513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73934018611908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70858013629913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71137666702271</t>
+    <t xml:space="preserve">1.74717020988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75052607059479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73934042453766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70858025550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71137702465057</t>
   </si>
   <si>
     <t xml:space="preserve">1.74213671684265</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74772953987122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73095154762268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72815465927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71417331695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79526770114899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76730418205261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77289700508118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.789675116539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77569317817688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78408205509186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78687858581543</t>
+    <t xml:space="preserve">1.74772930145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7309513092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72815489768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71417284011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79526782035828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7673043012619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77289664745331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78967499732971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77569305896759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78408217430115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78687846660614</t>
   </si>
   <si>
     <t xml:space="preserve">1.84560239315033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82323133945465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81763875484467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78128576278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84280562400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83441662788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86517703533173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87076938152313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85119521617889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86238050460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85958397388458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85678768157959</t>
+    <t xml:space="preserve">1.82323157787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81763863563538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78128588199615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84280586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83441686630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86517679691315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87076926231384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85119473934174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86238038539886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85958385467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85678780078888</t>
   </si>
   <si>
     <t xml:space="preserve">1.84000957012177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89034402370453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93820095062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92025458812714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9292277097702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89333534240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86641526222229</t>
+    <t xml:space="preserve">1.89034426212311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93820130825043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92025482654572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92922747135162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89333510398865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86641561985016</t>
   </si>
   <si>
     <t xml:space="preserve">1.87837994098663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90829026699066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92324542999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92623686790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91128158569336</t>
+    <t xml:space="preserve">1.90829062461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92324554920197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92623662948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91128146648407</t>
   </si>
   <si>
     <t xml:space="preserve">1.93221890926361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85445153713226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81257653236389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84248733520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84547853469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82753217220306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86940681934357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83052289485931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86342489719391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88137090206146</t>
+    <t xml:space="preserve">1.85445129871368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81257688999176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84248721599579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84547829627991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82753229141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86940670013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83052313327789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86342477798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88137102127075</t>
   </si>
   <si>
     <t xml:space="preserve">1.88436210155487</t>
@@ -287,49 +287,49 @@
     <t xml:space="preserve">1.89632642269135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91726362705231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89931750297546</t>
+    <t xml:space="preserve">1.91726350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89931702613831</t>
   </si>
   <si>
     <t xml:space="preserve">1.90529930591583</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96212923526764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94119191169739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93520963191986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94418323040009</t>
+    <t xml:space="preserve">1.96212911605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9411917924881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93520975112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94418334960938</t>
   </si>
   <si>
     <t xml:space="preserve">1.88735318183899</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90230846405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91427254676819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85744273662567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94717419147491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96512079238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00400400161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0129771232605</t>
+    <t xml:space="preserve">1.90230858325958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9142724275589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8574423789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9471743106842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96512043476105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00400424003601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01297736167908</t>
   </si>
   <si>
     <t xml:space="preserve">1.97409355640411</t>
@@ -338,121 +338,121 @@
     <t xml:space="preserve">2.01596808433533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05784320831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06083416938782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0339150428772</t>
+    <t xml:space="preserve">2.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06083393096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03391456604004</t>
   </si>
   <si>
     <t xml:space="preserve">2.00998616218567</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97708463668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913827419281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00699496269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06382489204407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05186080932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99503087997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9980217218399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95614719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97110283374786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13261914253235</t>
+    <t xml:space="preserve">1.97708451747894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913851261139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00699520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06382513046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05186057090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99503099918365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99802160263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95614731311798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97110271453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13261938095093</t>
   </si>
   <si>
     <t xml:space="preserve">2.12065505981445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03989672660828</t>
+    <t xml:space="preserve">2.03989696502686</t>
   </si>
   <si>
     <t xml:space="preserve">2.04587864875793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02494144439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904883861542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98007583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99203968048096</t>
+    <t xml:space="preserve">2.02494120597839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904895782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98007559776306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99203991889954</t>
   </si>
   <si>
     <t xml:space="preserve">1.95315647125244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87239813804626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86043345928192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83650529384613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8753889799118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08081102371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95236575603485</t>
+    <t xml:space="preserve">1.8723977804184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86043357849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83650505542755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87538933753967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08081126213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95236587524414</t>
   </si>
   <si>
     <t xml:space="preserve">1.94594347476959</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93952178955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92667710781097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86887657642365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83676517009735</t>
+    <t xml:space="preserve">1.9395215511322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92667698860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86887693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83676552772522</t>
   </si>
   <si>
     <t xml:space="preserve">1.83034288883209</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80465388298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79180932044983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7789648771286</t>
+    <t xml:space="preserve">1.80465400218964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79180955886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77896511554718</t>
   </si>
   <si>
     <t xml:space="preserve">1.77254283428192</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69547581672668</t>
+    <t xml:space="preserve">1.69547557830811</t>
   </si>
   <si>
     <t xml:space="preserve">1.73400938510895</t>
@@ -464,88 +464,88 @@
     <t xml:space="preserve">1.65051972866058</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66978645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70832026004791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72116470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67620897293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71474254131317</t>
+    <t xml:space="preserve">1.66978669166565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70832002162933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72116482257843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67620921134949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71474230289459</t>
   </si>
   <si>
     <t xml:space="preserve">1.66336405277252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64409744739532</t>
+    <t xml:space="preserve">1.64409756660461</t>
   </si>
   <si>
     <t xml:space="preserve">1.72758686542511</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74685347080231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74043154716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75327575206757</t>
+    <t xml:space="preserve">1.74685370922089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74043142795563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75327599048615</t>
   </si>
   <si>
     <t xml:space="preserve">1.7596982717514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70189797878265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263101577759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65694189071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63767552375793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61198627948761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60556399822235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5991415977478</t>
+    <t xml:space="preserve">1.70189809799194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263113498688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65694212913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63767528533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6119863986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60556411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59914195537567</t>
   </si>
   <si>
     <t xml:space="preserve">1.61840856075287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59271967411041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62483084201813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81749844551086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86245441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856032371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84961009025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82392072677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78538751602173</t>
+    <t xml:space="preserve">1.59271991252899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62483096122742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81749856472015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86245405673981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85603213310242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84960973262787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8239209651947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78538715839386</t>
   </si>
   <si>
     <t xml:space="preserve">1.81107640266418</t>
@@ -557,43 +557,43 @@
     <t xml:space="preserve">1.63125312328339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5156524181366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40005195140839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58629739284515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54134166240692</t>
+    <t xml:space="preserve">1.51565253734589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40005218982697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58629763126373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54134178161621</t>
   </si>
   <si>
     <t xml:space="preserve">1.41931855678558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43858540058136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35509610176086</t>
+    <t xml:space="preserve">1.43858528137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35509586334229</t>
   </si>
   <si>
     <t xml:space="preserve">1.33582925796509</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36151814460754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36794066429138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3165625333786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32940721511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32298457622528</t>
+    <t xml:space="preserve">1.36151826381683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36794078350067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31656241416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32940697669983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32298481464386</t>
   </si>
   <si>
     <t xml:space="preserve">1.37436294555664</t>
@@ -602,76 +602,76 @@
     <t xml:space="preserve">1.38720738887787</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34867370128632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38078510761261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47069668769836</t>
+    <t xml:space="preserve">1.34867382049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38078498840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47069656848907</t>
   </si>
   <si>
     <t xml:space="preserve">1.42574083805084</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43216300010681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49638569355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45785224437714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4128965139389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45142996311188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47711884975433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48354113101959</t>
+    <t xml:space="preserve">1.43216323852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49638557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45785236358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41289639472961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45143008232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47711873054504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48354125022888</t>
   </si>
   <si>
     <t xml:space="preserve">1.46427440643311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57345283031464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44500768184662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48996353149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55418598651886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76612067222595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90653884410858</t>
+    <t xml:space="preserve">1.57345247268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44500780105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48996341228485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55418622493744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76612055301666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90653848648071</t>
   </si>
   <si>
     <t xml:space="preserve">1.8516743183136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70079708099365</t>
+    <t xml:space="preserve">1.70079731941223</t>
   </si>
   <si>
     <t xml:space="preserve">1.68708074092865</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65279054641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68022286891937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65964865684509</t>
+    <t xml:space="preserve">1.65279078483582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6802225112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65964877605438</t>
   </si>
   <si>
     <t xml:space="preserve">1.64593279361725</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">1.61164224147797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6939389705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67336475849152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70765495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66650676727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71451306343079</t>
+    <t xml:space="preserve">1.69393920898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67336452007294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70765507221222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66650664806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71451318264008</t>
   </si>
   <si>
     <t xml:space="preserve">1.72822916507721</t>
@@ -701,28 +701,28 @@
     <t xml:space="preserve">1.74194526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63221633434296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59792613983154</t>
+    <t xml:space="preserve">1.63221669197083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59792602062225</t>
   </si>
   <si>
     <t xml:space="preserve">1.56363594532013</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55677783489227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5704939365387</t>
+    <t xml:space="preserve">1.55677807331085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57049381732941</t>
   </si>
   <si>
     <t xml:space="preserve">1.58421003818512</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59106826782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57735204696655</t>
+    <t xml:space="preserve">1.59106802940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57735180854797</t>
   </si>
   <si>
     <t xml:space="preserve">1.61850035190582</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">1.62535834312439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60478413105011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53620374202728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54991984367371</t>
+    <t xml:space="preserve">1.6047842502594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5362035036087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.549919962883</t>
   </si>
   <si>
     <t xml:space="preserve">1.63907468318939</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">1.54306185245514</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52934563159943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52248764038086</t>
+    <t xml:space="preserve">1.52934575080872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52248752117157</t>
   </si>
   <si>
     <t xml:space="preserve">1.515629529953</t>
@@ -758,61 +758,61 @@
     <t xml:space="preserve">1.50877153873444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50191342830658</t>
+    <t xml:space="preserve">1.50191354751587</t>
   </si>
   <si>
     <t xml:space="preserve">1.48133933544159</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48819744586945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46762323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45390689373016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39904272556305</t>
+    <t xml:space="preserve">1.48819732666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46762335300446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45390701293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39904260635376</t>
   </si>
   <si>
     <t xml:space="preserve">1.36475241184235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37846851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37161040306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35789453983307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35446548461914</t>
+    <t xml:space="preserve">1.37846839427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3716105222702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35789430141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35446536540985</t>
   </si>
   <si>
     <t xml:space="preserve">1.72137117385864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78309345245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81738388538361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79680955410004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78995168209076</t>
+    <t xml:space="preserve">1.7830935716629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8173840045929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79680967330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78995192050934</t>
   </si>
   <si>
     <t xml:space="preserve">1.77623522281647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81052601337433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83110010623932</t>
+    <t xml:space="preserve">1.81052577495575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83109974861145</t>
   </si>
   <si>
     <t xml:space="preserve">1.83795809745789</t>
@@ -824,106 +824,106 @@
     <t xml:space="preserve">1.84481596946716</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87224805355072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89968049526215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91339647769928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92711246013641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94082868099213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96140289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9751193523407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94768691062927</t>
+    <t xml:space="preserve">1.8722482919693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89968061447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91339659690857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92711269855499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94082880020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96140313148499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97511899471283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94768702983856</t>
   </si>
   <si>
     <t xml:space="preserve">1.92025434970856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8859646320343</t>
+    <t xml:space="preserve">1.88596451282501</t>
   </si>
   <si>
     <t xml:space="preserve">1.95454478263855</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93397080898285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96826076507568</t>
+    <t xml:space="preserve">1.93397092819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96826088428497</t>
   </si>
   <si>
     <t xml:space="preserve">2.0162672996521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0505576133728</t>
+    <t xml:space="preserve">2.05055785179138</t>
   </si>
   <si>
     <t xml:space="preserve">2.04369950294495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06427407264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03684186935425</t>
+    <t xml:space="preserve">2.06427359580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03684139251709</t>
   </si>
   <si>
     <t xml:space="preserve">2.02998352050781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05741596221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113218307495</t>
+    <t xml:space="preserve">2.05741572380066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113194465637</t>
   </si>
   <si>
     <t xml:space="preserve">2.07798981666565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08484768867493</t>
+    <t xml:space="preserve">2.08484792709351</t>
   </si>
   <si>
     <t xml:space="preserve">2.09903049468994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10612225532532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13448739051819</t>
+    <t xml:space="preserve">2.10612201690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13448715209961</t>
   </si>
   <si>
     <t xml:space="preserve">2.09193921089172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14157867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11321306228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12030434608459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12739610671997</t>
+    <t xml:space="preserve">2.14157843589783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11321330070496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12030458450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12739586830139</t>
   </si>
   <si>
     <t xml:space="preserve">2.16285228729248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1770350933075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22667455673218</t>
+    <t xml:space="preserve">2.17703485488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2266743183136</t>
   </si>
   <si>
     <t xml:space="preserve">2.20540022850037</t>
@@ -932,28 +932,28 @@
     <t xml:space="preserve">2.25503969192505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26213073730469</t>
+    <t xml:space="preserve">2.26213097572327</t>
   </si>
   <si>
     <t xml:space="preserve">2.24794840812683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21958327293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19830918312073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2337658405304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24085664749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21249127388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2834050655365</t>
+    <t xml:space="preserve">2.2195827960968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19830894470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23376560211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24085712432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21249151229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28340482711792</t>
   </si>
   <si>
     <t xml:space="preserve">2.26922202110291</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">2.29049611091614</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29758763313293</t>
+    <t xml:space="preserve">2.29758739471436</t>
   </si>
   <si>
     <t xml:space="preserve">2.31177020072937</t>
@@ -971,19 +971,19 @@
     <t xml:space="preserve">2.31886124610901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32595252990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33304405212402</t>
+    <t xml:space="preserve">2.32595276832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3330442905426</t>
   </si>
   <si>
     <t xml:space="preserve">2.30467891693115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36850047111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38977432250977</t>
+    <t xml:space="preserve">2.36850070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38977456092834</t>
   </si>
   <si>
     <t xml:space="preserve">2.37559199333191</t>
@@ -992,112 +992,112 @@
     <t xml:space="preserve">2.38268351554871</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39686632156372</t>
+    <t xml:space="preserve">2.39686608314514</t>
   </si>
   <si>
     <t xml:space="preserve">2.40395736694336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44650530815125</t>
+    <t xml:space="preserve">2.44650506973267</t>
   </si>
   <si>
     <t xml:space="preserve">2.43232250213623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49614453315735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51032686233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58124041557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55287504196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55996608734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6308798789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62378835678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60960531234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63797092437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58833169937134</t>
+    <t xml:space="preserve">2.49614429473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51032710075378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58124017715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55287480354309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55996632575989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63087940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62378811836243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60960555076599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63797068595886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58833146095276</t>
   </si>
   <si>
     <t xml:space="preserve">2.59542274475098</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61669683456421</t>
+    <t xml:space="preserve">2.61669707298279</t>
   </si>
   <si>
     <t xml:space="preserve">2.65215349197388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65924453735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7017924785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69470143318176</t>
+    <t xml:space="preserve">2.65924501419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70179271697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69470119476318</t>
   </si>
   <si>
     <t xml:space="preserve">2.72306656837463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.715975522995</t>
+    <t xml:space="preserve">2.71597528457642</t>
   </si>
   <si>
     <t xml:space="preserve">2.68760991096497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7088840007782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68051886558533</t>
+    <t xml:space="preserve">2.70888423919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68051838874817</t>
   </si>
   <si>
     <t xml:space="preserve">2.73092246055603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70907545089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76733493804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8110294342041</t>
+    <t xml:space="preserve">2.70907497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76733469963074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81102991104126</t>
   </si>
   <si>
     <t xml:space="preserve">2.8620069026947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84015941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81831192970276</t>
+    <t xml:space="preserve">2.84015965461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81831216812134</t>
   </si>
   <si>
     <t xml:space="preserve">2.80374717712402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83287692070007</t>
+    <t xml:space="preserve">2.83287739753723</t>
   </si>
   <si>
     <t xml:space="preserve">2.78189969062805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72364020347595</t>
+    <t xml:space="preserve">2.72363972663879</t>
   </si>
   <si>
     <t xml:space="preserve">2.70179295539856</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">2.752769947052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69451022148132</t>
+    <t xml:space="preserve">2.69450998306274</t>
   </si>
   <si>
     <t xml:space="preserve">2.71635770797729</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">2.73820471763611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77461719512939</t>
+    <t xml:space="preserve">2.77461743354797</t>
   </si>
   <si>
     <t xml:space="preserve">2.82559466362</t>
@@ -1127,40 +1127,40 @@
     <t xml:space="preserve">2.78918218612671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79646468162537</t>
+    <t xml:space="preserve">2.79646492004395</t>
   </si>
   <si>
     <t xml:space="preserve">2.76005244255066</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62896800041199</t>
+    <t xml:space="preserve">2.62896823883057</t>
   </si>
   <si>
     <t xml:space="preserve">2.62168550491333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66538023948669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86928939819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61440324783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55614352226257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5342960357666</t>
+    <t xml:space="preserve">2.66538047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86928963661194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61440300941467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55614328384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53429627418518</t>
   </si>
   <si>
     <t xml:space="preserve">2.43962407112122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31582260131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22843241691589</t>
+    <t xml:space="preserve">2.31582236289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22843313217163</t>
   </si>
   <si>
     <t xml:space="preserve">2.27212738990784</t>
@@ -1169,46 +1169,46 @@
     <t xml:space="preserve">2.40321159362793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41049432754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5488612651825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6580982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54157876968384</t>
+    <t xml:space="preserve">2.41049408912659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54886102676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65809798240662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54157829284668</t>
   </si>
   <si>
     <t xml:space="preserve">2.67266297340393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88385438919067</t>
+    <t xml:space="preserve">2.88385415077209</t>
   </si>
   <si>
     <t xml:space="preserve">2.89841914176941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95667886734009</t>
+    <t xml:space="preserve">2.95667839050293</t>
   </si>
   <si>
     <t xml:space="preserve">2.94211387634277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97124361991882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94939661026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91298389434814</t>
+    <t xml:space="preserve">2.9712438583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94939637184143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91298413276672</t>
   </si>
   <si>
     <t xml:space="preserve">2.85472440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97852659225464</t>
+    <t xml:space="preserve">2.97852635383606</t>
   </si>
   <si>
     <t xml:space="preserve">2.96396136283875</t>
@@ -1217,70 +1217,70 @@
     <t xml:space="preserve">2.89113664627075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90570139884949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92754912376404</t>
+    <t xml:space="preserve">2.90570163726807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92754888534546</t>
   </si>
   <si>
     <t xml:space="preserve">3.05783247947693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02717757225037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05016851425171</t>
+    <t xml:space="preserve">3.02717781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05016875267029</t>
   </si>
   <si>
     <t xml:space="preserve">3.01951384544373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98885893821716</t>
+    <t xml:space="preserve">2.98885917663574</t>
   </si>
   <si>
     <t xml:space="preserve">2.95054030418396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88923025131226</t>
+    <t xml:space="preserve">2.88923001289368</t>
   </si>
   <si>
     <t xml:space="preserve">2.91222143173218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77427411079407</t>
+    <t xml:space="preserve">2.77427387237549</t>
   </si>
   <si>
     <t xml:space="preserve">2.66698169708252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68230938911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67464566230774</t>
+    <t xml:space="preserve">2.68230891227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67464542388916</t>
   </si>
   <si>
     <t xml:space="preserve">2.68997287750244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.720627784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69763684272766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72829151153564</t>
+    <t xml:space="preserve">2.72062802314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6976363658905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72829174995422</t>
   </si>
   <si>
     <t xml:space="preserve">2.70530033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63632655143738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65165448188782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64399075508118</t>
+    <t xml:space="preserve">2.63632678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65165424346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6439905166626</t>
   </si>
   <si>
     <t xml:space="preserve">2.62099933624268</t>
@@ -1289,34 +1289,34 @@
     <t xml:space="preserve">2.59034442901611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65931820869446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61333584785461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56735324859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53669810295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52137041091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55968928337097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52903437614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55202531814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54436159133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59800815582275</t>
+    <t xml:space="preserve">2.65931797027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61333560943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56735301017761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53669786453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52137064933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55968976020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52903413772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55202579498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54436182975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59800839424133</t>
   </si>
   <si>
     <t xml:space="preserve">2.46772456169128</t>
@@ -1325,31 +1325,31 @@
     <t xml:space="preserve">2.49837923049927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43706965446472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45239686965942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49071550369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50604319572449</t>
+    <t xml:space="preserve">2.43706941604614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.452397108078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49071574211121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50604295730591</t>
   </si>
   <si>
     <t xml:space="preserve">2.47538805007935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46006083488464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48305177688599</t>
+    <t xml:space="preserve">2.46006059646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48305201530457</t>
   </si>
   <si>
     <t xml:space="preserve">2.71296405792236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78960132598877</t>
+    <t xml:space="preserve">2.78960156440735</t>
   </si>
   <si>
     <t xml:space="preserve">2.80492925643921</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">2.82792019844055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81259274482727</t>
+    <t xml:space="preserve">2.81259298324585</t>
   </si>
   <si>
     <t xml:space="preserve">2.85091137886047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86623930931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89019107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89817500114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92212677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91414260864258</t>
+    <t xml:space="preserve">2.86623859405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89019083976746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89817476272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92212653160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91414284706116</t>
   </si>
   <si>
     <t xml:space="preserve">2.8822066783905</t>
@@ -1388,55 +1388,52 @@
     <t xml:space="preserve">2.95406246185303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9620463848114</t>
+    <t xml:space="preserve">2.96204662322998</t>
   </si>
   <si>
     <t xml:space="preserve">2.97003030776978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94607877731323</t>
+    <t xml:space="preserve">2.94607853889465</t>
   </si>
   <si>
     <t xml:space="preserve">2.87422275543213</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86623907089233</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.90615892410278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93809461593628</t>
+    <t xml:space="preserve">2.9380943775177</t>
   </si>
   <si>
     <t xml:space="preserve">2.93011069297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99398231506348</t>
+    <t xml:space="preserve">2.9939820766449</t>
   </si>
   <si>
     <t xml:space="preserve">3.00196623802185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97801446914673</t>
+    <t xml:space="preserve">2.97801423072815</t>
   </si>
   <si>
     <t xml:space="preserve">3.06583786010742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08978939056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08180522918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0179340839386</t>
+    <t xml:space="preserve">3.08978962898254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08180570602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01793432235718</t>
   </si>
   <si>
     <t xml:space="preserve">3.04986977577209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9859983921051</t>
+    <t xml:space="preserve">2.98599815368652</t>
   </si>
   <si>
     <t xml:space="preserve">3.02591800689697</t>
@@ -1448,28 +1445,28 @@
     <t xml:space="preserve">3.11374163627625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0738217830658</t>
+    <t xml:space="preserve">3.07382202148438</t>
   </si>
   <si>
     <t xml:space="preserve">3.04188585281372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12172532081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12970924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0977737903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15366125106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10575747489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05785393714905</t>
+    <t xml:space="preserve">3.12172555923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12970948219299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09777355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15366148948669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10575771331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05785369873047</t>
   </si>
   <si>
     <t xml:space="preserve">3.24148464202881</t>
@@ -1481,7 +1478,7 @@
     <t xml:space="preserve">3.16164517402649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14567732810974</t>
+    <t xml:space="preserve">3.14567756652832</t>
   </si>
   <si>
     <t xml:space="preserve">3.13769340515137</t>
@@ -1502,10 +1499,10 @@
     <t xml:space="preserve">3.14398765563965</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15239405632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16920685768127</t>
+    <t xml:space="preserve">3.15239381790161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16920638084412</t>
   </si>
   <si>
     <t xml:space="preserve">3.11876845359802</t>
@@ -1517,13 +1514,13 @@
     <t xml:space="preserve">3.12717485427856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13558125495911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0935492515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10195589065552</t>
+    <t xml:space="preserve">3.13558101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09354901313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10195565223694</t>
   </si>
   <si>
     <t xml:space="preserve">3.08514308929443</t>
@@ -1532,37 +1529,37 @@
     <t xml:space="preserve">3.16080045700073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07673668861389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06833004951477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05151748657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04311108589172</t>
+    <t xml:space="preserve">3.07673645019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06833028793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05151724815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04311084747314</t>
   </si>
   <si>
     <t xml:space="preserve">3.0347044467926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05992388725281</t>
+    <t xml:space="preserve">3.05992364883423</t>
   </si>
   <si>
     <t xml:space="preserve">3.02629804611206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00948524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97585988044739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00107884407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0178918838501</t>
+    <t xml:space="preserve">3.00948548316956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97585964202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00107908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01789164543152</t>
   </si>
   <si>
     <t xml:space="preserve">2.95064067840576</t>
@@ -1577,28 +1574,28 @@
     <t xml:space="preserve">2.90860891342163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8665771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85817050933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87498331069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83295106887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91701507568359</t>
+    <t xml:space="preserve">2.86657691001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85817074775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87498354911804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83295130729675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91701531410217</t>
   </si>
   <si>
     <t xml:space="preserve">2.93382787704468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89179587364197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98426604270935</t>
+    <t xml:space="preserve">2.89179611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98426628112793</t>
   </si>
   <si>
     <t xml:space="preserve">2.92542171478271</t>
@@ -1610,7 +1607,7 @@
     <t xml:space="preserve">2.96745347976685</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99267244338989</t>
+    <t xml:space="preserve">2.99267268180847</t>
   </si>
   <si>
     <t xml:space="preserve">3.08550214767456</t>
@@ -1625,7 +1622,7 @@
     <t xml:space="preserve">3.11179900169373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12933015823364</t>
+    <t xml:space="preserve">3.12933039665222</t>
   </si>
   <si>
     <t xml:space="preserve">3.13809585571289</t>
@@ -1634,10 +1631,10 @@
     <t xml:space="preserve">3.15562701225281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19945549964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20822095870972</t>
+    <t xml:space="preserve">3.19945526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2082211971283</t>
   </si>
   <si>
     <t xml:space="preserve">3.22575211524963</t>
@@ -1649,10 +1646,10 @@
     <t xml:space="preserve">3.23451805114746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25204920768738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19068956375122</t>
+    <t xml:space="preserve">3.25204944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1906898021698</t>
   </si>
   <si>
     <t xml:space="preserve">3.16439270973206</t>
@@ -1673,31 +1670,31 @@
     <t xml:space="preserve">3.27834606170654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29587721824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3221743106842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31340837478638</t>
+    <t xml:space="preserve">3.29587745666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32217407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31340861320496</t>
   </si>
   <si>
     <t xml:space="preserve">3.33970546722412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43612718582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39229893684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44489312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45365858078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41859602928162</t>
+    <t xml:space="preserve">3.43612766265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39229917526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44489288330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45365881919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4185962677002</t>
   </si>
   <si>
     <t xml:space="preserve">3.48872113227844</t>
@@ -1712,7 +1709,7 @@
     <t xml:space="preserve">3.37476801872253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38353323936462</t>
+    <t xml:space="preserve">3.3835334777832</t>
   </si>
   <si>
     <t xml:space="preserve">3.47118973731995</t>
@@ -1730,28 +1727,28 @@
     <t xml:space="preserve">3.52378368377686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49748682975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54131484031677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53254961967468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55884599685669</t>
+    <t xml:space="preserve">3.49748706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54131507873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5325493812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55884623527527</t>
   </si>
   <si>
     <t xml:space="preserve">3.5939085483551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66403341293335</t>
+    <t xml:space="preserve">3.66403365135193</t>
   </si>
   <si>
     <t xml:space="preserve">3.6114399433136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60267472267151</t>
+    <t xml:space="preserve">3.60267448425293</t>
   </si>
   <si>
     <t xml:space="preserve">3.5500807762146</t>
@@ -1763,7 +1760,7 @@
     <t xml:space="preserve">3.58559513092041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6040301322937</t>
+    <t xml:space="preserve">3.60402989387512</t>
   </si>
   <si>
     <t xml:space="preserve">3.57637763023376</t>
@@ -1781,7 +1778,7 @@
     <t xml:space="preserve">3.52107262611389</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55794239044189</t>
+    <t xml:space="preserve">3.55794262886047</t>
   </si>
   <si>
     <t xml:space="preserve">3.56716012954712</t>
@@ -1796,13 +1793,13 @@
     <t xml:space="preserve">3.42889809608459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51185512542725</t>
+    <t xml:space="preserve">3.51185536384583</t>
   </si>
   <si>
     <t xml:space="preserve">3.47498536109924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53029036521912</t>
+    <t xml:space="preserve">3.53029012680054</t>
   </si>
   <si>
     <t xml:space="preserve">3.49342036247253</t>
@@ -1811,16 +1808,16 @@
     <t xml:space="preserve">3.54872512817383</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65011739730835</t>
+    <t xml:space="preserve">3.65011715888977</t>
   </si>
   <si>
     <t xml:space="preserve">3.6408998966217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63168239593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44733285903931</t>
+    <t xml:space="preserve">3.63168263435364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44733309745789</t>
   </si>
   <si>
     <t xml:space="preserve">3.50263786315918</t>
@@ -1829,7 +1826,7 @@
     <t xml:space="preserve">3.67776989936829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71463990211487</t>
+    <t xml:space="preserve">3.71463966369629</t>
   </si>
   <si>
     <t xml:space="preserve">3.78837943077087</t>
@@ -1838,10 +1835,10 @@
     <t xml:space="preserve">3.75150966644287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65933465957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77916193008423</t>
+    <t xml:space="preserve">3.659334897995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77916169166565</t>
   </si>
   <si>
     <t xml:space="preserve">3.80681443214417</t>
@@ -1853,7 +1850,7 @@
     <t xml:space="preserve">3.84368419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76994442939758</t>
+    <t xml:space="preserve">3.76994466781616</t>
   </si>
   <si>
     <t xml:space="preserve">3.81603169441223</t>
@@ -1868,7 +1865,7 @@
     <t xml:space="preserve">3.91742372512817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90820646286011</t>
+    <t xml:space="preserve">3.90820622444153</t>
   </si>
   <si>
     <t xml:space="preserve">3.89898896217346</t>
@@ -1877,7 +1874,7 @@
     <t xml:space="preserve">3.88055419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93585848808289</t>
+    <t xml:space="preserve">3.93585896492004</t>
   </si>
   <si>
     <t xml:space="preserve">3.94507646560669</t>
@@ -1889,7 +1886,7 @@
     <t xml:space="preserve">3.86211895942688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83446669578552</t>
+    <t xml:space="preserve">3.83446645736694</t>
   </si>
   <si>
     <t xml:space="preserve">3.83412289619446</t>
@@ -2295,6 +2292,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.80999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92999982833862</t>
   </si>
 </sst>
 </file>
@@ -36009,7 +36009,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1284" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36061,7 +36061,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1286" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36087,7 +36087,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1287" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36165,7 +36165,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36269,7 +36269,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1294" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36347,7 +36347,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1297" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36425,7 +36425,7 @@
         <v>3.75</v>
       </c>
       <c r="G1300" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36451,7 +36451,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1301" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36477,7 +36477,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1302" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36503,7 +36503,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1303" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36529,7 +36529,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1304" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36555,7 +36555,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1305" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36581,7 +36581,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1306" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36607,7 +36607,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1307" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36633,7 +36633,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36685,7 +36685,7 @@
         <v>3.75</v>
       </c>
       <c r="G1310" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36711,7 +36711,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36737,7 +36737,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1312" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36763,7 +36763,7 @@
         <v>3.75</v>
       </c>
       <c r="G1313" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36789,7 +36789,7 @@
         <v>3.75</v>
       </c>
       <c r="G1314" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36893,7 +36893,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36919,7 +36919,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36945,7 +36945,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36971,7 +36971,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1321" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36997,7 +36997,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1322" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37023,7 +37023,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1323" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37049,7 +37049,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1324" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37075,7 +37075,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1325" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37101,7 +37101,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1326" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37127,7 +37127,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1327" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37153,7 +37153,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1328" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37179,7 +37179,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1329" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37205,7 +37205,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37231,7 +37231,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1331" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37257,7 +37257,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1332" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37283,7 +37283,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1333" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37309,7 +37309,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1334" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37335,7 +37335,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37361,7 +37361,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1336" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37387,7 +37387,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1337" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37413,7 +37413,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1338" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37439,7 +37439,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37465,7 +37465,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1340" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37491,7 +37491,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1341" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37517,7 +37517,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1342" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37543,7 +37543,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1343" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37569,7 +37569,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37595,7 +37595,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1345" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37621,7 +37621,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1346" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37647,7 +37647,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37699,7 +37699,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1349" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37725,7 +37725,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1350" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37751,7 +37751,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1351" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37777,7 +37777,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1352" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37803,7 +37803,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1353" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37829,7 +37829,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37855,7 +37855,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1355" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37881,7 +37881,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1356" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37907,7 +37907,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1357" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37933,7 +37933,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1358" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37959,7 +37959,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1359" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37985,7 +37985,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1360" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38011,7 +38011,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1361" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38037,7 +38037,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1362" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38063,7 +38063,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1363" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38089,7 +38089,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1364" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38115,7 +38115,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1365" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38141,7 +38141,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1366" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38167,7 +38167,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38193,7 +38193,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1368" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38219,7 +38219,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38245,7 +38245,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1370" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38271,7 +38271,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1371" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38297,7 +38297,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38323,7 +38323,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1373" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38349,7 +38349,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1374" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38375,7 +38375,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1375" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38401,7 +38401,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38427,7 +38427,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1377" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38453,7 +38453,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1378" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38479,7 +38479,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1379" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38505,7 +38505,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1380" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38531,7 +38531,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38557,7 +38557,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1382" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38583,7 +38583,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38609,7 +38609,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1384" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38635,7 +38635,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1385" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38661,7 +38661,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1386" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38687,7 +38687,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38713,7 +38713,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1388" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38739,7 +38739,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38765,7 +38765,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1390" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38791,7 +38791,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38817,7 +38817,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1392" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38843,7 +38843,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1393" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38869,7 +38869,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38895,7 +38895,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1395" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38921,7 +38921,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1396" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38947,7 +38947,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1397" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38973,7 +38973,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1398" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38999,7 +38999,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1399" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39025,7 +39025,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1400" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39051,7 +39051,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1401" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39077,7 +39077,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1402" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39103,7 +39103,7 @@
         <v>3.75</v>
       </c>
       <c r="G1403" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39129,7 +39129,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39155,7 +39155,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1405" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39181,7 +39181,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1406" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39207,7 +39207,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1407" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39233,7 +39233,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1408" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39259,7 +39259,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1409" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39285,7 +39285,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1410" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39311,7 +39311,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1411" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39337,7 +39337,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1412" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39363,7 +39363,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1413" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39389,7 +39389,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1414" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39415,7 +39415,7 @@
         <v>3.75</v>
       </c>
       <c r="G1415" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39441,7 +39441,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39467,7 +39467,7 @@
         <v>3.75</v>
       </c>
       <c r="G1417" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39493,7 +39493,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1418" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39519,7 +39519,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39545,7 +39545,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1420" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39571,7 +39571,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1421" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39597,7 +39597,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1422" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39623,7 +39623,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39649,7 +39649,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1424" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39675,7 +39675,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1425" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39701,7 +39701,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1426" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39727,7 +39727,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1427" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39753,7 +39753,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1428" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39779,7 +39779,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39805,7 +39805,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1430" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39831,7 +39831,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39857,7 +39857,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39883,7 +39883,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1433" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39909,7 +39909,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39935,7 +39935,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1435" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39961,7 +39961,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1436" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39987,7 +39987,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1437" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40013,7 +40013,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1438" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40039,7 +40039,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1439" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40065,7 +40065,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40091,7 +40091,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1441" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40117,7 +40117,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40143,7 +40143,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1443" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40169,7 +40169,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1444" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40195,7 +40195,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1445" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40221,7 +40221,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1446" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40247,7 +40247,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1447" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40273,7 +40273,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1448" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40299,7 +40299,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1449" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40325,7 +40325,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1450" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40351,7 +40351,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1451" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40377,7 +40377,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1452" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40403,7 +40403,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40429,7 +40429,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40455,7 +40455,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40481,7 +40481,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40507,7 +40507,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1457" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40533,7 +40533,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40559,7 +40559,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1459" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40585,7 +40585,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1460" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40611,7 +40611,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40637,7 +40637,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1462" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40663,7 +40663,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40689,7 +40689,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1464" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40715,7 +40715,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40741,7 +40741,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1466" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40767,7 +40767,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1467" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40793,7 +40793,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1468" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40819,7 +40819,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1469" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40845,7 +40845,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1470" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40871,7 +40871,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1471" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40897,7 +40897,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1472" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40923,7 +40923,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1473" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40949,7 +40949,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40975,7 +40975,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1475" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41001,7 +41001,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1476" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41027,7 +41027,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1477" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41053,7 +41053,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1478" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41079,7 +41079,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1479" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41105,7 +41105,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41131,7 +41131,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41157,7 +41157,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1482" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41183,7 +41183,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1483" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41209,7 +41209,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1484" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41235,7 +41235,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1485" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41261,7 +41261,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1486" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41287,7 +41287,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1487" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41313,7 +41313,7 @@
         <v>3.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41339,7 +41339,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1489" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41365,7 +41365,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41391,7 +41391,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1491" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41417,7 +41417,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1492" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41443,7 +41443,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41469,7 +41469,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1494" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41495,7 +41495,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1495" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41521,7 +41521,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1496" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41547,7 +41547,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1497" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41573,7 +41573,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1498" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41599,7 +41599,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1499" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41625,7 +41625,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1500" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41651,7 +41651,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1501" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41677,7 +41677,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41703,7 +41703,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1503" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41729,7 +41729,7 @@
         <v>3.5</v>
       </c>
       <c r="G1504" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41755,7 +41755,7 @@
         <v>3.5</v>
       </c>
       <c r="G1505" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41781,7 +41781,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1506" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41807,7 +41807,7 @@
         <v>3.5</v>
       </c>
       <c r="G1507" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41833,7 +41833,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1508" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41859,7 +41859,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1509" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41885,7 +41885,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1510" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41911,7 +41911,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1511" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41937,7 +41937,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1512" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41963,7 +41963,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41989,7 +41989,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42015,7 +42015,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42041,7 +42041,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42067,7 +42067,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1517" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42093,7 +42093,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1518" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42119,7 +42119,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1519" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42145,7 +42145,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1520" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42171,7 +42171,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42197,7 +42197,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42223,7 +42223,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1523" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42249,7 +42249,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1524" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42275,7 +42275,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1525" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42301,7 +42301,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1526" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42327,7 +42327,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1527" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42353,7 +42353,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1528" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42379,7 +42379,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1529" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42405,7 +42405,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1530" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42431,7 +42431,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1531" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42457,7 +42457,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1532" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42483,7 +42483,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1533" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42509,7 +42509,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1534" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42535,7 +42535,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1535" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42561,7 +42561,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1536" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42587,7 +42587,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1537" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42613,7 +42613,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1538" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42639,7 +42639,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1539" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42665,7 +42665,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1540" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42691,7 +42691,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1541" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42717,7 +42717,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42743,7 +42743,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1543" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42769,7 +42769,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1544" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42795,7 +42795,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1545" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42821,7 +42821,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1546" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42847,7 +42847,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1547" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42873,7 +42873,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1548" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42899,7 +42899,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1549" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42925,7 +42925,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1550" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42951,7 +42951,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1551" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42977,7 +42977,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1552" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43003,7 +43003,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1553" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43029,7 +43029,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1554" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43055,7 +43055,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1555" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43081,7 +43081,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1556" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43107,7 +43107,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1557" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43133,7 +43133,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1558" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43159,7 +43159,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1559" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43185,7 +43185,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1560" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43211,7 +43211,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43237,7 +43237,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1562" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43263,7 +43263,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1563" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43289,7 +43289,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1564" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43315,7 +43315,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1565" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43341,7 +43341,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1566" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43367,7 +43367,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1567" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43393,7 +43393,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1568" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43419,7 +43419,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1569" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43445,7 +43445,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1570" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43471,7 +43471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1571" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43497,7 +43497,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1572" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43523,7 +43523,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1573" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43549,7 +43549,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1574" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43575,7 +43575,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1575" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43601,7 +43601,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1576" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43627,7 +43627,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1577" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43653,7 +43653,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1578" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43679,7 +43679,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1579" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43705,7 +43705,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1580" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43731,7 +43731,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1581" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43757,7 +43757,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1582" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43783,7 +43783,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1583" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43809,7 +43809,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1584" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43835,7 +43835,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1585" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43861,7 +43861,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1586" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43887,7 +43887,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1587" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43913,7 +43913,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1588" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43939,7 +43939,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1589" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43965,7 +43965,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1590" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43991,7 +43991,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1591" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44017,7 +44017,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1592" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44043,7 +44043,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1593" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44069,7 +44069,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1594" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44095,7 +44095,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1595" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44121,7 +44121,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1596" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44147,7 +44147,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1597" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44173,7 +44173,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1598" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44199,7 +44199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1599" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44225,7 +44225,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1600" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44251,7 +44251,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44277,7 +44277,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1602" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44303,7 +44303,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44329,7 +44329,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44355,7 +44355,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1605" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44381,7 +44381,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1606" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44407,7 +44407,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1607" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44433,7 +44433,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44459,7 +44459,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1609" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44485,7 +44485,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1610" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44511,7 +44511,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44537,7 +44537,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1612" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44563,7 +44563,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1613" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44589,7 +44589,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44615,7 +44615,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1615" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44641,7 +44641,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1616" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44667,7 +44667,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1617" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44693,7 +44693,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1618" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44719,7 +44719,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1619" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44745,7 +44745,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1620" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44771,7 +44771,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1621" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44797,7 +44797,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1622" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44823,7 +44823,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1623" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44849,7 +44849,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44875,7 +44875,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44901,7 +44901,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44927,7 +44927,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1627" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44953,7 +44953,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1628" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44979,7 +44979,7 @@
         <v>4</v>
       </c>
       <c r="G1629" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45005,7 +45005,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1630" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45031,7 +45031,7 @@
         <v>4</v>
       </c>
       <c r="G1631" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45057,7 +45057,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1632" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45083,7 +45083,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45109,7 +45109,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1634" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45135,7 +45135,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45161,7 +45161,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45187,7 +45187,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1637" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45213,7 +45213,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1638" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45239,7 +45239,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1639" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45265,7 +45265,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1640" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45291,7 +45291,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45317,7 +45317,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1642" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45343,7 +45343,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1643" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45369,7 +45369,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1644" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45395,7 +45395,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1645" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45421,7 +45421,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45447,7 +45447,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1647" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45473,7 +45473,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1648" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45499,7 +45499,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1649" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45525,7 +45525,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1650" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45551,7 +45551,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45577,7 +45577,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1652" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45603,7 +45603,7 @@
         <v>4</v>
       </c>
       <c r="G1653" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45629,7 +45629,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1654" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45655,7 +45655,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1655" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45681,7 +45681,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1656" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45707,7 +45707,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1657" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45733,7 +45733,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1658" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45759,7 +45759,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45785,7 +45785,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45811,7 +45811,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1661" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45837,7 +45837,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1662" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45863,7 +45863,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45889,7 +45889,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1664" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45915,7 +45915,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45941,7 +45941,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1666" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45967,7 +45967,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1667" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45993,7 +45993,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1668" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46019,7 +46019,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1669" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46045,7 +46045,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46071,7 +46071,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1671" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46097,7 +46097,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1672" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46123,7 +46123,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46149,7 +46149,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1674" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46175,7 +46175,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1675" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46201,7 +46201,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1676" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46227,7 +46227,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1677" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46253,7 +46253,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1678" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46279,7 +46279,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1679" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46305,7 +46305,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1680" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46331,7 +46331,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1681" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46357,7 +46357,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1682" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46383,7 +46383,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1683" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46409,7 +46409,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1684" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46435,7 +46435,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1685" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46461,7 +46461,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1686" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46487,7 +46487,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46513,7 +46513,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1688" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46539,7 +46539,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1689" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46565,7 +46565,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1690" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46591,7 +46591,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1691" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46617,7 +46617,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1692" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46643,7 +46643,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1693" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46669,7 +46669,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1694" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46695,7 +46695,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1695" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46721,7 +46721,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1696" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46747,7 +46747,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1697" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46773,7 +46773,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46799,7 +46799,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1699" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46825,7 +46825,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1700" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46851,7 +46851,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1701" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46877,7 +46877,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1702" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46903,7 +46903,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1703" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46929,7 +46929,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1704" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46955,7 +46955,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46981,7 +46981,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47007,7 +47007,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47033,7 +47033,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1708" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47059,7 +47059,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1709" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47085,7 +47085,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1710" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47111,7 +47111,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47137,7 +47137,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1712" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47163,7 +47163,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1713" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47189,7 +47189,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47215,7 +47215,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1715" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47241,7 +47241,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1716" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47267,7 +47267,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47293,7 +47293,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1718" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47319,7 +47319,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47345,7 +47345,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1720" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47371,7 +47371,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47397,7 +47397,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1722" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47423,7 +47423,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1723" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47449,7 +47449,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1724" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47475,7 +47475,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1725" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47501,7 +47501,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47527,7 +47527,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1727" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47553,7 +47553,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1728" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47579,7 +47579,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1729" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47605,7 +47605,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1730" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47631,7 +47631,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1731" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47657,7 +47657,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1732" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47683,7 +47683,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1733" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47709,7 +47709,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1734" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47735,7 +47735,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1735" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47761,7 +47761,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1736" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47787,7 +47787,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1737" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47813,7 +47813,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1738" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47839,7 +47839,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1739" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47865,7 +47865,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1740" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47891,7 +47891,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1741" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47917,7 +47917,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47943,7 +47943,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1743" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47969,7 +47969,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1744" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47995,7 +47995,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1745" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48021,7 +48021,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1746" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48047,7 +48047,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1747" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48073,7 +48073,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1748" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48099,7 +48099,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1749" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48125,7 +48125,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1750" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48151,7 +48151,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1751" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48177,7 +48177,7 @@
         <v>4.25</v>
       </c>
       <c r="G1752" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48203,7 +48203,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1753" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48229,7 +48229,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1754" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48255,7 +48255,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48281,7 +48281,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1756" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48307,7 +48307,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1757" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48333,7 +48333,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1758" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48359,7 +48359,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1759" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48385,7 +48385,7 @@
         <v>4.25</v>
       </c>
       <c r="G1760" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48411,7 +48411,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48437,7 +48437,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1762" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48463,7 +48463,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1763" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48489,7 +48489,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48515,7 +48515,7 @@
         <v>4.25</v>
       </c>
       <c r="G1765" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48541,7 +48541,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1766" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48567,7 +48567,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48593,7 +48593,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1768" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48619,7 +48619,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48645,7 +48645,7 @@
         <v>4.25</v>
       </c>
       <c r="G1770" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48671,7 +48671,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1771" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48697,7 +48697,7 @@
         <v>4.25</v>
       </c>
       <c r="G1772" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48723,7 +48723,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1773" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48749,7 +48749,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1774" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48775,7 +48775,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1775" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48801,7 +48801,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1776" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48827,7 +48827,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1777" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48853,7 +48853,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1778" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48879,7 +48879,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48905,7 +48905,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1780" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48931,7 +48931,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1781" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48957,7 +48957,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1782" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48983,7 +48983,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1783" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49009,7 +49009,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1784" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49035,7 +49035,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1785" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49061,7 +49061,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1786" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49087,7 +49087,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1787" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49113,7 +49113,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1788" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49139,7 +49139,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1789" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49165,7 +49165,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1790" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49191,7 +49191,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1791" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49217,7 +49217,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1792" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49243,7 +49243,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1793" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49269,7 +49269,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1794" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49295,7 +49295,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49321,7 +49321,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49347,7 +49347,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49373,7 +49373,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49399,7 +49399,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1799" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49425,7 +49425,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1800" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49451,7 +49451,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1801" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49477,7 +49477,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1802" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49503,7 +49503,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49529,7 +49529,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1804" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49555,7 +49555,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1805" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49581,7 +49581,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1806" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49607,7 +49607,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49633,7 +49633,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1808" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49659,7 +49659,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1809" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49685,7 +49685,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1810" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49711,7 +49711,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1811" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49737,7 +49737,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1812" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49763,7 +49763,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1813" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49789,7 +49789,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1814" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49815,7 +49815,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1815" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49841,7 +49841,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1816" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49867,7 +49867,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1817" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49893,7 +49893,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49919,7 +49919,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1819" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49945,7 +49945,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1820" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49971,7 +49971,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1821" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49997,7 +49997,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1822" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50023,7 +50023,7 @@
         <v>4.25</v>
       </c>
       <c r="G1823" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50049,7 +50049,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1824" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50075,7 +50075,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50101,7 +50101,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1826" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50127,7 +50127,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50153,7 +50153,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1828" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50179,7 +50179,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1829" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50205,7 +50205,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1830" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50231,7 +50231,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1831" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50257,7 +50257,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50283,7 +50283,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1833" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50309,7 +50309,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50335,7 +50335,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50361,7 +50361,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1836" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50387,7 +50387,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1837" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50413,7 +50413,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1838" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50439,7 +50439,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1839" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50465,7 +50465,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1840" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50491,7 +50491,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1841" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50517,7 +50517,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1842" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50543,7 +50543,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1843" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50569,7 +50569,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1844" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50595,7 +50595,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1845" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50621,7 +50621,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1846" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50647,7 +50647,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1847" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50673,7 +50673,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50699,7 +50699,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1849" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50725,7 +50725,7 @@
         <v>4.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50751,7 +50751,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1851" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50777,7 +50777,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50803,7 +50803,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1853" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50829,7 +50829,7 @@
         <v>4.25</v>
       </c>
       <c r="G1854" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50855,7 +50855,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1855" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50881,7 +50881,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1856" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50907,7 +50907,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1857" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50933,7 +50933,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1858" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50959,7 +50959,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50985,7 +50985,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1860" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51011,7 +51011,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1861" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51037,7 +51037,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51063,7 +51063,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1863" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51089,7 +51089,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1864" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51115,7 +51115,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1865" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51141,7 +51141,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1866" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51167,7 +51167,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1867" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51193,7 +51193,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1868" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51219,7 +51219,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1869" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51245,7 +51245,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1870" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51271,7 +51271,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1871" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51297,7 +51297,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1872" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51323,7 +51323,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1873" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51349,7 +51349,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1874" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51375,7 +51375,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1875" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51401,7 +51401,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1876" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51427,7 +51427,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1877" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51453,7 +51453,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1878" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51479,7 +51479,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1879" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51505,7 +51505,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1880" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51531,7 +51531,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1881" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51557,7 +51557,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1882" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51583,7 +51583,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1883" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51609,7 +51609,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1884" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51635,7 +51635,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1885" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51661,7 +51661,7 @@
         <v>4.25</v>
       </c>
       <c r="G1886" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51687,7 +51687,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51713,7 +51713,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1888" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51739,7 +51739,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51765,7 +51765,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1890" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51791,7 +51791,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1891" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51817,7 +51817,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1892" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51843,7 +51843,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1893" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51869,7 +51869,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1894" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51895,7 +51895,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1895" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51921,7 +51921,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51947,7 +51947,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1897" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51973,7 +51973,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1898" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51999,7 +51999,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1899" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52025,7 +52025,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1900" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52051,7 +52051,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52077,7 +52077,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1902" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52103,7 +52103,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1903" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52129,7 +52129,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1904" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52155,7 +52155,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1905" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52181,7 +52181,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52207,7 +52207,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52233,7 +52233,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1908" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52259,7 +52259,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1909" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52285,7 +52285,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1910" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52311,7 +52311,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1911" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52337,7 +52337,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52363,7 +52363,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1913" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52389,7 +52389,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1914" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52415,7 +52415,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1915" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52441,7 +52441,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1916" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52467,7 +52467,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1917" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52493,7 +52493,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1918" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52519,7 +52519,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1919" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52545,7 +52545,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1920" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52571,7 +52571,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1921" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52597,7 +52597,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1922" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52623,7 +52623,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G1923" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52649,7 +52649,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1924" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52675,7 +52675,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1925" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52701,7 +52701,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1926" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52727,7 +52727,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1927" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52753,7 +52753,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1928" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52779,7 +52779,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1929" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52805,7 +52805,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52831,7 +52831,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G1931" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52857,7 +52857,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1932" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52883,7 +52883,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1933" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52909,7 +52909,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1934" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52935,7 +52935,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1935" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52961,7 +52961,7 @@
         <v>4.5</v>
       </c>
       <c r="G1936" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52987,7 +52987,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1937" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53013,7 +53013,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1938" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53039,7 +53039,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1939" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53065,7 +53065,7 @@
         <v>4.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53091,7 +53091,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1941" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53117,7 +53117,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1942" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53143,7 +53143,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1943" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53169,7 +53169,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53195,7 +53195,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1945" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53221,7 +53221,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1946" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53247,7 +53247,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53273,7 +53273,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1948" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53299,7 +53299,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1949" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53325,7 +53325,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1950" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53351,7 +53351,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1951" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53377,7 +53377,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1952" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53403,7 +53403,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1953" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53429,7 +53429,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53455,7 +53455,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1955" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53481,7 +53481,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1956" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53507,7 +53507,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53533,7 +53533,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1958" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53559,7 +53559,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53585,7 +53585,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53611,7 +53611,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1961" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53637,7 +53637,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1962" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53663,7 +53663,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53689,7 +53689,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53715,7 +53715,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G1965" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53741,7 +53741,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1966" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53767,7 +53767,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1967" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53793,7 +53793,7 @@
         <v>5</v>
       </c>
       <c r="G1968" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53819,7 +53819,7 @@
         <v>5</v>
       </c>
       <c r="G1969" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53845,7 +53845,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1970" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53871,7 +53871,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1971" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53897,7 +53897,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G1972" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53923,7 +53923,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1973" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53949,7 +53949,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53975,7 +53975,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54001,7 +54001,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1976" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54027,7 +54027,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1977" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54053,7 +54053,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1978" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54079,7 +54079,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1979" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54105,7 +54105,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54131,7 +54131,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1981" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54157,7 +54157,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1982" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54183,7 +54183,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1983" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54209,7 +54209,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1984" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54235,7 +54235,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1985" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54261,7 +54261,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1986" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54287,7 +54287,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1987" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54313,7 +54313,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54339,7 +54339,7 @@
         <v>5.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54365,7 +54365,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1990" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54391,7 +54391,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1991" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54417,7 +54417,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54443,7 +54443,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1993" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54469,7 +54469,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1994" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54495,7 +54495,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1995" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54521,7 +54521,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1996" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54547,7 +54547,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1997" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54573,7 +54573,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1998" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54599,7 +54599,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54625,7 +54625,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2000" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54651,7 +54651,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2001" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54677,7 +54677,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G2002" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54703,7 +54703,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54729,7 +54729,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54755,7 +54755,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2005" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54781,7 +54781,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2006" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54807,7 +54807,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2007" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54833,7 +54833,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2008" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54859,7 +54859,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2009" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54885,7 +54885,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2010" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54911,7 +54911,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2011" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54937,7 +54937,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2012" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54963,7 +54963,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2013" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54989,7 +54989,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55015,7 +55015,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2015" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55041,7 +55041,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2016" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55067,7 +55067,7 @@
         <v>5.75</v>
       </c>
       <c r="G2017" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55093,7 +55093,7 @@
         <v>5.75</v>
       </c>
       <c r="G2018" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55119,7 +55119,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2019" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55145,7 +55145,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2020" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55171,7 +55171,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2021" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55197,7 +55197,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2022" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55223,7 +55223,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2023" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55231,7 +55231,7 @@
     </row>
     <row r="2024">
       <c r="A2024" s="1" t="n">
-        <v>45972.6912152778</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2024" t="n">
         <v>209995</v>
@@ -55249,9 +55249,35 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2024" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2024" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" s="1" t="n">
+        <v>45973.6911111111</v>
+      </c>
+      <c r="B2025" t="n">
+        <v>369064</v>
+      </c>
+      <c r="C2025" t="n">
+        <v>5.96000003814697</v>
+      </c>
+      <c r="D2025" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="E2025" t="n">
+        <v>5.76999998092651</v>
+      </c>
+      <c r="F2025" t="n">
+        <v>5.92999982833862</v>
+      </c>
+      <c r="G2025" t="s">
+        <v>760</v>
+      </c>
+      <c r="H2025" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="768">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61930751800537</t>
+    <t xml:space="preserve">1.61930739879608</t>
   </si>
   <si>
     <t xml:space="preserve">EQUI.MI</t>
@@ -47,55 +47,55 @@
     <t xml:space="preserve">1.6869148015976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71744740009308</t>
+    <t xml:space="preserve">1.71744751930237</t>
   </si>
   <si>
     <t xml:space="preserve">1.71417570114136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71090459823608</t>
+    <t xml:space="preserve">1.71090447902679</t>
   </si>
   <si>
     <t xml:space="preserve">1.70109033584595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67055821418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.674919962883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69018590450287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67710113525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65856325626373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65747284889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65529227256775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6378448009491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64656805992126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311110019684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65420162677765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64874923229218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65965390205383</t>
+    <t xml:space="preserve">1.67055785655975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491984367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69018626213074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67710065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65856337547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65747272968292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65529191493988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784468173981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64656853675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311133861542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65420138835907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64874947071075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65965378284454</t>
   </si>
   <si>
     <t xml:space="preserve">1.64002573490143</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">1.64329695701599</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62585008144379</t>
+    <t xml:space="preserve">1.62585020065308</t>
   </si>
   <si>
     <t xml:space="preserve">1.64765894412994</t>
@@ -113,40 +113,40 @@
     <t xml:space="preserve">1.67382943630219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68909573554993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67928183078766</t>
+    <t xml:space="preserve">1.68909585475922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67928159236908</t>
   </si>
   <si>
     <t xml:space="preserve">1.67819130420685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67164826393127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67273890972137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70327138900757</t>
+    <t xml:space="preserve">1.67164850234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67273879051208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70327162742615</t>
   </si>
   <si>
     <t xml:space="preserve">1.70654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69563841819763</t>
+    <t xml:space="preserve">1.69563806056976</t>
   </si>
   <si>
     <t xml:space="preserve">1.66565108299255</t>
   </si>
   <si>
-    <t xml:space="preserve">1.668377161026</t>
+    <t xml:space="preserve">1.66837692260742</t>
   </si>
   <si>
     <t xml:space="preserve">1.69836437702179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70381677150726</t>
+    <t xml:space="preserve">1.70381689071655</t>
   </si>
   <si>
     <t xml:space="preserve">1.687460064888</t>
@@ -155,232 +155,235 @@
     <t xml:space="preserve">1.68473374843597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67110335826874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016057491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72289943695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72835171222687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74470818042755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73107779026031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73925578594208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74198234081268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79923033714294</t>
+    <t xml:space="preserve">1.67110323905945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72289931774139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72835159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74470841884613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73107767105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73925590515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7419821023941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79923021793365</t>
   </si>
   <si>
     <t xml:space="preserve">1.77742159366608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77196931838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73652958869934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79650461673737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78832566738129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81831312179565</t>
+    <t xml:space="preserve">1.7719691991806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7365300655365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7965042591095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78832578659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81831347942352</t>
   </si>
   <si>
     <t xml:space="preserve">1.82376539707184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80468237400055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81558692455292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81286084651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81013464927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377770423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84284806251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88950228691101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200713157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88075459003448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84576368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81952059268951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83118438720703</t>
+    <t xml:space="preserve">1.80468273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8155871629715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81286108493805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81013453006744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377818107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84284818172455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8895024061203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200701236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88075482845306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84576380252838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81952083110809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83118450641632</t>
   </si>
   <si>
     <t xml:space="preserve">1.86034333705902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87492287158966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87783896923065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8632595539093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88367056846619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80785703659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76703476905823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79619383811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79910945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161406517029</t>
+    <t xml:space="preserve">1.87492263317108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87783873081207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86325919628143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88367092609406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80785763263702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76703488826752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79619348049164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79910957813263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161418437958</t>
   </si>
   <si>
     <t xml:space="preserve">1.82243692874908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78453004360199</t>
+    <t xml:space="preserve">1.78452980518341</t>
   </si>
   <si>
     <t xml:space="preserve">1.81660497188568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83410060405731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83701646327972</t>
+    <t xml:space="preserve">1.83410036563873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8370167016983</t>
   </si>
   <si>
     <t xml:space="preserve">1.84867990016937</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909127235413</t>
+    <t xml:space="preserve">1.86909091472626</t>
   </si>
   <si>
     <t xml:space="preserve">1.85159587860107</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85742712020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282939910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89241862297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8865864276886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89533424377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83993244171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85451173782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617517471313</t>
+    <t xml:space="preserve">1.84284794330597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85742747783661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282975673676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89241826534271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88658666610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89533448219299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83993208408356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85451185703278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617541313171</t>
   </si>
   <si>
     <t xml:space="preserve">1.81077289581299</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89825022220612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91574573516846</t>
+    <t xml:space="preserve">1.89824998378754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91574537754059</t>
   </si>
   <si>
     <t xml:space="preserve">1.95365226268768</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240043640137</t>
+    <t xml:space="preserve">1.96239972114563</t>
   </si>
   <si>
     <t xml:space="preserve">1.9244931936264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96531558036804</t>
+    <t xml:space="preserve">1.9653160572052</t>
   </si>
   <si>
     <t xml:space="preserve">2.00613832473755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00905442237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98281097412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9594841003418</t>
+    <t xml:space="preserve">2.00905394554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98281121253967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95948421955109</t>
   </si>
   <si>
     <t xml:space="preserve">1.92740905284882</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90991377830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9565681219101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01197028160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0003068447113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94490456581116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94782030582428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90699779987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92157769203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07903575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06737232208252</t>
+    <t xml:space="preserve">1.90991389751434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95656824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01197004318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00030660629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94490432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94782042503357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90699768066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92157733440399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07903599739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06737208366394</t>
   </si>
   <si>
     <t xml:space="preserve">1.98864316940308</t>
@@ -389,7 +392,7 @@
     <t xml:space="preserve">1.99447476863861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97406327724457</t>
+    <t xml:space="preserve">1.97406363487244</t>
   </si>
   <si>
     <t xml:space="preserve">1.93907260894775</t>
@@ -398,7 +401,7 @@
     <t xml:space="preserve">1.93032479286194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94198846817017</t>
+    <t xml:space="preserve">1.94198870658875</t>
   </si>
   <si>
     <t xml:space="preserve">1.90408194065094</t>
@@ -407,16 +410,16 @@
     <t xml:space="preserve">1.8253527879715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81368923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7903618812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82826852798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02852916717529</t>
+    <t xml:space="preserve">1.8136887550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79036200046539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82826840877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02852940559387</t>
   </si>
   <si>
     <t xml:space="preserve">1.90331149101257</t>
@@ -425,85 +428,85 @@
     <t xml:space="preserve">1.89705061912537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89078938961029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87826764583588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82191979885101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7906152009964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78435444831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75931107997894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74678897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73426747322083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72800660133362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65287566184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69044101238251</t>
+    <t xml:space="preserve">1.89078962802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87826824188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82191967964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79061508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78435456752777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75931072235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74678945541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73426759243011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72800636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65287590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69044125080109</t>
   </si>
   <si>
     <t xml:space="preserve">1.64661490917206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60904967784882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62783205509186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6653972864151</t>
+    <t xml:space="preserve">1.60904955863953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62783217430115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66539716720581</t>
   </si>
   <si>
     <t xml:space="preserve">1.67791938781738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63409280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67165863513947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62157130241394</t>
+    <t xml:space="preserve">1.63409292697906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67165851593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62157166004181</t>
   </si>
   <si>
     <t xml:space="preserve">1.60278856754303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68418025970459</t>
+    <t xml:space="preserve">1.68418049812317</t>
   </si>
   <si>
     <t xml:space="preserve">1.70296287536621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.696702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.709223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71548473834991</t>
+    <t xml:space="preserve">1.69670176506042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70922386646271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71548497676849</t>
   </si>
   <si>
     <t xml:space="preserve">1.65913665294647</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64035379886627</t>
+    <t xml:space="preserve">1.64035391807556</t>
   </si>
   <si>
     <t xml:space="preserve">1.61531043052673</t>
@@ -515,10 +518,10 @@
     <t xml:space="preserve">1.57148408889771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56522333621979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.558962225914</t>
+    <t xml:space="preserve">1.5652232170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55896246433258</t>
   </si>
   <si>
     <t xml:space="preserve">1.57774496078491</t>
@@ -527,25 +530,25 @@
     <t xml:space="preserve">1.55270147323608</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58400595188141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77183270454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81565892696381</t>
+    <t xml:space="preserve">1.58400571346283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77183258533478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81565916538239</t>
   </si>
   <si>
     <t xml:space="preserve">1.8093980550766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80313718318939</t>
+    <t xml:space="preserve">1.80313730239868</t>
   </si>
   <si>
     <t xml:space="preserve">1.77809381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052822589874</t>
+    <t xml:space="preserve">1.74052846431732</t>
   </si>
   <si>
     <t xml:space="preserve">1.76557183265686</t>
@@ -554,25 +557,25 @@
     <t xml:space="preserve">1.75305008888245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59026706218719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47757053375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36487472057343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54644048213959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50261449813843</t>
+    <t xml:space="preserve">1.59026718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47757077217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36487483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54644060134888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50261437892914</t>
   </si>
   <si>
     <t xml:space="preserve">1.38365733623505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40244007110596</t>
+    <t xml:space="preserve">1.40243995189667</t>
   </si>
   <si>
     <t xml:space="preserve">1.32104825973511</t>
@@ -584,34 +587,34 @@
     <t xml:space="preserve">1.3273092508316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33357048034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28348302841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29600489139557</t>
+    <t xml:space="preserve">1.33357036113739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28348290920258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29600501060486</t>
   </si>
   <si>
     <t xml:space="preserve">1.28974390029907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33983111381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35235297679901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31478750705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609198570251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43374454975128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38991808891296</t>
+    <t xml:space="preserve">1.3398312330246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3523530960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31478726863861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609186649323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43374443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38991820812225</t>
   </si>
   <si>
     <t xml:space="preserve">1.39617943763733</t>
@@ -620,160 +623,157 @@
     <t xml:space="preserve">1.45878791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42122268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37739646434784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41496169567108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44000542163849</t>
+    <t xml:space="preserve">1.42122280597687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37739634513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41496193408966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44000518321991</t>
   </si>
   <si>
     <t xml:space="preserve">1.44626617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42748367786407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391885757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40870094299316</t>
+    <t xml:space="preserve">1.4274834394455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391861915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40870070457458</t>
   </si>
   <si>
     <t xml:space="preserve">1.4525271654129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51513612270355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72174537181854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200701236725</t>
+    <t xml:space="preserve">1.51513588428497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72174561023712</t>
   </si>
   <si>
     <t xml:space="preserve">1.85863554477692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8051495552063</t>
+    <t xml:space="preserve">1.80514979362488</t>
   </si>
   <si>
     <t xml:space="preserve">1.65806317329407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64469194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61126315593719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63800632953644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61794900894165</t>
+    <t xml:space="preserve">1.64469182491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61126303672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63800621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61794912815094</t>
   </si>
   <si>
     <t xml:space="preserve">1.60457754135132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5711487531662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65137755870819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63132059574127</t>
+    <t xml:space="preserve">1.57114863395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65137779712677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63132035732269</t>
   </si>
   <si>
     <t xml:space="preserve">1.66474914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62463474273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67143499851227</t>
+    <t xml:space="preserve">1.62463462352753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67143476009369</t>
   </si>
   <si>
     <t xml:space="preserve">1.6848064661026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69817757606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59120607376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777740478516</t>
+    <t xml:space="preserve">1.69817817211151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59120619297028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777728557587</t>
   </si>
   <si>
     <t xml:space="preserve">1.52434849739075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51766288280487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5310343503952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54440557956696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55109143257141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53772008419037</t>
+    <t xml:space="preserve">1.51766276359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53103423118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54440581798553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5510915517807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53771984577179</t>
   </si>
   <si>
     <t xml:space="preserve">1.57783448696136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58452022075653</t>
+    <t xml:space="preserve">1.58452033996582</t>
   </si>
   <si>
     <t xml:space="preserve">1.56446290016174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49760556221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5109771490097</t>
+    <t xml:space="preserve">1.49760568141937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51097726821899</t>
   </si>
   <si>
     <t xml:space="preserve">1.59789180755615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50429153442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4909200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48423409461975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4775482416153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47086274623871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417713165283</t>
+    <t xml:space="preserve">1.50429141521454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49092018604279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48423421382904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47754848003387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47086250782013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417689323425</t>
   </si>
   <si>
     <t xml:space="preserve">1.44411993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45080554485321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43074822425842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41737675666809</t>
+    <t xml:space="preserve">1.45080530643463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43074834346771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4173766374588</t>
   </si>
   <si>
     <t xml:space="preserve">1.36389076709747</t>
@@ -788,43 +788,43 @@
     <t xml:space="preserve">1.33714783191681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32377648353577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32043349742889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67812061309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73829245567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77172100543976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75166356563568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74497759342194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73160636425018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7650351524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78509283065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79177796840668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75834941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79846394062042</t>
+    <t xml:space="preserve">1.32377636432648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3204333782196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67812049388885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73829209804535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77172076702118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75166368484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74497783184052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73160696029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76503539085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78509247303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79177832603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75834965705872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.798464179039</t>
   </si>
   <si>
     <t xml:space="preserve">1.82520699501038</t>
@@ -833,181 +833,181 @@
     <t xml:space="preserve">1.85194981098175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86532115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8786928653717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89206397533417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91212129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92549300193787</t>
+    <t xml:space="preserve">1.86532151699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87869250774384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89206421375275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91212105751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92549288272858</t>
   </si>
   <si>
     <t xml:space="preserve">1.89874982833862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83857834339142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90543556213379</t>
+    <t xml:space="preserve">1.83857846260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90543591976166</t>
   </si>
   <si>
     <t xml:space="preserve">1.88537859916687</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91880714893341</t>
+    <t xml:space="preserve">1.91880702972412</t>
   </si>
   <si>
     <t xml:space="preserve">1.96560740470886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99903607368469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99235022068024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01240730285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98566472530365</t>
+    <t xml:space="preserve">1.99903583526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99235045909882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01240754127502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98566496372223</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897899150848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00572156906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02577900886536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03246521949768</t>
+    <t xml:space="preserve">2.00572204589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909327507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02577877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03246450424194</t>
   </si>
   <si>
     <t xml:space="preserve">2.04629111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05320429801941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08085703849792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03937816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0877697467804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06011724472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06703066825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0739438533783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1085090637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12233519554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17072772979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14998817443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1983802318573</t>
+    <t xml:space="preserve">2.05320453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08085656166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03937840461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08777022361755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06011700630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06703019142151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07394361495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10850954055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12233567237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17072749137878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1499879360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19837999343872</t>
   </si>
   <si>
     <t xml:space="preserve">2.20529341697693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19146728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16381454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14307522773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764091491699</t>
+    <t xml:space="preserve">2.19146752357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16381478309631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14307546615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764139175415</t>
   </si>
   <si>
     <t xml:space="preserve">2.18455386161804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15690183639526</t>
+    <t xml:space="preserve">2.15690159797668</t>
   </si>
   <si>
     <t xml:space="preserve">2.22603273391724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21220660209656</t>
+    <t xml:space="preserve">2.21220684051514</t>
   </si>
   <si>
     <t xml:space="preserve">2.23294568061829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23985910415649</t>
+    <t xml:space="preserve">2.23985886573792</t>
   </si>
   <si>
     <t xml:space="preserve">2.25368571281433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2605984210968</t>
+    <t xml:space="preserve">2.26059865951538</t>
   </si>
   <si>
     <t xml:space="preserve">2.26751184463501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27442479133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24677228927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30899024009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32973003387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31590366363525</t>
+    <t xml:space="preserve">2.27442455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2467725276947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30899047851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32973027229309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31590414047241</t>
   </si>
   <si>
     <t xml:space="preserve">2.32281708717346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33664345741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34355640411377</t>
+    <t xml:space="preserve">2.33664298057556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34355616569519</t>
   </si>
   <si>
     <t xml:space="preserve">2.38503527641296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37120914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43342733383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44725322723389</t>
+    <t xml:space="preserve">2.37120890617371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43342709541321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44725346565247</t>
   </si>
   <si>
     <t xml:space="preserve">2.5163848400116</t>
@@ -1019,118 +1019,118 @@
     <t xml:space="preserve">2.49564552307129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56477689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55786371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54403734207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57168984413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5232982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53021121025085</t>
+    <t xml:space="preserve">2.56477737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55786395072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54403710365295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57169032096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52329850196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53021144866943</t>
   </si>
   <si>
     <t xml:space="preserve">2.55095076560974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58551645278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59242963790894</t>
+    <t xml:space="preserve">2.58551669120789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59242939949036</t>
   </si>
   <si>
     <t xml:space="preserve">2.63390851020813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62699508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65464782714844</t>
+    <t xml:space="preserve">2.62699556350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65464758872986</t>
   </si>
   <si>
     <t xml:space="preserve">2.64773440361023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62008237838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64082145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61316919326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66230654716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64100766181946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69780349731445</t>
+    <t xml:space="preserve">2.62008190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64082169532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61316895484924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66230630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64100813865662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69780397415161</t>
   </si>
   <si>
     <t xml:space="preserve">2.74040079116821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79009747505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76879858970642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74750018119812</t>
+    <t xml:space="preserve">2.79009699821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.768798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7475004196167</t>
   </si>
   <si>
     <t xml:space="preserve">2.73330140113831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76169919967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71200275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65520691871643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63390827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68360495567322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62680888175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64810752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67650556564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66940569877625</t>
+    <t xml:space="preserve">2.76169943809509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71200299263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65520715713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63390874862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68360471725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62680912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64810729026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67650532722473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66940593719482</t>
   </si>
   <si>
     <t xml:space="preserve">2.70490336418152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75459980964661</t>
+    <t xml:space="preserve">2.75459957122803</t>
   </si>
   <si>
     <t xml:space="preserve">2.71910190582275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72620177268982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6907045841217</t>
+    <t xml:space="preserve">2.72620153427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69070410728455</t>
   </si>
   <si>
     <t xml:space="preserve">2.56291365623474</t>
@@ -1139,55 +1139,55 @@
     <t xml:space="preserve">2.55581402778625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59841108322144</t>
+    <t xml:space="preserve">2.59841132164001</t>
   </si>
   <si>
     <t xml:space="preserve">2.79719662666321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49191880226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062039375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37832689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25763583183289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17244219779968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21503925323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34282946586609</t>
+    <t xml:space="preserve">2.54871439933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49191904067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062015533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37832736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25763559341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17244172096252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21503901481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34282994270325</t>
   </si>
   <si>
     <t xml:space="preserve">2.34992909431458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48481941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59131169319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47772026062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60551047325134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8113956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82559466362</t>
+    <t xml:space="preserve">2.48481965065002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59131193161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47771978378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60551071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81139540672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82559442520142</t>
   </si>
   <si>
     <t xml:space="preserve">2.88239026069641</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">2.8752908706665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83979368209839</t>
+    <t xml:space="preserve">2.83979344367981</t>
   </si>
   <si>
     <t xml:space="preserve">2.78299784660339</t>
@@ -1211,40 +1211,40 @@
     <t xml:space="preserve">2.90368890762329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8894898891449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81849503517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8326940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8539924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98100256919861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95111775398254</t>
+    <t xml:space="preserve">2.88949012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81849527359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83269381523132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85399270057678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98100280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95111751556396</t>
   </si>
   <si>
     <t xml:space="preserve">2.9735312461853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9436469078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91376209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87640595436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81663632392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83904981613159</t>
+    <t xml:space="preserve">2.94364666938782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91376185417175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87640619277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81663656234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83905005455017</t>
   </si>
   <si>
     <t xml:space="preserve">2.70456862449646</t>
@@ -1253,19 +1253,19 @@
     <t xml:space="preserve">2.59997200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61491441726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60744333267212</t>
+    <t xml:space="preserve">2.61491465568542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6074435710907</t>
   </si>
   <si>
     <t xml:space="preserve">2.62238597869873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65227055549622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62985706329346</t>
+    <t xml:space="preserve">2.65227007865906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62985682487488</t>
   </si>
   <si>
     <t xml:space="preserve">2.65974140167236</t>
@@ -1274,49 +1274,49 @@
     <t xml:space="preserve">2.63732814788818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57008767127991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58502960205078</t>
+    <t xml:space="preserve">2.57008743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58503007888794</t>
   </si>
   <si>
     <t xml:space="preserve">2.57755851745605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5551450252533</t>
+    <t xml:space="preserve">2.55514478683472</t>
   </si>
   <si>
     <t xml:space="preserve">2.52526044845581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59250116348267</t>
+    <t xml:space="preserve">2.59250068664551</t>
   </si>
   <si>
     <t xml:space="preserve">2.54767394065857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50284695625305</t>
+    <t xml:space="preserve">2.50284671783447</t>
   </si>
   <si>
     <t xml:space="preserve">2.47296190261841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45801949501038</t>
+    <t xml:space="preserve">2.45801973342896</t>
   </si>
   <si>
     <t xml:space="preserve">2.49537539482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4654905796051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4879047870636</t>
+    <t xml:space="preserve">2.46549105644226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48790407180786</t>
   </si>
   <si>
     <t xml:space="preserve">2.48043322563171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53273177146912</t>
+    <t xml:space="preserve">2.53273153305054</t>
   </si>
   <si>
     <t xml:space="preserve">2.40572142601013</t>
@@ -1325,37 +1325,37 @@
     <t xml:space="preserve">2.4356062412262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37583684921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3907790184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42813467979431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44307684898376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41319251060486</t>
+    <t xml:space="preserve">2.37583708763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39077877998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42813491821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44307708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41319274902344</t>
   </si>
   <si>
     <t xml:space="preserve">2.39825010299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42066359519958</t>
+    <t xml:space="preserve">2.42066383361816</t>
   </si>
   <si>
     <t xml:space="preserve">2.64479923248291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71951103210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73445320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939560890198</t>
+    <t xml:space="preserve">2.71951127052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7344536781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939584732056</t>
   </si>
   <si>
     <t xml:space="preserve">2.75686693191528</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">2.77928042411804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79422283172607</t>
+    <t xml:space="preserve">2.79422307014465</t>
   </si>
   <si>
     <t xml:space="preserve">2.81757283210754</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">2.84870648384094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84092307090759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80978965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87984013557434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88762307167053</t>
+    <t xml:space="preserve">2.84092330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80978941917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88762331008911</t>
   </si>
   <si>
     <t xml:space="preserve">2.89540648460388</t>
@@ -1400,19 +1400,19 @@
     <t xml:space="preserve">2.80200600624084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83313965797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86427307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85648965835571</t>
+    <t xml:space="preserve">2.8331401348114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86427283287048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85648989677429</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9265398979187</t>
+    <t xml:space="preserve">2.92653965950012</t>
   </si>
   <si>
     <t xml:space="preserve">2.90318965911865</t>
@@ -1421,16 +1421,16 @@
     <t xml:space="preserve">2.98880672454834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01215696334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00437307357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9421067237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97323989868164</t>
+    <t xml:space="preserve">3.01215648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00437331199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94210696220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97323966026306</t>
   </si>
   <si>
     <t xml:space="preserve">2.91097331047058</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">2.94989013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95767307281494</t>
+    <t xml:space="preserve">2.95767331123352</t>
   </si>
   <si>
     <t xml:space="preserve">3.03550672531128</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">2.99659013748169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96545672416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04329037666321</t>
+    <t xml:space="preserve">2.96545648574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04329013824463</t>
   </si>
   <si>
     <t xml:space="preserve">3.05107355117798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01994013786316</t>
+    <t xml:space="preserve">3.01994037628174</t>
   </si>
   <si>
     <t xml:space="preserve">3.07442355155945</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">3.02772355079651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98102355003357</t>
+    <t xml:space="preserve">2.98102331161499</t>
   </si>
   <si>
     <t xml:space="preserve">3.16004037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08999037742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08220720291138</t>
+    <t xml:space="preserve">3.08998990058899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08220672607422</t>
   </si>
   <si>
     <t xml:space="preserve">3.06664037704468</t>
@@ -1484,19 +1484,19 @@
     <t xml:space="preserve">3.05885720252991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09777355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11416411399841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13055419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10596871376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06499266624451</t>
+    <t xml:space="preserve">3.0977737903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11416387557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13055396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10596895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06499290466309</t>
   </si>
   <si>
     <t xml:space="preserve">3.07318806648254</t>
@@ -1505,46 +1505,46 @@
     <t xml:space="preserve">3.08957839012146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04040741920471</t>
+    <t xml:space="preserve">3.04040765762329</t>
   </si>
   <si>
     <t xml:space="preserve">3.03221225738525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04860234260559</t>
+    <t xml:space="preserve">3.04860258102417</t>
   </si>
   <si>
     <t xml:space="preserve">3.05679750442505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01582193374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02401685714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00762701034546</t>
+    <t xml:space="preserve">3.01582169532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0240170955658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00762677192688</t>
   </si>
   <si>
     <t xml:space="preserve">3.081383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99943137168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99123644828796</t>
+    <t xml:space="preserve">2.999431848526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99123668670654</t>
   </si>
   <si>
     <t xml:space="preserve">2.97484588623047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96665072441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95845580101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98304128646851</t>
+    <t xml:space="preserve">2.96665048599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95845556259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98304152488708</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026040077209</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">2.90108942985535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92567467689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94206523895264</t>
+    <t xml:space="preserve">2.9256751537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94206547737122</t>
   </si>
   <si>
     <t xml:space="preserve">2.87650418281555</t>
@@ -1571,43 +1571,43 @@
     <t xml:space="preserve">2.81094264984131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83552813529968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79455256462097</t>
+    <t xml:space="preserve">2.83552837371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79455232620239</t>
   </si>
   <si>
     <t xml:space="preserve">2.78635716438293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80274772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76177144050598</t>
+    <t xml:space="preserve">2.80274724960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76177167892456</t>
   </si>
   <si>
     <t xml:space="preserve">2.84372329711914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86011385917664</t>
+    <t xml:space="preserve">2.86011362075806</t>
   </si>
   <si>
     <t xml:space="preserve">2.81913805007935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90928483009338</t>
+    <t xml:space="preserve">2.9092845916748</t>
   </si>
   <si>
     <t xml:space="preserve">2.8519184589386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88469934463501</t>
+    <t xml:space="preserve">2.88469910621643</t>
   </si>
   <si>
     <t xml:space="preserve">2.89289426803589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91747975349426</t>
+    <t xml:space="preserve">2.91747999191284</t>
   </si>
   <si>
     <t xml:space="preserve">3.00797700881958</t>
@@ -1616,16 +1616,16 @@
     <t xml:space="preserve">3.04215860366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01652264595032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03361320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05070376396179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05924916267395</t>
+    <t xml:space="preserve">3.01652240753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03361296653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05070400238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05924940109253</t>
   </si>
   <si>
     <t xml:space="preserve">3.07633996009827</t>
@@ -1637,28 +1637,28 @@
     <t xml:space="preserve">3.12761259078979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14470338821411</t>
+    <t xml:space="preserve">3.14470314979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.16179394721985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15324831008911</t>
+    <t xml:space="preserve">3.15324854850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.17033958435059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1105215549469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.084885597229</t>
+    <t xml:space="preserve">3.11052203178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08488535881042</t>
   </si>
   <si>
     <t xml:space="preserve">3.10197639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09343075752258</t>
+    <t xml:space="preserve">3.093430519104</t>
   </si>
   <si>
     <t xml:space="preserve">3.13615775108337</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">3.18743014335632</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19597578048706</t>
+    <t xml:space="preserve">3.19597554206848</t>
   </si>
   <si>
     <t xml:space="preserve">3.2130663394928</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">3.34979271888733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30706572532654</t>
+    <t xml:space="preserve">3.30706548690796</t>
   </si>
   <si>
     <t xml:space="preserve">3.35833811759949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36688327789307</t>
+    <t xml:space="preserve">3.36688351631165</t>
   </si>
   <si>
     <t xml:space="preserve">3.33270168304443</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">3.31561088562012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28997468948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2985200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38397407531738</t>
+    <t xml:space="preserve">3.28997492790222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29852032661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3839738368988</t>
   </si>
   <si>
     <t xml:space="preserve">3.32415652275085</t>
@@ -1730,16 +1730,16 @@
     <t xml:space="preserve">3.40961050987244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45233726501465</t>
+    <t xml:space="preserve">3.45233702659607</t>
   </si>
   <si>
     <t xml:space="preserve">3.44379186630249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46942782402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5036096572876</t>
+    <t xml:space="preserve">3.46942806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50360941886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.57197260856628</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">3.52070021629333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51215505599976</t>
+    <t xml:space="preserve">3.51215481758118</t>
   </si>
   <si>
     <t xml:space="preserve">3.46088290214539</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">3.49550485610962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51347661018372</t>
+    <t xml:space="preserve">3.51347637176514</t>
   </si>
   <si>
     <t xml:space="preserve">3.48651885986328</t>
@@ -1772,10 +1772,10 @@
     <t xml:space="preserve">3.59434938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53144836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43260335922241</t>
+    <t xml:space="preserve">3.53144812583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43260359764099</t>
   </si>
   <si>
     <t xml:space="preserve">3.46854710578918</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">3.47753310203552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45057559013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3786883354187</t>
+    <t xml:space="preserve">3.45057535171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37868857383728</t>
   </si>
   <si>
     <t xml:space="preserve">3.34274482727051</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">3.45956110954285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55840587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54941987991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54043412208557</t>
+    <t xml:space="preserve">3.55840563774109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54942011833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54043436050415</t>
   </si>
   <si>
     <t xml:space="preserve">3.36071681976318</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">3.5853636264801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62130689620972</t>
+    <t xml:space="preserve">3.6213071346283</t>
   </si>
   <si>
     <t xml:space="preserve">3.69319415092468</t>
@@ -1838,19 +1838,19 @@
     <t xml:space="preserve">3.56739187240601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68420815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7111656665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7291374206543</t>
+    <t xml:space="preserve">3.68420791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71116590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72913765907288</t>
   </si>
   <si>
     <t xml:space="preserve">3.74710917472839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67522215843201</t>
+    <t xml:space="preserve">3.67522239685059</t>
   </si>
   <si>
     <t xml:space="preserve">3.72015142440796</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">3.75609493255615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81899619102478</t>
+    <t xml:space="preserve">3.8189959526062</t>
   </si>
   <si>
     <t xml:space="preserve">3.81001019477844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80102467536926</t>
+    <t xml:space="preserve">3.80102443695068</t>
   </si>
   <si>
     <t xml:space="preserve">3.78305292129517</t>
@@ -1880,25 +1880,25 @@
     <t xml:space="preserve">3.84595394134521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82798218727112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76508069038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73812294006348</t>
+    <t xml:space="preserve">3.8279824256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76508092880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73812317848206</t>
   </si>
   <si>
     <t xml:space="preserve">3.73778820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77507305145264</t>
+    <t xml:space="preserve">3.77507281303406</t>
   </si>
   <si>
     <t xml:space="preserve">3.71914577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68186092376709</t>
+    <t xml:space="preserve">3.68186116218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.66321873664856</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">3.69118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75643038749695</t>
+    <t xml:space="preserve">3.75643062591553</t>
   </si>
   <si>
     <t xml:space="preserve">3.7657516002655</t>
@@ -1922,34 +1922,34 @@
     <t xml:space="preserve">3.93353247642517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80303597450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88692665100098</t>
+    <t xml:space="preserve">3.80303621292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88692688941956</t>
   </si>
   <si>
     <t xml:space="preserve">3.84032082557678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8123574256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82167863845825</t>
+    <t xml:space="preserve">3.81235766410828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82167840003967</t>
   </si>
   <si>
     <t xml:space="preserve">3.83099985122681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87760519981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90556883811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91489028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96149611473083</t>
+    <t xml:space="preserve">3.87760543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90556907653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91488981246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96149587631226</t>
   </si>
   <si>
     <t xml:space="preserve">4.00810194015503</t>
@@ -1961,13 +1961,13 @@
     <t xml:space="preserve">4.04538679122925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01742267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03606557846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98013830184937</t>
+    <t xml:space="preserve">4.01742315292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03606510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98013854026794</t>
   </si>
   <si>
     <t xml:space="preserve">4.07334995269775</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">4.09199237823486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11063432693481</t>
+    <t xml:space="preserve">4.11063480377197</t>
   </si>
   <si>
     <t xml:space="preserve">4.1758828163147</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">3.9894597530365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9428539276123</t>
+    <t xml:space="preserve">3.94285368919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.9521746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97081732749939</t>
+    <t xml:space="preserve">3.97081756591797</t>
   </si>
   <si>
     <t xml:space="preserve">4.06402921676636</t>
@@ -2009,16 +2009,16 @@
     <t xml:space="preserve">4.11995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70050358772278</t>
+    <t xml:space="preserve">3.7005033493042</t>
   </si>
   <si>
     <t xml:space="preserve">3.68652153015137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90090847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92887210845947</t>
+    <t xml:space="preserve">3.90090823173523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92887234687805</t>
   </si>
   <si>
     <t xml:space="preserve">3.9242115020752</t>
@@ -2313,6 +2313,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.6399998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73000001907349</t>
   </si>
 </sst>
 </file>
@@ -6465,7 +6468,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G147" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6517,7 +6520,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G149" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6673,7 +6676,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G155" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6699,7 +6702,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G156" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6751,7 +6754,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G158" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6777,7 +6780,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G159" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -6959,7 +6962,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G166" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7011,7 +7014,7 @@
         <v>3.25</v>
       </c>
       <c r="G168" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7037,7 +7040,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G169" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7193,7 +7196,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G175" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7219,7 +7222,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G176" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7271,7 +7274,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G178" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7297,7 +7300,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G179" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7323,7 +7326,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G180" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7349,7 +7352,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G181" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7375,7 +7378,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G182" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7401,7 +7404,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G183" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7427,7 +7430,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G184" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7479,7 +7482,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G186" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7505,7 +7508,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G187" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7531,7 +7534,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G188" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7557,7 +7560,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G189" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7583,7 +7586,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G190" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7635,7 +7638,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G192" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7791,7 +7794,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G198" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7895,7 +7898,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G202" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7921,7 +7924,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G203" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -7973,7 +7976,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G205" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8025,7 +8028,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G207" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8051,7 +8054,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G208" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8077,7 +8080,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G209" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8103,7 +8106,7 @@
         <v>3.25</v>
       </c>
       <c r="G210" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8155,7 +8158,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G212" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8181,7 +8184,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G213" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8207,7 +8210,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G214" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8233,7 +8236,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G215" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8259,7 +8262,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G216" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8285,7 +8288,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G217" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8311,7 +8314,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G218" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8337,7 +8340,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G219" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8363,7 +8366,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G220" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8389,7 +8392,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G221" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8415,7 +8418,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8441,7 +8444,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G223" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8467,7 +8470,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8493,7 +8496,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G225" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8519,7 +8522,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G226" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8545,7 +8548,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G227" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8571,7 +8574,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G228" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8597,7 +8600,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G229" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8623,7 +8626,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G230" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8649,7 +8652,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G231" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8675,7 +8678,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8701,7 +8704,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G233" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8727,7 +8730,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G234" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8753,7 +8756,7 @@
         <v>3.25</v>
       </c>
       <c r="G235" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8779,7 +8782,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8805,7 +8808,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G237" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8831,7 +8834,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G238" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8857,7 +8860,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G239" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8883,7 +8886,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G240" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8909,7 +8912,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G241" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -8935,7 +8938,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G242" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -8961,7 +8964,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G243" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -8987,7 +8990,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G244" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9013,7 +9016,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G245" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9039,7 +9042,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G246" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9065,7 +9068,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G247" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9091,7 +9094,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G248" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9117,7 +9120,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G249" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9143,7 +9146,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G250" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9169,7 +9172,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G251" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9195,7 +9198,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G252" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9221,7 +9224,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G253" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9247,7 +9250,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G254" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9273,7 +9276,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9299,7 +9302,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G256" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9325,7 +9328,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G257" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9351,7 +9354,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G258" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9377,7 +9380,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G259" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9403,7 +9406,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G260" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9429,7 +9432,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G261" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9455,7 +9458,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G262" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9481,7 +9484,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9507,7 +9510,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9533,7 +9536,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G265" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9559,7 +9562,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G266" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9585,7 +9588,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9611,7 +9614,7 @@
         <v>3.25</v>
       </c>
       <c r="G268" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9637,7 +9640,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G269" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9663,7 +9666,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G270" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9689,7 +9692,7 @@
         <v>3.25</v>
       </c>
       <c r="G271" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9715,7 +9718,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9741,7 +9744,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9819,7 +9822,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G276" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9845,7 +9848,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G277" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10001,7 +10004,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G283" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10339,7 +10342,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G296" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10365,7 +10368,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G297" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10391,7 +10394,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G298" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10521,7 +10524,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G303" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10573,7 +10576,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G305" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10651,7 +10654,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G308" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10703,7 +10706,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G310" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10729,7 +10732,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10781,7 +10784,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G313" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10833,7 +10836,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G315" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10859,7 +10862,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G316" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10885,7 +10888,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G317" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10911,7 +10914,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G318" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11041,7 +11044,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G323" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11067,7 +11070,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G324" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11093,7 +11096,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G325" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11119,7 +11122,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G326" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11171,7 +11174,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G328" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11223,7 +11226,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G330" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11249,7 +11252,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11301,7 +11304,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11327,7 +11330,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11353,7 +11356,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G335" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11379,7 +11382,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G336" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11431,7 +11434,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G338" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11457,7 +11460,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G339" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11509,7 +11512,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G341" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11561,7 +11564,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G343" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11665,7 +11668,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G347" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11717,7 +11720,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G349" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11769,7 +11772,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G351" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -11795,7 +11798,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G352" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11821,7 +11824,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G353" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11847,7 +11850,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G354" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -11873,7 +11876,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G355" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11925,7 +11928,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G357" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -11951,7 +11954,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G358" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12003,7 +12006,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G360" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12029,7 +12032,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G361" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12081,7 +12084,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G363" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12107,7 +12110,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G364" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12133,7 +12136,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G365" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12159,7 +12162,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12185,7 +12188,7 @@
         <v>3</v>
       </c>
       <c r="G367" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12211,7 +12214,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G368" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12237,7 +12240,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G369" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12263,7 +12266,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G370" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12289,7 +12292,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G371" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12315,7 +12318,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G372" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12341,7 +12344,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G373" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12367,7 +12370,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G374" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12393,7 +12396,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G375" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12419,7 +12422,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12445,7 +12448,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G377" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12471,7 +12474,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G378" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12497,7 +12500,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G379" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12523,7 +12526,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G380" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12549,7 +12552,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G381" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12575,7 +12578,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G382" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12601,7 +12604,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G383" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12627,7 +12630,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G384" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12653,7 +12656,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G385" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12679,7 +12682,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G386" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12705,7 +12708,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G387" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12731,7 +12734,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G388" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12757,7 +12760,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G389" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12783,7 +12786,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G390" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12809,7 +12812,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G391" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12835,7 +12838,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12861,7 +12864,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G393" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12887,7 +12890,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G394" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12913,7 +12916,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G395" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -12939,7 +12942,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G396" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -12965,7 +12968,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G397" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -12991,7 +12994,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G398" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13017,7 +13020,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G399" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13043,7 +13046,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G400" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13069,7 +13072,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G401" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13095,7 +13098,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G402" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13121,7 +13124,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G403" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13147,7 +13150,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G404" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13173,7 +13176,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G405" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13199,7 +13202,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G406" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13225,7 +13228,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G407" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13251,7 +13254,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G408" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13277,7 +13280,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13303,7 +13306,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G410" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13329,7 +13332,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G411" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13355,7 +13358,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G412" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13381,7 +13384,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G413" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13407,7 +13410,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G414" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13433,7 +13436,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G415" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13459,7 +13462,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G416" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13485,7 +13488,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G417" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13511,7 +13514,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G418" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13537,7 +13540,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G419" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13563,7 +13566,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G420" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13589,7 +13592,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G421" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13615,7 +13618,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G422" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13641,7 +13644,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G423" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13667,7 +13670,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G424" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13693,7 +13696,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13719,7 +13722,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G426" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13745,7 +13748,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G427" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13771,7 +13774,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G428" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13797,7 +13800,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G429" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13823,7 +13826,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G430" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13849,7 +13852,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G431" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13875,7 +13878,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G432" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13901,7 +13904,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G433" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -13927,7 +13930,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G434" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -13953,7 +13956,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G435" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -13979,7 +13982,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G436" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14005,7 +14008,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G437" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14031,7 +14034,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G438" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14057,7 +14060,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G439" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14083,7 +14086,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G440" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14109,7 +14112,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G441" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14135,7 +14138,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G442" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14161,7 +14164,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G443" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14187,7 +14190,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G444" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14213,7 +14216,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G445" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14239,7 +14242,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G446" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14265,7 +14268,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G447" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14291,7 +14294,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G448" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14317,7 +14320,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G449" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14343,7 +14346,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G450" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14369,7 +14372,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G451" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14395,7 +14398,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G452" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14421,7 +14424,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G453" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14447,7 +14450,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G454" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14473,7 +14476,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G455" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14499,7 +14502,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G456" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14525,7 +14528,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14551,7 +14554,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G458" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14577,7 +14580,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G459" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14603,7 +14606,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G460" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14629,7 +14632,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G461" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14655,7 +14658,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G462" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14681,7 +14684,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G463" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14707,7 +14710,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G464" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14733,7 +14736,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G465" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14759,7 +14762,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G466" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14785,7 +14788,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G467" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14811,7 +14814,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G468" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14837,7 +14840,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G469" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14863,7 +14866,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G470" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14889,7 +14892,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G471" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14915,7 +14918,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G472" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -14941,7 +14944,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G473" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -14967,7 +14970,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -14993,7 +14996,7 @@
         <v>2.5</v>
       </c>
       <c r="G475" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15019,7 +15022,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G476" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15045,7 +15048,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G477" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15071,7 +15074,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G478" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15097,7 +15100,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G479" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15123,7 +15126,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G480" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15149,7 +15152,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G481" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15175,7 +15178,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G482" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15201,7 +15204,7 @@
         <v>2.5</v>
       </c>
       <c r="G483" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15227,7 +15230,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G484" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15253,7 +15256,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15279,7 +15282,7 @@
         <v>2.5</v>
       </c>
       <c r="G486" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15305,7 +15308,7 @@
         <v>2.5</v>
       </c>
       <c r="G487" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15331,7 +15334,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G488" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15357,7 +15360,7 @@
         <v>2.5</v>
       </c>
       <c r="G489" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15383,7 +15386,7 @@
         <v>2.5</v>
       </c>
       <c r="G490" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15409,7 +15412,7 @@
         <v>2.5</v>
       </c>
       <c r="G491" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15435,7 +15438,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G492" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15461,7 +15464,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G493" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15487,7 +15490,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G494" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15513,7 +15516,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G495" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15539,7 +15542,7 @@
         <v>2.5</v>
       </c>
       <c r="G496" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15565,7 +15568,7 @@
         <v>2.5</v>
       </c>
       <c r="G497" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15591,7 +15594,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G498" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15617,7 +15620,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G499" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15643,7 +15646,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G500" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15669,7 +15672,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G501" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15695,7 +15698,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G502" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15721,7 +15724,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G503" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15747,7 +15750,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G504" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15773,7 +15776,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G505" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15799,7 +15802,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G506" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15825,7 +15828,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G507" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15851,7 +15854,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G508" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15877,7 +15880,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G509" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15903,7 +15906,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G510" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -15929,7 +15932,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G511" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -15955,7 +15958,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -15981,7 +15984,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G513" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16007,7 +16010,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G514" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16033,7 +16036,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16059,7 +16062,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G516" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16085,7 +16088,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G517" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16111,7 +16114,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G518" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16137,7 +16140,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16163,7 +16166,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G520" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16189,7 +16192,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G521" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16215,7 +16218,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G522" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16241,7 +16244,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G523" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16267,7 +16270,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G524" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16293,7 +16296,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G525" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16319,7 +16322,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G526" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16345,7 +16348,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G527" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16371,7 +16374,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16397,7 +16400,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G529" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16423,7 +16426,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G530" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16449,7 +16452,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G531" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16475,7 +16478,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G532" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16501,7 +16504,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G533" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16527,7 +16530,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G534" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16553,7 +16556,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G535" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16579,7 +16582,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G536" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16605,7 +16608,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G537" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16631,7 +16634,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16657,7 +16660,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16683,7 +16686,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G540" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16709,7 +16712,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G541" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16735,7 +16738,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G542" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16761,7 +16764,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G543" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16787,7 +16790,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G544" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16813,7 +16816,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G545" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16839,7 +16842,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G546" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16865,7 +16868,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G547" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16891,7 +16894,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G548" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16917,7 +16920,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G549" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -16943,7 +16946,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G550" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -16969,7 +16972,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G551" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -16995,7 +16998,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G552" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17021,7 +17024,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G553" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17047,7 +17050,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G554" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17073,7 +17076,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G555" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17099,7 +17102,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G556" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17125,7 +17128,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G557" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17151,7 +17154,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G558" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17177,7 +17180,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G559" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17203,7 +17206,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G560" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17229,7 +17232,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G561" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17255,7 +17258,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G562" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17281,7 +17284,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G563" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17307,7 +17310,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G564" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17333,7 +17336,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G565" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17359,7 +17362,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G566" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17385,7 +17388,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G567" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17411,7 +17414,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G568" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17437,7 +17440,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G569" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17463,7 +17466,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G570" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17489,7 +17492,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G571" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17515,7 +17518,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G572" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17541,7 +17544,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G573" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17567,7 +17570,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G574" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17593,7 +17596,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G575" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17619,7 +17622,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G576" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17645,7 +17648,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G577" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17671,7 +17674,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G578" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17697,7 +17700,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G579" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17723,7 +17726,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G580" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17749,7 +17752,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17775,7 +17778,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G582" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17801,7 +17804,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G583" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17827,7 +17830,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G584" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17853,7 +17856,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G585" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17879,7 +17882,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G586" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17905,7 +17908,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G587" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -17931,7 +17934,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G588" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -17957,7 +17960,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G589" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -17983,7 +17986,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G590" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18009,7 +18012,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G591" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18035,7 +18038,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G592" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18061,7 +18064,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G593" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18087,7 +18090,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G594" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18113,7 +18116,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G595" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18139,7 +18142,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G596" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18165,7 +18168,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G597" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18191,7 +18194,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G598" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18217,7 +18220,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G599" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18243,7 +18246,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G600" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18269,7 +18272,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G601" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18295,7 +18298,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G602" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18321,7 +18324,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18347,7 +18350,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G604" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18373,7 +18376,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G605" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18399,7 +18402,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G606" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18425,7 +18428,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18451,7 +18454,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G608" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18477,7 +18480,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G609" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18503,7 +18506,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G610" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18529,7 +18532,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G611" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18555,7 +18558,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G612" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18581,7 +18584,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18607,7 +18610,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G614" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18633,7 +18636,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G615" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18659,7 +18662,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G616" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18685,7 +18688,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G617" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18711,7 +18714,7 @@
         <v>2.25</v>
       </c>
       <c r="G618" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18737,7 +18740,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G619" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18763,7 +18766,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G620" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18789,7 +18792,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G621" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18815,7 +18818,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G622" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18841,7 +18844,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18867,7 +18870,7 @@
         <v>2.25</v>
       </c>
       <c r="G624" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18893,7 +18896,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18919,7 +18922,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -18945,7 +18948,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G627" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -18971,7 +18974,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G628" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -18997,7 +19000,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G629" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19023,7 +19026,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G630" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19049,7 +19052,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G631" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19075,7 +19078,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19101,7 +19104,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G633" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19127,7 +19130,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G634" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19153,7 +19156,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G635" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19179,7 +19182,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19205,7 +19208,7 @@
         <v>2.75</v>
       </c>
       <c r="G637" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19231,7 +19234,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G638" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19257,7 +19260,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G639" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -23989,7 +23992,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G821" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24041,7 +24044,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G823" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24067,7 +24070,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G824" t="s">
-        <v>213</v>
+        <v>70</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -55457,7 +55460,7 @@
     </row>
     <row r="2032">
       <c r="A2032" s="1" t="n">
-        <v>45982.6910185185</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2032" t="n">
         <v>184459</v>
@@ -55478,6 +55481,32 @@
         <v>766</v>
       </c>
       <c r="H2032" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" s="1" t="n">
+        <v>45985.6911111111</v>
+      </c>
+      <c r="B2033" t="n">
+        <v>102466</v>
+      </c>
+      <c r="C2033" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="D2033" t="n">
+        <v>5.61999988555908</v>
+      </c>
+      <c r="E2033" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F2033" t="n">
+        <v>5.73000001907349</v>
+      </c>
+      <c r="G2033" t="s">
+        <v>767</v>
+      </c>
+      <c r="H2033" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="770">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61930739879608</t>
+    <t xml:space="preserve">1.6193071603775</t>
   </si>
   <si>
     <t xml:space="preserve">EQUI.MI</t>
@@ -47,475 +47,475 @@
     <t xml:space="preserve">1.6869148015976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71744751930237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71417570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71090447902679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70109033584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67055785655975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491984367371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69018626213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67710065841675</t>
+    <t xml:space="preserve">1.7174471616745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71417558193207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71090471744537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70109045505524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67055821418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491972446442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69018650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67710101604462</t>
   </si>
   <si>
     <t xml:space="preserve">1.65856337547302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65747272968292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65529191493988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784468173981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64656853675842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311133861542</t>
+    <t xml:space="preserve">1.6574729681015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65529227256775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784503936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64656865596771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311110019684</t>
   </si>
   <si>
     <t xml:space="preserve">1.65420138835907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64874947071075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65965378284454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64002573490143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64329695701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62585020065308</t>
+    <t xml:space="preserve">1.64874935150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65965366363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64002549648285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6432968378067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6258499622345</t>
   </si>
   <si>
     <t xml:space="preserve">1.64765894412994</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67382943630219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68909585475922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67928159236908</t>
+    <t xml:space="preserve">1.67382955551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68909573554993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67928183078766</t>
   </si>
   <si>
     <t xml:space="preserve">1.67819130420685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67164850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67273879051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70327162742615</t>
+    <t xml:space="preserve">1.67164874076843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67273902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70327138900757</t>
   </si>
   <si>
     <t xml:space="preserve">1.70654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69563806056976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66565108299255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66837692260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69836437702179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70381689071655</t>
+    <t xml:space="preserve">1.69563817977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66565120220184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66837728023529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6983642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70381665229797</t>
   </si>
   <si>
     <t xml:space="preserve">1.687460064888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68473374843597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67110323905945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016021728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72289931774139</t>
+    <t xml:space="preserve">1.68473362922668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67110335826874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016045570374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72289943695068</t>
   </si>
   <si>
     <t xml:space="preserve">1.72835159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74470841884613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73107767105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73925590515137</t>
+    <t xml:space="preserve">1.74470806121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73107779026031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73925578594208</t>
   </si>
   <si>
     <t xml:space="preserve">1.7419821023941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79923021793365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77742159366608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7719691991806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7365300655365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7965042591095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78832578659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81831347942352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82376539707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80468273162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8155871629715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81286108493805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81013453006744</t>
+    <t xml:space="preserve">1.79923033714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77742147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77196907997131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73652970790863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79650473594666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78832602500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81831300258636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82376527786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80468249320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81558692455292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81286072731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81013488769531</t>
   </si>
   <si>
     <t xml:space="preserve">1.79377818107605</t>
   </si>
   <si>
+    <t xml:space="preserve">1.84284842014313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88950228691101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200701236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88075494766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84576404094696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81952059268951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83118462562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86034333705902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87492287158966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87783885002136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86325919628143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88367056846619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80785691738129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76703476905823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79619383811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79910981655121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161442279816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82243680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78453016281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81660497188568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83410048484802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83701646327972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84867966175079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86909115314484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8515956401825</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.84284818172455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8895024061203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200701236725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88075482845306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84576380252838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81952083110809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83118450641632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86034333705902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87492263317108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87783873081207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86325919628143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88367092609406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80785763263702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76703488826752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79619348049164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79910957813263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161418437958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82243692874908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78452980518341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81660497188568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83410036563873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8370167016983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84867990016937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86909091472626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85159587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84284794330597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85742747783661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282975673676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89241826534271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88658666610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89533448219299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83993208408356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85451185703278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617541313171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81077289581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89824998378754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91574537754059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95365226268768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96239972114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9244931936264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9653160572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00613832473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905394554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98281121253967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95948421955109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92740905284882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90991389751434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95656824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01197004318237</t>
+    <t xml:space="preserve">1.8574275970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282951831818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89241850376129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8865864276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89533412456512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83993232250214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85451173782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617529392242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81077301502228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89825022220612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91574573516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95365250110626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96239984035492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92449331283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96531593799591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00613856315613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905418395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98281109333038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95948398113251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92740917205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90991401672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9565681219101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01197052001953</t>
   </si>
   <si>
     <t xml:space="preserve">2.00030660629272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94782042503357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90699768066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92157733440399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07903599739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06737208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98864316940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99447476863861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97406363487244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93907260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93032479286194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198870658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90408194065094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8253527879715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8136887550354</t>
+    <t xml:space="preserve">1.94490468502045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94782030582428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90699779987335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9215772151947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07903623580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0673725605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98864281177521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99447500705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97406351566315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93907272815704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93032503128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198858737946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90408205986023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82535290718079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81368899345398</t>
   </si>
   <si>
     <t xml:space="preserve">1.79036200046539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82826840877533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02852940559387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90331149101257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89705061912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89078962802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87826824188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82191967964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79061508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78435456752777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75931072235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74678945541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73426759243011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72800636291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65287590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69044125080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64661490917206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60904955863953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62783217430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66539716720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63409292697906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67165851593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62157166004181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60278856754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68418049812317</t>
+    <t xml:space="preserve">1.8282687664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02852916717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9033111333847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89705097675323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89078950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87826812267303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8219199180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79061543941498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7843542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75931107997894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74678897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73426723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72800648212433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65287578105927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69044101238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64661502838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60904967784882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62783229351044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66539764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791962623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63409316539764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6716582775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62157130241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60278832912445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68418025970459</t>
   </si>
   <si>
     <t xml:space="preserve">1.70296287536621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69670176506042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70922386646271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71548497676849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65913665294647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64035391807556</t>
+    <t xml:space="preserve">1.696702003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70922350883484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71548461914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65913677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64035379886627</t>
   </si>
   <si>
     <t xml:space="preserve">1.61531043052673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59652757644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57148408889771</t>
+    <t xml:space="preserve">1.59652769565582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57148420810699</t>
   </si>
   <si>
     <t xml:space="preserve">1.5652232170105</t>
@@ -524,46 +524,46 @@
     <t xml:space="preserve">1.55896246433258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57774496078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55270147323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58400571346283</t>
+    <t xml:space="preserve">1.57774519920349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55270171165466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58400595188141</t>
   </si>
   <si>
     <t xml:space="preserve">1.77183258533478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81565916538239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8093980550766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80313730239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77809381484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74052846431732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76557183265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75305008888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59026718139648</t>
+    <t xml:space="preserve">1.8156590461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80939793586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80313694477081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77809357643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74052834510803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76557147502899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75305020809174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59026670455933</t>
   </si>
   <si>
     <t xml:space="preserve">1.47757077217102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36487483978271</t>
+    <t xml:space="preserve">1.36487460136414</t>
   </si>
   <si>
     <t xml:space="preserve">1.54644060134888</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">1.38365733623505</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40243995189667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32104825973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30226564407349</t>
+    <t xml:space="preserve">1.40243983268738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32104849815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30226576328278</t>
   </si>
   <si>
     <t xml:space="preserve">1.3273092508316</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">1.33357036113739</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28348290920258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29600501060486</t>
+    <t xml:space="preserve">1.28348314762115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29600477218628</t>
   </si>
   <si>
     <t xml:space="preserve">1.28974390029907</t>
@@ -605,109 +605,109 @@
     <t xml:space="preserve">1.3523530960083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31478726863861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609186649323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43374443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38991820812225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39617943763733</t>
+    <t xml:space="preserve">1.31478750705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609198570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43374454975128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38991832733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39617919921875</t>
   </si>
   <si>
     <t xml:space="preserve">1.45878791809082</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42122280597687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37739634513855</t>
+    <t xml:space="preserve">1.42122268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37739658355713</t>
   </si>
   <si>
     <t xml:space="preserve">1.41496193408966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44000518321991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4274834394455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391861915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40870070457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4525271654129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51513588428497</t>
+    <t xml:space="preserve">1.44000542163849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4462662935257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42748367786407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391909599304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40870094299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45252704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51513624191284</t>
   </si>
   <si>
     <t xml:space="preserve">1.72174561023712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85863554477692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80514979362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65806317329407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64469182491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61126303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63800621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61794912815094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457754135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57114863395691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65137779712677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63132035732269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66474914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62463462352753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67143476009369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6848064661026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69817817211151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59120619297028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777728557587</t>
+    <t xml:space="preserve">1.8586357831955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80514967441559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65806353092194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64469194412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61126327514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63800632953644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61794900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457742214203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57114851474762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65137767791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63132047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66474902629852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62463474273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67143499851227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68480622768402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69817781448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5912059545517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777716636658</t>
   </si>
   <si>
     <t xml:space="preserve">1.52434849739075</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">1.51766276359558</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53103423118591</t>
+    <t xml:space="preserve">1.53103411197662</t>
   </si>
   <si>
     <t xml:space="preserve">1.54440581798553</t>
@@ -725,172 +725,172 @@
     <t xml:space="preserve">1.5510915517807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53771984577179</t>
+    <t xml:space="preserve">1.53772008419037</t>
   </si>
   <si>
     <t xml:space="preserve">1.57783448696136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58452033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56446290016174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49760568141937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51097726821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59789180755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50429141521454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49092018604279</t>
+    <t xml:space="preserve">1.58451998233795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56446301937103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49760556221008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5109771490097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59789168834686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50429129600525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49091994762421</t>
   </si>
   <si>
     <t xml:space="preserve">1.48423421382904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47754848003387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47086250782013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417689323425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44411993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45080530643463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43074834346771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4173766374588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36389076709747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33046209812164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34383356571198</t>
+    <t xml:space="preserve">1.47754859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.470862865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417701244354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44411981105804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45080542564392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43074822425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41737675666809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36389088630676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33046221733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34383368492126</t>
   </si>
   <si>
     <t xml:space="preserve">1.33714783191681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32377636432648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3204333782196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67812049388885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73829209804535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77172076702118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75166368484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74497783184052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73160696029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76503539085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78509247303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79177832603455</t>
+    <t xml:space="preserve">1.32377648353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32043361663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67812073230743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73829233646393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77172124385834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75166344642639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74497771263123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73160624504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76503503322601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78509223461151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79177856445312</t>
   </si>
   <si>
     <t xml:space="preserve">1.75834965705872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.798464179039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520699501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85194981098175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86532151699066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87869250774384</t>
+    <t xml:space="preserve">1.79846394062042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8252067565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85194993019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8653210401535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8786928653717</t>
   </si>
   <si>
     <t xml:space="preserve">1.89206421375275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91212105751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92549288272858</t>
+    <t xml:space="preserve">1.91212141513824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92549276351929</t>
   </si>
   <si>
     <t xml:space="preserve">1.89874982833862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83857846260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90543591976166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88537859916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91880702972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96560740470886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99903583526611</t>
+    <t xml:space="preserve">1.83857822418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90543556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.885378241539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91880691051483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96560764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99903619289398</t>
   </si>
   <si>
     <t xml:space="preserve">1.99235045909882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01240754127502</t>
+    <t xml:space="preserve">2.0124077796936</t>
   </si>
   <si>
     <t xml:space="preserve">1.98566496372223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97897899150848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00572204589844</t>
+    <t xml:space="preserve">1.97897887229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00572180747986</t>
   </si>
   <si>
     <t xml:space="preserve">2.01909327507019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02577877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03246450424194</t>
+    <t xml:space="preserve">2.02577924728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03246474266052</t>
   </si>
   <si>
     <t xml:space="preserve">2.04629111289978</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">2.05320453643799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08085656166077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03937840461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08777022361755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06011700630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06703019142151</t>
+    <t xml:space="preserve">2.08085703849792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03937816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08776998519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06011748313904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06703066825867</t>
   </si>
   <si>
     <t xml:space="preserve">2.07394361495972</t>
@@ -923,28 +923,28 @@
     <t xml:space="preserve">2.12233567237854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17072749137878</t>
+    <t xml:space="preserve">2.17072772979736</t>
   </si>
   <si>
     <t xml:space="preserve">2.1499879360199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19837999343872</t>
+    <t xml:space="preserve">2.1983802318573</t>
   </si>
   <si>
     <t xml:space="preserve">2.20529341697693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19146752357483</t>
+    <t xml:space="preserve">2.19146704673767</t>
   </si>
   <si>
     <t xml:space="preserve">2.16381478309631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14307546615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764139175415</t>
+    <t xml:space="preserve">2.14307498931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764091491699</t>
   </si>
   <si>
     <t xml:space="preserve">2.18455386161804</t>
@@ -953,58 +953,58 @@
     <t xml:space="preserve">2.15690159797668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22603273391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21220684051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23294568061829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23985886573792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25368571281433</t>
+    <t xml:space="preserve">2.22603249549866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21220660209656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23294615745544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23985934257507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25368547439575</t>
   </si>
   <si>
     <t xml:space="preserve">2.26059865951538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26751184463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27442455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2467725276947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30899047851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32973027229309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31590414047241</t>
+    <t xml:space="preserve">2.26751136779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27442479133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24677228927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3089907169342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32973003387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31590366363525</t>
   </si>
   <si>
     <t xml:space="preserve">2.32281708717346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33664298057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34355616569519</t>
+    <t xml:space="preserve">2.33664345741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34355664253235</t>
   </si>
   <si>
     <t xml:space="preserve">2.38503527641296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37120890617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43342709541321</t>
+    <t xml:space="preserve">2.37120866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43342733383179</t>
   </si>
   <si>
     <t xml:space="preserve">2.44725346565247</t>
@@ -1013,124 +1013,124 @@
     <t xml:space="preserve">2.5163848400116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873233795166</t>
+    <t xml:space="preserve">2.48873257637024</t>
   </si>
   <si>
     <t xml:space="preserve">2.49564552307129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56477737426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55786395072937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54403710365295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57169032096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52329850196838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53021144866943</t>
+    <t xml:space="preserve">2.564777135849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55786371231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54403758049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57169008255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52329802513123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53021121025085</t>
   </si>
   <si>
     <t xml:space="preserve">2.55095076560974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58551669120789</t>
+    <t xml:space="preserve">2.58551621437073</t>
   </si>
   <si>
     <t xml:space="preserve">2.59242939949036</t>
   </si>
   <si>
+    <t xml:space="preserve">2.63390874862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62699508666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65464806556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64773488044739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62008213996887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64082169532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61316919326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66230630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64100790023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69780349731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74040055274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79009747505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.768798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74750018119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73330116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76169919967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71200275421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65520691871643</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.63390851020813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62699556350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65464758872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64773440361023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62008190155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64082169532776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61316895484924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66230630874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64100813865662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69780397415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74040079116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79009699821472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.768798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7475004196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73330140113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76169943809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71200299263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65520715713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63390874862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68360471725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62680912017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64810729026794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67650532722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66940593719482</t>
+    <t xml:space="preserve">2.6836051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62680888175964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64810752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67650485038757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66940569877625</t>
   </si>
   <si>
     <t xml:space="preserve">2.70490336418152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75459957122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71910190582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72620153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69070410728455</t>
+    <t xml:space="preserve">2.75460004806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71910262107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72620224952698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69070434570312</t>
   </si>
   <si>
     <t xml:space="preserve">2.56291365623474</t>
@@ -1139,55 +1139,55 @@
     <t xml:space="preserve">2.55581402778625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59841132164001</t>
+    <t xml:space="preserve">2.59841108322144</t>
   </si>
   <si>
     <t xml:space="preserve">2.79719662666321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871439933777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49191904067993</t>
+    <t xml:space="preserve">2.54871487617493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49191880226135</t>
   </si>
   <si>
     <t xml:space="preserve">2.47062015533447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37832736968994</t>
+    <t xml:space="preserve">2.37832713127136</t>
   </si>
   <si>
     <t xml:space="preserve">2.25763559341431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17244172096252</t>
+    <t xml:space="preserve">2.17244219779968</t>
   </si>
   <si>
     <t xml:space="preserve">2.21503901481628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34282994270325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34992909431458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48481965065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59131193161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47771978378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60551071166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81139540672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82559442520142</t>
+    <t xml:space="preserve">2.34282946586609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.349928855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48481941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59131145477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47772002220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60551047325134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8113956451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82559466362</t>
   </si>
   <si>
     <t xml:space="preserve">2.88239026069641</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">2.8681914806366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8965892791748</t>
+    <t xml:space="preserve">2.89658951759338</t>
   </si>
   <si>
     <t xml:space="preserve">2.8752908706665</t>
@@ -1205,43 +1205,43 @@
     <t xml:space="preserve">2.83979344367981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78299784660339</t>
+    <t xml:space="preserve">2.78299736976624</t>
   </si>
   <si>
     <t xml:space="preserve">2.90368890762329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88949012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81849527359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83269381523132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85399270057678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98100280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95111751556396</t>
+    <t xml:space="preserve">2.8894898891449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81849479675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83269429206848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8539924621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98100256919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95111775398254</t>
   </si>
   <si>
     <t xml:space="preserve">2.9735312461853</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94364666938782</t>
+    <t xml:space="preserve">2.9436469078064</t>
   </si>
   <si>
     <t xml:space="preserve">2.91376185417175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87640619277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81663656234741</t>
+    <t xml:space="preserve">2.87640571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81663632392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.83905005455017</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">2.70456862449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59997200965881</t>
+    <t xml:space="preserve">2.59997224807739</t>
   </si>
   <si>
     <t xml:space="preserve">2.61491465568542</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">2.6074435710907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62238597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65227007865906</t>
+    <t xml:space="preserve">2.62238574028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65227031707764</t>
   </si>
   <si>
     <t xml:space="preserve">2.62985682487488</t>
@@ -1271,46 +1271,46 @@
     <t xml:space="preserve">2.65974140167236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63732814788818</t>
+    <t xml:space="preserve">2.6373279094696</t>
   </si>
   <si>
     <t xml:space="preserve">2.57008743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58503007888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57755851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55514478683472</t>
+    <t xml:space="preserve">2.58502960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57755875587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5551450252533</t>
   </si>
   <si>
     <t xml:space="preserve">2.52526044845581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59250068664551</t>
+    <t xml:space="preserve">2.59250116348267</t>
   </si>
   <si>
     <t xml:space="preserve">2.54767394065857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50284671783447</t>
+    <t xml:space="preserve">2.50284695625305</t>
   </si>
   <si>
     <t xml:space="preserve">2.47296190261841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45801973342896</t>
+    <t xml:space="preserve">2.45801949501038</t>
   </si>
   <si>
     <t xml:space="preserve">2.49537539482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46549105644226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48790407180786</t>
+    <t xml:space="preserve">2.4654905796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48790454864502</t>
   </si>
   <si>
     <t xml:space="preserve">2.48043322563171</t>
@@ -1325,49 +1325,49 @@
     <t xml:space="preserve">2.4356062412262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37583708763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39077877998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42813491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44307708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41319274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39825010299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42066383361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64479923248291</t>
+    <t xml:space="preserve">2.37583684921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39077925682068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42813467979431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44307732582092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41319251060486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39825034141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42066335678101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64479899406433</t>
   </si>
   <si>
     <t xml:space="preserve">2.71951127052307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7344536781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939584732056</t>
+    <t xml:space="preserve">2.73445343971252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939560890198</t>
   </si>
   <si>
     <t xml:space="preserve">2.75686693191528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74192452430725</t>
+    <t xml:space="preserve">2.74192476272583</t>
   </si>
   <si>
     <t xml:space="preserve">2.77928042411804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79422307014465</t>
+    <t xml:space="preserve">2.7942225933075</t>
   </si>
   <si>
     <t xml:space="preserve">2.81757283210754</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">2.82535624504089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84870648384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84092330932617</t>
+    <t xml:space="preserve">2.84870624542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84092307090759</t>
   </si>
   <si>
     <t xml:space="preserve">2.80978941917419</t>
@@ -1388,19 +1388,22 @@
     <t xml:space="preserve">2.87983989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88762331008911</t>
+    <t xml:space="preserve">2.88762307167053</t>
   </si>
   <si>
     <t xml:space="preserve">2.89540648460388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87205648422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80200600624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8331401348114</t>
+    <t xml:space="preserve">2.87205624580383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80200624465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79422283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83313965797424</t>
   </si>
   <si>
     <t xml:space="preserve">2.86427283287048</t>
@@ -1412,28 +1415,28 @@
     <t xml:space="preserve">2.91875648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92653965950012</t>
+    <t xml:space="preserve">2.9265398979187</t>
   </si>
   <si>
     <t xml:space="preserve">2.90318965911865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98880672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01215648651123</t>
+    <t xml:space="preserve">2.98880696296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01215672492981</t>
   </si>
   <si>
     <t xml:space="preserve">3.00437331199646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94210696220398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97323966026306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91097331047058</t>
+    <t xml:space="preserve">2.9421067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97324013710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910973072052</t>
   </si>
   <si>
     <t xml:space="preserve">2.94989013671875</t>
@@ -1442,13 +1445,13 @@
     <t xml:space="preserve">2.95767331123352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03550672531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99659013748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96545648574829</t>
+    <t xml:space="preserve">3.03550696372986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99658989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96545696258545</t>
   </si>
   <si>
     <t xml:space="preserve">3.04329013824463</t>
@@ -1460,7 +1463,7 @@
     <t xml:space="preserve">3.01994037628174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07442355155945</t>
+    <t xml:space="preserve">3.07442331314087</t>
   </si>
   <si>
     <t xml:space="preserve">3.02772355079651</t>
@@ -1472,40 +1475,40 @@
     <t xml:space="preserve">3.16004037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08998990058899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08220672607422</t>
+    <t xml:space="preserve">3.08999013900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0822069644928</t>
   </si>
   <si>
     <t xml:space="preserve">3.06664037704468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05885720252991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0977737903595</t>
+    <t xml:space="preserve">3.05885696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09777355194092</t>
   </si>
   <si>
     <t xml:space="preserve">3.11416387557983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13055396080017</t>
+    <t xml:space="preserve">3.13055419921875</t>
   </si>
   <si>
     <t xml:space="preserve">3.10596895217896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06499290466309</t>
+    <t xml:space="preserve">3.06499266624451</t>
   </si>
   <si>
     <t xml:space="preserve">3.07318806648254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08957839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04040765762329</t>
+    <t xml:space="preserve">3.08957815170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04040741920471</t>
   </si>
   <si>
     <t xml:space="preserve">3.03221225738525</t>
@@ -1520,100 +1523,100 @@
     <t xml:space="preserve">3.01582169532776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0240170955658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00762677192688</t>
+    <t xml:space="preserve">3.02401685714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00762701034546</t>
   </si>
   <si>
     <t xml:space="preserve">3.081383228302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.999431848526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99123668670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97484588623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96665048599243</t>
+    <t xml:space="preserve">2.99943137168884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99123644828796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97484612464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96665072441101</t>
   </si>
   <si>
     <t xml:space="preserve">2.95845556259155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98304152488708</t>
+    <t xml:space="preserve">2.98304128646851</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026040077209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93387031555176</t>
+    <t xml:space="preserve">2.93387007713318</t>
   </si>
   <si>
     <t xml:space="preserve">2.90108942985535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9256751537323</t>
+    <t xml:space="preserve">2.92567491531372</t>
   </si>
   <si>
     <t xml:space="preserve">2.94206547737122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87650418281555</t>
+    <t xml:space="preserve">2.87650394439697</t>
   </si>
   <si>
     <t xml:space="preserve">2.86830902099609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81094264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83552837371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79455232620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78635716438293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80274724960327</t>
+    <t xml:space="preserve">2.81094288825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8355278968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79455256462097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78635740280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80274748802185</t>
   </si>
   <si>
     <t xml:space="preserve">2.76177167892456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84372329711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86011362075806</t>
+    <t xml:space="preserve">2.84372353553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86011385917664</t>
   </si>
   <si>
     <t xml:space="preserve">2.81913805007935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9092845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8519184589386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88469910621643</t>
+    <t xml:space="preserve">2.90928483009338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85191869735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88469934463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.89289426803589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91747999191284</t>
+    <t xml:space="preserve">2.91747975349426</t>
   </si>
   <si>
     <t xml:space="preserve">3.00797700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04215860366821</t>
+    <t xml:space="preserve">3.04215836524963</t>
   </si>
   <si>
     <t xml:space="preserve">3.01652240753174</t>
@@ -1625,19 +1628,19 @@
     <t xml:space="preserve">3.05070400238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05924940109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07633996009827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11906719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12761259078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14470314979553</t>
+    <t xml:space="preserve">3.05924916267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07634019851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11906743049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12761235237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14470338821411</t>
   </si>
   <si>
     <t xml:space="preserve">3.16179394721985</t>
@@ -1646,25 +1649,25 @@
     <t xml:space="preserve">3.15324854850769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17033958435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11052203178406</t>
+    <t xml:space="preserve">3.17033934593201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11052179336548</t>
   </si>
   <si>
     <t xml:space="preserve">3.08488535881042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10197639465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.093430519104</t>
+    <t xml:space="preserve">3.10197615623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09343075752258</t>
   </si>
   <si>
     <t xml:space="preserve">3.13615775108337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18743014335632</t>
+    <t xml:space="preserve">3.1874303817749</t>
   </si>
   <si>
     <t xml:space="preserve">3.19597554206848</t>
@@ -1685,10 +1688,10 @@
     <t xml:space="preserve">3.34979271888733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30706548690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35833811759949</t>
+    <t xml:space="preserve">3.30706572532654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35833787918091</t>
   </si>
   <si>
     <t xml:space="preserve">3.36688351631165</t>
@@ -1700,25 +1703,25 @@
     <t xml:space="preserve">3.4010648727417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42670130729675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31561088562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28997492790222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29852032661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3839738368988</t>
+    <t xml:space="preserve">3.42670106887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3156111240387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28997468948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2985200881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38397407531738</t>
   </si>
   <si>
     <t xml:space="preserve">3.32415652275085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37542867660522</t>
+    <t xml:space="preserve">3.3754289150238</t>
   </si>
   <si>
     <t xml:space="preserve">3.41815567016602</t>
@@ -1727,28 +1730,28 @@
     <t xml:space="preserve">3.43524646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40961050987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45233702659607</t>
+    <t xml:space="preserve">3.40961027145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45233726501465</t>
   </si>
   <si>
     <t xml:space="preserve">3.44379186630249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46942806243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50360941886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57197260856628</t>
+    <t xml:space="preserve">3.46942782402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5036096572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57197237014771</t>
   </si>
   <si>
     <t xml:space="preserve">3.52070021629333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51215481758118</t>
+    <t xml:space="preserve">3.51215505599976</t>
   </si>
   <si>
     <t xml:space="preserve">3.46088290214539</t>
@@ -1757,10 +1760,10 @@
     <t xml:space="preserve">3.4865186214447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49550485610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51347637176514</t>
+    <t xml:space="preserve">3.49550461769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51347661018372</t>
   </si>
   <si>
     <t xml:space="preserve">3.48651885986328</t>
@@ -1772,28 +1775,28 @@
     <t xml:space="preserve">3.59434938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53144812583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43260359764099</t>
+    <t xml:space="preserve">3.53144836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43260335922241</t>
   </si>
   <si>
     <t xml:space="preserve">3.46854710578918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47753310203552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45057535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37868857383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34274482727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42361783981323</t>
+    <t xml:space="preserve">3.47753286361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45057559013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3786883354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34274506568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42361760139465</t>
   </si>
   <si>
     <t xml:space="preserve">3.38767409324646</t>
@@ -1805,19 +1808,19 @@
     <t xml:space="preserve">3.40564608573914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45956110954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55840563774109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54942011833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54043436050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36071681976318</t>
+    <t xml:space="preserve">3.45956134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55840587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54941987991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54043412208557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3607165813446</t>
   </si>
   <si>
     <t xml:space="preserve">3.41463184356689</t>
@@ -1832,19 +1835,19 @@
     <t xml:space="preserve">3.69319415092468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65725064277649</t>
+    <t xml:space="preserve">3.65725040435791</t>
   </si>
   <si>
     <t xml:space="preserve">3.56739187240601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68420791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71116590499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72913765907288</t>
+    <t xml:space="preserve">3.68420815467834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7111656665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7291374206543</t>
   </si>
   <si>
     <t xml:space="preserve">3.74710917472839</t>
@@ -1859,10 +1862,10 @@
     <t xml:space="preserve">3.70217967033386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75609493255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8189959526062</t>
+    <t xml:space="preserve">3.75609469413757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81899619102478</t>
   </si>
   <si>
     <t xml:space="preserve">3.81001019477844</t>
@@ -1877,13 +1880,13 @@
     <t xml:space="preserve">3.83696794509888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84595394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8279824256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76508092880249</t>
+    <t xml:space="preserve">3.84595370292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82798218727112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76508069038391</t>
   </si>
   <si>
     <t xml:space="preserve">3.73812317848206</t>
@@ -1892,13 +1895,13 @@
     <t xml:space="preserve">3.73778820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77507281303406</t>
+    <t xml:space="preserve">3.77507305145264</t>
   </si>
   <si>
     <t xml:space="preserve">3.71914577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68186116218567</t>
+    <t xml:space="preserve">3.68186092376709</t>
   </si>
   <si>
     <t xml:space="preserve">3.66321873664856</t>
@@ -1910,7 +1913,7 @@
     <t xml:space="preserve">3.69118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75643062591553</t>
+    <t xml:space="preserve">3.75643038749695</t>
   </si>
   <si>
     <t xml:space="preserve">3.7657516002655</t>
@@ -1922,34 +1925,34 @@
     <t xml:space="preserve">3.93353247642517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80303621292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88692688941956</t>
+    <t xml:space="preserve">3.80303597450256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88692665100098</t>
   </si>
   <si>
     <t xml:space="preserve">3.84032082557678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81235766410828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82167840003967</t>
+    <t xml:space="preserve">3.8123574256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82167863845825</t>
   </si>
   <si>
     <t xml:space="preserve">3.83099985122681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87760543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90556907653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91488981246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96149587631226</t>
+    <t xml:space="preserve">3.87760519981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90556883811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91489028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96149611473083</t>
   </si>
   <si>
     <t xml:space="preserve">4.00810194015503</t>
@@ -1961,13 +1964,13 @@
     <t xml:space="preserve">4.04538679122925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01742315292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03606510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98013854026794</t>
+    <t xml:space="preserve">4.01742267608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03606557846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98013830184937</t>
   </si>
   <si>
     <t xml:space="preserve">4.07334995269775</t>
@@ -1976,7 +1979,7 @@
     <t xml:space="preserve">4.09199237823486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11063480377197</t>
+    <t xml:space="preserve">4.11063432693481</t>
   </si>
   <si>
     <t xml:space="preserve">4.1758828163147</t>
@@ -1991,13 +1994,13 @@
     <t xml:space="preserve">3.9894597530365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94285368919373</t>
+    <t xml:space="preserve">3.9428539276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.9521746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97081756591797</t>
+    <t xml:space="preserve">3.97081732749939</t>
   </si>
   <si>
     <t xml:space="preserve">4.06402921676636</t>
@@ -2009,16 +2012,16 @@
     <t xml:space="preserve">4.11995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7005033493042</t>
+    <t xml:space="preserve">3.70050358772278</t>
   </si>
   <si>
     <t xml:space="preserve">3.68652153015137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90090823173523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92887234687805</t>
+    <t xml:space="preserve">3.90090847015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92887210845947</t>
   </si>
   <si>
     <t xml:space="preserve">3.9242115020752</t>
@@ -2316,6 +2319,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.73000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84000015258789</t>
   </si>
 </sst>
 </file>
@@ -36030,7 +36036,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1284" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36082,7 +36088,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1286" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36108,7 +36114,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1287" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36186,7 +36192,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36290,7 +36296,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1294" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36368,7 +36374,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1297" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36446,7 +36452,7 @@
         <v>3.75</v>
       </c>
       <c r="G1300" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36472,7 +36478,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1301" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36498,7 +36504,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1302" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36524,7 +36530,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1303" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36550,7 +36556,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1304" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36576,7 +36582,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1305" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36602,7 +36608,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1306" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36628,7 +36634,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1307" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36654,7 +36660,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36706,7 +36712,7 @@
         <v>3.75</v>
       </c>
       <c r="G1310" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36732,7 +36738,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36758,7 +36764,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1312" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36784,7 +36790,7 @@
         <v>3.75</v>
       </c>
       <c r="G1313" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36810,7 +36816,7 @@
         <v>3.75</v>
       </c>
       <c r="G1314" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36914,7 +36920,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36940,7 +36946,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36966,7 +36972,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36992,7 +36998,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1321" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37018,7 +37024,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1322" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37044,7 +37050,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1323" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37070,7 +37076,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1324" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37096,7 +37102,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1325" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37122,7 +37128,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1326" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37148,7 +37154,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1327" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37174,7 +37180,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1328" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37200,7 +37206,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1329" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37226,7 +37232,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37252,7 +37258,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1331" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37278,7 +37284,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1332" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37304,7 +37310,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1333" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37330,7 +37336,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1334" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37356,7 +37362,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37382,7 +37388,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1336" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37408,7 +37414,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1337" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37434,7 +37440,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1338" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37460,7 +37466,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37486,7 +37492,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1340" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37512,7 +37518,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1341" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37538,7 +37544,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1342" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37564,7 +37570,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1343" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37590,7 +37596,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37616,7 +37622,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1345" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37642,7 +37648,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1346" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37668,7 +37674,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37720,7 +37726,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1349" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37746,7 +37752,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1350" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37772,7 +37778,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1351" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37798,7 +37804,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1352" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37824,7 +37830,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1353" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37850,7 +37856,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37876,7 +37882,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1355" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37902,7 +37908,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1356" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37928,7 +37934,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1357" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37954,7 +37960,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1358" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37980,7 +37986,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1359" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38006,7 +38012,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1360" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38032,7 +38038,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1361" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38058,7 +38064,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1362" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38084,7 +38090,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1363" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38110,7 +38116,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1364" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38136,7 +38142,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1365" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38162,7 +38168,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1366" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38188,7 +38194,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38214,7 +38220,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1368" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38240,7 +38246,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38266,7 +38272,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1370" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38292,7 +38298,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1371" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38318,7 +38324,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38344,7 +38350,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1373" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38370,7 +38376,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1374" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38396,7 +38402,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1375" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38422,7 +38428,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38448,7 +38454,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1377" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38474,7 +38480,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1378" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38500,7 +38506,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1379" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38526,7 +38532,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1380" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38552,7 +38558,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38578,7 +38584,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1382" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38604,7 +38610,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38630,7 +38636,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1384" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38656,7 +38662,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1385" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38682,7 +38688,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1386" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38708,7 +38714,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38734,7 +38740,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1388" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38760,7 +38766,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38786,7 +38792,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1390" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38812,7 +38818,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38838,7 +38844,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1392" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38864,7 +38870,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1393" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38890,7 +38896,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38916,7 +38922,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1395" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38942,7 +38948,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1396" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38968,7 +38974,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1397" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38994,7 +39000,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1398" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39020,7 +39026,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1399" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39046,7 +39052,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1400" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39072,7 +39078,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1401" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39098,7 +39104,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1402" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39124,7 +39130,7 @@
         <v>3.75</v>
       </c>
       <c r="G1403" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39150,7 +39156,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39176,7 +39182,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1405" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39202,7 +39208,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1406" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39228,7 +39234,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1407" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39254,7 +39260,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1408" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39280,7 +39286,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1409" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39306,7 +39312,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1410" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39332,7 +39338,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1411" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39358,7 +39364,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1412" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39384,7 +39390,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1413" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39410,7 +39416,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1414" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39436,7 +39442,7 @@
         <v>3.75</v>
       </c>
       <c r="G1415" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39462,7 +39468,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39488,7 +39494,7 @@
         <v>3.75</v>
       </c>
       <c r="G1417" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39514,7 +39520,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1418" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39540,7 +39546,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39566,7 +39572,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1420" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39592,7 +39598,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1421" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39618,7 +39624,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1422" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39644,7 +39650,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39670,7 +39676,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1424" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39696,7 +39702,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1425" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39722,7 +39728,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1426" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39748,7 +39754,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1427" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39774,7 +39780,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1428" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39800,7 +39806,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39826,7 +39832,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1430" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39852,7 +39858,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39878,7 +39884,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39904,7 +39910,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1433" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39930,7 +39936,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39956,7 +39962,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1435" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39982,7 +39988,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1436" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40008,7 +40014,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1437" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40034,7 +40040,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1438" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40060,7 +40066,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1439" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40086,7 +40092,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40112,7 +40118,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1441" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40138,7 +40144,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40164,7 +40170,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1443" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40190,7 +40196,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1444" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40216,7 +40222,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1445" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40242,7 +40248,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1446" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40268,7 +40274,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1447" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40294,7 +40300,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1448" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40320,7 +40326,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1449" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40346,7 +40352,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1450" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40372,7 +40378,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1451" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40398,7 +40404,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1452" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40424,7 +40430,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40450,7 +40456,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40476,7 +40482,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40502,7 +40508,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40528,7 +40534,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1457" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40554,7 +40560,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40580,7 +40586,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1459" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40606,7 +40612,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1460" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40632,7 +40638,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40658,7 +40664,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1462" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40684,7 +40690,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40710,7 +40716,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1464" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40736,7 +40742,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40762,7 +40768,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1466" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40788,7 +40794,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1467" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40814,7 +40820,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1468" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40840,7 +40846,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1469" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40866,7 +40872,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1470" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40892,7 +40898,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1471" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40918,7 +40924,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1472" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40944,7 +40950,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1473" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40970,7 +40976,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40996,7 +41002,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1475" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41022,7 +41028,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1476" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41048,7 +41054,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1477" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41074,7 +41080,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1478" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41100,7 +41106,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1479" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41126,7 +41132,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41152,7 +41158,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41178,7 +41184,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1482" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41204,7 +41210,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1483" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41230,7 +41236,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1484" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41256,7 +41262,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1485" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41282,7 +41288,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1486" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41308,7 +41314,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1487" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41334,7 +41340,7 @@
         <v>3.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41360,7 +41366,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1489" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41386,7 +41392,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41412,7 +41418,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1491" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41438,7 +41444,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1492" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41464,7 +41470,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41490,7 +41496,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1494" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41516,7 +41522,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1495" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41542,7 +41548,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1496" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41568,7 +41574,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1497" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41594,7 +41600,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1498" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41620,7 +41626,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1499" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41646,7 +41652,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1500" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41672,7 +41678,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1501" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41698,7 +41704,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41724,7 +41730,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1503" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41750,7 +41756,7 @@
         <v>3.5</v>
       </c>
       <c r="G1504" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41776,7 +41782,7 @@
         <v>3.5</v>
       </c>
       <c r="G1505" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41802,7 +41808,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1506" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41828,7 +41834,7 @@
         <v>3.5</v>
       </c>
       <c r="G1507" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41854,7 +41860,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1508" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41880,7 +41886,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1509" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41906,7 +41912,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1510" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41932,7 +41938,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1511" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41958,7 +41964,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1512" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41984,7 +41990,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42010,7 +42016,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42036,7 +42042,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42062,7 +42068,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42088,7 +42094,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1517" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42114,7 +42120,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1518" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42140,7 +42146,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1519" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42166,7 +42172,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1520" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42192,7 +42198,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42218,7 +42224,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42244,7 +42250,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1523" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42270,7 +42276,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1524" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42296,7 +42302,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1525" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42322,7 +42328,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1526" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42348,7 +42354,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1527" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42374,7 +42380,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1528" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42400,7 +42406,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1529" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42426,7 +42432,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1530" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42452,7 +42458,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1531" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42478,7 +42484,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1532" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42504,7 +42510,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1533" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42530,7 +42536,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1534" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42556,7 +42562,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1535" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42582,7 +42588,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1536" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42608,7 +42614,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1537" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42634,7 +42640,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1538" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42660,7 +42666,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1539" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42686,7 +42692,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1540" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42712,7 +42718,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1541" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42738,7 +42744,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42764,7 +42770,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1543" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42790,7 +42796,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1544" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42816,7 +42822,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1545" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42842,7 +42848,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1546" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42868,7 +42874,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1547" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42894,7 +42900,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1548" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42920,7 +42926,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1549" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42946,7 +42952,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1550" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42972,7 +42978,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1551" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42998,7 +43004,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1552" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43024,7 +43030,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1553" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43050,7 +43056,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1554" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43076,7 +43082,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1555" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43102,7 +43108,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1556" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43128,7 +43134,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1557" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43154,7 +43160,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1558" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43180,7 +43186,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1559" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43206,7 +43212,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1560" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43232,7 +43238,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43258,7 +43264,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1562" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43284,7 +43290,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1563" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43310,7 +43316,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1564" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43336,7 +43342,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1565" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43362,7 +43368,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1566" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43388,7 +43394,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1567" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43414,7 +43420,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1568" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43440,7 +43446,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1569" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43466,7 +43472,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1570" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43492,7 +43498,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1571" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43518,7 +43524,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1572" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43544,7 +43550,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1573" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43570,7 +43576,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1574" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43596,7 +43602,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1575" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43622,7 +43628,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1576" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43648,7 +43654,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1577" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43674,7 +43680,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1578" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43700,7 +43706,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1579" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43726,7 +43732,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1580" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43752,7 +43758,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1581" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43778,7 +43784,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1582" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43804,7 +43810,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1583" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43830,7 +43836,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1584" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43856,7 +43862,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1585" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43882,7 +43888,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1586" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43908,7 +43914,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1587" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43934,7 +43940,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1588" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43960,7 +43966,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1589" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43986,7 +43992,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1590" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44012,7 +44018,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1591" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44038,7 +44044,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1592" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44064,7 +44070,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1593" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44090,7 +44096,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1594" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44116,7 +44122,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1595" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44142,7 +44148,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1596" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44168,7 +44174,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1597" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44194,7 +44200,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1598" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44220,7 +44226,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1599" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44246,7 +44252,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1600" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44272,7 +44278,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44298,7 +44304,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1602" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44324,7 +44330,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44350,7 +44356,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44376,7 +44382,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1605" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44402,7 +44408,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1606" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44428,7 +44434,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1607" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44454,7 +44460,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44480,7 +44486,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1609" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44506,7 +44512,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1610" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44532,7 +44538,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44558,7 +44564,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1612" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44584,7 +44590,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1613" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44610,7 +44616,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44636,7 +44642,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1615" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44662,7 +44668,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1616" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44688,7 +44694,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1617" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44714,7 +44720,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1618" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44740,7 +44746,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1619" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44766,7 +44772,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1620" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44792,7 +44798,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1621" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44818,7 +44824,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1622" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44844,7 +44850,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1623" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44870,7 +44876,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44896,7 +44902,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44922,7 +44928,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44948,7 +44954,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1627" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44974,7 +44980,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1628" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45000,7 +45006,7 @@
         <v>4</v>
       </c>
       <c r="G1629" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45026,7 +45032,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1630" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45052,7 +45058,7 @@
         <v>4</v>
       </c>
       <c r="G1631" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45078,7 +45084,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1632" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45104,7 +45110,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45130,7 +45136,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1634" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45156,7 +45162,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45182,7 +45188,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45208,7 +45214,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1637" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45234,7 +45240,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1638" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45260,7 +45266,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1639" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45286,7 +45292,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1640" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45312,7 +45318,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45338,7 +45344,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1642" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45364,7 +45370,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1643" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45390,7 +45396,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1644" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45416,7 +45422,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1645" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45442,7 +45448,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45468,7 +45474,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1647" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45494,7 +45500,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1648" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45520,7 +45526,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1649" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45546,7 +45552,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1650" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45572,7 +45578,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45598,7 +45604,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1652" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45624,7 +45630,7 @@
         <v>4</v>
       </c>
       <c r="G1653" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45650,7 +45656,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1654" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45676,7 +45682,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1655" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45702,7 +45708,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1656" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45728,7 +45734,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1657" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45754,7 +45760,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1658" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45780,7 +45786,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45806,7 +45812,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45832,7 +45838,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1661" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45858,7 +45864,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1662" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45884,7 +45890,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45910,7 +45916,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1664" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45936,7 +45942,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45962,7 +45968,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1666" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45988,7 +45994,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1667" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46014,7 +46020,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1668" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46040,7 +46046,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1669" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46066,7 +46072,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46092,7 +46098,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1671" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46118,7 +46124,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1672" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46144,7 +46150,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46170,7 +46176,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1674" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46196,7 +46202,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1675" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46222,7 +46228,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1676" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46248,7 +46254,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1677" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46274,7 +46280,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1678" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46300,7 +46306,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1679" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46326,7 +46332,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1680" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46352,7 +46358,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1681" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46378,7 +46384,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1682" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46404,7 +46410,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1683" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46430,7 +46436,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1684" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46456,7 +46462,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1685" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46482,7 +46488,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1686" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46508,7 +46514,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46534,7 +46540,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1688" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46560,7 +46566,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1689" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46586,7 +46592,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1690" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46612,7 +46618,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1691" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46638,7 +46644,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1692" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46664,7 +46670,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1693" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46690,7 +46696,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1694" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46716,7 +46722,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1695" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46742,7 +46748,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1696" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46768,7 +46774,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1697" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46794,7 +46800,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46820,7 +46826,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1699" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46846,7 +46852,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1700" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46872,7 +46878,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1701" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46898,7 +46904,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1702" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46924,7 +46930,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1703" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46950,7 +46956,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1704" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46976,7 +46982,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47002,7 +47008,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47028,7 +47034,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47054,7 +47060,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1708" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47080,7 +47086,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1709" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47106,7 +47112,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1710" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47132,7 +47138,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47158,7 +47164,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1712" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47184,7 +47190,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1713" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47210,7 +47216,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47236,7 +47242,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1715" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47262,7 +47268,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1716" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47288,7 +47294,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47314,7 +47320,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1718" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47340,7 +47346,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47366,7 +47372,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1720" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47392,7 +47398,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47418,7 +47424,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1722" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47444,7 +47450,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1723" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47470,7 +47476,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1724" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47496,7 +47502,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1725" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47522,7 +47528,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47548,7 +47554,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1727" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47574,7 +47580,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1728" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47600,7 +47606,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1729" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47626,7 +47632,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1730" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47652,7 +47658,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1731" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47678,7 +47684,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1732" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47704,7 +47710,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1733" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47730,7 +47736,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1734" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47756,7 +47762,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1735" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47782,7 +47788,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1736" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47808,7 +47814,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1737" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47834,7 +47840,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1738" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47860,7 +47866,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1739" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47886,7 +47892,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1740" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47912,7 +47918,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1741" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47938,7 +47944,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47964,7 +47970,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1743" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47990,7 +47996,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1744" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48016,7 +48022,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1745" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48042,7 +48048,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1746" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48068,7 +48074,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1747" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48094,7 +48100,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1748" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48120,7 +48126,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1749" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48146,7 +48152,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1750" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48172,7 +48178,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1751" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48198,7 +48204,7 @@
         <v>4.25</v>
       </c>
       <c r="G1752" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48224,7 +48230,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1753" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48250,7 +48256,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1754" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48276,7 +48282,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48302,7 +48308,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1756" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48328,7 +48334,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1757" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48354,7 +48360,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1758" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48380,7 +48386,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1759" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48406,7 +48412,7 @@
         <v>4.25</v>
       </c>
       <c r="G1760" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48432,7 +48438,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48458,7 +48464,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1762" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48484,7 +48490,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1763" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48510,7 +48516,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48536,7 +48542,7 @@
         <v>4.25</v>
       </c>
       <c r="G1765" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48562,7 +48568,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1766" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48588,7 +48594,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48614,7 +48620,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1768" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48640,7 +48646,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48666,7 +48672,7 @@
         <v>4.25</v>
       </c>
       <c r="G1770" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48692,7 +48698,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1771" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48718,7 +48724,7 @@
         <v>4.25</v>
       </c>
       <c r="G1772" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48744,7 +48750,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1773" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48770,7 +48776,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1774" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48796,7 +48802,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1775" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48822,7 +48828,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1776" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48848,7 +48854,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1777" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48874,7 +48880,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1778" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48900,7 +48906,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48926,7 +48932,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1780" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48952,7 +48958,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1781" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48978,7 +48984,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1782" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49004,7 +49010,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1783" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49030,7 +49036,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1784" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49056,7 +49062,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1785" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49082,7 +49088,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1786" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49108,7 +49114,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1787" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49134,7 +49140,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1788" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49160,7 +49166,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1789" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49186,7 +49192,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1790" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49212,7 +49218,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1791" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49238,7 +49244,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1792" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49264,7 +49270,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1793" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49290,7 +49296,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1794" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49316,7 +49322,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49342,7 +49348,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49368,7 +49374,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49394,7 +49400,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49420,7 +49426,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1799" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49446,7 +49452,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1800" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49472,7 +49478,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1801" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49498,7 +49504,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1802" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49524,7 +49530,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49550,7 +49556,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1804" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49576,7 +49582,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1805" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49602,7 +49608,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1806" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49628,7 +49634,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49654,7 +49660,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1808" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49680,7 +49686,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1809" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49706,7 +49712,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1810" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49732,7 +49738,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1811" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49758,7 +49764,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1812" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49784,7 +49790,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1813" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49810,7 +49816,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1814" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49836,7 +49842,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1815" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49862,7 +49868,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1816" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49888,7 +49894,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1817" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49914,7 +49920,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49940,7 +49946,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1819" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49966,7 +49972,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1820" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49992,7 +49998,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1821" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50018,7 +50024,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1822" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50044,7 +50050,7 @@
         <v>4.25</v>
       </c>
       <c r="G1823" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50070,7 +50076,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1824" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50096,7 +50102,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50122,7 +50128,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1826" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50148,7 +50154,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50174,7 +50180,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1828" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50200,7 +50206,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1829" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50226,7 +50232,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1830" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50252,7 +50258,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1831" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50278,7 +50284,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50304,7 +50310,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1833" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50330,7 +50336,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50356,7 +50362,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50382,7 +50388,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1836" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50408,7 +50414,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1837" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50434,7 +50440,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1838" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50460,7 +50466,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1839" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50486,7 +50492,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1840" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50512,7 +50518,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1841" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50538,7 +50544,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1842" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50564,7 +50570,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1843" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50590,7 +50596,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1844" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50616,7 +50622,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1845" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50642,7 +50648,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1846" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50668,7 +50674,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1847" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50694,7 +50700,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50720,7 +50726,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1849" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50746,7 +50752,7 @@
         <v>4.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50772,7 +50778,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1851" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50798,7 +50804,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50824,7 +50830,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1853" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50850,7 +50856,7 @@
         <v>4.25</v>
       </c>
       <c r="G1854" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50876,7 +50882,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1855" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50902,7 +50908,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1856" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50928,7 +50934,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1857" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50954,7 +50960,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1858" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50980,7 +50986,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51006,7 +51012,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1860" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51032,7 +51038,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1861" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51058,7 +51064,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51084,7 +51090,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1863" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51110,7 +51116,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1864" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51136,7 +51142,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1865" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51162,7 +51168,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1866" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51188,7 +51194,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1867" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51214,7 +51220,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1868" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51240,7 +51246,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1869" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51266,7 +51272,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1870" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51292,7 +51298,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1871" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51318,7 +51324,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1872" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51344,7 +51350,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1873" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51370,7 +51376,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1874" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51396,7 +51402,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1875" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51422,7 +51428,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1876" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51448,7 +51454,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1877" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51474,7 +51480,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1878" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51500,7 +51506,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1879" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51526,7 +51532,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1880" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51552,7 +51558,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1881" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51578,7 +51584,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1882" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51604,7 +51610,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1883" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51630,7 +51636,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1884" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51656,7 +51662,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1885" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51682,7 +51688,7 @@
         <v>4.25</v>
       </c>
       <c r="G1886" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51708,7 +51714,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51734,7 +51740,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1888" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51760,7 +51766,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51786,7 +51792,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1890" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51812,7 +51818,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1891" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51838,7 +51844,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1892" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51864,7 +51870,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1893" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51890,7 +51896,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1894" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51916,7 +51922,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1895" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51942,7 +51948,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51968,7 +51974,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1897" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51994,7 +52000,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1898" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52020,7 +52026,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1899" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52046,7 +52052,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1900" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52072,7 +52078,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52098,7 +52104,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1902" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52124,7 +52130,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1903" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52150,7 +52156,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1904" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52176,7 +52182,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1905" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52202,7 +52208,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52228,7 +52234,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52254,7 +52260,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1908" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52280,7 +52286,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1909" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52306,7 +52312,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1910" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52332,7 +52338,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1911" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52358,7 +52364,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52384,7 +52390,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1913" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52410,7 +52416,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1914" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52436,7 +52442,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1915" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52462,7 +52468,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1916" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52488,7 +52494,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1917" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52514,7 +52520,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1918" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52540,7 +52546,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1919" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52566,7 +52572,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1920" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52592,7 +52598,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1921" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52618,7 +52624,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1922" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52644,7 +52650,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G1923" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52670,7 +52676,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1924" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52696,7 +52702,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1925" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52722,7 +52728,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1926" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52748,7 +52754,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1927" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52774,7 +52780,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1928" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52800,7 +52806,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1929" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52826,7 +52832,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52852,7 +52858,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G1931" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52878,7 +52884,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1932" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52904,7 +52910,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1933" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52930,7 +52936,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1934" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52956,7 +52962,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1935" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52982,7 +52988,7 @@
         <v>4.5</v>
       </c>
       <c r="G1936" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53008,7 +53014,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1937" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53034,7 +53040,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1938" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53060,7 +53066,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1939" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53086,7 +53092,7 @@
         <v>4.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53112,7 +53118,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1941" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53138,7 +53144,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1942" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53164,7 +53170,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1943" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53190,7 +53196,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53216,7 +53222,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1945" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53242,7 +53248,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1946" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53268,7 +53274,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53294,7 +53300,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1948" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53320,7 +53326,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1949" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53346,7 +53352,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1950" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53372,7 +53378,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1951" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53398,7 +53404,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1952" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53424,7 +53430,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1953" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53450,7 +53456,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53476,7 +53482,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1955" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53502,7 +53508,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1956" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53528,7 +53534,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53554,7 +53560,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1958" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53580,7 +53586,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53606,7 +53612,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53632,7 +53638,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1961" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53658,7 +53664,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1962" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53684,7 +53690,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53710,7 +53716,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53736,7 +53742,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G1965" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53762,7 +53768,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1966" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53788,7 +53794,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1967" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53814,7 +53820,7 @@
         <v>5</v>
       </c>
       <c r="G1968" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53840,7 +53846,7 @@
         <v>5</v>
       </c>
       <c r="G1969" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53866,7 +53872,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1970" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53892,7 +53898,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1971" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53918,7 +53924,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G1972" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53944,7 +53950,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1973" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53970,7 +53976,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53996,7 +54002,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54022,7 +54028,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1976" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54048,7 +54054,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1977" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54074,7 +54080,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1978" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54100,7 +54106,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1979" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54126,7 +54132,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54152,7 +54158,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1981" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54178,7 +54184,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1982" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54204,7 +54210,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1983" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54230,7 +54236,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1984" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54256,7 +54262,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1985" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54282,7 +54288,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1986" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54308,7 +54314,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1987" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54334,7 +54340,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54360,7 +54366,7 @@
         <v>5.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54386,7 +54392,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1990" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54412,7 +54418,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1991" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54438,7 +54444,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54464,7 +54470,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1993" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54490,7 +54496,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1994" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54516,7 +54522,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1995" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54542,7 +54548,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1996" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54568,7 +54574,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1997" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54594,7 +54600,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1998" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54620,7 +54626,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54646,7 +54652,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2000" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54672,7 +54678,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2001" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54698,7 +54704,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G2002" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54724,7 +54730,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54750,7 +54756,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54776,7 +54782,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2005" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54802,7 +54808,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2006" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54828,7 +54834,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2007" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54854,7 +54860,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2008" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54880,7 +54886,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2009" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54906,7 +54912,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2010" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54932,7 +54938,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2011" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54958,7 +54964,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2012" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54984,7 +54990,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2013" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55010,7 +55016,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55036,7 +55042,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2015" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55062,7 +55068,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2016" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55088,7 +55094,7 @@
         <v>5.75</v>
       </c>
       <c r="G2017" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55114,7 +55120,7 @@
         <v>5.75</v>
       </c>
       <c r="G2018" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55140,7 +55146,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2019" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55166,7 +55172,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2020" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55192,7 +55198,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2021" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55218,7 +55224,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2022" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55244,7 +55250,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2023" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55270,7 +55276,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2024" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55296,7 +55302,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G2025" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55322,7 +55328,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2026" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55348,7 +55354,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G2027" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55374,7 +55380,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2028" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55400,7 +55406,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2029" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55426,7 +55432,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2030" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55452,7 +55458,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2031" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55478,7 +55484,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2032" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55486,7 +55492,7 @@
     </row>
     <row r="2033">
       <c r="A2033" s="1" t="n">
-        <v>45985.6911111111</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2033" t="n">
         <v>102466</v>
@@ -55504,9 +55510,35 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2033" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" s="1" t="n">
+        <v>45986.6909722222</v>
+      </c>
+      <c r="B2034" t="n">
+        <v>146444</v>
+      </c>
+      <c r="C2034" t="n">
+        <v>5.8600001335144</v>
+      </c>
+      <c r="D2034" t="n">
+        <v>5.65999984741211</v>
+      </c>
+      <c r="E2034" t="n">
+        <v>5.73000001907349</v>
+      </c>
+      <c r="F2034" t="n">
+        <v>5.84000015258789</v>
+      </c>
+      <c r="G2034" t="s">
+        <v>769</v>
+      </c>
+      <c r="H2034" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="771">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6193071603775</t>
+    <t xml:space="preserve">1.61930727958679</t>
   </si>
   <si>
     <t xml:space="preserve">EQUI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68691492080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71744728088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71417582035065</t>
+    <t xml:space="preserve">1.68691468238831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7174471616745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71417593955994</t>
   </si>
   <si>
     <t xml:space="preserve">1.71090459823608</t>
@@ -59,118 +59,118 @@
     <t xml:space="preserve">1.70109045505524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67055797576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67492008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69018638134003</t>
+    <t xml:space="preserve">1.67055785655975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67492020130157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69018626213074</t>
   </si>
   <si>
     <t xml:space="preserve">1.67710089683533</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65856337547302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65747284889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65529179573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784492015839</t>
+    <t xml:space="preserve">1.65856313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65747272968292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65529191493988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6378448009491</t>
   </si>
   <si>
     <t xml:space="preserve">1.64656841754913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65311086177826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65420114994049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64874935150146</t>
+    <t xml:space="preserve">1.65311098098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65420186519623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64874947071075</t>
   </si>
   <si>
     <t xml:space="preserve">1.65965378284454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64002561569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64329719543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62585008144379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64765906333923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67382943630219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68909573554993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67928147315979</t>
+    <t xml:space="preserve">1.6400260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64329695701599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62585043907166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64765882492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67382919788361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6890960931778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6792813539505</t>
   </si>
   <si>
     <t xml:space="preserve">1.67819118499756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67164850234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67273879051208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70327162742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70654296875</t>
+    <t xml:space="preserve">1.67164862155914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67273902893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70327174663544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70654284954071</t>
   </si>
   <si>
     <t xml:space="preserve">1.69563841819763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66565108299255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66837739944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69836437702179</t>
+    <t xml:space="preserve">1.66565120220184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66837751865387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69836473464966</t>
   </si>
   <si>
     <t xml:space="preserve">1.70381665229797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68746042251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68473386764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67110359668732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016057491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72289931774139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72835183143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74470794200897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73107755184174</t>
+    <t xml:space="preserve">1.687460064888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68473374843597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67110347747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016033649445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72289967536926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72835147380829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74470841884613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73107779026031</t>
   </si>
   <si>
     <t xml:space="preserve">1.73925590515137</t>
@@ -182,130 +182,130 @@
     <t xml:space="preserve">1.79923033714294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7774213552475</t>
+    <t xml:space="preserve">1.77742147445679</t>
   </si>
   <si>
     <t xml:space="preserve">1.77196943759918</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652994632721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7965042591095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78832602500916</t>
+    <t xml:space="preserve">1.7365300655365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79650413990021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78832590579987</t>
   </si>
   <si>
     <t xml:space="preserve">1.81831324100494</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82376539707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80468261241913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81558692455292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81286084651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8101350069046</t>
+    <t xml:space="preserve">1.82376503944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80468249320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81558704376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81286072731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81013464927673</t>
   </si>
   <si>
     <t xml:space="preserve">1.79377818107605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84284806251526</t>
+    <t xml:space="preserve">1.84284818172455</t>
   </si>
   <si>
     <t xml:space="preserve">1.8895024061203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87200713157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88075459003448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84576380252838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81952095031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83118462562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86034333705902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87492287158966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87783932685852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8632595539093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88367092609406</t>
+    <t xml:space="preserve">1.87200689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88075506687164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84576404094696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8195207118988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83118450641632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8603435754776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87492299079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87783896923065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86325919628143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88367056846619</t>
   </si>
   <si>
     <t xml:space="preserve">1.80785727500916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76703476905823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79619348049164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79910969734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161418437958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82243680953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78453004360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81660497188568</t>
+    <t xml:space="preserve">1.76703441143036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79619359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79910945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161430358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82243692874908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78453016281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81660509109497</t>
   </si>
   <si>
     <t xml:space="preserve">1.83410024642944</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83701634407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84867978096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86909103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85159552097321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85742771625519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282951831818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89241826534271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88658654689789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89533448219299</t>
+    <t xml:space="preserve">1.83701622486115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84868025779724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86909091472626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85159587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85742747783661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282963752747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.892418384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8865864276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89533400535583</t>
   </si>
   <si>
     <t xml:space="preserve">1.83993184566498</t>
@@ -314,112 +314,112 @@
     <t xml:space="preserve">1.8545116186142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86617529392242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81077313423157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89824998378754</t>
+    <t xml:space="preserve">1.86617517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81077337265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89825022220612</t>
   </si>
   <si>
     <t xml:space="preserve">1.91574573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95365226268768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9624000787735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9244931936264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96531581878662</t>
+    <t xml:space="preserve">1.95365214347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96239995956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92449355125427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96531593799591</t>
   </si>
   <si>
     <t xml:space="preserve">2.00613856315613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00905418395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98281168937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95948421955109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92740952968597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90991353988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95656776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01197028160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00030612945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94490432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94782042503357</t>
+    <t xml:space="preserve">2.00905442237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98281109333038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95948386192322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92740905284882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90991413593292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95656859874725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01197004318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00030660629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94490504264832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9478200674057</t>
   </si>
   <si>
     <t xml:space="preserve">1.90699791908264</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92157733440399</t>
+    <t xml:space="preserve">1.92157745361328</t>
   </si>
   <si>
     <t xml:space="preserve">2.07903599739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0673725605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98864340782166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99447476863861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97406339645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93907308578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93032455444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198858737946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90408217906952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82535302639008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81368911266327</t>
+    <t xml:space="preserve">2.06737208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98864305019379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99447464942932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97406351566315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93907272815704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93032515048981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198846817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90408194065094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82535243034363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81368887424469</t>
   </si>
   <si>
     <t xml:space="preserve">1.79036176204681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82826864719391</t>
+    <t xml:space="preserve">1.8282687664032</t>
   </si>
   <si>
     <t xml:space="preserve">2.02852940559387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90331161022186</t>
+    <t xml:space="preserve">1.90331149101257</t>
   </si>
   <si>
     <t xml:space="preserve">1.89705038070679</t>
@@ -431,196 +431,196 @@
     <t xml:space="preserve">1.87826788425446</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8219199180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79061532020569</t>
+    <t xml:space="preserve">1.82192039489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79061555862427</t>
   </si>
   <si>
     <t xml:space="preserve">1.78435444831848</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75931084156036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74678921699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73426747322083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72800672054291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65287566184998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69044125080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64661514759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60904967784882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62783193588257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66539740562439</t>
+    <t xml:space="preserve">1.75931107997894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74678945541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73426723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72800660133362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65287554264069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69044101238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64661490917206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60904955863953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62783229351044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66539788246155</t>
   </si>
   <si>
     <t xml:space="preserve">1.67791950702667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63409304618835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67165863513947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62157142162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60278856754303</t>
+    <t xml:space="preserve">1.63409328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67165851593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62157106399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60278868675232</t>
   </si>
   <si>
     <t xml:space="preserve">1.68418025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70296311378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69670236110687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.709223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7154848575592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65913677215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64035391807556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61531019210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59652781486511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57148432731628</t>
+    <t xml:space="preserve">1.7029629945755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69670212268829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70922386646271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71548473834991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65913665294647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64035379886627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61531031131744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59652769565582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57148420810699</t>
   </si>
   <si>
     <t xml:space="preserve">1.5652232170105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55896234512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57774519920349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55270171165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58400583267212</t>
+    <t xml:space="preserve">1.55896246433258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5777450799942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55270135402679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58400571346283</t>
   </si>
   <si>
     <t xml:space="preserve">1.77183270454407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81565928459167</t>
+    <t xml:space="preserve">1.81565880775452</t>
   </si>
   <si>
     <t xml:space="preserve">1.8093980550766</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80313730239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77809369564056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74052822589874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76557183265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75305008888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59026682376862</t>
+    <t xml:space="preserve">1.8031370639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77809357643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74052810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76557171344757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75304996967316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59026694297791</t>
   </si>
   <si>
     <t xml:space="preserve">1.47757077217102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.364874958992</t>
+    <t xml:space="preserve">1.36487483978271</t>
   </si>
   <si>
     <t xml:space="preserve">1.54644060134888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50261449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38365745544434</t>
+    <t xml:space="preserve">1.50261437892914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38365733623505</t>
   </si>
   <si>
     <t xml:space="preserve">1.40244019031525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32104825973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30226576328278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3273092508316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33357048034668</t>
+    <t xml:space="preserve">1.32104861736298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30226588249207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32730913162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3335702419281</t>
   </si>
   <si>
     <t xml:space="preserve">1.28348302841187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29600489139557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28974378108978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3398312330246</t>
+    <t xml:space="preserve">1.2960045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28974390029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33983099460602</t>
   </si>
   <si>
     <t xml:space="preserve">1.3523530960083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.31478750705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609222412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43374454975128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38991820812225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39617919921875</t>
+    <t xml:space="preserve">1.31478762626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3460921049118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43374443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38991808891296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39617908000946</t>
   </si>
   <si>
     <t xml:space="preserve">1.45878803730011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42122256755829</t>
+    <t xml:space="preserve">1.42122268676758</t>
   </si>
   <si>
     <t xml:space="preserve">1.37739646434784</t>
@@ -629,52 +629,52 @@
     <t xml:space="preserve">1.41496181488037</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44000542163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626617431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42748367786407</t>
+    <t xml:space="preserve">1.4400053024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626641273499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42748355865479</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391873836517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40870070457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45252728462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51513636112213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72174561023712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8586357831955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80514979362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65806341171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64469194412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61126327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63800621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61794900894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457766056061</t>
+    <t xml:space="preserve">1.40870106220245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45252704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51513612270355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72174525260925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85863542556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8051495552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65806329250336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6446920633316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61126339435577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63800609111786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61794877052307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457754135132</t>
   </si>
   <si>
     <t xml:space="preserve">1.5711487531662</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">1.65137767791748</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63132083415985</t>
+    <t xml:space="preserve">1.63132047653198</t>
   </si>
   <si>
     <t xml:space="preserve">1.66474914550781</t>
@@ -692,37 +692,37 @@
     <t xml:space="preserve">1.62463486194611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67143499851227</t>
+    <t xml:space="preserve">1.67143476009369</t>
   </si>
   <si>
     <t xml:space="preserve">1.68480634689331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69817769527435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59120607376099</t>
+    <t xml:space="preserve">1.69817793369293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59120619297028</t>
   </si>
   <si>
     <t xml:space="preserve">1.55777728557587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52434861660004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51766264438629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5310343503952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54440557956696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55109179019928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53772020339966</t>
+    <t xml:space="preserve">1.52434849739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51766288280487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53103423118591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54440605640411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55109131336212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53772008419037</t>
   </si>
   <si>
     <t xml:space="preserve">1.57783460617065</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">1.58451998233795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56446278095245</t>
+    <t xml:space="preserve">1.56446290016174</t>
   </si>
   <si>
     <t xml:space="preserve">1.49760580062866</t>
@@ -740,28 +740,28 @@
     <t xml:space="preserve">1.51097702980042</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59789204597473</t>
+    <t xml:space="preserve">1.59789180755615</t>
   </si>
   <si>
     <t xml:space="preserve">1.50429141521454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49091994762421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48423409461975</t>
+    <t xml:space="preserve">1.49091982841492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48423397541046</t>
   </si>
   <si>
     <t xml:space="preserve">1.47754848003387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47086262702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417701244354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44411981105804</t>
+    <t xml:space="preserve">1.470862865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417689323425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44411993026733</t>
   </si>
   <si>
     <t xml:space="preserve">1.45080554485321</t>
@@ -770,154 +770,154 @@
     <t xml:space="preserve">1.43074822425842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41737675666809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36389088630676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33046209812164</t>
+    <t xml:space="preserve">1.41737651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36389076709747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33046221733093</t>
   </si>
   <si>
     <t xml:space="preserve">1.34383368492126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3371479511261</t>
+    <t xml:space="preserve">1.33714783191681</t>
   </si>
   <si>
     <t xml:space="preserve">1.32377636432648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32043349742889</t>
+    <t xml:space="preserve">1.32043361663818</t>
   </si>
   <si>
     <t xml:space="preserve">1.67812073230743</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73829221725464</t>
+    <t xml:space="preserve">1.73829233646393</t>
   </si>
   <si>
     <t xml:space="preserve">1.77172112464905</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75166356563568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74497783184052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73160648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76503527164459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78509259223938</t>
+    <t xml:space="preserve">1.75166368484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74497818946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73160624504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76503491401672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78509247303009</t>
   </si>
   <si>
     <t xml:space="preserve">1.79177832603455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75834965705872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79846429824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520699501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85194969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86532127857208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87869274616241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89206445217133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91212153434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92549312114716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89874982833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83857846260071</t>
+    <t xml:space="preserve">1.75834953784943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79846394062042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520687580109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85194957256317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86532163619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87869298458099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89206421375275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91212165355682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92549288272858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89874994754791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83857810497284</t>
   </si>
   <si>
     <t xml:space="preserve">1.90543568134308</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88537883758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91880702972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96560740470886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99903631210327</t>
+    <t xml:space="preserve">1.88537847995758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9188072681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96560764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99903607368469</t>
   </si>
   <si>
     <t xml:space="preserve">1.99235022068024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01240754127502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98566448688507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9789787530899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00572204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909327507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02577877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0324649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04629135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05320429801941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08085680007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03937816619873</t>
+    <t xml:space="preserve">2.0124077796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98566460609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97897887229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00572180747986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02577900886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03246474266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04629111289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05320453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08085703849792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03937792778015</t>
   </si>
   <si>
     <t xml:space="preserve">2.08776998519897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06011748313904</t>
+    <t xml:space="preserve">2.06011724472046</t>
   </si>
   <si>
     <t xml:space="preserve">2.06703066825867</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07394337654114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10850954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12233519554138</t>
+    <t xml:space="preserve">2.07394361495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1085090637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12233567237854</t>
   </si>
   <si>
     <t xml:space="preserve">2.17072796821594</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">2.20529365539551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19146728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16381454467773</t>
+    <t xml:space="preserve">2.19146752357483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16381430625916</t>
   </si>
   <si>
     <t xml:space="preserve">2.14307498931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764091491699</t>
+    <t xml:space="preserve">2.17764115333557</t>
   </si>
   <si>
     <t xml:space="preserve">2.18455410003662</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">2.22603297233582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21220660209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23294568061829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23985886573792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25368523597717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2605984210968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26751208305359</t>
+    <t xml:space="preserve">2.21220636367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23294591903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23985910415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25368547439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26059865951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26751136779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.27442502975464</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">2.24677228927612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30899047851562</t>
+    <t xml:space="preserve">2.30899024009705</t>
   </si>
   <si>
     <t xml:space="preserve">2.32973027229309</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">2.31590366363525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32281708717346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33664298057556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34355616569519</t>
+    <t xml:space="preserve">2.32281684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33664321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34355640411377</t>
   </si>
   <si>
     <t xml:space="preserve">2.38503527641296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37120890617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43342709541321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44725346565247</t>
+    <t xml:space="preserve">2.37120866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43342733383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44725370407104</t>
   </si>
   <si>
     <t xml:space="preserve">2.5163848400116</t>
@@ -1013,25 +1013,25 @@
     <t xml:space="preserve">2.48873257637024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49564528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.564777135849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55786371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54403781890869</t>
+    <t xml:space="preserve">2.49564552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56477665901184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55786395072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54403758049011</t>
   </si>
   <si>
     <t xml:space="preserve">2.57169008255005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5232982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53021121025085</t>
+    <t xml:space="preserve">2.52329802513123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53021168708801</t>
   </si>
   <si>
     <t xml:space="preserve">2.55095076560974</t>
@@ -1040,25 +1040,25 @@
     <t xml:space="preserve">2.58551645278931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59242939949036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63390827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62699508666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65464758872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64773488044739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62008237838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64082145690918</t>
+    <t xml:space="preserve">2.59242963790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63390851020813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6269953250885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65464782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64773440361023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62008213996887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64082169532776</t>
   </si>
   <si>
     <t xml:space="preserve">2.61316871643066</t>
@@ -1070,25 +1070,25 @@
     <t xml:space="preserve">2.64100790023804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69780349731445</t>
+    <t xml:space="preserve">2.69780373573303</t>
   </si>
   <si>
     <t xml:space="preserve">2.74040055274963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79009699821472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76879835128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74749994277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73330140113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76169919967651</t>
+    <t xml:space="preserve">2.7900972366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.768798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74750018119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73330116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76169896125793</t>
   </si>
   <si>
     <t xml:space="preserve">2.71200275421143</t>
@@ -1097,109 +1097,109 @@
     <t xml:space="preserve">2.65520691871643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63390851020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68360447883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62680888175964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64810752868652</t>
+    <t xml:space="preserve">2.63390874862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68360495567322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62680912017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6481077671051</t>
   </si>
   <si>
     <t xml:space="preserve">2.67650532722473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66940593719482</t>
+    <t xml:space="preserve">2.6694061756134</t>
   </si>
   <si>
     <t xml:space="preserve">2.70490312576294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75459980964661</t>
+    <t xml:space="preserve">2.75459957122803</t>
   </si>
   <si>
     <t xml:space="preserve">2.71910238265991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72620153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6907045841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56291341781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55581426620483</t>
+    <t xml:space="preserve">2.72620177268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69070410728455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56291389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55581402778625</t>
   </si>
   <si>
     <t xml:space="preserve">2.59841108322144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79719662666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54871487617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49191880226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062063217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37832689285278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25763583183289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17244172096252</t>
+    <t xml:space="preserve">2.79719686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54871439933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49191904067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062039375305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37832713127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25763607025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1724419593811</t>
   </si>
   <si>
     <t xml:space="preserve">2.21503877639771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34282946586609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34992933273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48481917381287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59131169319153</t>
+    <t xml:space="preserve">2.34282970428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34992909431458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48481893539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59131145477295</t>
   </si>
   <si>
     <t xml:space="preserve">2.47771978378296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60551023483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81139588356018</t>
+    <t xml:space="preserve">2.60551047325134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8113956451416</t>
   </si>
   <si>
     <t xml:space="preserve">2.82559442520142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88239026069641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86819100379944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89658951759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87529134750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83979368209839</t>
+    <t xml:space="preserve">2.88239049911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86819171905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8965892791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87529110908508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83979320526123</t>
   </si>
   <si>
     <t xml:space="preserve">2.78299784660339</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">2.8894898891449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81849479675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83269429206848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85399270057678</t>
+    <t xml:space="preserve">2.81849527359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8326940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85399222373962</t>
   </si>
   <si>
     <t xml:space="preserve">2.98100280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95111775398254</t>
+    <t xml:space="preserve">2.95111799240112</t>
   </si>
   <si>
     <t xml:space="preserve">2.9735312461853</t>
@@ -1232,22 +1232,22 @@
     <t xml:space="preserve">2.94364666938782</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91376161575317</t>
+    <t xml:space="preserve">2.91376209259033</t>
   </si>
   <si>
     <t xml:space="preserve">2.87640595436096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81663632392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83904981613159</t>
+    <t xml:space="preserve">2.81663656234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83905005455017</t>
   </si>
   <si>
     <t xml:space="preserve">2.70456862449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59997224807739</t>
+    <t xml:space="preserve">2.59997200965881</t>
   </si>
   <si>
     <t xml:space="preserve">2.61491441726685</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">2.62238574028015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65227007865906</t>
+    <t xml:space="preserve">2.65227031707764</t>
   </si>
   <si>
     <t xml:space="preserve">2.62985682487488</t>
@@ -1268,10 +1268,10 @@
     <t xml:space="preserve">2.65974164009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63732814788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57008767127991</t>
+    <t xml:space="preserve">2.6373279094696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57008743286133</t>
   </si>
   <si>
     <t xml:space="preserve">2.58502984046936</t>
@@ -1280,49 +1280,49 @@
     <t xml:space="preserve">2.57755875587463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5551450252533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52526021003723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59250092506409</t>
+    <t xml:space="preserve">2.55514526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52526044845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59250116348267</t>
   </si>
   <si>
     <t xml:space="preserve">2.54767394065857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50284647941589</t>
+    <t xml:space="preserve">2.50284671783447</t>
   </si>
   <si>
     <t xml:space="preserve">2.47296214103699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45801973342896</t>
+    <t xml:space="preserve">2.45801949501038</t>
   </si>
   <si>
     <t xml:space="preserve">2.49537539482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46549081802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48790454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48043322563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53273153305054</t>
+    <t xml:space="preserve">2.4654905796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48790431022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48043346405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53273177146912</t>
   </si>
   <si>
     <t xml:space="preserve">2.40572118759155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43560600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37583661079407</t>
+    <t xml:space="preserve">2.43560576438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37583684921265</t>
   </si>
   <si>
     <t xml:space="preserve">2.3907790184021</t>
@@ -1331,22 +1331,22 @@
     <t xml:space="preserve">2.42813491821289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44307732582092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41319227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39825010299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42066335678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64479923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71951103210449</t>
+    <t xml:space="preserve">2.44307708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41319251060486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39825034141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42066359519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64479947090149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71951127052307</t>
   </si>
   <si>
     <t xml:space="preserve">2.73445343971252</t>
@@ -1355,52 +1355,55 @@
     <t xml:space="preserve">2.74939608573914</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75686717033386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74192452430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77928042411804</t>
+    <t xml:space="preserve">2.75686693191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74192476272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77928066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79422307014465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81757283210754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82535672187805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84870648384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84092307090759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80978941917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87983989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88762331008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89540648460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87205624580383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80200624465942</t>
   </si>
   <si>
     <t xml:space="preserve">2.79422283172607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81757283210754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82535624504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84870648384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84092307090759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80978965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87983989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88762307167053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8954062461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87205648422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.802006483078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83313989639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86427330970764</t>
+    <t xml:space="preserve">2.83313965797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86427307128906</t>
   </si>
   <si>
     <t xml:space="preserve">2.85648989677429</t>
@@ -1409,7 +1412,7 @@
     <t xml:space="preserve">2.91875648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92654013633728</t>
+    <t xml:space="preserve">2.9265398979187</t>
   </si>
   <si>
     <t xml:space="preserve">2.90318989753723</t>
@@ -1424,19 +1427,19 @@
     <t xml:space="preserve">3.00437331199646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94210648536682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97323989868164</t>
+    <t xml:space="preserve">2.9421067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97323966026306</t>
   </si>
   <si>
     <t xml:space="preserve">2.910973072052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94988989830017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95767307281494</t>
+    <t xml:space="preserve">2.94988965988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9576735496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.03550672531128</t>
@@ -1445,7 +1448,7 @@
     <t xml:space="preserve">2.99659013748169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96545648574829</t>
+    <t xml:space="preserve">2.96545672416687</t>
   </si>
   <si>
     <t xml:space="preserve">3.04329013824463</t>
@@ -1454,28 +1457,28 @@
     <t xml:space="preserve">3.05107378959656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01993989944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07442378997803</t>
+    <t xml:space="preserve">3.01994013786316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07442355155945</t>
   </si>
   <si>
     <t xml:space="preserve">3.02772355079651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98102355003357</t>
+    <t xml:space="preserve">2.98102307319641</t>
   </si>
   <si>
     <t xml:space="preserve">3.16004037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08998990058899</t>
+    <t xml:space="preserve">3.08999013900757</t>
   </si>
   <si>
     <t xml:space="preserve">3.0822069644928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0666401386261</t>
+    <t xml:space="preserve">3.06664037704468</t>
   </si>
   <si>
     <t xml:space="preserve">3.05885696411133</t>
@@ -1484,7 +1487,7 @@
     <t xml:space="preserve">3.09777355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11416387557983</t>
+    <t xml:space="preserve">3.11416411399841</t>
   </si>
   <si>
     <t xml:space="preserve">3.13055419921875</t>
@@ -1499,25 +1502,25 @@
     <t xml:space="preserve">3.07318806648254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08957839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04040741920471</t>
+    <t xml:space="preserve">3.08957862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04040718078613</t>
   </si>
   <si>
     <t xml:space="preserve">3.03221225738525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04860258102417</t>
+    <t xml:space="preserve">3.04860234260559</t>
   </si>
   <si>
     <t xml:space="preserve">3.05679774284363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01582217216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0240170955658</t>
+    <t xml:space="preserve">3.01582169532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02401733398438</t>
   </si>
   <si>
     <t xml:space="preserve">3.00762677192688</t>
@@ -1526,43 +1529,43 @@
     <t xml:space="preserve">3.08138346672058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99943137168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99123620986938</t>
+    <t xml:space="preserve">2.99943161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99123644828796</t>
   </si>
   <si>
     <t xml:space="preserve">2.97484612464905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96665072441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95845580101013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98304128646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026063919067</t>
+    <t xml:space="preserve">2.96665096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95845556259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98304104804993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026040077209</t>
   </si>
   <si>
     <t xml:space="preserve">2.93387007713318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90108942985535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9256751537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94206547737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87650394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86830854415894</t>
+    <t xml:space="preserve">2.90108966827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92567491531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94206523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87650418281555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86830902099609</t>
   </si>
   <si>
     <t xml:space="preserve">2.81094288825989</t>
@@ -1574,13 +1577,13 @@
     <t xml:space="preserve">2.79455256462097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78635740280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80274772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76177167892456</t>
+    <t xml:space="preserve">2.78635716438293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80274748802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76177144050598</t>
   </si>
   <si>
     <t xml:space="preserve">2.84372329711914</t>
@@ -1589,13 +1592,13 @@
     <t xml:space="preserve">2.86011362075806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81913805007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9092845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8519184589386</t>
+    <t xml:space="preserve">2.81913781166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90928483009338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85191869735718</t>
   </si>
   <si>
     <t xml:space="preserve">2.88469934463501</t>
@@ -1613,22 +1616,22 @@
     <t xml:space="preserve">3.04215836524963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01652240753174</t>
+    <t xml:space="preserve">3.01652264595032</t>
   </si>
   <si>
     <t xml:space="preserve">3.03361296653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05070400238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05924916267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07634019851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11906695365906</t>
+    <t xml:space="preserve">3.05070376396179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05924940109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07633996009827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11906719207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.12761235237122</t>
@@ -1637,19 +1640,19 @@
     <t xml:space="preserve">3.14470338821411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16179394721985</t>
+    <t xml:space="preserve">3.16179418563843</t>
   </si>
   <si>
     <t xml:space="preserve">3.15324854850769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17033934593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11052179336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.084885597229</t>
+    <t xml:space="preserve">3.17033958435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1105215549469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08488535881042</t>
   </si>
   <si>
     <t xml:space="preserve">3.10197639465332</t>
@@ -1667,7 +1670,7 @@
     <t xml:space="preserve">3.19597554206848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21306657791138</t>
+    <t xml:space="preserve">3.2130663394928</t>
   </si>
   <si>
     <t xml:space="preserve">3.23870253562927</t>
@@ -1676,16 +1679,16 @@
     <t xml:space="preserve">3.23015713691711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25579309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34979271888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30706548690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35833811759949</t>
+    <t xml:space="preserve">3.25579333305359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34979248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30706524848938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35833787918091</t>
   </si>
   <si>
     <t xml:space="preserve">3.36688327789307</t>
@@ -1694,28 +1697,28 @@
     <t xml:space="preserve">3.33270168304443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40106463432312</t>
+    <t xml:space="preserve">3.4010648727417</t>
   </si>
   <si>
     <t xml:space="preserve">3.42670130729675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31561088562012</t>
+    <t xml:space="preserve">3.3156111240387</t>
   </si>
   <si>
     <t xml:space="preserve">3.28997468948364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29851984977722</t>
+    <t xml:space="preserve">3.2985200881958</t>
   </si>
   <si>
     <t xml:space="preserve">3.38397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32415652275085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3754289150238</t>
+    <t xml:space="preserve">3.32415628433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542867660522</t>
   </si>
   <si>
     <t xml:space="preserve">3.41815567016602</t>
@@ -1724,43 +1727,46 @@
     <t xml:space="preserve">3.43524646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40961050987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45233702659607</t>
+    <t xml:space="preserve">3.40961027145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45233726501465</t>
   </si>
   <si>
     <t xml:space="preserve">3.44379186630249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46942806243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5036096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57197260856628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52070021629333</t>
+    <t xml:space="preserve">3.46942782402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50360941886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57197237014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52070045471191</t>
   </si>
   <si>
     <t xml:space="preserve">3.51215505599976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46088266372681</t>
+    <t xml:space="preserve">3.46088290214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4865186214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49550485610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51347637176514</t>
   </si>
   <si>
     <t xml:space="preserve">3.48651885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49550485610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51347661018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50449061393738</t>
+    <t xml:space="preserve">3.50449085235596</t>
   </si>
   <si>
     <t xml:space="preserve">3.59434938430786</t>
@@ -1769,31 +1775,31 @@
     <t xml:space="preserve">3.53144836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43260335922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46854686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47753286361694</t>
+    <t xml:space="preserve">3.43260359764099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46854710578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47753310203552</t>
   </si>
   <si>
     <t xml:space="preserve">3.45057535171509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37868857383728</t>
+    <t xml:space="preserve">3.3786883354187</t>
   </si>
   <si>
     <t xml:space="preserve">3.34274482727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42361760139465</t>
+    <t xml:space="preserve">3.42361783981323</t>
   </si>
   <si>
     <t xml:space="preserve">3.38767433166504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44158959388733</t>
+    <t xml:space="preserve">3.44158935546875</t>
   </si>
   <si>
     <t xml:space="preserve">3.40564608573914</t>
@@ -1811,7 +1817,7 @@
     <t xml:space="preserve">3.54043412208557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3607165813446</t>
+    <t xml:space="preserve">3.36071681976318</t>
   </si>
   <si>
     <t xml:space="preserve">3.41463184356689</t>
@@ -1832,7 +1838,7 @@
     <t xml:space="preserve">3.56739163398743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68420815467834</t>
+    <t xml:space="preserve">3.68420791625977</t>
   </si>
   <si>
     <t xml:space="preserve">3.7111656665802</t>
@@ -1841,13 +1847,13 @@
     <t xml:space="preserve">3.7291374206543</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74710917472839</t>
+    <t xml:space="preserve">3.74710941314697</t>
   </si>
   <si>
     <t xml:space="preserve">3.67522239685059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72015142440796</t>
+    <t xml:space="preserve">3.72015166282654</t>
   </si>
   <si>
     <t xml:space="preserve">3.70217967033386</t>
@@ -1856,10 +1862,10 @@
     <t xml:space="preserve">3.75609493255615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81899619102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81001043319702</t>
+    <t xml:space="preserve">3.8189959526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81001019477844</t>
   </si>
   <si>
     <t xml:space="preserve">3.80102443695068</t>
@@ -1868,31 +1874,31 @@
     <t xml:space="preserve">3.78305292129517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83696746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84595370292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82798218727112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76508069038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73812341690063</t>
+    <t xml:space="preserve">3.83696818351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84595394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8279824256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76508092880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73812317848206</t>
   </si>
   <si>
     <t xml:space="preserve">3.73778820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77507305145264</t>
+    <t xml:space="preserve">3.77507281303406</t>
   </si>
   <si>
     <t xml:space="preserve">3.71914577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68186092376709</t>
+    <t xml:space="preserve">3.68186116218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.66321873664856</t>
@@ -1904,7 +1910,7 @@
     <t xml:space="preserve">3.69118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75643038749695</t>
+    <t xml:space="preserve">3.75643062591553</t>
   </si>
   <si>
     <t xml:space="preserve">3.7657516002655</t>
@@ -1916,34 +1922,34 @@
     <t xml:space="preserve">3.93353247642517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80303597450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88692665100098</t>
+    <t xml:space="preserve">3.80303621292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88692688941956</t>
   </si>
   <si>
     <t xml:space="preserve">3.84032082557678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8123574256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82167863845825</t>
+    <t xml:space="preserve">3.81235766410828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82167840003967</t>
   </si>
   <si>
     <t xml:space="preserve">3.83099985122681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87760519981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90556883811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91489028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96149611473083</t>
+    <t xml:space="preserve">3.87760543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90556907653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91488981246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96149587631226</t>
   </si>
   <si>
     <t xml:space="preserve">4.00810194015503</t>
@@ -1955,13 +1961,13 @@
     <t xml:space="preserve">4.04538679122925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01742267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03606557846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98013830184937</t>
+    <t xml:space="preserve">4.01742315292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03606510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98013854026794</t>
   </si>
   <si>
     <t xml:space="preserve">4.07334995269775</t>
@@ -1970,7 +1976,7 @@
     <t xml:space="preserve">4.09199237823486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11063432693481</t>
+    <t xml:space="preserve">4.11063480377197</t>
   </si>
   <si>
     <t xml:space="preserve">4.1758828163147</t>
@@ -1985,13 +1991,13 @@
     <t xml:space="preserve">3.9894597530365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9428539276123</t>
+    <t xml:space="preserve">3.94285368919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.9521746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97081732749939</t>
+    <t xml:space="preserve">3.97081756591797</t>
   </si>
   <si>
     <t xml:space="preserve">4.06402921676636</t>
@@ -2003,16 +2009,16 @@
     <t xml:space="preserve">4.11995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70050358772278</t>
+    <t xml:space="preserve">3.7005033493042</t>
   </si>
   <si>
     <t xml:space="preserve">3.68652153015137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90090847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92887210845947</t>
+    <t xml:space="preserve">3.90090823173523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92887234687805</t>
   </si>
   <si>
     <t xml:space="preserve">3.9242115020752</t>
@@ -2316,6 +2322,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.82000017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78999996185303</t>
   </si>
 </sst>
 </file>
@@ -36030,7 +36039,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1284" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36082,7 +36091,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1286" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36108,7 +36117,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1287" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36186,7 +36195,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36290,7 +36299,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1294" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36368,7 +36377,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1297" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36446,7 +36455,7 @@
         <v>3.75</v>
       </c>
       <c r="G1300" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36472,7 +36481,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1301" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36498,7 +36507,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1302" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36524,7 +36533,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1303" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36550,7 +36559,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1304" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36576,7 +36585,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1305" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36602,7 +36611,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1306" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36628,7 +36637,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1307" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36654,7 +36663,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36706,7 +36715,7 @@
         <v>3.75</v>
       </c>
       <c r="G1310" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36732,7 +36741,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36758,7 +36767,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1312" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36784,7 +36793,7 @@
         <v>3.75</v>
       </c>
       <c r="G1313" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36810,7 +36819,7 @@
         <v>3.75</v>
       </c>
       <c r="G1314" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36914,7 +36923,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36940,7 +36949,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36966,7 +36975,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36992,7 +37001,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1321" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37018,7 +37027,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1322" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37044,7 +37053,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1323" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37070,7 +37079,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1324" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37096,7 +37105,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1325" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37122,7 +37131,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1326" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37148,7 +37157,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1327" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37174,7 +37183,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1328" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37200,7 +37209,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1329" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37226,7 +37235,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37252,7 +37261,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1331" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37278,7 +37287,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1332" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37304,7 +37313,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1333" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37330,7 +37339,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1334" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37356,7 +37365,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37382,7 +37391,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1336" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37408,7 +37417,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1337" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37434,7 +37443,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1338" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37460,7 +37469,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37486,7 +37495,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1340" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37512,7 +37521,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1341" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37538,7 +37547,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1342" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37564,7 +37573,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1343" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37590,7 +37599,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37616,7 +37625,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1345" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37642,7 +37651,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1346" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37668,7 +37677,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37720,7 +37729,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1349" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37746,7 +37755,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1350" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37772,7 +37781,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1351" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37798,7 +37807,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1352" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37824,7 +37833,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1353" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37850,7 +37859,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37876,7 +37885,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1355" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37902,7 +37911,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1356" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37928,7 +37937,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1357" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37954,7 +37963,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1358" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37980,7 +37989,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1359" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38006,7 +38015,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1360" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38032,7 +38041,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1361" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38058,7 +38067,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1362" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38084,7 +38093,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1363" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38110,7 +38119,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1364" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38136,7 +38145,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1365" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38162,7 +38171,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1366" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38188,7 +38197,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38214,7 +38223,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1368" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38240,7 +38249,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38266,7 +38275,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1370" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38292,7 +38301,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1371" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38318,7 +38327,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38344,7 +38353,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1373" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38370,7 +38379,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1374" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38396,7 +38405,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1375" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38422,7 +38431,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38448,7 +38457,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1377" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38474,7 +38483,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1378" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38500,7 +38509,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1379" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38526,7 +38535,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1380" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38552,7 +38561,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38578,7 +38587,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1382" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38604,7 +38613,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38630,7 +38639,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1384" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38656,7 +38665,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1385" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38682,7 +38691,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1386" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38708,7 +38717,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38734,7 +38743,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1388" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38760,7 +38769,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38786,7 +38795,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1390" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38812,7 +38821,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38838,7 +38847,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1392" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38864,7 +38873,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1393" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38890,7 +38899,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38916,7 +38925,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1395" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38942,7 +38951,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1396" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38968,7 +38977,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1397" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38994,7 +39003,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1398" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39020,7 +39029,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1399" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39046,7 +39055,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1400" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39072,7 +39081,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1401" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39098,7 +39107,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1402" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39124,7 +39133,7 @@
         <v>3.75</v>
       </c>
       <c r="G1403" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39150,7 +39159,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39176,7 +39185,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1405" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39202,7 +39211,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1406" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39228,7 +39237,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1407" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39254,7 +39263,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1408" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39280,7 +39289,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1409" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39306,7 +39315,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1410" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39332,7 +39341,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1411" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39358,7 +39367,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1412" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39384,7 +39393,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1413" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39410,7 +39419,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1414" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39436,7 +39445,7 @@
         <v>3.75</v>
       </c>
       <c r="G1415" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39462,7 +39471,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39488,7 +39497,7 @@
         <v>3.75</v>
       </c>
       <c r="G1417" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39514,7 +39523,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1418" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39540,7 +39549,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39566,7 +39575,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1420" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39592,7 +39601,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1421" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39618,7 +39627,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1422" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39644,7 +39653,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39670,7 +39679,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1424" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39696,7 +39705,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1425" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39722,7 +39731,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1426" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39748,7 +39757,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1427" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39774,7 +39783,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1428" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39800,7 +39809,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39826,7 +39835,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1430" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39852,7 +39861,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39878,7 +39887,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39904,7 +39913,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1433" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39930,7 +39939,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39956,7 +39965,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1435" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39982,7 +39991,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1436" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40008,7 +40017,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1437" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40034,7 +40043,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1438" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40060,7 +40069,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1439" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40086,7 +40095,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40112,7 +40121,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1441" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40138,7 +40147,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40164,7 +40173,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1443" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40190,7 +40199,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1444" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40216,7 +40225,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1445" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40242,7 +40251,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1446" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40268,7 +40277,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1447" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40294,7 +40303,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1448" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40320,7 +40329,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1449" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40346,7 +40355,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1450" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40372,7 +40381,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1451" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40398,7 +40407,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1452" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40424,7 +40433,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40450,7 +40459,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40476,7 +40485,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40502,7 +40511,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40528,7 +40537,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1457" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40554,7 +40563,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40580,7 +40589,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1459" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40606,7 +40615,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1460" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40632,7 +40641,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40658,7 +40667,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1462" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40684,7 +40693,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40710,7 +40719,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1464" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40736,7 +40745,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40762,7 +40771,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1466" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40788,7 +40797,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1467" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40814,7 +40823,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1468" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40840,7 +40849,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1469" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40866,7 +40875,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1470" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40892,7 +40901,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1471" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40918,7 +40927,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1472" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40944,7 +40953,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1473" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40970,7 +40979,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40996,7 +41005,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1475" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41022,7 +41031,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1476" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41048,7 +41057,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1477" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41074,7 +41083,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1478" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41100,7 +41109,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1479" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41126,7 +41135,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41152,7 +41161,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41178,7 +41187,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1482" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41204,7 +41213,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1483" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41230,7 +41239,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1484" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41256,7 +41265,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1485" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41282,7 +41291,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1486" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41308,7 +41317,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1487" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41334,7 +41343,7 @@
         <v>3.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41360,7 +41369,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1489" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41386,7 +41395,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41412,7 +41421,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1491" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41438,7 +41447,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1492" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41464,7 +41473,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41490,7 +41499,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1494" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41516,7 +41525,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1495" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41542,7 +41551,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1496" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41568,7 +41577,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1497" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41594,7 +41603,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1498" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41620,7 +41629,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1499" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41646,7 +41655,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1500" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41672,7 +41681,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1501" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41698,7 +41707,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41724,7 +41733,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1503" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41750,7 +41759,7 @@
         <v>3.5</v>
       </c>
       <c r="G1504" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41776,7 +41785,7 @@
         <v>3.5</v>
       </c>
       <c r="G1505" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41802,7 +41811,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1506" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41828,7 +41837,7 @@
         <v>3.5</v>
       </c>
       <c r="G1507" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41854,7 +41863,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1508" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41880,7 +41889,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1509" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41906,7 +41915,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1510" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41932,7 +41941,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1511" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41958,7 +41967,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1512" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41984,7 +41993,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42010,7 +42019,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42036,7 +42045,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42062,7 +42071,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42088,7 +42097,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1517" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42114,7 +42123,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1518" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42140,7 +42149,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1519" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42166,7 +42175,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1520" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42192,7 +42201,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42218,7 +42227,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42244,7 +42253,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1523" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42270,7 +42279,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1524" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42296,7 +42305,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1525" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42322,7 +42331,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1526" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42348,7 +42357,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1527" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42374,7 +42383,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1528" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42400,7 +42409,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1529" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42426,7 +42435,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1530" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42452,7 +42461,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1531" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42478,7 +42487,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1532" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42504,7 +42513,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1533" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42530,7 +42539,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1534" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42556,7 +42565,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1535" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42582,7 +42591,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1536" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42608,7 +42617,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1537" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42634,7 +42643,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1538" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42660,7 +42669,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1539" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42686,7 +42695,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1540" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42712,7 +42721,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1541" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42738,7 +42747,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42764,7 +42773,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1543" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42790,7 +42799,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1544" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42816,7 +42825,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1545" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42842,7 +42851,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1546" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42868,7 +42877,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1547" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42894,7 +42903,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1548" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42920,7 +42929,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1549" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42946,7 +42955,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1550" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42972,7 +42981,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1551" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42998,7 +43007,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1552" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43024,7 +43033,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1553" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43050,7 +43059,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1554" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43076,7 +43085,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1555" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43102,7 +43111,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1556" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43128,7 +43137,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1557" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43154,7 +43163,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1558" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43180,7 +43189,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1559" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43206,7 +43215,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1560" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43232,7 +43241,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43258,7 +43267,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1562" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43284,7 +43293,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1563" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43310,7 +43319,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1564" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43336,7 +43345,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1565" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43362,7 +43371,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1566" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43388,7 +43397,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1567" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43414,7 +43423,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1568" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43440,7 +43449,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1569" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43466,7 +43475,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1570" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43492,7 +43501,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1571" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43518,7 +43527,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1572" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43544,7 +43553,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1573" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43570,7 +43579,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1574" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43596,7 +43605,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1575" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43622,7 +43631,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1576" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43648,7 +43657,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1577" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43674,7 +43683,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1578" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43700,7 +43709,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1579" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43726,7 +43735,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1580" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43752,7 +43761,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1581" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43778,7 +43787,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1582" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43804,7 +43813,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1583" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43830,7 +43839,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1584" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43856,7 +43865,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1585" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43882,7 +43891,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1586" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43908,7 +43917,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1587" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43934,7 +43943,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1588" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43960,7 +43969,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1589" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43986,7 +43995,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1590" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44012,7 +44021,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1591" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44038,7 +44047,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1592" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44064,7 +44073,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1593" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44090,7 +44099,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1594" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44116,7 +44125,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1595" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44142,7 +44151,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1596" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44168,7 +44177,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1597" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44194,7 +44203,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1598" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44220,7 +44229,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1599" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44246,7 +44255,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1600" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44272,7 +44281,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44298,7 +44307,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1602" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44324,7 +44333,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44350,7 +44359,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44376,7 +44385,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1605" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44402,7 +44411,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1606" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44428,7 +44437,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1607" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44454,7 +44463,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44480,7 +44489,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1609" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44506,7 +44515,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1610" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44532,7 +44541,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44558,7 +44567,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1612" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44584,7 +44593,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1613" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44610,7 +44619,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44636,7 +44645,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1615" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44662,7 +44671,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1616" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44688,7 +44697,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1617" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44714,7 +44723,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1618" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44740,7 +44749,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1619" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44766,7 +44775,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1620" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44792,7 +44801,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1621" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44818,7 +44827,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1622" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44844,7 +44853,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1623" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44870,7 +44879,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44896,7 +44905,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44922,7 +44931,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44948,7 +44957,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1627" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44974,7 +44983,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1628" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45000,7 +45009,7 @@
         <v>4</v>
       </c>
       <c r="G1629" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45026,7 +45035,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1630" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45052,7 +45061,7 @@
         <v>4</v>
       </c>
       <c r="G1631" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45078,7 +45087,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1632" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45104,7 +45113,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45130,7 +45139,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1634" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45156,7 +45165,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45182,7 +45191,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45208,7 +45217,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1637" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45234,7 +45243,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1638" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45260,7 +45269,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1639" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45286,7 +45295,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1640" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45312,7 +45321,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45338,7 +45347,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1642" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45364,7 +45373,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1643" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45390,7 +45399,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1644" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45416,7 +45425,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1645" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45442,7 +45451,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45468,7 +45477,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1647" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45494,7 +45503,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1648" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45520,7 +45529,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1649" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45546,7 +45555,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1650" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45572,7 +45581,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45598,7 +45607,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1652" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45624,7 +45633,7 @@
         <v>4</v>
       </c>
       <c r="G1653" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45650,7 +45659,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1654" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45676,7 +45685,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1655" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45702,7 +45711,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1656" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45728,7 +45737,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1657" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45754,7 +45763,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1658" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45780,7 +45789,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45806,7 +45815,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45832,7 +45841,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1661" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45858,7 +45867,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1662" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45884,7 +45893,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45910,7 +45919,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1664" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45936,7 +45945,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45962,7 +45971,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1666" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45988,7 +45997,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1667" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46014,7 +46023,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1668" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46040,7 +46049,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1669" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46066,7 +46075,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46092,7 +46101,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1671" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46118,7 +46127,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1672" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46144,7 +46153,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46170,7 +46179,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1674" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46196,7 +46205,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1675" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46222,7 +46231,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1676" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46248,7 +46257,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1677" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46274,7 +46283,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1678" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46300,7 +46309,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1679" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46326,7 +46335,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1680" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46352,7 +46361,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1681" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46378,7 +46387,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1682" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46404,7 +46413,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1683" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46430,7 +46439,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1684" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46456,7 +46465,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1685" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46482,7 +46491,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1686" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46508,7 +46517,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46534,7 +46543,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1688" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46560,7 +46569,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1689" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46586,7 +46595,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1690" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46612,7 +46621,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1691" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46638,7 +46647,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1692" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46664,7 +46673,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1693" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46690,7 +46699,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1694" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46716,7 +46725,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1695" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46742,7 +46751,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1696" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46768,7 +46777,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1697" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46794,7 +46803,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46820,7 +46829,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1699" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46846,7 +46855,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1700" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46872,7 +46881,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1701" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46898,7 +46907,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1702" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46924,7 +46933,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1703" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46950,7 +46959,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1704" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46976,7 +46985,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47002,7 +47011,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47028,7 +47037,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47054,7 +47063,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1708" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47080,7 +47089,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1709" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47106,7 +47115,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1710" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47132,7 +47141,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47158,7 +47167,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1712" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47184,7 +47193,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1713" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47210,7 +47219,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47236,7 +47245,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1715" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47262,7 +47271,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1716" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47288,7 +47297,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47314,7 +47323,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1718" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47340,7 +47349,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47366,7 +47375,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1720" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47392,7 +47401,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47418,7 +47427,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1722" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47444,7 +47453,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1723" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47470,7 +47479,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1724" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47496,7 +47505,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1725" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47522,7 +47531,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47548,7 +47557,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1727" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47574,7 +47583,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1728" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47600,7 +47609,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1729" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47626,7 +47635,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1730" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47652,7 +47661,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1731" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47678,7 +47687,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1732" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47704,7 +47713,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1733" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47730,7 +47739,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1734" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47756,7 +47765,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1735" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47782,7 +47791,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1736" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47808,7 +47817,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1737" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47834,7 +47843,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1738" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47860,7 +47869,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1739" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47886,7 +47895,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1740" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47912,7 +47921,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1741" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47938,7 +47947,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47964,7 +47973,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1743" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47990,7 +47999,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1744" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48016,7 +48025,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1745" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48042,7 +48051,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1746" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48068,7 +48077,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1747" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48094,7 +48103,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1748" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48120,7 +48129,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1749" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48146,7 +48155,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1750" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48172,7 +48181,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1751" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48198,7 +48207,7 @@
         <v>4.25</v>
       </c>
       <c r="G1752" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48224,7 +48233,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1753" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48250,7 +48259,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1754" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48276,7 +48285,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48302,7 +48311,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1756" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48328,7 +48337,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1757" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48354,7 +48363,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1758" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48380,7 +48389,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1759" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48406,7 +48415,7 @@
         <v>4.25</v>
       </c>
       <c r="G1760" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48432,7 +48441,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48458,7 +48467,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1762" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48484,7 +48493,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1763" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48510,7 +48519,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48536,7 +48545,7 @@
         <v>4.25</v>
       </c>
       <c r="G1765" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48562,7 +48571,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1766" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48588,7 +48597,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48614,7 +48623,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1768" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48640,7 +48649,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48666,7 +48675,7 @@
         <v>4.25</v>
       </c>
       <c r="G1770" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48692,7 +48701,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1771" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48718,7 +48727,7 @@
         <v>4.25</v>
       </c>
       <c r="G1772" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48744,7 +48753,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1773" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48770,7 +48779,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1774" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48796,7 +48805,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1775" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48822,7 +48831,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1776" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48848,7 +48857,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1777" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48874,7 +48883,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1778" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48900,7 +48909,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48926,7 +48935,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1780" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48952,7 +48961,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1781" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48978,7 +48987,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1782" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49004,7 +49013,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1783" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49030,7 +49039,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1784" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49056,7 +49065,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1785" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49082,7 +49091,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1786" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49108,7 +49117,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1787" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49134,7 +49143,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1788" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49160,7 +49169,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1789" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49186,7 +49195,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1790" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49212,7 +49221,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1791" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49238,7 +49247,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1792" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49264,7 +49273,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1793" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49290,7 +49299,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1794" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49316,7 +49325,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49342,7 +49351,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49368,7 +49377,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49394,7 +49403,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49420,7 +49429,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1799" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49446,7 +49455,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1800" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49472,7 +49481,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1801" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49498,7 +49507,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1802" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49524,7 +49533,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49550,7 +49559,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1804" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49576,7 +49585,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1805" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49602,7 +49611,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1806" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49628,7 +49637,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49654,7 +49663,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1808" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49680,7 +49689,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1809" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49706,7 +49715,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1810" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49732,7 +49741,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1811" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49758,7 +49767,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1812" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49784,7 +49793,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1813" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49810,7 +49819,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1814" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49836,7 +49845,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1815" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49862,7 +49871,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1816" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49888,7 +49897,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1817" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49914,7 +49923,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49940,7 +49949,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1819" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49966,7 +49975,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1820" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49992,7 +50001,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1821" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50018,7 +50027,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1822" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50044,7 +50053,7 @@
         <v>4.25</v>
       </c>
       <c r="G1823" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50070,7 +50079,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1824" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50096,7 +50105,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50122,7 +50131,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1826" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50148,7 +50157,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50174,7 +50183,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1828" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50200,7 +50209,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1829" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50226,7 +50235,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1830" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50252,7 +50261,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1831" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50278,7 +50287,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50304,7 +50313,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1833" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50330,7 +50339,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50356,7 +50365,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50382,7 +50391,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1836" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50408,7 +50417,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1837" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50434,7 +50443,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1838" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50460,7 +50469,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1839" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50486,7 +50495,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1840" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50512,7 +50521,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1841" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50538,7 +50547,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1842" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50564,7 +50573,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1843" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50590,7 +50599,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1844" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50616,7 +50625,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1845" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50642,7 +50651,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1846" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50668,7 +50677,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1847" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50694,7 +50703,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50720,7 +50729,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1849" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50746,7 +50755,7 @@
         <v>4.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50772,7 +50781,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1851" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50798,7 +50807,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50824,7 +50833,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1853" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50850,7 +50859,7 @@
         <v>4.25</v>
       </c>
       <c r="G1854" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50876,7 +50885,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1855" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50902,7 +50911,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1856" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50928,7 +50937,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1857" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50954,7 +50963,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1858" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50980,7 +50989,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51006,7 +51015,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1860" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51032,7 +51041,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1861" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51058,7 +51067,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51084,7 +51093,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1863" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51110,7 +51119,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1864" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51136,7 +51145,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1865" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51162,7 +51171,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1866" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51188,7 +51197,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1867" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51214,7 +51223,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1868" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51240,7 +51249,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1869" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51266,7 +51275,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1870" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51292,7 +51301,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1871" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51318,7 +51327,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1872" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51344,7 +51353,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1873" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51370,7 +51379,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1874" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51396,7 +51405,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1875" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51422,7 +51431,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1876" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51448,7 +51457,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1877" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51474,7 +51483,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1878" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51500,7 +51509,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1879" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51526,7 +51535,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1880" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51552,7 +51561,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1881" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51578,7 +51587,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1882" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51604,7 +51613,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1883" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51630,7 +51639,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1884" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51656,7 +51665,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1885" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51682,7 +51691,7 @@
         <v>4.25</v>
       </c>
       <c r="G1886" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51708,7 +51717,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51734,7 +51743,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1888" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51760,7 +51769,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51786,7 +51795,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1890" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51812,7 +51821,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1891" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51838,7 +51847,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1892" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51864,7 +51873,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1893" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51890,7 +51899,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1894" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51916,7 +51925,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1895" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51942,7 +51951,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51968,7 +51977,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1897" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51994,7 +52003,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1898" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52020,7 +52029,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1899" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52046,7 +52055,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1900" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52072,7 +52081,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52098,7 +52107,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1902" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52124,7 +52133,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1903" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52150,7 +52159,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1904" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52176,7 +52185,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1905" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52202,7 +52211,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52228,7 +52237,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52254,7 +52263,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1908" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52280,7 +52289,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1909" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52306,7 +52315,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1910" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52332,7 +52341,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1911" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52358,7 +52367,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52384,7 +52393,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1913" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52410,7 +52419,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1914" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52436,7 +52445,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1915" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52462,7 +52471,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1916" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52488,7 +52497,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1917" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52514,7 +52523,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1918" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52540,7 +52549,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1919" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52566,7 +52575,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1920" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52592,7 +52601,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1921" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52618,7 +52627,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1922" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52644,7 +52653,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G1923" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52670,7 +52679,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1924" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52696,7 +52705,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1925" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52722,7 +52731,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1926" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52748,7 +52757,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1927" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52774,7 +52783,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1928" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52800,7 +52809,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1929" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52826,7 +52835,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52852,7 +52861,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G1931" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52878,7 +52887,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1932" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52904,7 +52913,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1933" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52930,7 +52939,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1934" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52956,7 +52965,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1935" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52982,7 +52991,7 @@
         <v>4.5</v>
       </c>
       <c r="G1936" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53008,7 +53017,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1937" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53034,7 +53043,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1938" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53060,7 +53069,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1939" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53086,7 +53095,7 @@
         <v>4.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53112,7 +53121,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1941" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53138,7 +53147,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1942" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53164,7 +53173,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1943" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53190,7 +53199,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53216,7 +53225,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1945" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53242,7 +53251,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1946" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53268,7 +53277,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53294,7 +53303,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1948" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53320,7 +53329,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1949" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53346,7 +53355,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1950" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53372,7 +53381,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1951" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53398,7 +53407,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1952" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53424,7 +53433,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1953" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53450,7 +53459,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53476,7 +53485,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1955" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53502,7 +53511,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1956" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53528,7 +53537,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53554,7 +53563,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1958" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53580,7 +53589,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53606,7 +53615,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53632,7 +53641,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1961" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53658,7 +53667,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1962" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53684,7 +53693,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53710,7 +53719,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53736,7 +53745,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G1965" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53762,7 +53771,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1966" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53788,7 +53797,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1967" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53814,7 +53823,7 @@
         <v>5</v>
       </c>
       <c r="G1968" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53840,7 +53849,7 @@
         <v>5</v>
       </c>
       <c r="G1969" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53866,7 +53875,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1970" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53892,7 +53901,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1971" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53918,7 +53927,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G1972" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53944,7 +53953,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1973" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53970,7 +53979,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53996,7 +54005,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54022,7 +54031,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1976" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54048,7 +54057,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1977" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54074,7 +54083,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1978" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54100,7 +54109,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1979" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54126,7 +54135,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54152,7 +54161,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1981" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54178,7 +54187,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1982" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54204,7 +54213,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1983" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54230,7 +54239,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1984" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54256,7 +54265,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1985" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54282,7 +54291,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1986" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54308,7 +54317,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1987" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54334,7 +54343,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54360,7 +54369,7 @@
         <v>5.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54386,7 +54395,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1990" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54412,7 +54421,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1991" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54438,7 +54447,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54464,7 +54473,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1993" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54490,7 +54499,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1994" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54516,7 +54525,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1995" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54542,7 +54551,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1996" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54568,7 +54577,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1997" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54594,7 +54603,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1998" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54620,7 +54629,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54646,7 +54655,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2000" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54672,7 +54681,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2001" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54698,7 +54707,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G2002" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54724,7 +54733,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54750,7 +54759,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54776,7 +54785,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2005" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54802,7 +54811,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2006" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54828,7 +54837,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2007" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54854,7 +54863,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2008" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54880,7 +54889,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2009" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54906,7 +54915,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2010" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54932,7 +54941,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2011" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54958,7 +54967,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2012" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54984,7 +54993,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2013" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55010,7 +55019,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55036,7 +55045,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2015" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55062,7 +55071,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2016" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55088,7 +55097,7 @@
         <v>5.75</v>
       </c>
       <c r="G2017" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55114,7 +55123,7 @@
         <v>5.75</v>
       </c>
       <c r="G2018" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55140,7 +55149,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2019" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55166,7 +55175,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2020" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55192,7 +55201,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2021" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55218,7 +55227,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2022" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55244,7 +55253,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2023" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55270,7 +55279,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2024" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55296,7 +55305,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G2025" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55322,7 +55331,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2026" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55348,7 +55357,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G2027" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55374,7 +55383,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2028" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55400,7 +55409,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2029" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55426,7 +55435,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2030" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55452,7 +55461,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2031" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55478,7 +55487,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2032" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55504,7 +55513,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55530,7 +55539,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2034" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55538,7 +55547,7 @@
     </row>
     <row r="2035">
       <c r="A2035" s="1" t="n">
-        <v>45987.6913078704</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2035" t="n">
         <v>99938</v>
@@ -55556,9 +55565,35 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2035" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H2035" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2036">
+      <c r="A2036" s="1" t="n">
+        <v>45988.6910185185</v>
+      </c>
+      <c r="B2036" t="n">
+        <v>67731</v>
+      </c>
+      <c r="C2036" t="n">
+        <v>5.8899998664856</v>
+      </c>
+      <c r="D2036" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="E2036" t="n">
+        <v>5.84999990463257</v>
+      </c>
+      <c r="F2036" t="n">
+        <v>5.78999996185303</v>
+      </c>
+      <c r="G2036" t="s">
+        <v>770</v>
+      </c>
+      <c r="H2036" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="784">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61930739879608</t>
+    <t xml:space="preserve">1.61930727958679</t>
   </si>
   <si>
     <t xml:space="preserve">EQUI.MI</t>
@@ -50,82 +50,82 @@
     <t xml:space="preserve">1.71744728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71417570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71090471744537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70109021663666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67055833339691</t>
+    <t xml:space="preserve">1.71417593955994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71090447902679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70109057426453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67055821418762</t>
   </si>
   <si>
     <t xml:space="preserve">1.67491984367371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69018602371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67710089683533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65856325626373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65747261047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65529179573059</t>
+    <t xml:space="preserve">1.69018590450287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67710065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65856349468231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65747308731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65529203414917</t>
   </si>
   <si>
     <t xml:space="preserve">1.63784468173981</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64656829833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311110019684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65420162677765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6487489938736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65965366363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64002573490143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64329707622528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62585020065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64765882492065</t>
+    <t xml:space="preserve">1.64656853675842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311098098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65420150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64874923229218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65965378284454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64002549648285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64329719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62585008144379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64765930175781</t>
   </si>
   <si>
     <t xml:space="preserve">1.6738293170929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68909597396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67928171157837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67819130420685</t>
+    <t xml:space="preserve">1.68909561634064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67928159236908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67819106578827</t>
   </si>
   <si>
     <t xml:space="preserve">1.67164850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67273926734924</t>
+    <t xml:space="preserve">1.67273902893066</t>
   </si>
   <si>
     <t xml:space="preserve">1.70327138900757</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">1.70654284954071</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69563853740692</t>
+    <t xml:space="preserve">1.69563806056976</t>
   </si>
   <si>
     <t xml:space="preserve">1.66565120220184</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66837704181671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69836461544037</t>
+    <t xml:space="preserve">1.668377161026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69836413860321</t>
   </si>
   <si>
     <t xml:space="preserve">1.70381689071655</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">1.687460064888</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68473410606384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67110323905945</t>
+    <t xml:space="preserve">1.68473398685455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67110347747803</t>
   </si>
   <si>
     <t xml:space="preserve">1.75016057491302</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">1.72289931774139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72835183143616</t>
+    <t xml:space="preserve">1.72835195064545</t>
   </si>
   <si>
     <t xml:space="preserve">1.74470829963684</t>
@@ -173,37 +173,37 @@
     <t xml:space="preserve">1.73107755184174</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73925578594208</t>
+    <t xml:space="preserve">1.73925626277924</t>
   </si>
   <si>
     <t xml:space="preserve">1.74198222160339</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79923057556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77742123603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77196931838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73653018474579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79650413990021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78832578659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81831336021423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82376539707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80468249320984</t>
+    <t xml:space="preserve">1.79923033714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7774213552475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77196955680847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7365300655365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7965042591095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78832566738129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81831324100494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82376563549042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80468225479126</t>
   </si>
   <si>
     <t xml:space="preserve">1.81558680534363</t>
@@ -212,61 +212,61 @@
     <t xml:space="preserve">1.81286096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81013453006744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377841949463</t>
+    <t xml:space="preserve">1.81013488769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377794265747</t>
   </si>
   <si>
     <t xml:space="preserve">1.84284794330597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88950252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200725078583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88075494766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84576392173767</t>
+    <t xml:space="preserve">1.88950228691101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88075482845306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84576404094696</t>
   </si>
   <si>
     <t xml:space="preserve">1.81952095031738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83118462562561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86034369468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87492275238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87783873081207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86325931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8836704492569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80785727500916</t>
+    <t xml:space="preserve">1.83118438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86034345626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87492311000824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87783885002136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86325943470001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88367104530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80785715579987</t>
   </si>
   <si>
     <t xml:space="preserve">1.76703488826752</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79619383811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79910957813263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161442279816</t>
+    <t xml:space="preserve">1.79619371891022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79910969734192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161430358887</t>
   </si>
   <si>
     <t xml:space="preserve">1.82243692874908</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">1.81660497188568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83410012722015</t>
+    <t xml:space="preserve">1.83410036563873</t>
   </si>
   <si>
     <t xml:space="preserve">1.83701634407043</t>
@@ -287,235 +287,235 @@
     <t xml:space="preserve">1.84868001937866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86909103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8515956401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85742771625519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9128292798996</t>
+    <t xml:space="preserve">1.86909091472626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85159575939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8574275970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282939910889</t>
   </si>
   <si>
     <t xml:space="preserve">1.89241826534271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88658666610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89533448219299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83993196487427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8545116186142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8107727766037</t>
+    <t xml:space="preserve">1.88658654689789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89533424377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83993220329285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85451185703278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617529392242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81077337265015</t>
   </si>
   <si>
     <t xml:space="preserve">1.89825022220612</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91574597358704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95365238189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96239972114563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9244931936264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96531593799591</t>
+    <t xml:space="preserve">1.91574573516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9536520242691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96239984035492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92449343204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96531581878662</t>
   </si>
   <si>
     <t xml:space="preserve">2.00613856315613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00905418395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98281157016754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95948421955109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92740917205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90991377830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95656824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01197004318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00030636787415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94490432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94782042503357</t>
+    <t xml:space="preserve">2.00905394554138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98281121253967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95948398113251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92740941047668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90991389751434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95656847953796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01197028160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00030660629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94490456581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94781994819641</t>
   </si>
   <si>
     <t xml:space="preserve">1.90699779987335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92157769203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07903575897217</t>
+    <t xml:space="preserve">1.92157709598541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07903599739075</t>
   </si>
   <si>
     <t xml:space="preserve">2.06737208366394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98864316940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99447500705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97406351566315</t>
+    <t xml:space="preserve">1.9886429309845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99447476863861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97406363487244</t>
   </si>
   <si>
     <t xml:space="preserve">1.93907260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93032503128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198858737946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90408194065094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82535290718079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81368911266327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7903618812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82826828956604</t>
+    <t xml:space="preserve">1.93032479286194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198870658875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90408217906952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82535302639008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81368887424469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79036164283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82826852798462</t>
   </si>
   <si>
     <t xml:space="preserve">2.02852940559387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90331125259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89705085754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89078962802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87826788425446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82192003726959</t>
+    <t xml:space="preserve">1.90331161022186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89705061912537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89078986644745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87826800346375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82192015647888</t>
   </si>
   <si>
     <t xml:space="preserve">1.79061532020569</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78435444831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75931084156036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74678921699524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73426723480225</t>
+    <t xml:space="preserve">1.78435468673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75931096076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74678897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7342677116394</t>
   </si>
   <si>
     <t xml:space="preserve">1.72800636291504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65287578105927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69044125080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64661514759064</t>
+    <t xml:space="preserve">1.65287566184998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6904411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64661490917206</t>
   </si>
   <si>
     <t xml:space="preserve">1.60904943943024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62783217430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66539776325226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791974544525</t>
+    <t xml:space="preserve">1.62783229351044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66539764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791962623596</t>
   </si>
   <si>
     <t xml:space="preserve">1.63409304618835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67165851593018</t>
+    <t xml:space="preserve">1.67165839672089</t>
   </si>
   <si>
     <t xml:space="preserve">1.62157106399536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60278880596161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6841801404953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70296311378479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.696702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70922374725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7154848575592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65913641452789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64035367965698</t>
+    <t xml:space="preserve">1.60278868675232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68418049812317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7029629945755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69670188426971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70922386646271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71548461914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65913665294647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64035391807556</t>
   </si>
   <si>
     <t xml:space="preserve">1.61531043052673</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5965279340744</t>
+    <t xml:space="preserve">1.59652781486511</t>
   </si>
   <si>
     <t xml:space="preserve">1.57148420810699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5652232170105</t>
+    <t xml:space="preserve">1.56522297859192</t>
   </si>
   <si>
     <t xml:space="preserve">1.558962225914</t>
@@ -527,46 +527,46 @@
     <t xml:space="preserve">1.55270135402679</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58400583267212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77183294296265</t>
+    <t xml:space="preserve">1.58400595188141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77183270454407</t>
   </si>
   <si>
     <t xml:space="preserve">1.8156590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80939817428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80313718318939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77809345722198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74052846431732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76557183265686</t>
+    <t xml:space="preserve">1.8093980550766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80313742160797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77809381484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74052810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76557171344757</t>
   </si>
   <si>
     <t xml:space="preserve">1.75305008888245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59026682376862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47757089138031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36487448215485</t>
+    <t xml:space="preserve">1.59026694297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47757077217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36487472057343</t>
   </si>
   <si>
     <t xml:space="preserve">1.54644072055817</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50261449813843</t>
+    <t xml:space="preserve">1.50261461734772</t>
   </si>
   <si>
     <t xml:space="preserve">1.38365745544434</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">1.3210483789444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.30226588249207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32730937004089</t>
+    <t xml:space="preserve">1.3022655248642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3273092508316</t>
   </si>
   <si>
     <t xml:space="preserve">1.33357036113739</t>
@@ -590,34 +590,34 @@
     <t xml:space="preserve">1.28348302841187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29600477218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28974401950836</t>
+    <t xml:space="preserve">1.29600489139557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28974390029907</t>
   </si>
   <si>
     <t xml:space="preserve">1.33983111381531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3523530960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31478750705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609186649323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4337443113327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38991832733154</t>
+    <t xml:space="preserve">1.35235297679901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31478774547577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609198570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43374454975128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38991820812225</t>
   </si>
   <si>
     <t xml:space="preserve">1.39617908000946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4587881565094</t>
+    <t xml:space="preserve">1.45878803730011</t>
   </si>
   <si>
     <t xml:space="preserve">1.42122280597687</t>
@@ -626,43 +626,43 @@
     <t xml:space="preserve">1.37739646434784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41496181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4400053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4462662935257</t>
+    <t xml:space="preserve">1.41496193408966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44000542163849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626605510712</t>
   </si>
   <si>
     <t xml:space="preserve">1.42748355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53391885757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40870106220245</t>
+    <t xml:space="preserve">1.53391861915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40870082378387</t>
   </si>
   <si>
     <t xml:space="preserve">1.4525271654129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51513600349426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72174561023712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85863566398621</t>
+    <t xml:space="preserve">1.51513612270355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72174549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85863542556763</t>
   </si>
   <si>
     <t xml:space="preserve">1.80514979362488</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65806341171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64469194412231</t>
+    <t xml:space="preserve">1.65806317329407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6446920633316</t>
   </si>
   <si>
     <t xml:space="preserve">1.61126327514648</t>
@@ -671,76 +671,76 @@
     <t xml:space="preserve">1.63800621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61794888973236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457766056061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57114887237549</t>
+    <t xml:space="preserve">1.61794865131378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457754135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57114863395691</t>
   </si>
   <si>
     <t xml:space="preserve">1.65137779712677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63132047653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66474938392639</t>
+    <t xml:space="preserve">1.63132035732269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66474914550781</t>
   </si>
   <si>
     <t xml:space="preserve">1.62463486194611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6714346408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68480622768402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69817745685577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5912059545517</t>
+    <t xml:space="preserve">1.67143487930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6848064661026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69817817211151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59120619297028</t>
   </si>
   <si>
     <t xml:space="preserve">1.55777728557587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52434861660004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51766276359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53103446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54440593719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55109167098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53771996498108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57783424854279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58452010154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56446290016174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49760568141937</t>
+    <t xml:space="preserve">1.52434849739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51766300201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53103458881378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54440557956696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55109143257141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53772032260895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57783436775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58451998233795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56446278095245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49760556221008</t>
   </si>
   <si>
     <t xml:space="preserve">1.5109771490097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59789180755615</t>
+    <t xml:space="preserve">1.59789133071899</t>
   </si>
   <si>
     <t xml:space="preserve">1.50429129600525</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">1.49091994762421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48423397541046</t>
+    <t xml:space="preserve">1.48423433303833</t>
   </si>
   <si>
     <t xml:space="preserve">1.47754836082458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47086274623871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417677402496</t>
+    <t xml:space="preserve">1.47086262702942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417725086212</t>
   </si>
   <si>
     <t xml:space="preserve">1.44411969184875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.45080542564392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43074822425842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41737675666809</t>
+    <t xml:space="preserve">1.45080554485321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43074834346771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4173766374588</t>
   </si>
   <si>
     <t xml:space="preserve">1.36389076709747</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">1.33046221733093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34383356571198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33714783191681</t>
+    <t xml:space="preserve">1.34383368492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3371479511261</t>
   </si>
   <si>
     <t xml:space="preserve">1.32377636432648</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">1.32043361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67812061309814</t>
+    <t xml:space="preserve">1.67812049388885</t>
   </si>
   <si>
     <t xml:space="preserve">1.73829209804535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77172088623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7516633272171</t>
+    <t xml:space="preserve">1.77172064781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75166344642639</t>
   </si>
   <si>
     <t xml:space="preserve">1.7449779510498</t>
@@ -809,61 +809,64 @@
     <t xml:space="preserve">1.73160648345947</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7650351524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78509259223938</t>
+    <t xml:space="preserve">1.76503503322601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7850923538208</t>
   </si>
   <si>
     <t xml:space="preserve">1.79177820682526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75834953784943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79846405982971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520687580109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85194969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86532139778137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87869250774384</t>
+    <t xml:space="preserve">1.75834941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79846394062042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520699501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85195004940033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86532115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87869238853455</t>
   </si>
   <si>
     <t xml:space="preserve">1.89206421375275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91212141513824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92549312114716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89875018596649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83857846260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90543568134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88537871837616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91880738735199</t>
+    <t xml:space="preserve">1.91212129592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92549300193787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89874994754791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200713157654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83857834339142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90543580055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.885378241539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9188072681427</t>
   </si>
   <si>
     <t xml:space="preserve">1.96560764312744</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99903583526611</t>
+    <t xml:space="preserve">1.99903607368469</t>
   </si>
   <si>
     <t xml:space="preserve">1.99235022068024</t>
@@ -872,13 +875,13 @@
     <t xml:space="preserve">2.01240754127502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98566436767578</t>
+    <t xml:space="preserve">1.98566472530365</t>
   </si>
   <si>
     <t xml:space="preserve">1.97897899150848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00572180747986</t>
+    <t xml:space="preserve">2.00572204589844</t>
   </si>
   <si>
     <t xml:space="preserve">2.01909303665161</t>
@@ -887,40 +890,40 @@
     <t xml:space="preserve">2.02577900886536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03246450424194</t>
+    <t xml:space="preserve">2.0324649810791</t>
   </si>
   <si>
     <t xml:space="preserve">2.04629111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05320405960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08085680007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03937816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0877697467804</t>
+    <t xml:space="preserve">2.05320429801941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08085656166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03937792778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08776950836182</t>
   </si>
   <si>
     <t xml:space="preserve">2.06011724472046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06703042984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07394337654114</t>
+    <t xml:space="preserve">2.06703066825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0739438533783</t>
   </si>
   <si>
     <t xml:space="preserve">2.10850930213928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12233543395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17072772979736</t>
+    <t xml:space="preserve">2.12233567237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17072725296021</t>
   </si>
   <si>
     <t xml:space="preserve">2.1499879360199</t>
@@ -938,22 +941,22 @@
     <t xml:space="preserve">2.16381478309631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14307498931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764067649841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18455386161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15690112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22603297233582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21220636367798</t>
+    <t xml:space="preserve">2.14307522773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764115333557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18455410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15690159797668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22603321075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21220660209656</t>
   </si>
   <si>
     <t xml:space="preserve">2.23294591903687</t>
@@ -962,37 +965,37 @@
     <t xml:space="preserve">2.23985910415649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25368547439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26059889793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26751160621643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27442479133606</t>
+    <t xml:space="preserve">2.25368523597717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2605984210968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26751184463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27442455291748</t>
   </si>
   <si>
     <t xml:space="preserve">2.2467725276947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3089907169342</t>
+    <t xml:space="preserve">2.30899047851562</t>
   </si>
   <si>
     <t xml:space="preserve">2.32973003387451</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31590366363525</t>
+    <t xml:space="preserve">2.31590390205383</t>
   </si>
   <si>
     <t xml:space="preserve">2.3228166103363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33664345741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34355640411377</t>
+    <t xml:space="preserve">2.33664321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34355616569519</t>
   </si>
   <si>
     <t xml:space="preserve">2.38503503799438</t>
@@ -1001,16 +1004,16 @@
     <t xml:space="preserve">2.37120890617371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43342709541321</t>
+    <t xml:space="preserve">2.43342733383179</t>
   </si>
   <si>
     <t xml:space="preserve">2.44725346565247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51638531684875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48873233795166</t>
+    <t xml:space="preserve">2.5163848400116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873209953308</t>
   </si>
   <si>
     <t xml:space="preserve">2.49564552307129</t>
@@ -1019,7 +1022,7 @@
     <t xml:space="preserve">2.56477737426758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55786371231079</t>
+    <t xml:space="preserve">2.55786395072937</t>
   </si>
   <si>
     <t xml:space="preserve">2.54403758049011</t>
@@ -1028,19 +1031,19 @@
     <t xml:space="preserve">2.57168984413147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52329802513123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53021097183228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55095052719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58551645278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59242963790894</t>
+    <t xml:space="preserve">2.5232982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53021121025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55095076560974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58551669120789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59242939949036</t>
   </si>
   <si>
     <t xml:space="preserve">2.63390827178955</t>
@@ -1052,139 +1055,139 @@
     <t xml:space="preserve">2.65464782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64773488044739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62008213996887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64082169532776</t>
+    <t xml:space="preserve">2.64773511886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62008190155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64082145690918</t>
   </si>
   <si>
     <t xml:space="preserve">2.61316895484924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66230654716492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64100790023804</t>
+    <t xml:space="preserve">2.66230630874634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64100766181946</t>
   </si>
   <si>
     <t xml:space="preserve">2.69780373573303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74040031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79009699821472</t>
+    <t xml:space="preserve">2.74040079116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7900972366333</t>
   </si>
   <si>
     <t xml:space="preserve">2.76879858970642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74750018119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73330140113831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76169919967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71200251579285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65520668029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63390851020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68360447883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62680864334106</t>
+    <t xml:space="preserve">2.74749994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73330092430115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76169943809509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71200275421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65520715713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63390874862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68360471725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62680912017822</t>
   </si>
   <si>
     <t xml:space="preserve">2.64810729026794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67650556564331</t>
+    <t xml:space="preserve">2.67650532722473</t>
   </si>
   <si>
     <t xml:space="preserve">2.66940593719482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70490336418152</t>
+    <t xml:space="preserve">2.70490312576294</t>
   </si>
   <si>
     <t xml:space="preserve">2.75459980964661</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71910238265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72620153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69070434570312</t>
+    <t xml:space="preserve">2.71910262107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72620177268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69070410728455</t>
   </si>
   <si>
     <t xml:space="preserve">2.56291365623474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55581402778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59841084480286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79719662666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49191880226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062063217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37832689285278</t>
+    <t xml:space="preserve">2.55581378936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59841108322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79719638824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54871487617493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49191856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062015533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37832713127136</t>
   </si>
   <si>
     <t xml:space="preserve">2.25763583183289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17244172096252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21503853797913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34282970428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.349928855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48481941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59131145477295</t>
+    <t xml:space="preserve">2.17244219779968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21503901481628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34282946586609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34992933273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48481917381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59131169319153</t>
   </si>
   <si>
     <t xml:space="preserve">2.47772002220154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60551023483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8113956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82559442520142</t>
+    <t xml:space="preserve">2.60551071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81139540672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82559466362</t>
   </si>
   <si>
     <t xml:space="preserve">2.88239049911499</t>
@@ -1196,22 +1199,22 @@
     <t xml:space="preserve">2.8965892791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87529110908508</t>
+    <t xml:space="preserve">2.87529134750366</t>
   </si>
   <si>
     <t xml:space="preserve">2.83979368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78299784660339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90368914604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88949036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81849503517151</t>
+    <t xml:space="preserve">2.78299808502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90368890762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88948965072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81849479675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.8326940536499</t>
@@ -1220,7 +1223,7 @@
     <t xml:space="preserve">2.8539924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98100280761719</t>
+    <t xml:space="preserve">2.98100256919861</t>
   </si>
   <si>
     <t xml:space="preserve">2.95111775398254</t>
@@ -1229,13 +1232,13 @@
     <t xml:space="preserve">2.97353148460388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9436469078064</t>
+    <t xml:space="preserve">2.94364643096924</t>
   </si>
   <si>
     <t xml:space="preserve">2.91376185417175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87640595436096</t>
+    <t xml:space="preserve">2.87640571594238</t>
   </si>
   <si>
     <t xml:space="preserve">2.81663632392883</t>
@@ -1256,10 +1259,10 @@
     <t xml:space="preserve">2.6074435710907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62238597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65227031707764</t>
+    <t xml:space="preserve">2.62238550186157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65227055549622</t>
   </si>
   <si>
     <t xml:space="preserve">2.62985682487488</t>
@@ -1268,55 +1271,55 @@
     <t xml:space="preserve">2.65974164009094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63732814788818</t>
+    <t xml:space="preserve">2.6373279094696</t>
   </si>
   <si>
     <t xml:space="preserve">2.57008767127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58502960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57755899429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5551450252533</t>
+    <t xml:space="preserve">2.58502984046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57755851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55514526367188</t>
   </si>
   <si>
     <t xml:space="preserve">2.52526044845581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59250092506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54767370223999</t>
+    <t xml:space="preserve">2.59250140190125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54767394065857</t>
   </si>
   <si>
     <t xml:space="preserve">2.50284671783447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47296190261841</t>
+    <t xml:space="preserve">2.47296237945557</t>
   </si>
   <si>
     <t xml:space="preserve">2.45801949501038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49537515640259</t>
+    <t xml:space="preserve">2.49537563323975</t>
   </si>
   <si>
     <t xml:space="preserve">2.4654905796051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48790454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48043346405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53273177146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40572118759155</t>
+    <t xml:space="preserve">2.48790431022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48043298721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53273153305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40572166442871</t>
   </si>
   <si>
     <t xml:space="preserve">2.43560600280762</t>
@@ -1328,10 +1331,10 @@
     <t xml:space="preserve">2.3907790184021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42813515663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44307732582092</t>
+    <t xml:space="preserve">2.42813491821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44307708740234</t>
   </si>
   <si>
     <t xml:space="preserve">2.41319251060486</t>
@@ -1340,34 +1343,34 @@
     <t xml:space="preserve">2.39825010299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42066335678101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64479923248291</t>
+    <t xml:space="preserve">2.42066359519958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64479899406433</t>
   </si>
   <si>
     <t xml:space="preserve">2.71951103210449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7344536781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939608573914</t>
+    <t xml:space="preserve">2.73445343971252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939584732056</t>
   </si>
   <si>
     <t xml:space="preserve">2.75686693191528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74192452430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77928066253662</t>
+    <t xml:space="preserve">2.74192476272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77928018569946</t>
   </si>
   <si>
     <t xml:space="preserve">2.79422283172607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81757283210754</t>
+    <t xml:space="preserve">2.81757307052612</t>
   </si>
   <si>
     <t xml:space="preserve">2.82535624504089</t>
@@ -1385,64 +1388,61 @@
     <t xml:space="preserve">2.87983989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88762307167053</t>
+    <t xml:space="preserve">2.88762331008911</t>
   </si>
   <si>
     <t xml:space="preserve">2.89540648460388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87205672264099</t>
+    <t xml:space="preserve">2.87205624580383</t>
   </si>
   <si>
     <t xml:space="preserve">2.80200624465942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7942225933075</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.83313989639282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86427330970764</t>
+    <t xml:space="preserve">2.86427307128906</t>
   </si>
   <si>
     <t xml:space="preserve">2.85648989677429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91875672340393</t>
+    <t xml:space="preserve">2.91875624656677</t>
   </si>
   <si>
     <t xml:space="preserve">2.92654013633728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90318989753723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98880672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01215696334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00437331199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9421067237854</t>
+    <t xml:space="preserve">2.90318965911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98880648612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01215672492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00437355041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94210624694824</t>
   </si>
   <si>
     <t xml:space="preserve">2.97323989868164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.910973072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94989013671875</t>
+    <t xml:space="preserve">2.91097331047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94988965988159</t>
   </si>
   <si>
     <t xml:space="preserve">2.95767331123352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03550672531128</t>
+    <t xml:space="preserve">3.03550696372986</t>
   </si>
   <si>
     <t xml:space="preserve">2.99658989906311</t>
@@ -1454,91 +1454,91 @@
     <t xml:space="preserve">3.04329037666321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05107355117798</t>
+    <t xml:space="preserve">3.05107378959656</t>
   </si>
   <si>
     <t xml:space="preserve">3.01994013786316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07442378997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02772331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98102331161499</t>
+    <t xml:space="preserve">3.07442355155945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02772378921509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98102307319641</t>
   </si>
   <si>
     <t xml:space="preserve">3.16004037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08998990058899</t>
+    <t xml:space="preserve">3.08999037742615</t>
   </si>
   <si>
     <t xml:space="preserve">3.0822069644928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0666401386261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05885696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09777331352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11416387557983</t>
+    <t xml:space="preserve">3.06664037704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05885672569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09777355194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11416411399841</t>
   </si>
   <si>
     <t xml:space="preserve">3.13055419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10596871376038</t>
+    <t xml:space="preserve">3.10596895217896</t>
   </si>
   <si>
     <t xml:space="preserve">3.06499266624451</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07318806648254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08957839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04040741920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03221201896667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04860258102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05679774284363</t>
+    <t xml:space="preserve">3.07318782806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08957815170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04040765762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03221225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04860234260559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05679750442505</t>
   </si>
   <si>
     <t xml:space="preserve">3.01582217216492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02401733398438</t>
+    <t xml:space="preserve">3.0240170955658</t>
   </si>
   <si>
     <t xml:space="preserve">3.00762677192688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.081383228302</t>
+    <t xml:space="preserve">3.08138298988342</t>
   </si>
   <si>
     <t xml:space="preserve">2.99943137168884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99123644828796</t>
+    <t xml:space="preserve">2.99123620986938</t>
   </si>
   <si>
     <t xml:space="preserve">2.97484612464905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96665072441101</t>
+    <t xml:space="preserve">2.96665048599243</t>
   </si>
   <si>
     <t xml:space="preserve">2.95845556259155</t>
@@ -1550,28 +1550,28 @@
     <t xml:space="preserve">2.95026040077209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93387007713318</t>
+    <t xml:space="preserve">2.93387031555176</t>
   </si>
   <si>
     <t xml:space="preserve">2.90108942985535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92567491531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94206523895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87650394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86830854415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81094264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83552813529968</t>
+    <t xml:space="preserve">2.9256751537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94206547737122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87650418281555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86830878257751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81094288825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83552837371826</t>
   </si>
   <si>
     <t xml:space="preserve">2.79455256462097</t>
@@ -1580,34 +1580,34 @@
     <t xml:space="preserve">2.78635740280151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80274772644043</t>
+    <t xml:space="preserve">2.80274748802185</t>
   </si>
   <si>
     <t xml:space="preserve">2.76177167892456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84372329711914</t>
+    <t xml:space="preserve">2.84372353553772</t>
   </si>
   <si>
     <t xml:space="preserve">2.86011362075806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81913781166077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90928483009338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8519184589386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88469934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89289450645447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91747999191284</t>
+    <t xml:space="preserve">2.81913805007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9092845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85191869735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88469910621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89289426803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91747975349426</t>
   </si>
   <si>
     <t xml:space="preserve">3.00797700881958</t>
@@ -1616,16 +1616,16 @@
     <t xml:space="preserve">3.04215860366821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01652240753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03361320495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05070376396179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05924916267395</t>
+    <t xml:space="preserve">3.01652216911316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03361296653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05070400238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05924940109253</t>
   </si>
   <si>
     <t xml:space="preserve">3.07633996009827</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">3.12761235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14470338821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16179370880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15324878692627</t>
+    <t xml:space="preserve">3.14470314979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16179394721985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15324854850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.17033934593201</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">3.13615775108337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18743014335632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1959753036499</t>
+    <t xml:space="preserve">3.1874303817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19597554206848</t>
   </si>
   <si>
     <t xml:space="preserve">3.2130663394928</t>
@@ -1676,19 +1676,19 @@
     <t xml:space="preserve">3.23870253562927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23015689849854</t>
+    <t xml:space="preserve">3.23015713691711</t>
   </si>
   <si>
     <t xml:space="preserve">3.25579333305359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34979248046875</t>
+    <t xml:space="preserve">3.34979271888733</t>
   </si>
   <si>
     <t xml:space="preserve">3.30706548690796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35833811759949</t>
+    <t xml:space="preserve">3.35833787918091</t>
   </si>
   <si>
     <t xml:space="preserve">3.36688327789307</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">3.40106463432312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42670130729675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31561088562012</t>
+    <t xml:space="preserve">3.42670106887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3156111240387</t>
   </si>
   <si>
     <t xml:space="preserve">3.28997468948364</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">3.29851984977722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3839738368988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32415652275085</t>
+    <t xml:space="preserve">3.38397431373596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32415676116943</t>
   </si>
   <si>
     <t xml:space="preserve">3.3754289150238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41815543174744</t>
+    <t xml:space="preserve">3.41815567016602</t>
   </si>
   <si>
     <t xml:space="preserve">3.43524646759033</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">3.46942806243896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50360941886902</t>
+    <t xml:space="preserve">3.5036096572876</t>
   </si>
   <si>
     <t xml:space="preserve">3.57197260856628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52069997787476</t>
+    <t xml:space="preserve">3.52070021629333</t>
   </si>
   <si>
     <t xml:space="preserve">3.51215505599976</t>
@@ -1772,16 +1772,16 @@
     <t xml:space="preserve">3.59434938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53144812583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43260359764099</t>
+    <t xml:space="preserve">3.53144836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43260335922241</t>
   </si>
   <si>
     <t xml:space="preserve">3.46854686737061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47753310203552</t>
+    <t xml:space="preserve">3.47753286361694</t>
   </si>
   <si>
     <t xml:space="preserve">3.45057535171509</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">3.42361760139465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38767409324646</t>
+    <t xml:space="preserve">3.38767433166504</t>
   </si>
   <si>
     <t xml:space="preserve">3.44158959388733</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">3.5853636264801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62130737304688</t>
+    <t xml:space="preserve">3.6213071346283</t>
   </si>
   <si>
     <t xml:space="preserve">3.69319415092468</t>
@@ -1841,16 +1841,16 @@
     <t xml:space="preserve">3.68420815467834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71116590499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72913765907288</t>
+    <t xml:space="preserve">3.7111656665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7291374206543</t>
   </si>
   <si>
     <t xml:space="preserve">3.74710917472839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67522215843201</t>
+    <t xml:space="preserve">3.67522239685059</t>
   </si>
   <si>
     <t xml:space="preserve">3.72015142440796</t>
@@ -1862,7 +1862,7 @@
     <t xml:space="preserve">3.75609493255615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8189959526062</t>
+    <t xml:space="preserve">3.81899619102478</t>
   </si>
   <si>
     <t xml:space="preserve">3.81001043319702</t>
@@ -1874,16 +1874,16 @@
     <t xml:space="preserve">3.78305292129517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8369677066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84595394134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8279824256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76508092880249</t>
+    <t xml:space="preserve">3.83696746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84595370292664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82798218727112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76508069038391</t>
   </si>
   <si>
     <t xml:space="preserve">3.73812341690063</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">3.73778820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77507281303406</t>
+    <t xml:space="preserve">3.77507305145264</t>
   </si>
   <si>
     <t xml:space="preserve">3.71914577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68186116218567</t>
+    <t xml:space="preserve">3.68186092376709</t>
   </si>
   <si>
     <t xml:space="preserve">3.66321873664856</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">3.69118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75643062591553</t>
+    <t xml:space="preserve">3.75643038749695</t>
   </si>
   <si>
     <t xml:space="preserve">3.7657516002655</t>
@@ -1922,34 +1922,34 @@
     <t xml:space="preserve">3.93353247642517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80303621292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88692688941956</t>
+    <t xml:space="preserve">3.80303597450256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88692665100098</t>
   </si>
   <si>
     <t xml:space="preserve">3.84032082557678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81235766410828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82167840003967</t>
+    <t xml:space="preserve">3.8123574256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82167863845825</t>
   </si>
   <si>
     <t xml:space="preserve">3.83099985122681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87760543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90556907653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91488981246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96149587631226</t>
+    <t xml:space="preserve">3.87760519981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90556883811951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91489028930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96149611473083</t>
   </si>
   <si>
     <t xml:space="preserve">4.00810194015503</t>
@@ -1961,13 +1961,13 @@
     <t xml:space="preserve">4.04538679122925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01742315292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03606510162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98013854026794</t>
+    <t xml:space="preserve">4.01742267608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03606557846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98013830184937</t>
   </si>
   <si>
     <t xml:space="preserve">4.07334995269775</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">4.09199237823486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11063480377197</t>
+    <t xml:space="preserve">4.11063432693481</t>
   </si>
   <si>
     <t xml:space="preserve">4.1758828163147</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">3.9894597530365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94285368919373</t>
+    <t xml:space="preserve">3.9428539276123</t>
   </si>
   <si>
     <t xml:space="preserve">3.9521746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97081756591797</t>
+    <t xml:space="preserve">3.97081732749939</t>
   </si>
   <si>
     <t xml:space="preserve">4.06402921676636</t>
@@ -2009,16 +2009,16 @@
     <t xml:space="preserve">4.11995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7005033493042</t>
+    <t xml:space="preserve">3.70050358772278</t>
   </si>
   <si>
     <t xml:space="preserve">3.68652153015137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90090823173523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92887234687805</t>
+    <t xml:space="preserve">3.90090847015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92887210845947</t>
   </si>
   <si>
     <t xml:space="preserve">3.9242115020752</t>
@@ -2361,6 +2361,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.17000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19000005722046</t>
   </si>
 </sst>
 </file>
@@ -24037,7 +24040,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G821" t="s">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24063,7 +24066,7 @@
         <v>2.75</v>
       </c>
       <c r="G822" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24089,7 +24092,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G823" t="s">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24115,7 +24118,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G824" t="s">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24167,7 +24170,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G826" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24245,7 +24248,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G829" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24349,7 +24352,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G833" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24375,7 +24378,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G834" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24427,7 +24430,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G836" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -24453,7 +24456,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G837" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -24479,7 +24482,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G838" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -24505,7 +24508,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G839" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -24531,7 +24534,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G840" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -24557,7 +24560,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G841" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -24583,7 +24586,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G842" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -24609,7 +24612,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G843" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -24635,7 +24638,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G844" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24661,7 +24664,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G845" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24687,7 +24690,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G846" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24713,7 +24716,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G847" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24739,7 +24742,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G848" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24765,7 +24768,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G849" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24791,7 +24794,7 @@
         <v>3</v>
       </c>
       <c r="G850" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24817,7 +24820,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G851" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24843,7 +24846,7 @@
         <v>3</v>
       </c>
       <c r="G852" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24869,7 +24872,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G853" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24895,7 +24898,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G854" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24921,7 +24924,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G855" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24947,7 +24950,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G856" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24973,7 +24976,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G857" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24999,7 +25002,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G858" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25025,7 +25028,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G859" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25051,7 +25054,7 @@
         <v>3</v>
       </c>
       <c r="G860" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25077,7 +25080,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G861" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25103,7 +25106,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G862" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25129,7 +25132,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G863" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25155,7 +25158,7 @@
         <v>3</v>
       </c>
       <c r="G864" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25181,7 +25184,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G865" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25207,7 +25210,7 @@
         <v>3</v>
       </c>
       <c r="G866" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25233,7 +25236,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G867" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25259,7 +25262,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G868" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25285,7 +25288,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G869" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -25311,7 +25314,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G870" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -25337,7 +25340,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G871" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -25363,7 +25366,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G872" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -25389,7 +25392,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G873" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -25415,7 +25418,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G874" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -25441,7 +25444,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G875" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -25467,7 +25470,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G876" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -25493,7 +25496,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G877" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -25519,7 +25522,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G878" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -25545,7 +25548,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G879" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -25571,7 +25574,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G880" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -25597,7 +25600,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G881" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25623,7 +25626,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G882" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -25649,7 +25652,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G883" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -25675,7 +25678,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G884" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25701,7 +25704,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G885" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25727,7 +25730,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G886" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -25753,7 +25756,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G887" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -25779,7 +25782,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G888" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -25805,7 +25808,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G889" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -25831,7 +25834,7 @@
         <v>3</v>
       </c>
       <c r="G890" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -25857,7 +25860,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G891" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -25883,7 +25886,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G892" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -25909,7 +25912,7 @@
         <v>3</v>
       </c>
       <c r="G893" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25935,7 +25938,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G894" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -25961,7 +25964,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G895" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -25987,7 +25990,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G896" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26013,7 +26016,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G897" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26039,7 +26042,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G898" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26065,7 +26068,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G899" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26091,7 +26094,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G900" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26117,7 +26120,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G901" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26143,7 +26146,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G902" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26169,7 +26172,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G903" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26195,7 +26198,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G904" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26221,7 +26224,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G905" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26247,7 +26250,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G906" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26273,7 +26276,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G907" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -26299,7 +26302,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G908" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -26325,7 +26328,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G909" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -26351,7 +26354,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G910" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -26377,7 +26380,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G911" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -26403,7 +26406,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G912" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -26429,7 +26432,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G913" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -26455,7 +26458,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G914" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -26481,7 +26484,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G915" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -26507,7 +26510,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G916" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -26533,7 +26536,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G917" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -26559,7 +26562,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G918" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -26585,7 +26588,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G919" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -26611,7 +26614,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G920" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -26637,7 +26640,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G921" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26663,7 +26666,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G922" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26689,7 +26692,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G923" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26715,7 +26718,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G924" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26741,7 +26744,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G925" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -26767,7 +26770,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G926" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -26793,7 +26796,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G927" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -26819,7 +26822,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G928" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26845,7 +26848,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G929" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26871,7 +26874,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G930" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26897,7 +26900,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G931" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26923,7 +26926,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G932" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26949,7 +26952,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G933" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26975,7 +26978,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G934" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27001,7 +27004,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G935" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27027,7 +27030,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G936" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27053,7 +27056,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G937" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27079,7 +27082,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G938" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27105,7 +27108,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G939" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27131,7 +27134,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G940" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27157,7 +27160,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G941" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27183,7 +27186,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G942" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27209,7 +27212,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G943" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27235,7 +27238,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G944" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27261,7 +27264,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G945" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27287,7 +27290,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G946" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -27313,7 +27316,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G947" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -27339,7 +27342,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G948" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -27365,7 +27368,7 @@
         <v>3.25</v>
       </c>
       <c r="G949" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -27391,7 +27394,7 @@
         <v>3.25</v>
       </c>
       <c r="G950" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -27417,7 +27420,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G951" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -27443,7 +27446,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G952" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -27469,7 +27472,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G953" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -27495,7 +27498,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G954" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -27521,7 +27524,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G955" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -27547,7 +27550,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G956" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -27573,7 +27576,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G957" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -27599,7 +27602,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G958" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -27625,7 +27628,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G959" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -27651,7 +27654,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G960" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27677,7 +27680,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G961" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27703,7 +27706,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G962" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27729,7 +27732,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G963" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27755,7 +27758,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G964" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27781,7 +27784,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G965" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27807,7 +27810,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G966" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27833,7 +27836,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G967" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27859,7 +27862,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G968" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27885,7 +27888,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G969" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27911,7 +27914,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G970" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27937,7 +27940,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G971" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27963,7 +27966,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G972" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27989,7 +27992,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G973" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28015,7 +28018,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G974" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28041,7 +28044,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G975" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28067,7 +28070,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G976" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28093,7 +28096,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G977" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28119,7 +28122,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G978" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28145,7 +28148,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G979" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28171,7 +28174,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G980" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28197,7 +28200,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G981" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28223,7 +28226,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G982" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28249,7 +28252,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G983" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28275,7 +28278,7 @@
         <v>3.75</v>
       </c>
       <c r="G984" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -28301,7 +28304,7 @@
         <v>3.75</v>
       </c>
       <c r="G985" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -28327,7 +28330,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G986" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -28353,7 +28356,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G987" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -28379,7 +28382,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G988" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -28405,7 +28408,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G989" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -28431,7 +28434,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G990" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -28457,7 +28460,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G991" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -28483,7 +28486,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G992" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -28509,7 +28512,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G993" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -28535,7 +28538,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G994" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -28561,7 +28564,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G995" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -28587,7 +28590,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G996" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -28613,7 +28616,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G997" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -28639,7 +28642,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G998" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28665,7 +28668,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G999" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28691,7 +28694,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1000" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28717,7 +28720,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1001" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28743,7 +28746,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1002" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28769,7 +28772,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1003" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28795,7 +28798,7 @@
         <v>3.75</v>
       </c>
       <c r="G1004" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28821,7 +28824,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1005" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28847,7 +28850,7 @@
         <v>3.75</v>
       </c>
       <c r="G1006" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28873,7 +28876,7 @@
         <v>3.75</v>
       </c>
       <c r="G1007" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28899,7 +28902,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1008" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28925,7 +28928,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1009" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28951,7 +28954,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1010" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -28977,7 +28980,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1011" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29003,7 +29006,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1012" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29029,7 +29032,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1013" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29055,7 +29058,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1014" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29081,7 +29084,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1015" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29107,7 +29110,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1016" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29133,7 +29136,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1017" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29159,7 +29162,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1018" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29185,7 +29188,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1019" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29211,7 +29214,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1020" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29237,7 +29240,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1021" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29263,7 +29266,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1022" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29289,7 +29292,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1023" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29315,7 +29318,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1024" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -29341,7 +29344,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1025" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -29367,7 +29370,7 @@
         <v>3.75</v>
       </c>
       <c r="G1026" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -29393,7 +29396,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1027" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29419,7 +29422,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1028" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -29445,7 +29448,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1029" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -29471,7 +29474,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1030" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -29497,7 +29500,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1031" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29523,7 +29526,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1032" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29549,7 +29552,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1033" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29575,7 +29578,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1034" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29601,7 +29604,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1035" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -29627,7 +29630,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1036" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -29653,7 +29656,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1037" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29679,7 +29682,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1038" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29705,7 +29708,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1039" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29731,7 +29734,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1040" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29757,7 +29760,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1041" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29783,7 +29786,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1042" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29809,7 +29812,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1043" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29835,7 +29838,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1044" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29861,7 +29864,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1045" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29887,7 +29890,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1046" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29913,7 +29916,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29939,7 +29942,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1048" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29965,7 +29968,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29991,7 +29994,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1050" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30017,7 +30020,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1051" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30043,7 +30046,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1052" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30069,7 +30072,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1053" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30095,7 +30098,7 @@
         <v>3.75</v>
       </c>
       <c r="G1054" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30121,7 +30124,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1055" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30147,7 +30150,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1056" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30173,7 +30176,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1057" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30199,7 +30202,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1058" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30225,7 +30228,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1059" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30251,7 +30254,7 @@
         <v>3.75</v>
       </c>
       <c r="G1060" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30277,7 +30280,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1061" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30303,7 +30306,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1062" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -30329,7 +30332,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1063" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -30355,7 +30358,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1064" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30381,7 +30384,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1065" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30407,7 +30410,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1066" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30433,7 +30436,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1067" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30459,7 +30462,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1068" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30485,7 +30488,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1069" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -30511,7 +30514,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1070" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -30537,7 +30540,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1071" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -30563,7 +30566,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1072" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30589,7 +30592,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1073" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30615,7 +30618,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1074" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30641,7 +30644,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1075" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30667,7 +30670,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1076" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30693,7 +30696,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1077" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30719,7 +30722,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1078" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30745,7 +30748,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1079" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30771,7 +30774,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1080" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30797,7 +30800,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1081" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30823,7 +30826,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1082" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30849,7 +30852,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1083" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30875,7 +30878,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1084" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30901,7 +30904,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1085" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30927,7 +30930,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1086" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30953,7 +30956,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1087" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30979,7 +30982,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1088" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31005,7 +31008,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1089" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31031,7 +31034,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1090" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31057,7 +31060,7 @@
         <v>3.5</v>
       </c>
       <c r="G1091" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31083,7 +31086,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1092" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31109,7 +31112,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1093" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31135,7 +31138,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1094" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31161,7 +31164,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31187,7 +31190,7 @@
         <v>3.75</v>
       </c>
       <c r="G1096" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31213,7 +31216,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1097" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31239,7 +31242,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1098" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31265,7 +31268,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1099" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31291,7 +31294,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1100" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -31317,7 +31320,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1101" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31343,7 +31346,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1102" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -31369,7 +31372,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1103" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -31395,7 +31398,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1104" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -31421,7 +31424,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1105" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31447,7 +31450,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31473,7 +31476,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1107" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31499,7 +31502,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1108" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31525,7 +31528,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1109" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31551,7 +31554,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1110" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31577,7 +31580,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1111" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31603,7 +31606,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1112" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -31629,7 +31632,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1113" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31655,7 +31658,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1114" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31681,7 +31684,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1115" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31707,7 +31710,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31733,7 +31736,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1117" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31759,7 +31762,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1118" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31785,7 +31788,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1119" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31811,7 +31814,7 @@
         <v>4</v>
       </c>
       <c r="G1120" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31837,7 +31840,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1121" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31863,7 +31866,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1122" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31889,7 +31892,7 @@
         <v>4</v>
       </c>
       <c r="G1123" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31915,7 +31918,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1124" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31941,7 +31944,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1125" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31967,7 +31970,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1126" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31993,7 +31996,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1127" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32019,7 +32022,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32045,7 +32048,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1129" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32071,7 +32074,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1130" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32097,7 +32100,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1131" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32123,7 +32126,7 @@
         <v>4</v>
       </c>
       <c r="G1132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32149,7 +32152,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1133" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32175,7 +32178,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1134" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32201,7 +32204,7 @@
         <v>4</v>
       </c>
       <c r="G1135" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32227,7 +32230,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32253,7 +32256,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1137" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32279,7 +32282,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32305,7 +32308,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32331,7 +32334,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32357,7 +32360,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32383,7 +32386,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1142" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32409,7 +32412,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1143" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32435,7 +32438,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1144" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32461,7 +32464,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1145" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32487,7 +32490,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1146" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32513,7 +32516,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1147" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32539,7 +32542,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1148" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32565,7 +32568,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32591,7 +32594,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1150" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32617,7 +32620,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1151" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32643,7 +32646,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1152" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32669,7 +32672,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1153" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32695,7 +32698,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1154" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32721,7 +32724,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32747,7 +32750,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32773,7 +32776,7 @@
         <v>3.5</v>
       </c>
       <c r="G1157" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32799,7 +32802,7 @@
         <v>3.5</v>
       </c>
       <c r="G1158" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32825,7 +32828,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1159" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32851,7 +32854,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1160" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32877,7 +32880,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1161" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32903,7 +32906,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1162" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32929,7 +32932,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1163" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32955,7 +32958,7 @@
         <v>3.5</v>
       </c>
       <c r="G1164" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32981,7 +32984,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1165" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33007,7 +33010,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1166" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33033,7 +33036,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1167" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33059,7 +33062,7 @@
         <v>3.5</v>
       </c>
       <c r="G1168" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33085,7 +33088,7 @@
         <v>3.5</v>
       </c>
       <c r="G1169" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33111,7 +33114,7 @@
         <v>3.5</v>
       </c>
       <c r="G1170" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33137,7 +33140,7 @@
         <v>3.5</v>
       </c>
       <c r="G1171" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33163,7 +33166,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1172" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33189,7 +33192,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1173" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33215,7 +33218,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1174" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33241,7 +33244,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1175" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33267,7 +33270,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1176" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33293,7 +33296,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1177" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33319,7 +33322,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1178" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33345,7 +33348,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1179" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33371,7 +33374,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1180" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33397,7 +33400,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1181" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33423,7 +33426,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1182" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33449,7 +33452,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1183" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33475,7 +33478,7 @@
         <v>3.5</v>
       </c>
       <c r="G1184" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33501,7 +33504,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1185" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33527,7 +33530,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1186" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33553,7 +33556,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1187" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33579,7 +33582,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1188" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33605,7 +33608,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1189" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33631,7 +33634,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1190" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33657,7 +33660,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1191" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33683,7 +33686,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1192" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33709,7 +33712,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1193" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33735,7 +33738,7 @@
         <v>3.5</v>
       </c>
       <c r="G1194" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33761,7 +33764,7 @@
         <v>3.5</v>
       </c>
       <c r="G1195" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33787,7 +33790,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1196" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33813,7 +33816,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1197" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33839,7 +33842,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1198" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33865,7 +33868,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1199" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33891,7 +33894,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1200" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33917,7 +33920,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33943,7 +33946,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1202" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33969,7 +33972,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1203" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33995,7 +33998,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1204" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34021,7 +34024,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1205" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34047,7 +34050,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1206" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34073,7 +34076,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1207" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34099,7 +34102,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1208" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34125,7 +34128,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1209" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34151,7 +34154,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34177,7 +34180,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1211" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34203,7 +34206,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1212" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34229,7 +34232,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1213" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34255,7 +34258,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1214" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34281,7 +34284,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1215" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34307,7 +34310,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1216" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34333,7 +34336,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1217" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34359,7 +34362,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1218" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34385,7 +34388,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1219" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34411,7 +34414,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1220" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34437,7 +34440,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1221" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34463,7 +34466,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1222" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34489,7 +34492,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1223" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34515,7 +34518,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1224" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34541,7 +34544,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1225" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34567,7 +34570,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1226" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34593,7 +34596,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1227" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34619,7 +34622,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1228" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34645,7 +34648,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1229" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34671,7 +34674,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1230" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34697,7 +34700,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1231" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34723,7 +34726,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1232" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34749,7 +34752,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1233" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34775,7 +34778,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1234" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34801,7 +34804,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1235" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34827,7 +34830,7 @@
         <v>3.25</v>
       </c>
       <c r="G1236" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34853,7 +34856,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1237" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34879,7 +34882,7 @@
         <v>3.25</v>
       </c>
       <c r="G1238" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34905,7 +34908,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1239" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34931,7 +34934,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1240" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34957,7 +34960,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1241" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34983,7 +34986,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1242" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35009,7 +35012,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1243" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35035,7 +35038,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1244" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35061,7 +35064,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1245" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35087,7 +35090,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1246" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35113,7 +35116,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1247" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35139,7 +35142,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1248" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35165,7 +35168,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1249" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35191,7 +35194,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1250" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35217,7 +35220,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35243,7 +35246,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1252" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35269,7 +35272,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1253" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35295,7 +35298,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1254" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35321,7 +35324,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1255" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35347,7 +35350,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1256" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35373,7 +35376,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1257" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35399,7 +35402,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1258" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35425,7 +35428,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1259" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35451,7 +35454,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1260" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35477,7 +35480,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1261" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35503,7 +35506,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35529,7 +35532,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1263" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35555,7 +35558,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1264" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35581,7 +35584,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1265" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35607,7 +35610,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1266" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35633,7 +35636,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1267" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35659,7 +35662,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1268" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35685,7 +35688,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1269" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35711,7 +35714,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1270" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35737,7 +35740,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1271" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35763,7 +35766,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1272" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35789,7 +35792,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1273" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35815,7 +35818,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1274" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35841,7 +35844,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1275" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35867,7 +35870,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1276" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35893,7 +35896,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1277" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35919,7 +35922,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1278" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35945,7 +35948,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1279" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35971,7 +35974,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1280" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35997,7 +36000,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1281" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36023,7 +36026,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1282" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36049,7 +36052,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1283" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36075,7 +36078,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1284" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36101,7 +36104,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1285" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36179,7 +36182,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1288" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36205,7 +36208,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1289" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36257,7 +36260,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1291" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36283,7 +36286,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1292" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36309,7 +36312,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1293" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36361,7 +36364,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1295" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36387,7 +36390,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1296" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36439,7 +36442,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1298" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36465,7 +36468,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1299" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36725,7 +36728,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1309" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36881,7 +36884,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1315" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36907,7 +36910,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1316" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36933,7 +36936,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1317" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37739,7 +37742,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1348" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -56025,13 +56028,13 @@
     </row>
     <row r="2052">
       <c r="A2052" s="1" t="n">
-        <v>46010.6911805556</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2052" t="n">
         <v>80153</v>
       </c>
       <c r="C2052" t="n">
-        <v>6.15999984741211</v>
+        <v>6.17000007629395</v>
       </c>
       <c r="D2052" t="n">
         <v>6.07000017166138</v>
@@ -56046,6 +56049,32 @@
         <v>782</v>
       </c>
       <c r="H2052" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2053">
+      <c r="A2053" s="1" t="n">
+        <v>46013.6910069444</v>
+      </c>
+      <c r="B2053" t="n">
+        <v>144438</v>
+      </c>
+      <c r="C2053" t="n">
+        <v>6.19000005722046</v>
+      </c>
+      <c r="D2053" t="n">
+        <v>6.09000015258789</v>
+      </c>
+      <c r="E2053" t="n">
+        <v>6.09000015258789</v>
+      </c>
+      <c r="F2053" t="n">
+        <v>6.19000005722046</v>
+      </c>
+      <c r="G2053" t="s">
+        <v>783</v>
+      </c>
+      <c r="H2053" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="785">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61930727958679</t>
+    <t xml:space="preserve">1.61930751800537</t>
   </si>
   <si>
     <t xml:space="preserve">EQUI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68691504001617</t>
+    <t xml:space="preserve">1.6869148015976</t>
   </si>
   <si>
     <t xml:space="preserve">1.71744728088379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71417593955994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71090447902679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70109057426453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67055821418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67491984367371</t>
+    <t xml:space="preserve">1.71417617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71090471744537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70109069347382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67055809497833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.674919962883</t>
   </si>
   <si>
     <t xml:space="preserve">1.69018590450287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67710065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65856349468231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65747308731079</t>
+    <t xml:space="preserve">1.67710077762604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65856337547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65747272968292</t>
   </si>
   <si>
     <t xml:space="preserve">1.65529203414917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63784468173981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64656853675842</t>
+    <t xml:space="preserve">1.63784456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64656829833984</t>
   </si>
   <si>
     <t xml:space="preserve">1.65311098098755</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">1.65420150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64874923229218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65965378284454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64002549648285</t>
+    <t xml:space="preserve">1.64874935150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65965354442596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64002561569214</t>
   </si>
   <si>
     <t xml:space="preserve">1.64329719543457</t>
@@ -107,46 +107,46 @@
     <t xml:space="preserve">1.62585008144379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64765930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6738293170929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68909561634064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67928159236908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67819106578827</t>
+    <t xml:space="preserve">1.64765882492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67382979393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68909549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6792813539505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67819118499756</t>
   </si>
   <si>
     <t xml:space="preserve">1.67164850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67273902893066</t>
+    <t xml:space="preserve">1.67273926734924</t>
   </si>
   <si>
     <t xml:space="preserve">1.70327138900757</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70654284954071</t>
+    <t xml:space="preserve">1.70654273033142</t>
   </si>
   <si>
     <t xml:space="preserve">1.69563806056976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66565120220184</t>
+    <t xml:space="preserve">1.66565132141113</t>
   </si>
   <si>
     <t xml:space="preserve">1.668377161026</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69836413860321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70381689071655</t>
+    <t xml:space="preserve">1.69836461544037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70381665229797</t>
   </si>
   <si>
     <t xml:space="preserve">1.687460064888</t>
@@ -155,142 +155,142 @@
     <t xml:space="preserve">1.68473398685455</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67110347747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016057491302</t>
+    <t xml:space="preserve">1.67110335826874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016021728516</t>
   </si>
   <si>
     <t xml:space="preserve">1.72289931774139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72835195064545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74470829963684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73107755184174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73925626277924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74198222160339</t>
+    <t xml:space="preserve">1.72835183143616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74470782279968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73107767105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73925638198853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74198234081268</t>
   </si>
   <si>
     <t xml:space="preserve">1.79923033714294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7774213552475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77196955680847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7365300655365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7965042591095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78832566738129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81831324100494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82376563549042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80468225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81558680534363</t>
+    <t xml:space="preserve">1.77742171287537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77196943759918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73653018474579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79650449752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78832578659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81831312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82376527786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80468273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81558704376221</t>
   </si>
   <si>
     <t xml:space="preserve">1.81286096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81013488769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377794265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84284794330597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88950228691101</t>
+    <t xml:space="preserve">1.8101350069046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377818107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84284818172455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88950252532959</t>
   </si>
   <si>
     <t xml:space="preserve">1.87200689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88075482845306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84576404094696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81952095031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83118438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86034345626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87492311000824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87783885002136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86325943470001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88367104530334</t>
+    <t xml:space="preserve">1.88075459003448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84576380252838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8195207118988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83118462562561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8603435754776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87492287158966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87783908843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8632595539093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88367056846619</t>
   </si>
   <si>
     <t xml:space="preserve">1.80785715579987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76703488826752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79619371891022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79910969734192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161430358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82243692874908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7845299243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81660497188568</t>
+    <t xml:space="preserve">1.76703464984894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79619324207306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79910933971405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161418437958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82243680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78453016281128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81660521030426</t>
   </si>
   <si>
     <t xml:space="preserve">1.83410036563873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83701634407043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84868001937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86909091472626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85159575939178</t>
+    <t xml:space="preserve">1.83701646327972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84867990016937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86909079551697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8515956401825</t>
   </si>
   <si>
     <t xml:space="preserve">1.8574275970459</t>
@@ -299,25 +299,25 @@
     <t xml:space="preserve">1.91282939910889</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89241826534271</t>
+    <t xml:space="preserve">1.89241802692413</t>
   </si>
   <si>
     <t xml:space="preserve">1.88658654689789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89533424377441</t>
+    <t xml:space="preserve">1.89533448219299</t>
   </si>
   <si>
     <t xml:space="preserve">1.83993220329285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85451185703278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617529392242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81077337265015</t>
+    <t xml:space="preserve">1.8545116186142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617505550385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81077325344086</t>
   </si>
   <si>
     <t xml:space="preserve">1.89825022220612</t>
@@ -329,130 +329,130 @@
     <t xml:space="preserve">1.9536520242691</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96239984035492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92449343204498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96531581878662</t>
+    <t xml:space="preserve">1.9624000787735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92449331283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96531546115875</t>
   </si>
   <si>
     <t xml:space="preserve">2.00613856315613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00905394554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98281121253967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95948398113251</t>
+    <t xml:space="preserve">2.00905442237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98281133174896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95948374271393</t>
   </si>
   <si>
     <t xml:space="preserve">1.92740941047668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90991389751434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95656847953796</t>
+    <t xml:space="preserve">1.90991377830505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9565681219101</t>
   </si>
   <si>
     <t xml:space="preserve">2.01197028160095</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00030660629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94490456581116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94781994819641</t>
+    <t xml:space="preserve">2.0003068447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94490444660187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94782054424286</t>
   </si>
   <si>
     <t xml:space="preserve">1.90699779987335</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92157709598541</t>
+    <t xml:space="preserve">1.92157745361328</t>
   </si>
   <si>
     <t xml:space="preserve">2.07903599739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06737208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9886429309845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99447476863861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97406363487244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93907260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93032479286194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198870658875</t>
+    <t xml:space="preserve">2.06737232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98864328861237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99447524547577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97406375408173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93907272815704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93032515048981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198846817017</t>
   </si>
   <si>
     <t xml:space="preserve">1.90408217906952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82535302639008</t>
+    <t xml:space="preserve">1.8253527879715</t>
   </si>
   <si>
     <t xml:space="preserve">1.81368887424469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79036164283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82826852798462</t>
+    <t xml:space="preserve">1.79036211967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82826864719391</t>
   </si>
   <si>
     <t xml:space="preserve">2.02852940559387</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90331161022186</t>
+    <t xml:space="preserve">1.90331125259399</t>
   </si>
   <si>
     <t xml:space="preserve">1.89705061912537</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89078986644745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87826800346375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82192015647888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79061532020569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78435468673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75931096076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74678897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7342677116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72800636291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65287566184998</t>
+    <t xml:space="preserve">1.89078962802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87826788425446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82192003726959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79061555862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78435444831848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75931084156036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74678909778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73426723480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72800648212433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65287578105927</t>
   </si>
   <si>
     <t xml:space="preserve">1.6904411315918</t>
@@ -461,127 +461,127 @@
     <t xml:space="preserve">1.64661490917206</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60904943943024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62783229351044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66539764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791962623596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63409304618835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67165839672089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62157106399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60278868675232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68418049812317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7029629945755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69670188426971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70922386646271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71548461914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65913665294647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64035391807556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61531043052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59652781486511</t>
+    <t xml:space="preserve">1.60904955863953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62783193588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66539752483368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791938781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63409292697906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6716582775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62157142162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60278856754303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6841801404953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70296287536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69670176506042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70922362804413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71548473834991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65913677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64035379886627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61531054973602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59652769565582</t>
   </si>
   <si>
     <t xml:space="preserve">1.57148420810699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56522297859192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.558962225914</t>
+    <t xml:space="preserve">1.56522333621979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55896246433258</t>
   </si>
   <si>
     <t xml:space="preserve">1.57774496078491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55270135402679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58400595188141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77183270454407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8156590461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8093980550766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80313742160797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77809381484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74052810668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76557171344757</t>
+    <t xml:space="preserve">1.55270159244537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58400583267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77183246612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81565880775452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80939829349518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80313718318939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77809345722198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74052822589874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76557147502899</t>
   </si>
   <si>
     <t xml:space="preserve">1.75305008888245</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59026694297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47757077217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36487472057343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54644072055817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50261461734772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38365745544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40244007110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3210483789444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3022655248642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3273092508316</t>
+    <t xml:space="preserve">1.59026682376862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47757053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36487460136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54644083976746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50261437892914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38365733623505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40243995189667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32104825973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30226576328278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32730913162231</t>
   </si>
   <si>
     <t xml:space="preserve">1.33357036113739</t>
@@ -590,37 +590,37 @@
     <t xml:space="preserve">1.28348302841187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.29600489139557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28974390029907</t>
+    <t xml:space="preserve">1.29600477218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28974401950836</t>
   </si>
   <si>
     <t xml:space="preserve">1.33983111381531</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35235297679901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31478774547577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34609198570251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43374454975128</t>
+    <t xml:space="preserve">1.3523530960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31478750705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4337443113327</t>
   </si>
   <si>
     <t xml:space="preserve">1.38991820812225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39617908000946</t>
+    <t xml:space="preserve">1.39617919921875</t>
   </si>
   <si>
     <t xml:space="preserve">1.45878803730011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42122280597687</t>
+    <t xml:space="preserve">1.42122268676758</t>
   </si>
   <si>
     <t xml:space="preserve">1.37739646434784</t>
@@ -629,76 +629,76 @@
     <t xml:space="preserve">1.41496193408966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44000542163849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44626605510712</t>
+    <t xml:space="preserve">1.4400053024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626617431641</t>
   </si>
   <si>
     <t xml:space="preserve">1.42748355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53391861915588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40870082378387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4525271654129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51513612270355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72174549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85863542556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80514979362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65806317329407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6446920633316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61126327514648</t>
+    <t xml:space="preserve">1.53391885757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40870094299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45252704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51513624191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72174561023712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85863554477692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80514967441559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65806341171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64469182491302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61126315593719</t>
   </si>
   <si>
     <t xml:space="preserve">1.63800621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61794865131378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457754135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57114863395691</t>
+    <t xml:space="preserve">1.61794900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457766056061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5711487531662</t>
   </si>
   <si>
     <t xml:space="preserve">1.65137779712677</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63132035732269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66474914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62463486194611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67143487930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6848064661026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69817817211151</t>
+    <t xml:space="preserve">1.63132071495056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6647492647171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62463462352753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67143499851227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68480634689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69817781448364</t>
   </si>
   <si>
     <t xml:space="preserve">1.59120619297028</t>
@@ -707,82 +707,82 @@
     <t xml:space="preserve">1.55777728557587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52434849739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51766300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53103458881378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54440557956696</t>
+    <t xml:space="preserve">1.52434861660004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51766276359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53103411197662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54440581798553</t>
   </si>
   <si>
     <t xml:space="preserve">1.55109143257141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53772032260895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57783436775208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58451998233795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56446278095245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49760556221008</t>
+    <t xml:space="preserve">1.53771996498108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57783424854279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58452033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56446301937103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49760544300079</t>
   </si>
   <si>
     <t xml:space="preserve">1.5109771490097</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59789133071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50429129600525</t>
+    <t xml:space="preserve">1.59789156913757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50429141521454</t>
   </si>
   <si>
     <t xml:space="preserve">1.49091994762421</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48423433303833</t>
+    <t xml:space="preserve">1.48423421382904</t>
   </si>
   <si>
     <t xml:space="preserve">1.47754836082458</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47086262702942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417725086212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44411969184875</t>
+    <t xml:space="preserve">1.47086274623871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417701244354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44411993026733</t>
   </si>
   <si>
     <t xml:space="preserve">1.45080554485321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43074834346771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4173766374588</t>
+    <t xml:space="preserve">1.43074822425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41737651824951</t>
   </si>
   <si>
     <t xml:space="preserve">1.36389076709747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33046221733093</t>
+    <t xml:space="preserve">1.33046209812164</t>
   </si>
   <si>
     <t xml:space="preserve">1.34383368492126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3371479511261</t>
+    <t xml:space="preserve">1.33714783191681</t>
   </si>
   <si>
     <t xml:space="preserve">1.32377636432648</t>
@@ -791,85 +791,85 @@
     <t xml:space="preserve">1.32043361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67812049388885</t>
+    <t xml:space="preserve">1.67812061309814</t>
   </si>
   <si>
     <t xml:space="preserve">1.73829209804535</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77172064781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75166344642639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7449779510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73160648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76503503322601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7850923538208</t>
+    <t xml:space="preserve">1.77172112464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75166356563568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74497783184052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73160660266876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76503527164459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78509223461151</t>
   </si>
   <si>
     <t xml:space="preserve">1.79177820682526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75834941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79846394062042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520699501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85195004940033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86532115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87869238853455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89206421375275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91212129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92549300193787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89874994754791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200713157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83857834339142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90543580055237</t>
+    <t xml:space="preserve">1.75834953784943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79846382141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520663738251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85194969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86532127857208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87869274616241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89206397533417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91212153434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92549288272858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89874982833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200701236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83857846260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90543556213379</t>
   </si>
   <si>
     <t xml:space="preserve">1.885378241539</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9188072681427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96560764312744</t>
+    <t xml:space="preserve">1.91880702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96560704708099</t>
   </si>
   <si>
     <t xml:space="preserve">1.99903607368469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99235022068024</t>
+    <t xml:space="preserve">1.99235010147095</t>
   </si>
   <si>
     <t xml:space="preserve">2.01240754127502</t>
@@ -878,100 +878,100 @@
     <t xml:space="preserve">1.98566472530365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97897899150848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00572204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909303665161</t>
+    <t xml:space="preserve">1.97897911071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00572180747986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909351348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.02577900886536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0324649810791</t>
+    <t xml:space="preserve">2.03246474266052</t>
   </si>
   <si>
     <t xml:space="preserve">2.04629111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05320429801941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08085656166077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03937792778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08776950836182</t>
+    <t xml:space="preserve">2.05320405960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08085680007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03937768936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08776998519897</t>
   </si>
   <si>
     <t xml:space="preserve">2.06011724472046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06703066825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0739438533783</t>
+    <t xml:space="preserve">2.06703042984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07394361495972</t>
   </si>
   <si>
     <t xml:space="preserve">2.10850930213928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12233567237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17072725296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1499879360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1983802318573</t>
+    <t xml:space="preserve">2.12233543395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17072772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14998817443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19838047027588</t>
   </si>
   <si>
     <t xml:space="preserve">2.20529341697693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19146704673767</t>
+    <t xml:space="preserve">2.19146680831909</t>
   </si>
   <si>
     <t xml:space="preserve">2.16381478309631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14307522773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764115333557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18455410003662</t>
+    <t xml:space="preserve">2.14307498931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18455386161804</t>
   </si>
   <si>
     <t xml:space="preserve">2.15690159797668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22603321075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21220660209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23294591903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23985910415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25368523597717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2605984210968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26751184463501</t>
+    <t xml:space="preserve">2.22603273391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2122061252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23294615745544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23985934257507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25368547439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26059794425964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26751136779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.27442455291748</t>
@@ -983,64 +983,64 @@
     <t xml:space="preserve">2.30899047851562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32973003387451</t>
+    <t xml:space="preserve">2.32972979545593</t>
   </si>
   <si>
     <t xml:space="preserve">2.31590390205383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3228166103363</t>
+    <t xml:space="preserve">2.32281684875488</t>
   </si>
   <si>
     <t xml:space="preserve">2.33664321899414</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34355616569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38503503799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37120890617371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43342733383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44725346565247</t>
+    <t xml:space="preserve">2.34355640411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38503551483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37120866775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43342709541321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44725322723389</t>
   </si>
   <si>
     <t xml:space="preserve">2.5163848400116</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873209953308</t>
+    <t xml:space="preserve">2.48873257637024</t>
   </si>
   <si>
     <t xml:space="preserve">2.49564552307129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56477737426758</t>
+    <t xml:space="preserve">2.56477689743042</t>
   </si>
   <si>
     <t xml:space="preserve">2.55786395072937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54403758049011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57168984413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5232982635498</t>
+    <t xml:space="preserve">2.54403734207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57169032096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52329802513123</t>
   </si>
   <si>
     <t xml:space="preserve">2.53021121025085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55095076560974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58551669120789</t>
+    <t xml:space="preserve">2.55095052719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58551645278931</t>
   </si>
   <si>
     <t xml:space="preserve">2.59242939949036</t>
@@ -1052,34 +1052,34 @@
     <t xml:space="preserve">2.6269953250885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65464782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64773511886597</t>
+    <t xml:space="preserve">2.65464806556702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64773488044739</t>
   </si>
   <si>
     <t xml:space="preserve">2.62008190155029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64082145690918</t>
+    <t xml:space="preserve">2.6408212184906</t>
   </si>
   <si>
     <t xml:space="preserve">2.61316895484924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66230630874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64100766181946</t>
+    <t xml:space="preserve">2.66230607032776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64100790023804</t>
   </si>
   <si>
     <t xml:space="preserve">2.69780373573303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74040079116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7900972366333</t>
+    <t xml:space="preserve">2.74040055274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79009675979614</t>
   </si>
   <si>
     <t xml:space="preserve">2.76879858970642</t>
@@ -1088,19 +1088,16 @@
     <t xml:space="preserve">2.74749994277954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73330092430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76169943809509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71200275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65520715713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63390874862671</t>
+    <t xml:space="preserve">2.73330116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76169919967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71200251579285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65520691871643</t>
   </si>
   <si>
     <t xml:space="preserve">2.68360471725464</t>
@@ -1109,7 +1106,7 @@
     <t xml:space="preserve">2.62680912017822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64810729026794</t>
+    <t xml:space="preserve">2.64810752868652</t>
   </si>
   <si>
     <t xml:space="preserve">2.67650532722473</t>
@@ -1121,10 +1118,10 @@
     <t xml:space="preserve">2.70490312576294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75459980964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71910262107849</t>
+    <t xml:space="preserve">2.75460004806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71910238265991</t>
   </si>
   <si>
     <t xml:space="preserve">2.72620177268982</t>
@@ -1136,19 +1133,19 @@
     <t xml:space="preserve">2.56291365623474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55581378936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59841108322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79719638824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54871487617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49191856384277</t>
+    <t xml:space="preserve">2.55581402778625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59841084480286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79719662666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54871439933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49191880226135</t>
   </si>
   <si>
     <t xml:space="preserve">2.47062015533447</t>
@@ -1160,25 +1157,25 @@
     <t xml:space="preserve">2.25763583183289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17244219779968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21503901481628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34282946586609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34992933273315</t>
+    <t xml:space="preserve">2.1724419593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21503877639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34282922744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34992909431458</t>
   </si>
   <si>
     <t xml:space="preserve">2.48481917381287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59131169319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47772002220154</t>
+    <t xml:space="preserve">2.59131145477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47771978378296</t>
   </si>
   <si>
     <t xml:space="preserve">2.60551071166992</t>
@@ -1187,7 +1184,7 @@
     <t xml:space="preserve">2.81139540672302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82559466362</t>
+    <t xml:space="preserve">2.82559442520142</t>
   </si>
   <si>
     <t xml:space="preserve">2.88239049911499</t>
@@ -1196,43 +1193,43 @@
     <t xml:space="preserve">2.8681914806366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8965892791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87529134750366</t>
+    <t xml:space="preserve">2.89658904075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87529110908508</t>
   </si>
   <si>
     <t xml:space="preserve">2.83979368209839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78299808502197</t>
+    <t xml:space="preserve">2.78299784660339</t>
   </si>
   <si>
     <t xml:space="preserve">2.90368890762329</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88948965072632</t>
+    <t xml:space="preserve">2.8894898891449</t>
   </si>
   <si>
     <t xml:space="preserve">2.81849479675293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8326940536499</t>
+    <t xml:space="preserve">2.83269429206848</t>
   </si>
   <si>
     <t xml:space="preserve">2.8539924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98100256919861</t>
+    <t xml:space="preserve">2.98100280761719</t>
   </si>
   <si>
     <t xml:space="preserve">2.95111775398254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97353148460388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94364643096924</t>
+    <t xml:space="preserve">2.9735312461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94364666938782</t>
   </si>
   <si>
     <t xml:space="preserve">2.91376185417175</t>
@@ -1241,7 +1238,7 @@
     <t xml:space="preserve">2.87640571594238</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81663632392883</t>
+    <t xml:space="preserve">2.81663656234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.83905005455017</t>
@@ -1253,16 +1250,16 @@
     <t xml:space="preserve">2.59997200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61491441726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6074435710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62238550186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65227055549622</t>
+    <t xml:space="preserve">2.61491417884827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60744333267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62238574028015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65227031707764</t>
   </si>
   <si>
     <t xml:space="preserve">2.62985682487488</t>
@@ -1274,7 +1271,7 @@
     <t xml:space="preserve">2.6373279094696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57008767127991</t>
+    <t xml:space="preserve">2.57008743286133</t>
   </si>
   <si>
     <t xml:space="preserve">2.58502984046936</t>
@@ -1283,34 +1280,34 @@
     <t xml:space="preserve">2.57755851745605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55514526367188</t>
+    <t xml:space="preserve">2.5551450252533</t>
   </si>
   <si>
     <t xml:space="preserve">2.52526044845581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59250140190125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54767394065857</t>
+    <t xml:space="preserve">2.59250116348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54767370223999</t>
   </si>
   <si>
     <t xml:space="preserve">2.50284671783447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47296237945557</t>
+    <t xml:space="preserve">2.47296214103699</t>
   </si>
   <si>
     <t xml:space="preserve">2.45801949501038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49537563323975</t>
+    <t xml:space="preserve">2.49537539482117</t>
   </si>
   <si>
     <t xml:space="preserve">2.4654905796051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48790431022644</t>
+    <t xml:space="preserve">2.48790407180786</t>
   </si>
   <si>
     <t xml:space="preserve">2.48043298721313</t>
@@ -1319,22 +1316,22 @@
     <t xml:space="preserve">2.53273153305054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40572166442871</t>
+    <t xml:space="preserve">2.40572118759155</t>
   </si>
   <si>
     <t xml:space="preserve">2.43560600280762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37583684921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3907790184021</t>
+    <t xml:space="preserve">2.37583708763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39077877998352</t>
   </si>
   <si>
     <t xml:space="preserve">2.42813491821289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44307708740234</t>
+    <t xml:space="preserve">2.44307684898376</t>
   </si>
   <si>
     <t xml:space="preserve">2.41319251060486</t>
@@ -1352,7 +1349,7 @@
     <t xml:space="preserve">2.71951103210449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73445343971252</t>
+    <t xml:space="preserve">2.73445320129395</t>
   </si>
   <si>
     <t xml:space="preserve">2.74939584732056</t>
@@ -1361,34 +1358,34 @@
     <t xml:space="preserve">2.75686693191528</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74192476272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77928018569946</t>
+    <t xml:space="preserve">2.74192500114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77928042411804</t>
   </si>
   <si>
     <t xml:space="preserve">2.79422283172607</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81757307052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82535624504089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84870648384094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84092307090759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80978965759277</t>
+    <t xml:space="preserve">2.81757283210754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82535648345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84870624542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84092283248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80978941917419</t>
   </si>
   <si>
     <t xml:space="preserve">2.87983989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88762331008911</t>
+    <t xml:space="preserve">2.88762283325195</t>
   </si>
   <si>
     <t xml:space="preserve">2.89540648460388</t>
@@ -1400,7 +1397,10 @@
     <t xml:space="preserve">2.80200624465942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83313989639282</t>
+    <t xml:space="preserve">2.7942225933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83313965797424</t>
   </si>
   <si>
     <t xml:space="preserve">2.86427307128906</t>
@@ -1412,25 +1412,25 @@
     <t xml:space="preserve">2.91875624656677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92654013633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90318965911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98880648612976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01215672492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00437355041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94210624694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97323989868164</t>
+    <t xml:space="preserve">2.9265398979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90318989753723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98880672454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01215648651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00437331199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9421067237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97323966026306</t>
   </si>
   <si>
     <t xml:space="preserve">2.91097331047058</t>
@@ -1451,28 +1451,28 @@
     <t xml:space="preserve">2.96545648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04329037666321</t>
+    <t xml:space="preserve">3.04329013824463</t>
   </si>
   <si>
     <t xml:space="preserve">3.05107378959656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01994013786316</t>
+    <t xml:space="preserve">3.01994037628174</t>
   </si>
   <si>
     <t xml:space="preserve">3.07442355155945</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02772378921509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98102307319641</t>
+    <t xml:space="preserve">3.02772355079651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98102331161499</t>
   </si>
   <si>
     <t xml:space="preserve">3.16004037857056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08999037742615</t>
+    <t xml:space="preserve">3.08999013900757</t>
   </si>
   <si>
     <t xml:space="preserve">3.0822069644928</t>
@@ -1487,61 +1487,61 @@
     <t xml:space="preserve">3.09777355194092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11416411399841</t>
+    <t xml:space="preserve">3.11416387557983</t>
   </si>
   <si>
     <t xml:space="preserve">3.13055419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10596895217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06499266624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07318782806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08957815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04040765762329</t>
+    <t xml:space="preserve">3.10596871376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06499290466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07318806648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08957862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04040741920471</t>
   </si>
   <si>
     <t xml:space="preserve">3.03221225738525</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04860234260559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05679750442505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01582217216492</t>
+    <t xml:space="preserve">3.04860258102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05679774284363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01582193374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.0240170955658</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00762677192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08138298988342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99943137168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99123620986938</t>
+    <t xml:space="preserve">3.00762701034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08138346672058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99943161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99123644828796</t>
   </si>
   <si>
     <t xml:space="preserve">2.97484612464905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96665048599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95845556259155</t>
+    <t xml:space="preserve">2.96665072441101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95845532417297</t>
   </si>
   <si>
     <t xml:space="preserve">2.98304128646851</t>
@@ -1550,28 +1550,28 @@
     <t xml:space="preserve">2.95026040077209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93387031555176</t>
+    <t xml:space="preserve">2.9338698387146</t>
   </si>
   <si>
     <t xml:space="preserve">2.90108942985535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9256751537323</t>
+    <t xml:space="preserve">2.92567491531372</t>
   </si>
   <si>
     <t xml:space="preserve">2.94206547737122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87650418281555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86830878257751</t>
+    <t xml:space="preserve">2.87650394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86830902099609</t>
   </si>
   <si>
     <t xml:space="preserve">2.81094288825989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83552837371826</t>
+    <t xml:space="preserve">2.83552813529968</t>
   </si>
   <si>
     <t xml:space="preserve">2.79455256462097</t>
@@ -1583,25 +1583,25 @@
     <t xml:space="preserve">2.80274748802185</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76177167892456</t>
+    <t xml:space="preserve">2.76177144050598</t>
   </si>
   <si>
     <t xml:space="preserve">2.84372353553772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86011362075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81913805007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9092845916748</t>
+    <t xml:space="preserve">2.86011385917664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81913781166077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90928483009338</t>
   </si>
   <si>
     <t xml:space="preserve">2.85191869735718</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88469910621643</t>
+    <t xml:space="preserve">2.88469934463501</t>
   </si>
   <si>
     <t xml:space="preserve">2.89289426803589</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">3.00797700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04215860366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01652216911316</t>
+    <t xml:space="preserve">3.04215836524963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01652240753174</t>
   </si>
   <si>
     <t xml:space="preserve">3.03361296653748</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">3.05070400238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05924940109253</t>
+    <t xml:space="preserve">3.05924916267395</t>
   </si>
   <si>
     <t xml:space="preserve">3.07633996009827</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">3.12761235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14470314979553</t>
+    <t xml:space="preserve">3.14470338821411</t>
   </si>
   <si>
     <t xml:space="preserve">3.16179394721985</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">3.2130663394928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23870253562927</t>
+    <t xml:space="preserve">3.23870277404785</t>
   </si>
   <si>
     <t xml:space="preserve">3.23015713691711</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">3.25579333305359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34979271888733</t>
+    <t xml:space="preserve">3.34979248046875</t>
   </si>
   <si>
     <t xml:space="preserve">3.30706548690796</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">3.35833787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36688327789307</t>
+    <t xml:space="preserve">3.36688351631165</t>
   </si>
   <si>
     <t xml:space="preserve">3.33270168304443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40106463432312</t>
+    <t xml:space="preserve">3.4010648727417</t>
   </si>
   <si>
     <t xml:space="preserve">3.42670106887817</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">3.29851984977722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38397431373596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32415676116943</t>
+    <t xml:space="preserve">3.38397407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32415652275085</t>
   </si>
   <si>
     <t xml:space="preserve">3.3754289150238</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">3.40961027145386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45233702659607</t>
+    <t xml:space="preserve">3.45233726501465</t>
   </si>
   <si>
     <t xml:space="preserve">3.44379210472107</t>
@@ -1742,13 +1742,13 @@
     <t xml:space="preserve">3.5036096572876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57197260856628</t>
+    <t xml:space="preserve">3.57197237014771</t>
   </si>
   <si>
     <t xml:space="preserve">3.52070021629333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51215505599976</t>
+    <t xml:space="preserve">3.51215529441833</t>
   </si>
   <si>
     <t xml:space="preserve">3.46088290214539</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">3.4865186214447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49550485610962</t>
+    <t xml:space="preserve">3.49550461769104</t>
   </si>
   <si>
     <t xml:space="preserve">3.51347661018372</t>
@@ -1778,40 +1778,40 @@
     <t xml:space="preserve">3.43260335922241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46854686737061</t>
+    <t xml:space="preserve">3.46854710578918</t>
   </si>
   <si>
     <t xml:space="preserve">3.47753286361694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45057535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37868857383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34274482727051</t>
+    <t xml:space="preserve">3.45057559013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3786883354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34274506568909</t>
   </si>
   <si>
     <t xml:space="preserve">3.42361760139465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38767433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44158959388733</t>
+    <t xml:space="preserve">3.38767409324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44158935546875</t>
   </si>
   <si>
     <t xml:space="preserve">3.40564608573914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45956110954285</t>
+    <t xml:space="preserve">3.45956134796143</t>
   </si>
   <si>
     <t xml:space="preserve">3.55840587615967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54942011833191</t>
+    <t xml:space="preserve">3.54941987991333</t>
   </si>
   <si>
     <t xml:space="preserve">3.54043412208557</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">3.69319415092468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65725064277649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56739163398743</t>
+    <t xml:space="preserve">3.65725040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56739187240601</t>
   </si>
   <si>
     <t xml:space="preserve">3.68420815467834</t>
@@ -1859,13 +1859,13 @@
     <t xml:space="preserve">3.70217967033386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75609493255615</t>
+    <t xml:space="preserve">3.75609469413757</t>
   </si>
   <si>
     <t xml:space="preserve">3.81899619102478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81001043319702</t>
+    <t xml:space="preserve">3.81001019477844</t>
   </si>
   <si>
     <t xml:space="preserve">3.80102443695068</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">3.78305292129517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83696746826172</t>
+    <t xml:space="preserve">3.83696794509888</t>
   </si>
   <si>
     <t xml:space="preserve">3.84595370292664</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">3.76508069038391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73812341690063</t>
+    <t xml:space="preserve">3.73812317848206</t>
   </si>
   <si>
     <t xml:space="preserve">3.73778820037842</t>
@@ -2364,6 +2364,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.19000005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15999984741211</t>
   </si>
 </sst>
 </file>
@@ -29214,7 +29217,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1020" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29240,7 +29243,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1021" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29292,7 +29295,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1023" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -29396,7 +29399,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1027" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -29500,7 +29503,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1031" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -29526,7 +29529,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1032" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -29552,7 +29555,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1033" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -29578,7 +29581,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1034" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -29682,7 +29685,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1038" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29708,7 +29711,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1039" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29734,7 +29737,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1040" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29786,7 +29789,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1042" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29838,7 +29841,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1044" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29890,7 +29893,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1046" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29916,7 +29919,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1047" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29942,7 +29945,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1048" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29968,7 +29971,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1049" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29994,7 +29997,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1050" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30020,7 +30023,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1051" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30072,7 +30075,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1053" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30124,7 +30127,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1055" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30176,7 +30179,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1057" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30202,7 +30205,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1058" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30228,7 +30231,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1059" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30280,7 +30283,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1061" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -30358,7 +30361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1064" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -30384,7 +30387,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1065" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -30410,7 +30413,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1066" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -30436,7 +30439,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1067" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -30462,7 +30465,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1068" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -30566,7 +30569,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1072" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -30592,7 +30595,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1073" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -30618,7 +30621,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1074" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -30644,7 +30647,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1075" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30722,7 +30725,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1078" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30774,7 +30777,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1080" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30800,7 +30803,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1081" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30826,7 +30829,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1082" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30852,7 +30855,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1083" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30878,7 +30881,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1084" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30904,7 +30907,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1085" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30930,7 +30933,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1086" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30956,7 +30959,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1087" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30982,7 +30985,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G1088" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31008,7 +31011,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1089" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31034,7 +31037,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1090" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31060,7 +31063,7 @@
         <v>3.5</v>
       </c>
       <c r="G1091" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31086,7 +31089,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1092" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31112,7 +31115,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1093" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31138,7 +31141,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1094" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31164,7 +31167,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1095" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31216,7 +31219,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1097" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31320,7 +31323,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1101" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -31424,7 +31427,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1105" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -31450,7 +31453,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1106" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31476,7 +31479,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1107" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -31502,7 +31505,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1108" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -31528,7 +31531,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1109" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -31554,7 +31557,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1110" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -31580,7 +31583,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1111" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -31632,7 +31635,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1113" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -31658,7 +31661,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1114" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31684,7 +31687,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1115" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31710,7 +31713,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31736,7 +31739,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1117" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31762,7 +31765,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1118" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31788,7 +31791,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1119" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31814,7 +31817,7 @@
         <v>4</v>
       </c>
       <c r="G1120" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31840,7 +31843,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1121" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31866,7 +31869,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1122" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31892,7 +31895,7 @@
         <v>4</v>
       </c>
       <c r="G1123" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31918,7 +31921,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1124" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31944,7 +31947,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1125" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31970,7 +31973,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1126" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31996,7 +31999,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1127" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32022,7 +32025,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1128" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32048,7 +32051,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1129" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32126,7 +32129,7 @@
         <v>4</v>
       </c>
       <c r="G1132" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32152,7 +32155,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1133" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32178,7 +32181,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1134" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32204,7 +32207,7 @@
         <v>4</v>
       </c>
       <c r="G1135" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32230,7 +32233,7 @@
         <v>4</v>
       </c>
       <c r="G1136" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32256,7 +32259,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1137" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32282,7 +32285,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1138" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -32308,7 +32311,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1139" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -32334,7 +32337,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1140" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -32360,7 +32363,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1141" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -32386,7 +32389,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1142" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -32412,7 +32415,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1143" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -32438,7 +32441,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1144" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -32464,7 +32467,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1145" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -32490,7 +32493,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1146" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -32516,7 +32519,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1147" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -32542,7 +32545,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1148" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -32568,7 +32571,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1149" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32594,7 +32597,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1150" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -32620,7 +32623,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1151" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -32646,7 +32649,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1152" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32672,7 +32675,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1153" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32698,7 +32701,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1154" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32724,7 +32727,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1155" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32750,7 +32753,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1156" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -32776,7 +32779,7 @@
         <v>3.5</v>
       </c>
       <c r="G1157" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32802,7 +32805,7 @@
         <v>3.5</v>
       </c>
       <c r="G1158" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32828,7 +32831,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1159" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32854,7 +32857,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1160" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32880,7 +32883,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1161" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32906,7 +32909,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1162" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32932,7 +32935,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1163" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32958,7 +32961,7 @@
         <v>3.5</v>
       </c>
       <c r="G1164" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32984,7 +32987,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1165" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33010,7 +33013,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1166" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33036,7 +33039,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1167" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33062,7 +33065,7 @@
         <v>3.5</v>
       </c>
       <c r="G1168" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33088,7 +33091,7 @@
         <v>3.5</v>
       </c>
       <c r="G1169" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33114,7 +33117,7 @@
         <v>3.5</v>
       </c>
       <c r="G1170" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33140,7 +33143,7 @@
         <v>3.5</v>
       </c>
       <c r="G1171" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33166,7 +33169,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1172" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33192,7 +33195,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1173" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33218,7 +33221,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1174" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33244,7 +33247,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1175" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33270,7 +33273,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1176" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -33296,7 +33299,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1177" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -33322,7 +33325,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1178" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -33348,7 +33351,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1179" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -33374,7 +33377,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1180" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -33400,7 +33403,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1181" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -33426,7 +33429,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1182" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -33452,7 +33455,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1183" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -33478,7 +33481,7 @@
         <v>3.5</v>
       </c>
       <c r="G1184" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -33504,7 +33507,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1185" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -33530,7 +33533,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1186" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -33556,7 +33559,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1187" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -33582,7 +33585,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1188" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -33608,7 +33611,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1189" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -33634,7 +33637,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1190" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -33660,7 +33663,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1191" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33686,7 +33689,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1192" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33712,7 +33715,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1193" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33738,7 +33741,7 @@
         <v>3.5</v>
       </c>
       <c r="G1194" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33764,7 +33767,7 @@
         <v>3.5</v>
       </c>
       <c r="G1195" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33790,7 +33793,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1196" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33816,7 +33819,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1197" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33842,7 +33845,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1198" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33868,7 +33871,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1199" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33894,7 +33897,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1200" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33920,7 +33923,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1201" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33946,7 +33949,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1202" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33972,7 +33975,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1203" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33998,7 +34001,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1204" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34024,7 +34027,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1205" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34050,7 +34053,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1206" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34076,7 +34079,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1207" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34102,7 +34105,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1208" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34128,7 +34131,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1209" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34154,7 +34157,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1210" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34180,7 +34183,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1211" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34206,7 +34209,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1212" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34232,7 +34235,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1213" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34258,7 +34261,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1214" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34284,7 +34287,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1215" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -34310,7 +34313,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1216" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -34336,7 +34339,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1217" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -34362,7 +34365,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1218" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -34388,7 +34391,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1219" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -34414,7 +34417,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1220" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -34440,7 +34443,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1221" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -34466,7 +34469,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1222" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -34492,7 +34495,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1223" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -34518,7 +34521,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1224" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -34544,7 +34547,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1225" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -34570,7 +34573,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1226" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -34596,7 +34599,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1227" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -34622,7 +34625,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1228" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -34648,7 +34651,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G1229" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34674,7 +34677,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1230" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34700,7 +34703,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1231" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34726,7 +34729,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1232" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34752,7 +34755,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1233" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34778,7 +34781,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1234" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34804,7 +34807,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1235" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34830,7 +34833,7 @@
         <v>3.25</v>
       </c>
       <c r="G1236" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34856,7 +34859,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1237" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34882,7 +34885,7 @@
         <v>3.25</v>
       </c>
       <c r="G1238" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34908,7 +34911,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1239" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34934,7 +34937,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1240" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34960,7 +34963,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G1241" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34986,7 +34989,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1242" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35012,7 +35015,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1243" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35038,7 +35041,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1244" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35064,7 +35067,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1245" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35090,7 +35093,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1246" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35116,7 +35119,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1247" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35142,7 +35145,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1248" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35168,7 +35171,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1249" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35194,7 +35197,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1250" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35220,7 +35223,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1251" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35246,7 +35249,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1252" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35272,7 +35275,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1253" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -35298,7 +35301,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1254" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -35324,7 +35327,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1255" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -35350,7 +35353,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1256" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -35376,7 +35379,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1257" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -35402,7 +35405,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1258" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -35428,7 +35431,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1259" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -35454,7 +35457,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1260" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -35480,7 +35483,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1261" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -35506,7 +35509,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1262" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -35532,7 +35535,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1263" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -35558,7 +35561,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1264" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -35584,7 +35587,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1265" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -35610,7 +35613,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1266" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -35636,7 +35639,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1267" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -35662,7 +35665,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1268" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35688,7 +35691,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1269" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35714,7 +35717,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1270" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35740,7 +35743,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1271" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35766,7 +35769,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1272" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35792,7 +35795,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1273" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35818,7 +35821,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1274" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35844,7 +35847,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1275" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35870,7 +35873,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1276" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35896,7 +35899,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1277" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35922,7 +35925,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1278" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35948,7 +35951,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1279" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35974,7 +35977,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1280" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -36000,7 +36003,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1281" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -36026,7 +36029,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1282" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -36052,7 +36055,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1283" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -36078,7 +36081,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1284" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36104,7 +36107,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1285" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -36182,7 +36185,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1288" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -36208,7 +36211,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1289" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -36260,7 +36263,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1291" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -36286,7 +36289,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1292" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -36312,7 +36315,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1293" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -36364,7 +36367,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1295" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -36390,7 +36393,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1296" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -36442,7 +36445,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1298" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -36468,7 +36471,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1299" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -36728,7 +36731,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1309" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36884,7 +36887,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1315" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36910,7 +36913,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1316" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36936,7 +36939,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1317" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -37742,7 +37745,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1348" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -56054,7 +56057,7 @@
     </row>
     <row r="2053">
       <c r="A2053" s="1" t="n">
-        <v>46013.6910069444</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2053" t="n">
         <v>144438</v>
@@ -56075,6 +56078,32 @@
         <v>783</v>
       </c>
       <c r="H2053" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="1" t="n">
+        <v>46014.6913078704</v>
+      </c>
+      <c r="B2054" t="n">
+        <v>39467</v>
+      </c>
+      <c r="C2054" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>6.1100001335144</v>
+      </c>
+      <c r="E2054" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F2054" t="n">
+        <v>6.15999984741211</v>
+      </c>
+      <c r="G2054" t="s">
+        <v>784</v>
+      </c>
+      <c r="H2054" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="789">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,271 +44,268 @@
     <t xml:space="preserve">EQUI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68691468238831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7174471616745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71417593955994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71090483665466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70109057426453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67055773735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.674919962883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69018626213074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67710089683533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65856301784515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65747284889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65529227256775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784492015839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64656865596771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311110019684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65420162677765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64874923229218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65965354442596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64002585411072</t>
+    <t xml:space="preserve">1.68691492080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71744728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71417570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71090459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70109021663666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67055797576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491984367371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69018602371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67710077762604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65856313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65747308731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65529215335846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64656841754913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311121940613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65420138835907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64874935150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65965402126312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64002573490143</t>
   </si>
   <si>
     <t xml:space="preserve">1.64329719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62585031986237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64765894412994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67382943630219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68909573554993</t>
+    <t xml:space="preserve">1.6258499622345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64765882492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67382955551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68909561634064</t>
   </si>
   <si>
     <t xml:space="preserve">1.67928159236908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67819118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67164874076843</t>
+    <t xml:space="preserve">1.67819142341614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67164850234985</t>
   </si>
   <si>
     <t xml:space="preserve">1.67273902893066</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70327138900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70654284954071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69563829898834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66565096378326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.668377161026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69836473464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70381677150726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68473386764526</t>
+    <t xml:space="preserve">1.70327150821686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70654273033142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69563806056976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66565132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66837751865387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69836461544037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70381665229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.687460064888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68473398685455</t>
   </si>
   <si>
     <t xml:space="preserve">1.67110311985016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75016033649445</t>
+    <t xml:space="preserve">1.75016093254089</t>
   </si>
   <si>
     <t xml:space="preserve">1.72289955615997</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72835147380829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74470853805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73107779026031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73925590515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74198234081268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79922997951508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77742183208466</t>
+    <t xml:space="preserve">1.728351354599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74470829963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73107802867889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73925602436066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74198186397552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79923057556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7774213552475</t>
   </si>
   <si>
     <t xml:space="preserve">1.77196931838989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7365300655365</t>
+    <t xml:space="preserve">1.73652982711792</t>
   </si>
   <si>
     <t xml:space="preserve">1.7965042591095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78832578659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81831288337708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82376551628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80468237400055</t>
+    <t xml:space="preserve">1.78832566738129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81831300258636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82376503944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80468261241913</t>
   </si>
   <si>
     <t xml:space="preserve">1.81558692455292</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81286096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81013488769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377806186676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84284806251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88950264453888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200689315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8807544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84576380252838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81952095031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83118450641632</t>
+    <t xml:space="preserve">1.81286120414734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81013453006744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377830028534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84284842014313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8895024061203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88075482845306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84576392173767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8195207118988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83118438720703</t>
   </si>
   <si>
     <t xml:space="preserve">1.86034333705902</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87492299079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87783849239349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8632595539093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88367056846619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80785739421844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7670351266861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79619359970093</t>
+    <t xml:space="preserve">1.87492263317108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87783896923065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86325919628143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8836704492569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80785715579987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76703464984894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79619371891022</t>
   </si>
   <si>
     <t xml:space="preserve">1.79910957813263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.781613945961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82243692874908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7845299243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81660532951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83410036563873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83701622486115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84867978096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86909127235413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85159587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84284830093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85742771625519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282951831818</t>
+    <t xml:space="preserve">1.78161418437958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82243680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78453004360199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81660497188568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83410060405731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83701658248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84868013858795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86909115314484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85159575939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85742735862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9128292798996</t>
   </si>
   <si>
     <t xml:space="preserve">1.89241826534271</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88658654689789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89533424377441</t>
+    <t xml:space="preserve">1.8865864276886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89533412456512</t>
   </si>
   <si>
     <t xml:space="preserve">1.83993220329285</t>
@@ -320,106 +317,106 @@
     <t xml:space="preserve">1.866175532341</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81077349185944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89825010299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91574549674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95365226268768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96239984035492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92449283599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9653160572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00613832473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905418395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98281133174896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95948433876038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9274092912674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90991377830505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9565681219101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01197028160095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0003068447113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94490432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94782054424286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90699779987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92157733440399</t>
+    <t xml:space="preserve">1.81077337265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89825046062469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91574573516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95365190505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9624000787735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92449331283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96531569957733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00613856315613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905442237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98281145095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95948386192322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92740917205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90991365909576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95656824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01197004318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00030660629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94490456581116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94782042503357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90699756145477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9215772151947</t>
   </si>
   <si>
     <t xml:space="preserve">2.07903599739075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06737208366394</t>
+    <t xml:space="preserve">2.06737232208252</t>
   </si>
   <si>
     <t xml:space="preserve">1.98864305019379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99447512626648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97406375408173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93907284736633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93032479286194</t>
+    <t xml:space="preserve">1.99447476863861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97406351566315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93907272815704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93032491207123</t>
   </si>
   <si>
     <t xml:space="preserve">1.94198858737946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90408229827881</t>
+    <t xml:space="preserve">1.90408194065094</t>
   </si>
   <si>
     <t xml:space="preserve">1.8253527879715</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81368899345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7903618812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8282687664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02852940559387</t>
+    <t xml:space="preserve">1.81368887424469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79036200046539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82826852798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02852916717529</t>
   </si>
   <si>
     <t xml:space="preserve">1.90331161022186</t>
@@ -428,43 +425,43 @@
     <t xml:space="preserve">1.89705073833466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89078962802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87826800346375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82192027568817</t>
+    <t xml:space="preserve">1.89078986644745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87826788425446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82191979885101</t>
   </si>
   <si>
     <t xml:space="preserve">1.7906152009964</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78435409069061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75931096076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74678909778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73426747322083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72800648212433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65287590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6904411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64661514759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60904943943024</t>
+    <t xml:space="preserve">1.78435456752777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75931107997894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74678897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73426711559296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72800672054291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65287578105927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69044101238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64661478996277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60904955863953</t>
   </si>
   <si>
     <t xml:space="preserve">1.62783217430115</t>
@@ -473,55 +470,55 @@
     <t xml:space="preserve">1.66539764404297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67791938781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63409328460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67165839672089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62157118320465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60278844833374</t>
+    <t xml:space="preserve">1.67791950702667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63409304618835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67165851593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62157106399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60278880596161</t>
   </si>
   <si>
     <t xml:space="preserve">1.68418037891388</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70296275615692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.696702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70922386646271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71548497676849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65913665294647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64035391807556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61531054973602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59652757644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57148432731628</t>
+    <t xml:space="preserve">1.70296287536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69670212268829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70922362804413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71548449993134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65913677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64035379886627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61531007289886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59652769565582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57148420810699</t>
   </si>
   <si>
     <t xml:space="preserve">1.5652232170105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.558962225914</t>
+    <t xml:space="preserve">1.55896246433258</t>
   </si>
   <si>
     <t xml:space="preserve">1.57774496078491</t>
@@ -536,112 +533,112 @@
     <t xml:space="preserve">1.77183282375336</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81565892696381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80939793586731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80313718318939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77809345722198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74052822589874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76557159423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75305020809174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59026694297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47757065296173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36487472057343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54644072055817</t>
+    <t xml:space="preserve">1.81565916538239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80939781665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80313730239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77809357643127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74052834510803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76557171344757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75304996967316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59026682376862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47757077217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36487460136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54644048213959</t>
   </si>
   <si>
     <t xml:space="preserve">1.50261425971985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38365733623505</t>
+    <t xml:space="preserve">1.38365745544434</t>
   </si>
   <si>
     <t xml:space="preserve">1.40243995189667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32104849815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30226564407349</t>
+    <t xml:space="preserve">1.3210483789444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30226588249207</t>
   </si>
   <si>
     <t xml:space="preserve">1.3273092508316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33357036113739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28348290920258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29600489139557</t>
+    <t xml:space="preserve">1.3335702419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28348314762115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29600465297699</t>
   </si>
   <si>
     <t xml:space="preserve">1.28974390029907</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33983135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35235285758972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31478750705719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3460921049118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43374443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38991808891296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39617908000946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45878791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42122268676758</t>
+    <t xml:space="preserve">1.3398312330246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35235297679901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31478762626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609186649323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43374454975128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38991820812225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39617919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45878827571869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.421222448349</t>
   </si>
   <si>
     <t xml:space="preserve">1.37739646434784</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41496181488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44000542163849</t>
+    <t xml:space="preserve">1.41496193408966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44000554084778</t>
   </si>
   <si>
     <t xml:space="preserve">1.4462662935257</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42748367786407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53391885757446</t>
+    <t xml:space="preserve">1.4274834394455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53391897678375</t>
   </si>
   <si>
     <t xml:space="preserve">1.40870094299316</t>
@@ -650,16 +647,19 @@
     <t xml:space="preserve">1.4525271654129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51513612270355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72174561023712</t>
+    <t xml:space="preserve">1.51513624191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72174549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200725078583</t>
   </si>
   <si>
     <t xml:space="preserve">1.85863554477692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8051495552063</t>
+    <t xml:space="preserve">1.80514979362488</t>
   </si>
   <si>
     <t xml:space="preserve">1.65806353092194</t>
@@ -668,31 +668,31 @@
     <t xml:space="preserve">1.64469170570374</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61126327514648</t>
+    <t xml:space="preserve">1.61126315593719</t>
   </si>
   <si>
     <t xml:space="preserve">1.63800632953644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61794888973236</t>
+    <t xml:space="preserve">1.61794900894165</t>
   </si>
   <si>
     <t xml:space="preserve">1.60457742214203</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57114851474762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65137779712677</t>
+    <t xml:space="preserve">1.57114863395691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65137767791748</t>
   </si>
   <si>
     <t xml:space="preserve">1.63132059574127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66474890708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62463462352753</t>
+    <t xml:space="preserve">1.66474938392639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62463474273682</t>
   </si>
   <si>
     <t xml:space="preserve">1.67143487930298</t>
@@ -701,58 +701,58 @@
     <t xml:space="preserve">1.68480622768402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69817793369293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59120619297028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777716636658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52434861660004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51766288280487</t>
+    <t xml:space="preserve">1.69817769527435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59120607376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777752399445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52434849739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51766264438629</t>
   </si>
   <si>
     <t xml:space="preserve">1.5310343503952</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54440581798553</t>
+    <t xml:space="preserve">1.54440569877625</t>
   </si>
   <si>
     <t xml:space="preserve">1.5510915517807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53772008419037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57783448696136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58452010154724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56446290016174</t>
+    <t xml:space="preserve">1.53772020339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57783436775208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58451998233795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56446301937103</t>
   </si>
   <si>
     <t xml:space="preserve">1.49760556221008</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51097702980042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59789168834686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50429129600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49091982841492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48423397541046</t>
+    <t xml:space="preserve">1.5109771490097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59789192676544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50429141521454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4909200668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48423409461975</t>
   </si>
   <si>
     <t xml:space="preserve">1.47754836082458</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">1.46417689323425</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44411969184875</t>
+    <t xml:space="preserve">1.44411981105804</t>
   </si>
   <si>
     <t xml:space="preserve">1.4508056640625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.430748462677</t>
+    <t xml:space="preserve">1.43074822425842</t>
   </si>
   <si>
     <t xml:space="preserve">1.4173766374588</t>
@@ -779,109 +779,109 @@
     <t xml:space="preserve">1.36389088630676</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33046221733093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34383368492126</t>
+    <t xml:space="preserve">1.33046233654022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34383356571198</t>
   </si>
   <si>
     <t xml:space="preserve">1.3371479511261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32377636432648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32043361663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67812073230743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73829233646393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77172088623047</t>
+    <t xml:space="preserve">1.32377648353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32043349742889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67812061309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73829221725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77172112464905</t>
   </si>
   <si>
     <t xml:space="preserve">1.75166368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74497818946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73160648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76503539085388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7850923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79177820682526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75834977626801</t>
+    <t xml:space="preserve">1.7449779510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73160636425018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76503527164459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78509247303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79177844524384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75834941864014</t>
   </si>
   <si>
     <t xml:space="preserve">1.79846405982971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82520699501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85194993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86532115936279</t>
+    <t xml:space="preserve">1.82520687580109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85194957256317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86532139778137</t>
   </si>
   <si>
     <t xml:space="preserve">1.8786928653717</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89206433296204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91212129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92549300193787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89874970912933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200725078583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83857834339142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9054354429245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.885378241539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91880714893341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96560764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9990359544754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99235057830811</t>
+    <t xml:space="preserve">1.89206397533417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91212141513824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92549347877502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89874982833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200701236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83857822418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90543556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88537847995758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9188072681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96560740470886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99903619289398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99235010147095</t>
   </si>
   <si>
     <t xml:space="preserve">2.0124077796936</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98566472530365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97897887229919</t>
+    <t xml:space="preserve">1.98566448688507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9789787530899</t>
   </si>
   <si>
     <t xml:space="preserve">2.00572180747986</t>
@@ -890,52 +890,52 @@
     <t xml:space="preserve">2.01909327507019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02577924728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03246474266052</t>
+    <t xml:space="preserve">2.02577900886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03246450424194</t>
   </si>
   <si>
     <t xml:space="preserve">2.04629111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05320405960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08085680007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03937792778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08777022361755</t>
+    <t xml:space="preserve">2.05320429801941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08085703849792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03937816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08776998519897</t>
   </si>
   <si>
     <t xml:space="preserve">2.06011724472046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06703042984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07394361495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10850954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12233567237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17072796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14998841285706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1983802318573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20529341697693</t>
+    <t xml:space="preserve">2.06703066825867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07394337654114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10850882530212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12233591079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17072772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14998817443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19838047027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20529365539551</t>
   </si>
   <si>
     <t xml:space="preserve">2.19146728515625</t>
@@ -944,46 +944,46 @@
     <t xml:space="preserve">2.16381478309631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14307498931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764067649841</t>
+    <t xml:space="preserve">2.14307522773743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764091491699</t>
   </si>
   <si>
     <t xml:space="preserve">2.18455386161804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15690112113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22603273391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21220660209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23294591903687</t>
+    <t xml:space="preserve">2.15690135955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22603297233582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2122061252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23294615745544</t>
   </si>
   <si>
     <t xml:space="preserve">2.23985910415649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25368547439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26059865951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26751184463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27442479133606</t>
+    <t xml:space="preserve">2.25368523597717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26059889793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26751160621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27442502975464</t>
   </si>
   <si>
     <t xml:space="preserve">2.24677228927612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30899047851562</t>
+    <t xml:space="preserve">2.3089907169342</t>
   </si>
   <si>
     <t xml:space="preserve">2.32973003387451</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">2.31590342521667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32281684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33664321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34355640411377</t>
+    <t xml:space="preserve">2.32281708717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3366436958313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34355616569519</t>
   </si>
   <si>
     <t xml:space="preserve">2.38503527641296</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">2.43342733383179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44725322723389</t>
+    <t xml:space="preserve">2.44725370407104</t>
   </si>
   <si>
     <t xml:space="preserve">2.51638507843018</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">2.48873233795166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49564576148987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56477689743042</t>
+    <t xml:space="preserve">2.49564528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.564777135849</t>
   </si>
   <si>
     <t xml:space="preserve">2.55786371231079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54403758049011</t>
+    <t xml:space="preserve">2.54403781890869</t>
   </si>
   <si>
     <t xml:space="preserve">2.57169008255005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52329802513123</t>
+    <t xml:space="preserve">2.5232982635498</t>
   </si>
   <si>
     <t xml:space="preserve">2.53021121025085</t>
@@ -1043,70 +1043,70 @@
     <t xml:space="preserve">2.55095076560974</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58551621437073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59242939949036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63390874862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62699556350708</t>
+    <t xml:space="preserve">2.58551645278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59242987632751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63390827178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6269953250885</t>
   </si>
   <si>
     <t xml:space="preserve">2.65464782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64773488044739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62008237838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64082169532776</t>
+    <t xml:space="preserve">2.64773464202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62008213996887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64082145690918</t>
   </si>
   <si>
     <t xml:space="preserve">2.61316895484924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66230630874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64100790023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69780421257019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74040079116821</t>
+    <t xml:space="preserve">2.66230654716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64100766181946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69780349731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74040055274963</t>
   </si>
   <si>
     <t xml:space="preserve">2.7900972366333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76879906654358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74750018119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73330092430115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76169943809509</t>
+    <t xml:space="preserve">2.768798828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7475004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73330140113831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76169919967651</t>
   </si>
   <si>
     <t xml:space="preserve">2.71200275421143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65520691871643</t>
+    <t xml:space="preserve">2.65520668029785</t>
   </si>
   <si>
     <t xml:space="preserve">2.63390851020813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68360471725464</t>
+    <t xml:space="preserve">2.68360495567322</t>
   </si>
   <si>
     <t xml:space="preserve">2.62680888175964</t>
@@ -1118,37 +1118,37 @@
     <t xml:space="preserve">2.67650532722473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66940569877625</t>
+    <t xml:space="preserve">2.66940593719482</t>
   </si>
   <si>
     <t xml:space="preserve">2.70490336418152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75459957122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71910238265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72620153427124</t>
+    <t xml:space="preserve">2.75459980964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71910190582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72620177268982</t>
   </si>
   <si>
     <t xml:space="preserve">2.69070434570312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56291365623474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55581402778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59841108322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79719662666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54871439933777</t>
+    <t xml:space="preserve">2.56291389465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55581426620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59841132164001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79719686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54871463775635</t>
   </si>
   <si>
     <t xml:space="preserve">2.49191880226135</t>
@@ -1169,37 +1169,37 @@
     <t xml:space="preserve">2.21503877639771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34282946586609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.349928855896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48481941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59131145477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47771978378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60551047325134</t>
+    <t xml:space="preserve">2.34282994270325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34992909431458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48481917381287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59131169319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47771954536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60551071166992</t>
   </si>
   <si>
     <t xml:space="preserve">2.81139540672302</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82559466362</t>
+    <t xml:space="preserve">2.82559418678284</t>
   </si>
   <si>
     <t xml:space="preserve">2.88239049911499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86819124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8965892791748</t>
+    <t xml:space="preserve">2.8681914806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89658951759338</t>
   </si>
   <si>
     <t xml:space="preserve">2.8752908706665</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">2.78299784660339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368890762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8894898891449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81849503517151</t>
+    <t xml:space="preserve">2.90368914604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88949012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81849479675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.8326940536499</t>
@@ -1226,61 +1226,61 @@
     <t xml:space="preserve">2.8539924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98100233078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95111751556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9735312461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9436469078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91376209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8764054775238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81663632392883</t>
+    <t xml:space="preserve">2.98100280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95111775398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97353100776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94364714622498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91376185417175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87640619277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81663656234741</t>
   </si>
   <si>
     <t xml:space="preserve">2.83905005455017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70456862449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59997200965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61491465568542</t>
+    <t xml:space="preserve">2.70456838607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59997224807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61491441726685</t>
   </si>
   <si>
     <t xml:space="preserve">2.60744333267212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62238574028015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65227055549622</t>
+    <t xml:space="preserve">2.62238597869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65227031707764</t>
   </si>
   <si>
     <t xml:space="preserve">2.62985682487488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65974140167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6373279094696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57008767127991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58502984046936</t>
+    <t xml:space="preserve">2.65974164009094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63732814788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57008743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58502960205078</t>
   </si>
   <si>
     <t xml:space="preserve">2.57755851745605</t>
@@ -1289,22 +1289,22 @@
     <t xml:space="preserve">2.5551450252533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52526044845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59250116348267</t>
+    <t xml:space="preserve">2.52526021003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59250092506409</t>
   </si>
   <si>
     <t xml:space="preserve">2.54767394065857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50284671783447</t>
+    <t xml:space="preserve">2.50284647941589</t>
   </si>
   <si>
     <t xml:space="preserve">2.47296166419983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45801949501038</t>
+    <t xml:space="preserve">2.45801973342896</t>
   </si>
   <si>
     <t xml:space="preserve">2.49537539482117</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.46549081802368</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48790454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48043274879456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53273177146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40572142601013</t>
+    <t xml:space="preserve">2.48790431022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48043322563171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53273153305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40572118759155</t>
   </si>
   <si>
     <t xml:space="preserve">2.43560600280762</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">2.37583684921265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39077877998352</t>
+    <t xml:space="preserve">2.3907790184021</t>
   </si>
   <si>
     <t xml:space="preserve">2.42813491821289</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">2.41319251060486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39824986457825</t>
+    <t xml:space="preserve">2.39825010299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.42066359519958</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">2.64479923248291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71951103210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73445343971252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939584732056</t>
+    <t xml:space="preserve">2.71951150894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7344536781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939560890198</t>
   </si>
   <si>
     <t xml:space="preserve">2.75686717033386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74192452430725</t>
+    <t xml:space="preserve">2.74192476272583</t>
   </si>
   <si>
     <t xml:space="preserve">2.77928066253662</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7942225933075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81757283210754</t>
+    <t xml:space="preserve">2.79422283172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81757259368896</t>
   </si>
   <si>
     <t xml:space="preserve">2.82535624504089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84870648384094</t>
+    <t xml:space="preserve">2.84870672225952</t>
   </si>
   <si>
     <t xml:space="preserve">2.84092307090759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80978965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87983989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88762307167053</t>
+    <t xml:space="preserve">2.80978941917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87983965873718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88762331008911</t>
   </si>
   <si>
     <t xml:space="preserve">2.89540648460388</t>
@@ -1400,10 +1400,7 @@
     <t xml:space="preserve">2.87205648422241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80200600624084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79422283172607</t>
+    <t xml:space="preserve">2.80200624465942</t>
   </si>
   <si>
     <t xml:space="preserve">2.83313965797424</t>
@@ -1412,70 +1409,70 @@
     <t xml:space="preserve">2.86427307128906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85648965835571</t>
+    <t xml:space="preserve">2.85648989677429</t>
   </si>
   <si>
     <t xml:space="preserve">2.91875648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92653965950012</t>
+    <t xml:space="preserve">2.9265398979187</t>
   </si>
   <si>
     <t xml:space="preserve">2.90318965911865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98880672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01215672492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00437331199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9421067237854</t>
+    <t xml:space="preserve">2.98880648612976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01215696334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00437355041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94210648536682</t>
   </si>
   <si>
     <t xml:space="preserve">2.97323989868164</t>
   </si>
   <si>
-    <t xml:space="preserve">2.910973072052</t>
+    <t xml:space="preserve">2.91097331047058</t>
   </si>
   <si>
     <t xml:space="preserve">2.94989013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9576735496521</t>
+    <t xml:space="preserve">2.95767331123352</t>
   </si>
   <si>
     <t xml:space="preserve">3.03550696372986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99658966064453</t>
+    <t xml:space="preserve">2.99659013748169</t>
   </si>
   <si>
     <t xml:space="preserve">2.96545672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04329037666321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05107378959656</t>
+    <t xml:space="preserve">3.04329013824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05107355117798</t>
   </si>
   <si>
     <t xml:space="preserve">3.01994013786316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07442331314087</t>
+    <t xml:space="preserve">3.07442355155945</t>
   </si>
   <si>
     <t xml:space="preserve">3.02772355079651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98102355003357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16004037857056</t>
+    <t xml:space="preserve">2.98102307319641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16004061698914</t>
   </si>
   <si>
     <t xml:space="preserve">3.08999037742615</t>
@@ -1490,34 +1487,34 @@
     <t xml:space="preserve">3.05885696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09777355194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11416411399841</t>
+    <t xml:space="preserve">3.0977737903595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11416387557983</t>
   </si>
   <si>
     <t xml:space="preserve">3.13055419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10596871376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06499266624451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07318782806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08957815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04040741920471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03221225738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04860234260559</t>
+    <t xml:space="preserve">3.10596895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06499290466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07318806648254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08957839012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04040765762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03221201896667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04860258102417</t>
   </si>
   <si>
     <t xml:space="preserve">3.05679750442505</t>
@@ -1526,34 +1523,34 @@
     <t xml:space="preserve">3.01582193374634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02401685714722</t>
+    <t xml:space="preserve">3.0240170955658</t>
   </si>
   <si>
     <t xml:space="preserve">3.00762677192688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08138298988342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99943161010742</t>
+    <t xml:space="preserve">3.081383228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.999431848526</t>
   </si>
   <si>
     <t xml:space="preserve">2.99123644828796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97484612464905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96665072441101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95845580101013</t>
+    <t xml:space="preserve">2.97484588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96665048599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95845556259155</t>
   </si>
   <si>
     <t xml:space="preserve">2.98304128646851</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026063919067</t>
+    <t xml:space="preserve">2.95026040077209</t>
   </si>
   <si>
     <t xml:space="preserve">2.93387031555176</t>
@@ -1562,28 +1559,28 @@
     <t xml:space="preserve">2.90108942985535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9256751537323</t>
+    <t xml:space="preserve">2.92567491531372</t>
   </si>
   <si>
     <t xml:space="preserve">2.94206523895264</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87650418281555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86830902099609</t>
+    <t xml:space="preserve">2.87650394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86830878257751</t>
   </si>
   <si>
     <t xml:space="preserve">2.81094264984131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83552837371826</t>
+    <t xml:space="preserve">2.83552813529968</t>
   </si>
   <si>
     <t xml:space="preserve">2.79455256462097</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78635740280151</t>
+    <t xml:space="preserve">2.78635716438293</t>
   </si>
   <si>
     <t xml:space="preserve">2.80274748802185</t>
@@ -1595,7 +1592,7 @@
     <t xml:space="preserve">2.84372353553772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86011385917664</t>
+    <t xml:space="preserve">2.86011362075806</t>
   </si>
   <si>
     <t xml:space="preserve">2.81913805007935</t>
@@ -1604,7 +1601,7 @@
     <t xml:space="preserve">2.9092845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85191869735718</t>
+    <t xml:space="preserve">2.8519184589386</t>
   </si>
   <si>
     <t xml:space="preserve">2.88469910621643</t>
@@ -1619,7 +1616,7 @@
     <t xml:space="preserve">3.00797700881958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04215836524963</t>
+    <t xml:space="preserve">3.04215860366821</t>
   </si>
   <si>
     <t xml:space="preserve">3.01652240753174</t>
@@ -1631,19 +1628,19 @@
     <t xml:space="preserve">3.05070400238037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05924916267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07634019851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11906695365906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12761235237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14470338821411</t>
+    <t xml:space="preserve">3.05924940109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07633996009827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11906719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12761259078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14470314979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.16179394721985</t>
@@ -1652,19 +1649,19 @@
     <t xml:space="preserve">3.15324854850769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17033934593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11052179336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.084885597229</t>
+    <t xml:space="preserve">3.17033958435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11052203178406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08488535881042</t>
   </si>
   <si>
     <t xml:space="preserve">3.10197639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09343075752258</t>
+    <t xml:space="preserve">3.093430519104</t>
   </si>
   <si>
     <t xml:space="preserve">3.13615775108337</t>
@@ -1676,7 +1673,7 @@
     <t xml:space="preserve">3.19597554206848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21306657791138</t>
+    <t xml:space="preserve">3.2130663394928</t>
   </si>
   <si>
     <t xml:space="preserve">3.23870253562927</t>
@@ -1685,7 +1682,7 @@
     <t xml:space="preserve">3.23015713691711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25579309463501</t>
+    <t xml:space="preserve">3.25579333305359</t>
   </si>
   <si>
     <t xml:space="preserve">3.34979271888733</t>
@@ -1697,13 +1694,13 @@
     <t xml:space="preserve">3.35833811759949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36688327789307</t>
+    <t xml:space="preserve">3.36688351631165</t>
   </si>
   <si>
     <t xml:space="preserve">3.33270168304443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40106463432312</t>
+    <t xml:space="preserve">3.4010648727417</t>
   </si>
   <si>
     <t xml:space="preserve">3.42670130729675</t>
@@ -1712,19 +1709,19 @@
     <t xml:space="preserve">3.31561088562012</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28997468948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29851984977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38397407531738</t>
+    <t xml:space="preserve">3.28997492790222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29852032661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3839738368988</t>
   </si>
   <si>
     <t xml:space="preserve">3.32415652275085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3754289150238</t>
+    <t xml:space="preserve">3.37542867660522</t>
   </si>
   <si>
     <t xml:space="preserve">3.41815567016602</t>
@@ -1745,7 +1742,7 @@
     <t xml:space="preserve">3.46942806243896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5036096572876</t>
+    <t xml:space="preserve">3.50360941886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.57197260856628</t>
@@ -1754,37 +1751,40 @@
     <t xml:space="preserve">3.52070021629333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51215505599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46088266372681</t>
+    <t xml:space="preserve">3.51215481758118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46088290214539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4865186214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49550485610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51347637176514</t>
   </si>
   <si>
     <t xml:space="preserve">3.48651885986328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49550485610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51347661018372</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.50449061393738</t>
   </si>
   <si>
     <t xml:space="preserve">3.59434938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53144836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43260335922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46854686737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47753286361694</t>
+    <t xml:space="preserve">3.53144812583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43260359764099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46854710578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47753310203552</t>
   </si>
   <si>
     <t xml:space="preserve">3.45057535171509</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">3.34274482727051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42361760139465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38767433166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44158959388733</t>
+    <t xml:space="preserve">3.42361783981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38767409324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44158935546875</t>
   </si>
   <si>
     <t xml:space="preserve">3.40564608573914</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">3.45956110954285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55840587615967</t>
+    <t xml:space="preserve">3.55840563774109</t>
   </si>
   <si>
     <t xml:space="preserve">3.54942011833191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54043412208557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3607165813446</t>
+    <t xml:space="preserve">3.54043436050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36071681976318</t>
   </si>
   <si>
     <t xml:space="preserve">3.41463184356689</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">3.65725064277649</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56739163398743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68420815467834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7111656665802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7291374206543</t>
+    <t xml:space="preserve">3.56739187240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68420791625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71116590499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72913765907288</t>
   </si>
   <si>
     <t xml:space="preserve">3.74710917472839</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">3.75609493255615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81899619102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81001043319702</t>
+    <t xml:space="preserve">3.8189959526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81001019477844</t>
   </si>
   <si>
     <t xml:space="preserve">3.80102443695068</t>
@@ -1877,31 +1877,31 @@
     <t xml:space="preserve">3.78305292129517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83696746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84595370292664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82798218727112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76508069038391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73812341690063</t>
+    <t xml:space="preserve">3.83696794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84595394134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8279824256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76508092880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73812317848206</t>
   </si>
   <si>
     <t xml:space="preserve">3.73778820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77507305145264</t>
+    <t xml:space="preserve">3.77507281303406</t>
   </si>
   <si>
     <t xml:space="preserve">3.71914577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68186092376709</t>
+    <t xml:space="preserve">3.68186116218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.66321873664856</t>
@@ -1913,7 +1913,7 @@
     <t xml:space="preserve">3.69118213653564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75643038749695</t>
+    <t xml:space="preserve">3.75643062591553</t>
   </si>
   <si>
     <t xml:space="preserve">3.7657516002655</t>
@@ -1925,34 +1925,34 @@
     <t xml:space="preserve">3.93353247642517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80303597450256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88692665100098</t>
+    <t xml:space="preserve">3.80303621292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88692688941956</t>
   </si>
   <si>
     <t xml:space="preserve">3.84032082557678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8123574256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82167863845825</t>
+    <t xml:space="preserve">3.81235766410828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82167840003967</t>
   </si>
   <si>
     <t xml:space="preserve">3.83099985122681</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87760519981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90556883811951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91489028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96149611473083</t>
+    <t xml:space="preserve">3.87760543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90556907653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91488981246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96149587631226</t>
   </si>
   <si>
     <t xml:space="preserve">4.00810194015503</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">4.04538679122925</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01742267608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03606557846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98013830184937</t>
+    <t xml:space="preserve">4.01742315292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03606510162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98013854026794</t>
   </si>
   <si>
     <t xml:space="preserve">4.07334995269775</t>
@@ -1979,7 +1979,7 @@
     <t xml:space="preserve">4.09199237823486</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11063432693481</t>
+    <t xml:space="preserve">4.11063480377197</t>
   </si>
   <si>
     <t xml:space="preserve">4.1758828163147</t>
@@ -1994,13 +1994,13 @@
     <t xml:space="preserve">3.9894597530365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9428539276123</t>
+    <t xml:space="preserve">3.94285368919373</t>
   </si>
   <si>
     <t xml:space="preserve">3.9521746635437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97081732749939</t>
+    <t xml:space="preserve">3.97081756591797</t>
   </si>
   <si>
     <t xml:space="preserve">4.06402921676636</t>
@@ -2012,16 +2012,16 @@
     <t xml:space="preserve">4.11995601654053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70050358772278</t>
+    <t xml:space="preserve">3.7005033493042</t>
   </si>
   <si>
     <t xml:space="preserve">3.68652153015137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90090847015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92887210845947</t>
+    <t xml:space="preserve">3.90090823173523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92887234687805</t>
   </si>
   <si>
     <t xml:space="preserve">3.9242115020752</t>
@@ -2376,6 +2376,9 @@
   </si>
   <si>
     <t xml:space="preserve">6.26999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32000017166138</t>
   </si>
 </sst>
 </file>
@@ -6528,7 +6531,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G147" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -6580,7 +6583,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G149" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -6736,7 +6739,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G155" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -6762,7 +6765,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G156" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -6814,7 +6817,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G158" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -6840,7 +6843,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G159" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -7022,7 +7025,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G166" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -7074,7 +7077,7 @@
         <v>3.25</v>
       </c>
       <c r="G168" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -7100,7 +7103,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G169" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -7256,7 +7259,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G175" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -7282,7 +7285,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G176" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H176" t="s">
         <v>9</v>
@@ -7334,7 +7337,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G178" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -7360,7 +7363,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G179" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -7386,7 +7389,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G180" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -7412,7 +7415,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G181" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -7438,7 +7441,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G182" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -7464,7 +7467,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G183" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -7490,7 +7493,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G184" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -7542,7 +7545,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G186" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -7568,7 +7571,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G187" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -7594,7 +7597,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G188" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -7620,7 +7623,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G189" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -7646,7 +7649,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G190" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -7698,7 +7701,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G192" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -7854,7 +7857,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G198" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -7958,7 +7961,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G202" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -7984,7 +7987,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G203" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -8036,7 +8039,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G205" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -8088,7 +8091,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G207" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -8114,7 +8117,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G208" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -8140,7 +8143,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G209" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -8166,7 +8169,7 @@
         <v>3.25</v>
       </c>
       <c r="G210" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -8218,7 +8221,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G212" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -8244,7 +8247,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G213" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -8270,7 +8273,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G214" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H214" t="s">
         <v>9</v>
@@ -8296,7 +8299,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G215" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -8322,7 +8325,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G216" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -8348,7 +8351,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G217" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -8374,7 +8377,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G218" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -8400,7 +8403,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G219" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -8426,7 +8429,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G220" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -8452,7 +8455,7 @@
         <v>3.4449999332428</v>
       </c>
       <c r="G221" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -8478,7 +8481,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G222" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -8504,7 +8507,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G223" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -8530,7 +8533,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G224" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -8556,7 +8559,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G225" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -8582,7 +8585,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G226" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -8608,7 +8611,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G227" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -8634,7 +8637,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G228" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -8660,7 +8663,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G229" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -8686,7 +8689,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G230" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -8712,7 +8715,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G231" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -8738,7 +8741,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G232" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -8764,7 +8767,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G233" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -8790,7 +8793,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G234" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -8816,7 +8819,7 @@
         <v>3.25</v>
       </c>
       <c r="G235" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -8842,7 +8845,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G236" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -8868,7 +8871,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G237" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -8894,7 +8897,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G238" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -8920,7 +8923,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G239" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -8946,7 +8949,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G240" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -8972,7 +8975,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G241" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -8998,7 +9001,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G242" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -9024,7 +9027,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G243" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -9050,7 +9053,7 @@
         <v>3.56500005722046</v>
       </c>
       <c r="G244" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -9076,7 +9079,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G245" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H245" t="s">
         <v>9</v>
@@ -9102,7 +9105,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G246" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -9128,7 +9131,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G247" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H247" t="s">
         <v>9</v>
@@ -9154,7 +9157,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G248" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H248" t="s">
         <v>9</v>
@@ -9180,7 +9183,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G249" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -9206,7 +9209,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G250" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -9232,7 +9235,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G251" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -9258,7 +9261,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G252" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -9284,7 +9287,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G253" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -9310,7 +9313,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G254" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -9336,7 +9339,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G255" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -9362,7 +9365,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G256" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -9388,7 +9391,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G257" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -9414,7 +9417,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G258" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -9440,7 +9443,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G259" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -9466,7 +9469,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G260" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H260" t="s">
         <v>9</v>
@@ -9492,7 +9495,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G261" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -9518,7 +9521,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G262" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -9544,7 +9547,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G263" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -9570,7 +9573,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G264" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -9596,7 +9599,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G265" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -9622,7 +9625,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G266" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H266" t="s">
         <v>9</v>
@@ -9648,7 +9651,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G267" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -9674,7 +9677,7 @@
         <v>3.25</v>
       </c>
       <c r="G268" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -9700,7 +9703,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G269" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -9726,7 +9729,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G270" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H270" t="s">
         <v>9</v>
@@ -9752,7 +9755,7 @@
         <v>3.25</v>
       </c>
       <c r="G271" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -9778,7 +9781,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G272" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -9804,7 +9807,7 @@
         <v>3.25</v>
       </c>
       <c r="G273" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -9882,7 +9885,7 @@
         <v>3.26500010490417</v>
       </c>
       <c r="G276" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -9908,7 +9911,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G277" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -10064,7 +10067,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G283" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -10402,7 +10405,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G296" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -10428,7 +10431,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G297" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -10454,7 +10457,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G298" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -10584,7 +10587,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G303" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -10636,7 +10639,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G305" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -10714,7 +10717,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G308" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -10766,7 +10769,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G310" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -10792,7 +10795,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G311" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -10844,7 +10847,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G313" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -10896,7 +10899,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G315" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -10922,7 +10925,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G316" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H316" t="s">
         <v>9</v>
@@ -10948,7 +10951,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G317" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -10974,7 +10977,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G318" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -11104,7 +11107,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G323" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -11130,7 +11133,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G324" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -11156,7 +11159,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G325" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H325" t="s">
         <v>9</v>
@@ -11182,7 +11185,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G326" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H326" t="s">
         <v>9</v>
@@ -11234,7 +11237,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G328" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -11286,7 +11289,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G330" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H330" t="s">
         <v>9</v>
@@ -11312,7 +11315,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G331" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -11364,7 +11367,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G333" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -11390,7 +11393,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G334" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -11416,7 +11419,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G335" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -11442,7 +11445,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G336" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -11494,7 +11497,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G338" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -11520,7 +11523,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G339" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -11572,7 +11575,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G341" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -11624,7 +11627,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G343" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -11728,7 +11731,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G347" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -11780,7 +11783,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G349" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -11832,7 +11835,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G351" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -11858,7 +11861,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G352" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -11884,7 +11887,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G353" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -11910,7 +11913,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G354" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -11936,7 +11939,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G355" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -11988,7 +11991,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G357" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -12014,7 +12017,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G358" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -12066,7 +12069,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G360" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -12092,7 +12095,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G361" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -12144,7 +12147,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G363" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -12170,7 +12173,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G364" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -12196,7 +12199,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G365" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -12222,7 +12225,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G366" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -12248,7 +12251,7 @@
         <v>3</v>
       </c>
       <c r="G367" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -12274,7 +12277,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G368" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -12300,7 +12303,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G369" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -12326,7 +12329,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G370" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -12352,7 +12355,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G371" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -12378,7 +12381,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G372" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -12404,7 +12407,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G373" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -12430,7 +12433,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G374" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -12456,7 +12459,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G375" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -12482,7 +12485,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G376" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -12508,7 +12511,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G377" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -12534,7 +12537,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G378" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -12560,7 +12563,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G379" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -12586,7 +12589,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G380" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -12612,7 +12615,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G381" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -12638,7 +12641,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G382" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -12664,7 +12667,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G383" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -12690,7 +12693,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G384" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -12716,7 +12719,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G385" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -12742,7 +12745,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G386" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -12768,7 +12771,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G387" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -12794,7 +12797,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G388" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -12820,7 +12823,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G389" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -12846,7 +12849,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G390" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -12872,7 +12875,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G391" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -12898,7 +12901,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G392" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -12924,7 +12927,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G393" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -12950,7 +12953,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G394" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -12976,7 +12979,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G395" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -13002,7 +13005,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G396" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -13028,7 +13031,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G397" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -13054,7 +13057,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G398" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -13080,7 +13083,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G399" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -13106,7 +13109,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G400" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -13132,7 +13135,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G401" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -13158,7 +13161,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G402" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -13184,7 +13187,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G403" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -13210,7 +13213,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G404" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -13236,7 +13239,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G405" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -13262,7 +13265,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G406" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -13288,7 +13291,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G407" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -13314,7 +13317,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G408" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -13340,7 +13343,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G409" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -13366,7 +13369,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G410" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -13392,7 +13395,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G411" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -13418,7 +13421,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G412" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -13444,7 +13447,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G413" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -13470,7 +13473,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G414" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -13496,7 +13499,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G415" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -13522,7 +13525,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G416" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -13548,7 +13551,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G417" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -13574,7 +13577,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G418" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -13600,7 +13603,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G419" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -13626,7 +13629,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G420" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -13652,7 +13655,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G421" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -13678,7 +13681,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G422" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -13704,7 +13707,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G423" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -13730,7 +13733,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G424" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -13756,7 +13759,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G425" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -13782,7 +13785,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G426" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -13808,7 +13811,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G427" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -13834,7 +13837,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G428" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -13860,7 +13863,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G429" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -13886,7 +13889,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G430" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -13912,7 +13915,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G431" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -13938,7 +13941,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G432" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -13964,7 +13967,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G433" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -13990,7 +13993,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G434" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -14016,7 +14019,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G435" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -14042,7 +14045,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G436" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -14068,7 +14071,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G437" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -14094,7 +14097,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G438" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -14120,7 +14123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G439" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -14146,7 +14149,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G440" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -14172,7 +14175,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G441" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -14198,7 +14201,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G442" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -14224,7 +14227,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G443" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -14250,7 +14253,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G444" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -14276,7 +14279,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G445" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -14302,7 +14305,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G446" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -14328,7 +14331,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G447" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -14354,7 +14357,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G448" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -14380,7 +14383,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G449" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -14406,7 +14409,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G450" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -14432,7 +14435,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G451" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -14458,7 +14461,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G452" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -14484,7 +14487,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G453" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -14510,7 +14513,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G454" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -14536,7 +14539,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G455" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -14562,7 +14565,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G456" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -14588,7 +14591,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G457" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -14614,7 +14617,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G458" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -14640,7 +14643,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G459" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -14666,7 +14669,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G460" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -14692,7 +14695,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G461" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -14718,7 +14721,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G462" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -14744,7 +14747,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G463" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -14770,7 +14773,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G464" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -14796,7 +14799,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G465" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -14822,7 +14825,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G466" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -14848,7 +14851,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G467" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -14874,7 +14877,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G468" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -14900,7 +14903,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G469" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -14926,7 +14929,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G470" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -14952,7 +14955,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G471" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -14978,7 +14981,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G472" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -15004,7 +15007,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G473" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -15030,7 +15033,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G474" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -15056,7 +15059,7 @@
         <v>2.5</v>
       </c>
       <c r="G475" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -15082,7 +15085,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G476" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -15108,7 +15111,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G477" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -15134,7 +15137,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G478" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -15160,7 +15163,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G479" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -15186,7 +15189,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G480" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -15212,7 +15215,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G481" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -15238,7 +15241,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G482" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -15264,7 +15267,7 @@
         <v>2.5</v>
       </c>
       <c r="G483" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -15290,7 +15293,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G484" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -15316,7 +15319,7 @@
         <v>2.5</v>
       </c>
       <c r="G485" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -15342,7 +15345,7 @@
         <v>2.5</v>
       </c>
       <c r="G486" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -15368,7 +15371,7 @@
         <v>2.5</v>
       </c>
       <c r="G487" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -15394,7 +15397,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G488" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -15420,7 +15423,7 @@
         <v>2.5</v>
       </c>
       <c r="G489" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -15446,7 +15449,7 @@
         <v>2.5</v>
       </c>
       <c r="G490" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -15472,7 +15475,7 @@
         <v>2.5</v>
       </c>
       <c r="G491" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -15498,7 +15501,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G492" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -15524,7 +15527,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G493" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -15550,7 +15553,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G494" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -15576,7 +15579,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G495" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -15602,7 +15605,7 @@
         <v>2.5</v>
       </c>
       <c r="G496" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -15628,7 +15631,7 @@
         <v>2.5</v>
       </c>
       <c r="G497" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -15654,7 +15657,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G498" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -15680,7 +15683,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G499" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -15706,7 +15709,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G500" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -15732,7 +15735,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G501" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -15758,7 +15761,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G502" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -15784,7 +15787,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G503" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -15810,7 +15813,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G504" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -15836,7 +15839,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G505" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -15862,7 +15865,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G506" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -15888,7 +15891,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G507" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -15914,7 +15917,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G508" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -15940,7 +15943,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G509" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -15966,7 +15969,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G510" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -15992,7 +15995,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G511" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -16018,7 +16021,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G512" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -16044,7 +16047,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G513" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -16070,7 +16073,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G514" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -16096,7 +16099,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G515" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -16122,7 +16125,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G516" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -16148,7 +16151,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G517" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -16174,7 +16177,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G518" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -16200,7 +16203,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G519" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -16226,7 +16229,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G520" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -16252,7 +16255,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G521" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -16278,7 +16281,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G522" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -16304,7 +16307,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G523" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -16330,7 +16333,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G524" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -16356,7 +16359,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G525" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -16382,7 +16385,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G526" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -16408,7 +16411,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G527" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -16434,7 +16437,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G528" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -16460,7 +16463,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G529" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -16486,7 +16489,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G530" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -16512,7 +16515,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G531" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -16538,7 +16541,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G532" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -16564,7 +16567,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G533" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -16590,7 +16593,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G534" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -16616,7 +16619,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G535" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -16642,7 +16645,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G536" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -16668,7 +16671,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G537" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -16694,7 +16697,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G538" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -16720,7 +16723,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G539" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -16746,7 +16749,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G540" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -16772,7 +16775,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G541" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -16798,7 +16801,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G542" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -16824,7 +16827,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G543" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -16850,7 +16853,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G544" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -16876,7 +16879,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G545" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -16902,7 +16905,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G546" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -16928,7 +16931,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G547" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -16954,7 +16957,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G548" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -16980,7 +16983,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G549" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -17006,7 +17009,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G550" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -17032,7 +17035,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G551" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -17058,7 +17061,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G552" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -17084,7 +17087,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G553" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -17110,7 +17113,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G554" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -17136,7 +17139,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G555" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -17162,7 +17165,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G556" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -17188,7 +17191,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G557" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -17214,7 +17217,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G558" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -17240,7 +17243,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G559" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -17266,7 +17269,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G560" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -17292,7 +17295,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G561" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -17318,7 +17321,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G562" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -17344,7 +17347,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G563" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -17370,7 +17373,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G564" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -17396,7 +17399,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G565" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -17422,7 +17425,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G566" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -17448,7 +17451,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G567" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -17474,7 +17477,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G568" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -17500,7 +17503,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G569" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -17526,7 +17529,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G570" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -17552,7 +17555,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G571" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -17578,7 +17581,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G572" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -17604,7 +17607,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G573" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -17630,7 +17633,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G574" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -17656,7 +17659,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G575" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -17682,7 +17685,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G576" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -17708,7 +17711,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G577" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -17734,7 +17737,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G578" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -17760,7 +17763,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G579" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -17786,7 +17789,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G580" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -17812,7 +17815,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G581" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -17838,7 +17841,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G582" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -17864,7 +17867,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G583" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -17890,7 +17893,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G584" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -17916,7 +17919,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G585" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -17942,7 +17945,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G586" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -17968,7 +17971,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G587" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -17994,7 +17997,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G588" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -18020,7 +18023,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G589" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -18046,7 +18049,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G590" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -18072,7 +18075,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G591" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -18098,7 +18101,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G592" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -18124,7 +18127,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G593" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -18150,7 +18153,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G594" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -18176,7 +18179,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G595" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -18202,7 +18205,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G596" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -18228,7 +18231,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G597" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -18254,7 +18257,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G598" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -18280,7 +18283,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G599" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -18306,7 +18309,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G600" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -18332,7 +18335,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G601" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -18358,7 +18361,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G602" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -18384,7 +18387,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G603" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -18410,7 +18413,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G604" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -18436,7 +18439,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G605" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -18462,7 +18465,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G606" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -18488,7 +18491,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G607" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -18514,7 +18517,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G608" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -18540,7 +18543,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G609" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -18566,7 +18569,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G610" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -18592,7 +18595,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G611" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -18618,7 +18621,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G612" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -18644,7 +18647,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G613" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -18670,7 +18673,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G614" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -18696,7 +18699,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G615" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -18722,7 +18725,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G616" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -18748,7 +18751,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G617" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -18774,7 +18777,7 @@
         <v>2.25</v>
       </c>
       <c r="G618" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -18800,7 +18803,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G619" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -18826,7 +18829,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G620" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -18852,7 +18855,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G621" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -18878,7 +18881,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G622" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -18904,7 +18907,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G623" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -18930,7 +18933,7 @@
         <v>2.25</v>
       </c>
       <c r="G624" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -18956,7 +18959,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G625" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -18982,7 +18985,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G626" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19008,7 +19011,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G627" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19034,7 +19037,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G628" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19060,7 +19063,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G629" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19086,7 +19089,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G630" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19112,7 +19115,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G631" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19138,7 +19141,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G632" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19164,7 +19167,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G633" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19190,7 +19193,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G634" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19216,7 +19219,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G635" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19242,7 +19245,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19268,7 +19271,7 @@
         <v>2.75</v>
       </c>
       <c r="G637" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19294,7 +19297,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G638" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19320,7 +19323,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G639" t="s">
-        <v>70</v>
+        <v>213</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -36090,7 +36093,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1284" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36142,7 +36145,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1286" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36168,7 +36171,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1287" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36246,7 +36249,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36350,7 +36353,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1294" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36428,7 +36431,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1297" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36506,7 +36509,7 @@
         <v>3.75</v>
       </c>
       <c r="G1300" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36532,7 +36535,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1301" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36558,7 +36561,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1302" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36584,7 +36587,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1303" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36610,7 +36613,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1304" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36636,7 +36639,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1305" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36662,7 +36665,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1306" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36688,7 +36691,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1307" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36714,7 +36717,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36766,7 +36769,7 @@
         <v>3.75</v>
       </c>
       <c r="G1310" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36792,7 +36795,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36818,7 +36821,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1312" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36844,7 +36847,7 @@
         <v>3.75</v>
       </c>
       <c r="G1313" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36870,7 +36873,7 @@
         <v>3.75</v>
       </c>
       <c r="G1314" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36974,7 +36977,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37000,7 +37003,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37026,7 +37029,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37052,7 +37055,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1321" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37078,7 +37081,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1322" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37104,7 +37107,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1323" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37130,7 +37133,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1324" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37156,7 +37159,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1325" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37182,7 +37185,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1326" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37208,7 +37211,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1327" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37234,7 +37237,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1328" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37260,7 +37263,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1329" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37286,7 +37289,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37312,7 +37315,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1331" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37338,7 +37341,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1332" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37364,7 +37367,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1333" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37390,7 +37393,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1334" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37416,7 +37419,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37442,7 +37445,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1336" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37468,7 +37471,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1337" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37494,7 +37497,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1338" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37520,7 +37523,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37546,7 +37549,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1340" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37572,7 +37575,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1341" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37598,7 +37601,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1342" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37624,7 +37627,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1343" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37650,7 +37653,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37676,7 +37679,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1345" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37702,7 +37705,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1346" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37728,7 +37731,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37780,7 +37783,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1349" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37806,7 +37809,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1350" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37832,7 +37835,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1351" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37858,7 +37861,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1352" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37884,7 +37887,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1353" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37910,7 +37913,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37936,7 +37939,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1355" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37962,7 +37965,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1356" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37988,7 +37991,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1357" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38014,7 +38017,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1358" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38040,7 +38043,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1359" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38066,7 +38069,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1360" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38092,7 +38095,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1361" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38118,7 +38121,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1362" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38144,7 +38147,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1363" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38170,7 +38173,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1364" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38196,7 +38199,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1365" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38222,7 +38225,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1366" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38248,7 +38251,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38274,7 +38277,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1368" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38300,7 +38303,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38326,7 +38329,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1370" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38352,7 +38355,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1371" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38378,7 +38381,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38404,7 +38407,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1373" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38430,7 +38433,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1374" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38456,7 +38459,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1375" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38482,7 +38485,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38508,7 +38511,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1377" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38534,7 +38537,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1378" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38560,7 +38563,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1379" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38586,7 +38589,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1380" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38612,7 +38615,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38638,7 +38641,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1382" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38664,7 +38667,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38690,7 +38693,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1384" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38716,7 +38719,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1385" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38742,7 +38745,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1386" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38768,7 +38771,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38794,7 +38797,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1388" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38820,7 +38823,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38846,7 +38849,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1390" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38872,7 +38875,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38898,7 +38901,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1392" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38924,7 +38927,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1393" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38950,7 +38953,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38976,7 +38979,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1395" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39002,7 +39005,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1396" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39028,7 +39031,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1397" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -39054,7 +39057,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1398" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39080,7 +39083,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1399" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39106,7 +39109,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1400" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39132,7 +39135,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1401" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39158,7 +39161,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1402" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39184,7 +39187,7 @@
         <v>3.75</v>
       </c>
       <c r="G1403" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39210,7 +39213,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39236,7 +39239,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1405" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39262,7 +39265,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1406" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39288,7 +39291,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1407" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39314,7 +39317,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1408" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39340,7 +39343,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1409" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39366,7 +39369,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1410" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39392,7 +39395,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1411" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39418,7 +39421,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1412" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39444,7 +39447,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1413" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39470,7 +39473,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1414" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39496,7 +39499,7 @@
         <v>3.75</v>
       </c>
       <c r="G1415" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39522,7 +39525,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39548,7 +39551,7 @@
         <v>3.75</v>
       </c>
       <c r="G1417" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39574,7 +39577,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1418" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39600,7 +39603,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39626,7 +39629,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1420" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39652,7 +39655,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1421" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39678,7 +39681,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1422" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39704,7 +39707,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39730,7 +39733,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1424" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39756,7 +39759,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1425" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39782,7 +39785,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1426" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39808,7 +39811,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1427" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39834,7 +39837,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1428" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39860,7 +39863,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39886,7 +39889,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1430" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39912,7 +39915,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39938,7 +39941,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39964,7 +39967,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1433" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39990,7 +39993,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40016,7 +40019,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1435" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -40042,7 +40045,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1436" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40068,7 +40071,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1437" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40094,7 +40097,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1438" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40120,7 +40123,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1439" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40146,7 +40149,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40172,7 +40175,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1441" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40198,7 +40201,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40224,7 +40227,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1443" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40250,7 +40253,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1444" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40276,7 +40279,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1445" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40302,7 +40305,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1446" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40328,7 +40331,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1447" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40354,7 +40357,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1448" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40380,7 +40383,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1449" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40406,7 +40409,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1450" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40432,7 +40435,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1451" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40458,7 +40461,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1452" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40484,7 +40487,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40510,7 +40513,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40536,7 +40539,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40562,7 +40565,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40588,7 +40591,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1457" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40614,7 +40617,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40640,7 +40643,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1459" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40666,7 +40669,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1460" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40692,7 +40695,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40718,7 +40721,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1462" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40744,7 +40747,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40770,7 +40773,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1464" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40796,7 +40799,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40822,7 +40825,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1466" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40848,7 +40851,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1467" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40874,7 +40877,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1468" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40900,7 +40903,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1469" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40926,7 +40929,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1470" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40952,7 +40955,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1471" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40978,7 +40981,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1472" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41004,7 +41007,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1473" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41030,7 +41033,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -41056,7 +41059,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1475" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41082,7 +41085,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1476" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41108,7 +41111,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1477" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41134,7 +41137,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1478" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41160,7 +41163,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1479" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41186,7 +41189,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41212,7 +41215,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41238,7 +41241,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1482" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41264,7 +41267,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1483" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41290,7 +41293,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1484" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41316,7 +41319,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1485" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41342,7 +41345,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1486" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41368,7 +41371,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1487" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41394,7 +41397,7 @@
         <v>3.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41420,7 +41423,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1489" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41446,7 +41449,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41472,7 +41475,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1491" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41498,7 +41501,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1492" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41524,7 +41527,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41550,7 +41553,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1494" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41576,7 +41579,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1495" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41602,7 +41605,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1496" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41628,7 +41631,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1497" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41654,7 +41657,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1498" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41680,7 +41683,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1499" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41706,7 +41709,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1500" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41732,7 +41735,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1501" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41758,7 +41761,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41784,7 +41787,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1503" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41810,7 +41813,7 @@
         <v>3.5</v>
       </c>
       <c r="G1504" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41836,7 +41839,7 @@
         <v>3.5</v>
       </c>
       <c r="G1505" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41862,7 +41865,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1506" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41888,7 +41891,7 @@
         <v>3.5</v>
       </c>
       <c r="G1507" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41914,7 +41917,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1508" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41940,7 +41943,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1509" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41966,7 +41969,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1510" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41992,7 +41995,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1511" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42018,7 +42021,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1512" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42044,7 +42047,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42070,7 +42073,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42096,7 +42099,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42122,7 +42125,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42148,7 +42151,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1517" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42174,7 +42177,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1518" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42200,7 +42203,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1519" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42226,7 +42229,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1520" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42252,7 +42255,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42278,7 +42281,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42304,7 +42307,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1523" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42330,7 +42333,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1524" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42356,7 +42359,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1525" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42382,7 +42385,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1526" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42408,7 +42411,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1527" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42434,7 +42437,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1528" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42460,7 +42463,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1529" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42486,7 +42489,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1530" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42512,7 +42515,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1531" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42538,7 +42541,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1532" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42564,7 +42567,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1533" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42590,7 +42593,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1534" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42616,7 +42619,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1535" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42642,7 +42645,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1536" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42668,7 +42671,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1537" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42694,7 +42697,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1538" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42720,7 +42723,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1539" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42746,7 +42749,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1540" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42772,7 +42775,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1541" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42798,7 +42801,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42824,7 +42827,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1543" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42850,7 +42853,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1544" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42876,7 +42879,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1545" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42902,7 +42905,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1546" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42928,7 +42931,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1547" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42954,7 +42957,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1548" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42980,7 +42983,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1549" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -43006,7 +43009,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1550" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43032,7 +43035,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1551" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43058,7 +43061,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1552" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43084,7 +43087,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1553" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43110,7 +43113,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1554" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43136,7 +43139,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1555" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43162,7 +43165,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1556" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43188,7 +43191,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1557" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43214,7 +43217,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1558" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43240,7 +43243,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1559" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43266,7 +43269,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1560" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43292,7 +43295,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43318,7 +43321,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1562" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43344,7 +43347,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1563" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43370,7 +43373,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1564" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43396,7 +43399,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1565" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43422,7 +43425,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1566" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43448,7 +43451,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1567" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43474,7 +43477,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1568" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43500,7 +43503,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1569" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43526,7 +43529,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1570" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43552,7 +43555,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1571" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43578,7 +43581,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1572" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43604,7 +43607,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1573" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43630,7 +43633,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1574" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43656,7 +43659,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1575" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43682,7 +43685,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1576" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43708,7 +43711,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1577" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43734,7 +43737,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1578" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43760,7 +43763,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1579" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43786,7 +43789,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1580" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43812,7 +43815,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1581" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43838,7 +43841,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1582" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43864,7 +43867,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1583" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43890,7 +43893,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1584" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43916,7 +43919,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1585" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43942,7 +43945,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1586" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43968,7 +43971,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1587" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43994,7 +43997,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1588" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44020,7 +44023,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1589" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44046,7 +44049,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1590" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44072,7 +44075,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1591" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44098,7 +44101,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1592" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44124,7 +44127,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1593" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44150,7 +44153,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1594" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44176,7 +44179,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1595" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44202,7 +44205,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1596" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44228,7 +44231,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1597" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44254,7 +44257,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1598" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44280,7 +44283,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1599" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44306,7 +44309,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1600" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44332,7 +44335,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44358,7 +44361,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1602" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44384,7 +44387,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44410,7 +44413,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44436,7 +44439,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1605" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44462,7 +44465,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1606" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44488,7 +44491,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1607" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44514,7 +44517,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44540,7 +44543,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1609" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44566,7 +44569,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1610" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44592,7 +44595,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44618,7 +44621,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1612" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44644,7 +44647,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1613" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44670,7 +44673,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44696,7 +44699,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1615" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44722,7 +44725,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1616" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44748,7 +44751,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1617" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44774,7 +44777,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1618" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44800,7 +44803,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1619" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44826,7 +44829,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1620" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44852,7 +44855,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1621" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44878,7 +44881,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1622" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44904,7 +44907,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1623" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44930,7 +44933,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44956,7 +44959,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44982,7 +44985,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45008,7 +45011,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1627" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45034,7 +45037,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1628" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45060,7 +45063,7 @@
         <v>4</v>
       </c>
       <c r="G1629" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45086,7 +45089,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1630" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45112,7 +45115,7 @@
         <v>4</v>
       </c>
       <c r="G1631" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45138,7 +45141,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1632" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45164,7 +45167,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45190,7 +45193,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1634" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45216,7 +45219,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45242,7 +45245,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45268,7 +45271,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1637" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45294,7 +45297,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1638" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45320,7 +45323,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1639" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45346,7 +45349,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1640" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45372,7 +45375,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45398,7 +45401,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1642" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45424,7 +45427,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1643" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45450,7 +45453,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1644" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45476,7 +45479,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1645" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45502,7 +45505,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45528,7 +45531,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1647" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45554,7 +45557,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1648" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45580,7 +45583,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1649" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45606,7 +45609,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1650" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45632,7 +45635,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45762,7 +45765,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1656" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -46230,7 +46233,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1674" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46464,7 +46467,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1683" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46490,7 +46493,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1684" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46516,7 +46519,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1685" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46594,7 +46597,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1688" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46698,7 +46701,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1692" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46750,7 +46753,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1694" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46828,7 +46831,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1697" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47218,7 +47221,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1712" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47530,7 +47533,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1724" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47712,7 +47715,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1731" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -56165,6 +56168,32 @@
         <v>787</v>
       </c>
       <c r="H2056" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2057">
+      <c r="A2057" s="1" t="n">
+        <v>46024.6909722222</v>
+      </c>
+      <c r="B2057" t="n">
+        <v>85263</v>
+      </c>
+      <c r="C2057" t="n">
+        <v>6.36999988555908</v>
+      </c>
+      <c r="D2057" t="n">
+        <v>6.21999979019165</v>
+      </c>
+      <c r="E2057" t="n">
+        <v>6.36999988555908</v>
+      </c>
+      <c r="F2057" t="n">
+        <v>6.32000017166138</v>
+      </c>
+      <c r="G2057" t="s">
+        <v>788</v>
+      </c>
+      <c r="H2057" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="789">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="790">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">EQUI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6869148015976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71744740009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71417593955994</t>
+    <t xml:space="preserve">1.68691468238831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7174471616745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71417570114136</t>
   </si>
   <si>
     <t xml:space="preserve">1.71090471744537</t>
@@ -59,217 +59,217 @@
     <t xml:space="preserve">1.70109045505524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67055821418762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.674919962883</t>
+    <t xml:space="preserve">1.67055809497833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67491984367371</t>
   </si>
   <si>
     <t xml:space="preserve">1.69018626213074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67710065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65856337547302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65747284889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65529227256775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784492015839</t>
+    <t xml:space="preserve">1.67710077762604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65856349468231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65747272968292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65529203414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784468173981</t>
   </si>
   <si>
     <t xml:space="preserve">1.64656841754913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65311121940613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65420174598694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64874947071075</t>
+    <t xml:space="preserve">1.65311098098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65420162677765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64874923229218</t>
   </si>
   <si>
     <t xml:space="preserve">1.65965378284454</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64002585411072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64329695701599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62584984302521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64765882492065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67382967472076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68909573554993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67928147315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67819118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67164885997772</t>
+    <t xml:space="preserve">1.64002561569214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64329719543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6258499622345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64765894412994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67382955551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68909597396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67928171157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67819130420685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67164862155914</t>
   </si>
   <si>
     <t xml:space="preserve">1.67273914813995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70327174663544</t>
+    <t xml:space="preserve">1.70327138900757</t>
   </si>
   <si>
     <t xml:space="preserve">1.70654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69563841819763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66565144062042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66837728023529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69836449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70381689071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.687460064888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68473386764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67110288143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016057491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72289967536926</t>
+    <t xml:space="preserve">1.69563817977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66565132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66837739944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6983642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70381665229797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68745982646942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68473410606384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67110300064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016069412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7228991985321</t>
   </si>
   <si>
     <t xml:space="preserve">1.72835159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74470829963684</t>
+    <t xml:space="preserve">1.74470818042755</t>
   </si>
   <si>
     <t xml:space="preserve">1.73107767105103</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73925614356995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7419821023941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79923033714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77742123603821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77196931838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73652994632721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79650413990021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78832578659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81831300258636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82376551628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80468273162842</t>
+    <t xml:space="preserve">1.73925626277924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74198186397552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79923009872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77742147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77196943759918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73652982711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79650449752808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78832590579987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81831312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82376527786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80468261241913</t>
   </si>
   <si>
     <t xml:space="preserve">1.81558704376221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81286072731018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81013488769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377794265747</t>
+    <t xml:space="preserve">1.81286096572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8101350069046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377830028534</t>
   </si>
   <si>
     <t xml:space="preserve">1.84284806251526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88950264453888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200713157654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88075470924377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84576392173767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81952083110809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83118438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8603435754776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87492322921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87783849239349</t>
+    <t xml:space="preserve">1.8895024061203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200701236725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88075459003448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84576416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81952059268951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8311847448349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86034345626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87492299079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87783885002136</t>
   </si>
   <si>
     <t xml:space="preserve">1.8632595539093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88367068767548</t>
+    <t xml:space="preserve">1.8836704492569</t>
   </si>
   <si>
     <t xml:space="preserve">1.80785715579987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76703476905823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79619371891022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79910945892334</t>
+    <t xml:space="preserve">1.76703488826752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79619336128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7991099357605</t>
   </si>
   <si>
     <t xml:space="preserve">1.78161442279816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82243669033051</t>
+    <t xml:space="preserve">1.82243692874908</t>
   </si>
   <si>
     <t xml:space="preserve">1.78453016281128</t>
@@ -278,46 +278,46 @@
     <t xml:space="preserve">1.81660497188568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8341007232666</t>
+    <t xml:space="preserve">1.83410036563873</t>
   </si>
   <si>
     <t xml:space="preserve">1.83701634407043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84867990016937</t>
+    <t xml:space="preserve">1.84868013858795</t>
   </si>
   <si>
     <t xml:space="preserve">1.86909127235413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8515956401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8574275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282975673676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89241826534271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88658666610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8953343629837</t>
+    <t xml:space="preserve">1.85159575939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85742747783661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282939910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89241814613342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88658654689789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89533400535583</t>
   </si>
   <si>
     <t xml:space="preserve">1.83993220329285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85451173782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617505550385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81077313423157</t>
+    <t xml:space="preserve">1.85451185703278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81077337265015</t>
   </si>
   <si>
     <t xml:space="preserve">1.89825034141541</t>
@@ -326,34 +326,34 @@
     <t xml:space="preserve">1.91574573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95365214347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96239995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92449343204498</t>
+    <t xml:space="preserve">1.95365250110626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9624000787735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9244931936264</t>
   </si>
   <si>
     <t xml:space="preserve">1.96531569957733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00613832473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00905394554138</t>
+    <t xml:space="preserve">2.00613808631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00905442237854</t>
   </si>
   <si>
     <t xml:space="preserve">1.98281109333038</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95948350429535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92740917205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90991377830505</t>
+    <t xml:space="preserve">1.95948398113251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9274092912674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90991365909576</t>
   </si>
   <si>
     <t xml:space="preserve">1.9565681219101</t>
@@ -365,16 +365,16 @@
     <t xml:space="preserve">2.00030660629272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94490456581116</t>
+    <t xml:space="preserve">1.94490444660187</t>
   </si>
   <si>
     <t xml:space="preserve">1.94782030582428</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90699779987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92157745361328</t>
+    <t xml:space="preserve">1.90699756145477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92157757282257</t>
   </si>
   <si>
     <t xml:space="preserve">2.07903575897217</t>
@@ -383,28 +383,28 @@
     <t xml:space="preserve">2.06737232208252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98864269256592</t>
+    <t xml:space="preserve">1.98864281177521</t>
   </si>
   <si>
     <t xml:space="preserve">1.99447500705719</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97406375408173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93907284736633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93032467365265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198858737946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90408205986023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82535254955292</t>
+    <t xml:space="preserve">1.97406327724457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93907272815704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93032491207123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198834896088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90408217906952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82535266876221</t>
   </si>
   <si>
     <t xml:space="preserve">1.81368899345398</t>
@@ -413,118 +413,118 @@
     <t xml:space="preserve">1.79036176204681</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82826864719391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02852964401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90331125259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89705038070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89078962802887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87826788425446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82192015647888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79061532020569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78435444831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75931107997894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74678945541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73426759243011</t>
+    <t xml:space="preserve">1.82826840877533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02852940559387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90331137180328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89705073833466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89078950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8782674074173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82191956043243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79061555862427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78435468673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75931060314178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74678921699524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73426711559296</t>
   </si>
   <si>
     <t xml:space="preserve">1.72800636291504</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65287578105927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69044125080109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64661514759064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60904967784882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62783229351044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66539764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791950702667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63409304618835</t>
+    <t xml:space="preserve">1.65287601947784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69044101238251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64661502838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60904955863953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62783193588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66539776325226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791974544525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63409292697906</t>
   </si>
   <si>
     <t xml:space="preserve">1.67165851593018</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62157154083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60278856754303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68418025970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70296311378479</t>
+    <t xml:space="preserve">1.62157142162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60278844833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68418049812317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70296275615692</t>
   </si>
   <si>
     <t xml:space="preserve">1.69670188426971</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70922386646271</t>
+    <t xml:space="preserve">1.70922350883484</t>
   </si>
   <si>
     <t xml:space="preserve">1.71548461914062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65913665294647</t>
+    <t xml:space="preserve">1.65913677215576</t>
   </si>
   <si>
     <t xml:space="preserve">1.64035391807556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61531031131744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59652757644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57148385047913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56522345542908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55896234512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57774496078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55270147323608</t>
+    <t xml:space="preserve">1.61531019210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59652769565582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57148432731628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5652232170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55896210670471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5777450799942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55270159244537</t>
   </si>
   <si>
     <t xml:space="preserve">1.58400595188141</t>
@@ -533,73 +533,73 @@
     <t xml:space="preserve">1.77183270454407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81565940380096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8093980550766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80313742160797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77809345722198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74052822589874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76557195186615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75305020809174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59026694297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47757065296173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36487460136414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54644072055817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50261449813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38365757465363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40244007110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3210483789444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30226576328278</t>
+    <t xml:space="preserve">1.8156590461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80939793586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8031370639801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77809369564056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74052810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76557183265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75304996967316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59026670455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47757077217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36487483978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54644083976746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50261437892914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38365745544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40243995189667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32104849815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30226564407349</t>
   </si>
   <si>
     <t xml:space="preserve">1.3273092508316</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33357048034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28348290920258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29600489139557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28974413871765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33983111381531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35235285758972</t>
+    <t xml:space="preserve">1.3335702419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28348314762115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29600501060486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28974390029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33983099460602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35235297679901</t>
   </si>
   <si>
     <t xml:space="preserve">1.31478750705719</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">1.34609198570251</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43374454975128</t>
+    <t xml:space="preserve">1.43374466896057</t>
   </si>
   <si>
     <t xml:space="preserve">1.38991832733154</t>
@@ -617,19 +617,19 @@
     <t xml:space="preserve">1.39617908000946</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4587881565094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42122268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37739658355713</t>
+    <t xml:space="preserve">1.45878803730011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42122256755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37739646434784</t>
   </si>
   <si>
     <t xml:space="preserve">1.41496193408966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44000542163849</t>
+    <t xml:space="preserve">1.44000554084778</t>
   </si>
   <si>
     <t xml:space="preserve">1.4462662935257</t>
@@ -638,82 +638,82 @@
     <t xml:space="preserve">1.42748355865479</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53391873836517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40870082378387</t>
+    <t xml:space="preserve">1.53391861915588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40870118141174</t>
   </si>
   <si>
     <t xml:space="preserve">1.4525271654129</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51513624191284</t>
+    <t xml:space="preserve">1.51513612270355</t>
   </si>
   <si>
     <t xml:space="preserve">1.72174561023712</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87200689315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85863554477692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8051495552063</t>
+    <t xml:space="preserve">1.87200677394867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85863542556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80514967441559</t>
   </si>
   <si>
     <t xml:space="preserve">1.65806353092194</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64469218254089</t>
+    <t xml:space="preserve">1.6446920633316</t>
   </si>
   <si>
     <t xml:space="preserve">1.61126327514648</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63800621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61794888973236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457742214203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57114851474762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65137779712677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63132059574127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66474902629852</t>
+    <t xml:space="preserve">1.63800597190857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61794900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457754135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57114887237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65137791633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63132047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66474890708923</t>
   </si>
   <si>
     <t xml:space="preserve">1.62463486194611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6714346408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68480658531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69817793369293</t>
+    <t xml:space="preserve">1.67143487930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68480634689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69817769527435</t>
   </si>
   <si>
     <t xml:space="preserve">1.59120607376099</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55777716636658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52434861660004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51766300201416</t>
+    <t xml:space="preserve">1.55777728557587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52434849739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51766276359558</t>
   </si>
   <si>
     <t xml:space="preserve">1.53103446960449</t>
@@ -725,49 +725,49 @@
     <t xml:space="preserve">1.5510915517807</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53772008419037</t>
+    <t xml:space="preserve">1.53772020339966</t>
   </si>
   <si>
     <t xml:space="preserve">1.57783460617065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58452033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56446301937103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49760556221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51097726821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59789192676544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50429129600525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4909200668335</t>
+    <t xml:space="preserve">1.58452010154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56446278095245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49760568141937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5109771490097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59789180755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50429153442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49091982841492</t>
   </si>
   <si>
     <t xml:space="preserve">1.48423421382904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47754848003387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.470862865448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46417713165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44411993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4508056640625</t>
+    <t xml:space="preserve">1.47754859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47086274623871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46417701244354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44411981105804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45080542564392</t>
   </si>
   <si>
     <t xml:space="preserve">1.43074822425842</t>
@@ -776,94 +776,94 @@
     <t xml:space="preserve">1.41737675666809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36389088630676</t>
+    <t xml:space="preserve">1.36389076709747</t>
   </si>
   <si>
     <t xml:space="preserve">1.33046209812164</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34383380413055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33714807033539</t>
+    <t xml:space="preserve">1.34383368492126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3371479511261</t>
   </si>
   <si>
     <t xml:space="preserve">1.32377648353577</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3204333782196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67812073230743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73829221725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77172076702118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75166356563568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74497807025909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7316061258316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7650351524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78509247303009</t>
+    <t xml:space="preserve">1.32043349742889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67812085151672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73829197883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77172100543976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75166380405426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74497783184052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73160660266876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76503539085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7850923538208</t>
   </si>
   <si>
     <t xml:space="preserve">1.79177856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75834953784943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79846382141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8252067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85194993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86532139778137</t>
+    <t xml:space="preserve">1.75834965705872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79846405982971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520699501038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85194969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86532151699066</t>
   </si>
   <si>
     <t xml:space="preserve">1.87869262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89206409454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91212129592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92549312114716</t>
+    <t xml:space="preserve">1.89206421375275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91212153434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92549288272858</t>
   </si>
   <si>
     <t xml:space="preserve">1.8987500667572</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83857810497284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9054354429245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88537871837616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91880738735199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96560740470886</t>
+    <t xml:space="preserve">1.83857846260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90543568134308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88537847995758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91880702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96560728549957</t>
   </si>
   <si>
     <t xml:space="preserve">1.99903583526611</t>
@@ -872,34 +872,34 @@
     <t xml:space="preserve">1.99235022068024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01240730285645</t>
+    <t xml:space="preserve">2.01240801811218</t>
   </si>
   <si>
     <t xml:space="preserve">1.98566508293152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97897851467133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00572204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02577924728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0324649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0462908744812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05320429801941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08085680007935</t>
+    <t xml:space="preserve">1.97897863388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00572156906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909327507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02577900886536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03246474266052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04629111289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05320453643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08085703849792</t>
   </si>
   <si>
     <t xml:space="preserve">2.03937816619873</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">2.06011748313904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06703066825867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0739438533783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10850930213928</t>
+    <t xml:space="preserve">2.06703042984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07394337654114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10850954055786</t>
   </si>
   <si>
     <t xml:space="preserve">2.12233567237854</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">2.1499879360199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1983802318573</t>
+    <t xml:space="preserve">2.19838047027588</t>
   </si>
   <si>
     <t xml:space="preserve">2.20529341697693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19146704673767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16381454467773</t>
+    <t xml:space="preserve">2.19146728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16381478309631</t>
   </si>
   <si>
     <t xml:space="preserve">2.14307498931885</t>
@@ -947,22 +947,22 @@
     <t xml:space="preserve">2.17764091491699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18455386161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15690135955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22603273391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21220660209656</t>
+    <t xml:space="preserve">2.18455362319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15690112113953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22603297233582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21220636367798</t>
   </si>
   <si>
     <t xml:space="preserve">2.23294591903687</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23985910415649</t>
+    <t xml:space="preserve">2.23985934257507</t>
   </si>
   <si>
     <t xml:space="preserve">2.25368547439575</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">2.2605984210968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26751184463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27442502975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2467725276947</t>
+    <t xml:space="preserve">2.26751160621643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27442455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24677205085754</t>
   </si>
   <si>
     <t xml:space="preserve">2.3089907169342</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">2.32972979545593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31590390205383</t>
+    <t xml:space="preserve">2.31590414047241</t>
   </si>
   <si>
     <t xml:space="preserve">2.32281708717346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33664345741272</t>
+    <t xml:space="preserve">2.33664321899414</t>
   </si>
   <si>
     <t xml:space="preserve">2.34355640411377</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">2.43342709541321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44725370407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51638507843018</t>
+    <t xml:space="preserve">2.44725346565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51638531684875</t>
   </si>
   <si>
     <t xml:space="preserve">2.48873233795166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49564552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56477737426758</t>
+    <t xml:space="preserve">2.49564528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.564777135849</t>
   </si>
   <si>
     <t xml:space="preserve">2.55786395072937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54403758049011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57168984413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5232982635498</t>
+    <t xml:space="preserve">2.54403805732727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57169032096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52329802513123</t>
   </si>
   <si>
     <t xml:space="preserve">2.53021121025085</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">2.59242963790894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63390827178955</t>
+    <t xml:space="preserve">2.63390851020813</t>
   </si>
   <si>
     <t xml:space="preserve">2.62699508666992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65464782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64773488044739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62008213996887</t>
+    <t xml:space="preserve">2.65464758872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64773464202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62008237838745</t>
   </si>
   <si>
     <t xml:space="preserve">2.64082145690918</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">2.61316895484924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66230630874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64100790023804</t>
+    <t xml:space="preserve">2.66230654716492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64100813865662</t>
   </si>
   <si>
     <t xml:space="preserve">2.69780349731445</t>
@@ -1079,100 +1079,100 @@
     <t xml:space="preserve">2.74040055274963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79009675979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.768798828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7475004196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73330116271973</t>
+    <t xml:space="preserve">2.79009699821472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76879858970642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74750018119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73330092430115</t>
   </si>
   <si>
     <t xml:space="preserve">2.76169943809509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71200275421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65520715713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63390851020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68360447883606</t>
+    <t xml:space="preserve">2.71200251579285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65520691871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63390874862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68360471725464</t>
   </si>
   <si>
     <t xml:space="preserve">2.62680912017822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64810752868652</t>
+    <t xml:space="preserve">2.64810729026794</t>
   </si>
   <si>
     <t xml:space="preserve">2.67650532722473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66940593719482</t>
+    <t xml:space="preserve">2.66940569877625</t>
   </si>
   <si>
     <t xml:space="preserve">2.70490336418152</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75459957122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71910214424133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72620153427124</t>
+    <t xml:space="preserve">2.75460004806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71910262107849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7262020111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.69070434570312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5629141330719</t>
+    <t xml:space="preserve">2.56291365623474</t>
   </si>
   <si>
     <t xml:space="preserve">2.55581402778625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59841132164001</t>
+    <t xml:space="preserve">2.59841108322144</t>
   </si>
   <si>
     <t xml:space="preserve">2.79719662666321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871463775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49191880226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062039375305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37832713127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25763607025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1724419593811</t>
+    <t xml:space="preserve">2.54871439933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49191856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062015533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3783266544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25763583183289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17244219779968</t>
   </si>
   <si>
     <t xml:space="preserve">2.21503877639771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34282970428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34992909431458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48481917381287</t>
+    <t xml:space="preserve">2.34282946586609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.349928855896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48481941223145</t>
   </si>
   <si>
     <t xml:space="preserve">2.59131145477295</t>
@@ -1181,25 +1181,25 @@
     <t xml:space="preserve">2.47772002220154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60551023483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8113956451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82559466362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88239049911499</t>
+    <t xml:space="preserve">2.60551071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81139540672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82559442520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88239073753357</t>
   </si>
   <si>
     <t xml:space="preserve">2.8681914806366</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89658951759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87529110908508</t>
+    <t xml:space="preserve">2.8965892791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8752908706665</t>
   </si>
   <si>
     <t xml:space="preserve">2.83979368209839</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">2.78299784660339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368890762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88949012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81849503517151</t>
+    <t xml:space="preserve">2.90368914604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88948965072632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81849479675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.8326940536499</t>
@@ -1223,37 +1223,37 @@
     <t xml:space="preserve">2.8539924621582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98100256919861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95111751556396</t>
+    <t xml:space="preserve">2.98100233078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95111775398254</t>
   </si>
   <si>
     <t xml:space="preserve">2.97353148460388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94364666938782</t>
+    <t xml:space="preserve">2.94364643096924</t>
   </si>
   <si>
     <t xml:space="preserve">2.91376185417175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87640595436096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81663632392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83905005455017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70456862449646</t>
+    <t xml:space="preserve">2.87640571594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81663656234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83904981613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70456886291504</t>
   </si>
   <si>
     <t xml:space="preserve">2.59997224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61491441726685</t>
+    <t xml:space="preserve">2.61491465568542</t>
   </si>
   <si>
     <t xml:space="preserve">2.6074435710907</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">2.62238574028015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65227007865906</t>
+    <t xml:space="preserve">2.65227031707764</t>
   </si>
   <si>
     <t xml:space="preserve">2.62985682487488</t>
@@ -1277,22 +1277,22 @@
     <t xml:space="preserve">2.57008767127991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58502984046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57755875587463</t>
+    <t xml:space="preserve">2.58503007888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57755851745605</t>
   </si>
   <si>
     <t xml:space="preserve">2.5551450252533</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52526044845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59250092506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54767417907715</t>
+    <t xml:space="preserve">2.52526021003723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59250116348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54767394065857</t>
   </si>
   <si>
     <t xml:space="preserve">2.50284671783447</t>
@@ -1301,16 +1301,16 @@
     <t xml:space="preserve">2.47296190261841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45801949501038</t>
+    <t xml:space="preserve">2.4580192565918</t>
   </si>
   <si>
     <t xml:space="preserve">2.49537539482117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46549081802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48790454864502</t>
+    <t xml:space="preserve">2.4654905796051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48790407180786</t>
   </si>
   <si>
     <t xml:space="preserve">2.48043322563171</t>
@@ -1319,25 +1319,25 @@
     <t xml:space="preserve">2.53273177146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40572094917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43560600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37583637237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39077925682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42813515663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44307708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41319227218628</t>
+    <t xml:space="preserve">2.40572142601013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43560576438904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37583684921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3907790184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42813491821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44307732582092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41319251060486</t>
   </si>
   <si>
     <t xml:space="preserve">2.39825034141541</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">2.64479923248291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71951103210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7344536781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74939560890198</t>
+    <t xml:space="preserve">2.71951079368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73445343971252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74939584732056</t>
   </si>
   <si>
     <t xml:space="preserve">2.75686717033386</t>
@@ -1364,16 +1364,16 @@
     <t xml:space="preserve">2.74192476272583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77928042411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79422283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81757283210754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82535624504089</t>
+    <t xml:space="preserve">2.77928066253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79422307014465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81757307052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82535648345947</t>
   </si>
   <si>
     <t xml:space="preserve">2.84870648384094</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">2.84092307090759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80978989601135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87983989715576</t>
+    <t xml:space="preserve">2.80978941917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87984013557434</t>
   </si>
   <si>
     <t xml:space="preserve">2.88762307167053</t>
@@ -1394,34 +1394,37 @@
     <t xml:space="preserve">2.89540648460388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87205672264099</t>
+    <t xml:space="preserve">2.87205648422241</t>
   </si>
   <si>
     <t xml:space="preserve">2.80200624465942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83313989639282</t>
+    <t xml:space="preserve">2.7942225933075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83313941955566</t>
   </si>
   <si>
     <t xml:space="preserve">2.86427307128906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85648965835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91875648498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92654013633728</t>
+    <t xml:space="preserve">2.85648989677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91875672340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9265398979187</t>
   </si>
   <si>
     <t xml:space="preserve">2.90318965911865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98880648612976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01215672492981</t>
+    <t xml:space="preserve">2.98880696296692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01215648651123</t>
   </si>
   <si>
     <t xml:space="preserve">3.00437331199646</t>
@@ -1430,13 +1433,13 @@
     <t xml:space="preserve">2.94210648536682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97323989868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910973072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94988989830017</t>
+    <t xml:space="preserve">2.97324013710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91097331047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94989013671875</t>
   </si>
   <si>
     <t xml:space="preserve">2.95767307281494</t>
@@ -1451,10 +1454,10 @@
     <t xml:space="preserve">2.96545672416687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04328989982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05107355117798</t>
+    <t xml:space="preserve">3.04329037666321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0510733127594</t>
   </si>
   <si>
     <t xml:space="preserve">3.01994013786316</t>
@@ -1463,58 +1466,58 @@
     <t xml:space="preserve">3.07442355155945</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02772355079651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98102331161499</t>
+    <t xml:space="preserve">3.02772331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98102355003357</t>
   </si>
   <si>
     <t xml:space="preserve">3.16004014015198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08999013900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0822069644928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06664037704468</t>
+    <t xml:space="preserve">3.08999037742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08220672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0666401386261</t>
   </si>
   <si>
     <t xml:space="preserve">3.05885696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09777355194092</t>
+    <t xml:space="preserve">3.0977737903595</t>
   </si>
   <si>
     <t xml:space="preserve">3.11416363716125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13055419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10596871376038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06499290466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07318806648254</t>
+    <t xml:space="preserve">3.13055443763733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10596895217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06499314308167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07318830490112</t>
   </si>
   <si>
     <t xml:space="preserve">3.08957839012146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04040765762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03221225738525</t>
+    <t xml:space="preserve">3.04040741920471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03221249580383</t>
   </si>
   <si>
     <t xml:space="preserve">3.04860258102417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05679774284363</t>
+    <t xml:space="preserve">3.05679750442505</t>
   </si>
   <si>
     <t xml:space="preserve">3.01582193374634</t>
@@ -1532,19 +1535,19 @@
     <t xml:space="preserve">2.99943161010742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99123620986938</t>
+    <t xml:space="preserve">2.99123644828796</t>
   </si>
   <si>
     <t xml:space="preserve">2.97484612464905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96665072441101</t>
+    <t xml:space="preserve">2.96665096282959</t>
   </si>
   <si>
     <t xml:space="preserve">2.95845556259155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98304128646851</t>
+    <t xml:space="preserve">2.98304104804993</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026040077209</t>
@@ -1553,25 +1556,25 @@
     <t xml:space="preserve">2.93387031555176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90108942985535</t>
+    <t xml:space="preserve">2.90108966827393</t>
   </si>
   <si>
     <t xml:space="preserve">2.92567491531372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94206523895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87650394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86830878257751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81094264984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83552813529968</t>
+    <t xml:space="preserve">2.94206500053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87650418281555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86830902099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81094288825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83552837371826</t>
   </si>
   <si>
     <t xml:space="preserve">2.79455232620239</t>
@@ -1580,37 +1583,37 @@
     <t xml:space="preserve">2.78635740280151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80274772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76177167892456</t>
+    <t xml:space="preserve">2.80274748802185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76177144050598</t>
   </si>
   <si>
     <t xml:space="preserve">2.84372353553772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86011362075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81913781166077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90928483009338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8519184589386</t>
+    <t xml:space="preserve">2.86011385917664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81913805007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9092845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85191869735718</t>
   </si>
   <si>
     <t xml:space="preserve">2.88469910621643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89289474487305</t>
+    <t xml:space="preserve">2.89289450645447</t>
   </si>
   <si>
     <t xml:space="preserve">2.91747975349426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.007976770401</t>
+    <t xml:space="preserve">3.00797700881958</t>
   </si>
   <si>
     <t xml:space="preserve">3.04215836524963</t>
@@ -1619,7 +1622,7 @@
     <t xml:space="preserve">3.01652264595032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03361320495605</t>
+    <t xml:space="preserve">3.03361296653748</t>
   </si>
   <si>
     <t xml:space="preserve">3.05070376396179</t>
@@ -1631,16 +1634,16 @@
     <t xml:space="preserve">3.07633996009827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11906695365906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12761259078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14470314979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16179394721985</t>
+    <t xml:space="preserve">3.11906719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12761235237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14470338821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16179418563843</t>
   </si>
   <si>
     <t xml:space="preserve">3.15324854850769</t>
@@ -1649,7 +1652,7 @@
     <t xml:space="preserve">3.17033958435059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11052179336548</t>
+    <t xml:space="preserve">3.1105215549469</t>
   </si>
   <si>
     <t xml:space="preserve">3.08488535881042</t>
@@ -1676,7 +1679,7 @@
     <t xml:space="preserve">3.23870253562927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23015689849854</t>
+    <t xml:space="preserve">3.23015713691711</t>
   </si>
   <si>
     <t xml:space="preserve">3.25579333305359</t>
@@ -1685,16 +1688,16 @@
     <t xml:space="preserve">3.34979248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30706548690796</t>
+    <t xml:space="preserve">3.30706524848938</t>
   </si>
   <si>
     <t xml:space="preserve">3.35833787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36688351631165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33270192146301</t>
+    <t xml:space="preserve">3.36688327789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33270168304443</t>
   </si>
   <si>
     <t xml:space="preserve">3.4010648727417</t>
@@ -1709,13 +1712,13 @@
     <t xml:space="preserve">3.28997468948364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29852032661438</t>
+    <t xml:space="preserve">3.2985200881958</t>
   </si>
   <si>
     <t xml:space="preserve">3.38397407531738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32415652275085</t>
+    <t xml:space="preserve">3.32415628433228</t>
   </si>
   <si>
     <t xml:space="preserve">3.37542867660522</t>
@@ -1727,13 +1730,13 @@
     <t xml:space="preserve">3.43524646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40961050987244</t>
+    <t xml:space="preserve">3.40961027145386</t>
   </si>
   <si>
     <t xml:space="preserve">3.45233726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44379210472107</t>
+    <t xml:space="preserve">3.44379186630249</t>
   </si>
   <si>
     <t xml:space="preserve">3.46942782402039</t>
@@ -1751,7 +1754,7 @@
     <t xml:space="preserve">3.51215505599976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46088266372681</t>
+    <t xml:space="preserve">3.46088290214539</t>
   </si>
   <si>
     <t xml:space="preserve">3.4865186214447</t>
@@ -36093,7 +36096,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1284" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -36145,7 +36148,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1286" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -36171,7 +36174,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1287" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -36249,7 +36252,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1290" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -36353,7 +36356,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1294" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -36431,7 +36434,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1297" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -36509,7 +36512,7 @@
         <v>3.75</v>
       </c>
       <c r="G1300" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -36535,7 +36538,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1301" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -36561,7 +36564,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1302" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -36587,7 +36590,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1303" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -36613,7 +36616,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1304" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -36639,7 +36642,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1305" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -36665,7 +36668,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1306" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36691,7 +36694,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1307" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36717,7 +36720,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1308" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36769,7 +36772,7 @@
         <v>3.75</v>
       </c>
       <c r="G1310" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36795,7 +36798,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1311" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36821,7 +36824,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1312" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36847,7 +36850,7 @@
         <v>3.75</v>
       </c>
       <c r="G1313" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36873,7 +36876,7 @@
         <v>3.75</v>
       </c>
       <c r="G1314" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36977,7 +36980,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1318" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -37003,7 +37006,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1319" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -37029,7 +37032,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1320" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -37055,7 +37058,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1321" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -37081,7 +37084,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1322" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -37107,7 +37110,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1323" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -37133,7 +37136,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1324" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -37159,7 +37162,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1325" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -37185,7 +37188,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1326" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -37211,7 +37214,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1327" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -37237,7 +37240,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1328" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -37263,7 +37266,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1329" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -37289,7 +37292,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1330" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -37315,7 +37318,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1331" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -37341,7 +37344,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1332" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -37367,7 +37370,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1333" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -37393,7 +37396,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1334" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -37419,7 +37422,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1335" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -37445,7 +37448,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1336" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -37471,7 +37474,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1337" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -37497,7 +37500,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1338" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -37523,7 +37526,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1339" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -37549,7 +37552,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1340" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -37575,7 +37578,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1341" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -37601,7 +37604,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1342" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -37627,7 +37630,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1343" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -37653,7 +37656,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1344" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -37679,7 +37682,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1345" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37705,7 +37708,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1346" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37731,7 +37734,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1347" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37783,7 +37786,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1349" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37809,7 +37812,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1350" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37835,7 +37838,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1351" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37861,7 +37864,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1352" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37887,7 +37890,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1353" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37913,7 +37916,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1354" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37939,7 +37942,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1355" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37965,7 +37968,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1356" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37991,7 +37994,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1357" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -38017,7 +38020,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1358" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -38043,7 +38046,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1359" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -38069,7 +38072,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1360" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -38095,7 +38098,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1361" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -38121,7 +38124,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1362" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -38147,7 +38150,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1363" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -38173,7 +38176,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1364" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -38199,7 +38202,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1365" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -38225,7 +38228,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1366" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -38251,7 +38254,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1367" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -38277,7 +38280,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1368" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -38303,7 +38306,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1369" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -38329,7 +38332,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1370" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -38355,7 +38358,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1371" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -38381,7 +38384,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1372" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -38407,7 +38410,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1373" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -38433,7 +38436,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1374" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -38459,7 +38462,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1375" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -38485,7 +38488,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1376" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -38511,7 +38514,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1377" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -38537,7 +38540,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1378" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -38563,7 +38566,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1379" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -38589,7 +38592,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1380" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -38615,7 +38618,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1381" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -38641,7 +38644,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1382" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -38667,7 +38670,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1383" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38693,7 +38696,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1384" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38719,7 +38722,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1385" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38745,7 +38748,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1386" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38771,7 +38774,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1387" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38797,7 +38800,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1388" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38823,7 +38826,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1389" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38849,7 +38852,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1390" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38875,7 +38878,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1391" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38901,7 +38904,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1392" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38927,7 +38930,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1393" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38953,7 +38956,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1394" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38979,7 +38982,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1395" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -39005,7 +39008,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1396" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -39031,7 +39034,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1397" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -39057,7 +39060,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1398" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -39083,7 +39086,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1399" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -39109,7 +39112,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1400" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -39135,7 +39138,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1401" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -39161,7 +39164,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1402" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -39187,7 +39190,7 @@
         <v>3.75</v>
       </c>
       <c r="G1403" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -39213,7 +39216,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1404" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -39239,7 +39242,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1405" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -39265,7 +39268,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1406" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -39291,7 +39294,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1407" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -39317,7 +39320,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1408" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -39343,7 +39346,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1409" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -39369,7 +39372,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1410" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -39395,7 +39398,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1411" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -39421,7 +39424,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1412" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -39447,7 +39450,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1413" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -39473,7 +39476,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1414" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -39499,7 +39502,7 @@
         <v>3.75</v>
       </c>
       <c r="G1415" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -39525,7 +39528,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1416" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -39551,7 +39554,7 @@
         <v>3.75</v>
       </c>
       <c r="G1417" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -39577,7 +39580,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1418" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -39603,7 +39606,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1419" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -39629,7 +39632,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1420" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -39655,7 +39658,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1421" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39681,7 +39684,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1422" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39707,7 +39710,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1423" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39733,7 +39736,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1424" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39759,7 +39762,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1425" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39785,7 +39788,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1426" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39811,7 +39814,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1427" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39837,7 +39840,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1428" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39863,7 +39866,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1429" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39889,7 +39892,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1430" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39915,7 +39918,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1431" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39941,7 +39944,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1432" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39967,7 +39970,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1433" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39993,7 +39996,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1434" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -40019,7 +40022,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1435" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -40045,7 +40048,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1436" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -40071,7 +40074,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1437" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -40097,7 +40100,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1438" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -40123,7 +40126,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1439" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -40149,7 +40152,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1440" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -40175,7 +40178,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1441" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -40201,7 +40204,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1442" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -40227,7 +40230,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1443" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -40253,7 +40256,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1444" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -40279,7 +40282,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1445" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -40305,7 +40308,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1446" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -40331,7 +40334,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1447" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -40357,7 +40360,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1448" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -40383,7 +40386,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1449" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -40409,7 +40412,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1450" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -40435,7 +40438,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1451" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -40461,7 +40464,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1452" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -40487,7 +40490,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1453" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -40513,7 +40516,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1454" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -40539,7 +40542,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1455" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -40565,7 +40568,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -40591,7 +40594,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1457" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -40617,7 +40620,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1458" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -40643,7 +40646,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1459" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -40669,7 +40672,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1460" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40695,7 +40698,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40721,7 +40724,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1462" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40747,7 +40750,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1463" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40773,7 +40776,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1464" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40799,7 +40802,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1465" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40825,7 +40828,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1466" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40851,7 +40854,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1467" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40877,7 +40880,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1468" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40903,7 +40906,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1469" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40929,7 +40932,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1470" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40955,7 +40958,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1471" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40981,7 +40984,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1472" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -41007,7 +41010,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1473" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -41033,7 +41036,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1474" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -41059,7 +41062,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1475" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -41085,7 +41088,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1476" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -41111,7 +41114,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1477" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -41137,7 +41140,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1478" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -41163,7 +41166,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1479" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -41189,7 +41192,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1480" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -41215,7 +41218,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1481" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -41241,7 +41244,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1482" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -41267,7 +41270,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1483" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -41293,7 +41296,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1484" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -41319,7 +41322,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1485" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -41345,7 +41348,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1486" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -41371,7 +41374,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1487" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -41397,7 +41400,7 @@
         <v>3.5</v>
       </c>
       <c r="G1488" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -41423,7 +41426,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1489" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -41449,7 +41452,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1490" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -41475,7 +41478,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1491" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -41501,7 +41504,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1492" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -41527,7 +41530,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1493" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -41553,7 +41556,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1494" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -41579,7 +41582,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1495" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -41605,7 +41608,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1496" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -41631,7 +41634,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1497" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -41657,7 +41660,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1498" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41683,7 +41686,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1499" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41709,7 +41712,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1500" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41735,7 +41738,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1501" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41761,7 +41764,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1502" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41787,7 +41790,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1503" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41813,7 +41816,7 @@
         <v>3.5</v>
       </c>
       <c r="G1504" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41839,7 +41842,7 @@
         <v>3.5</v>
       </c>
       <c r="G1505" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41865,7 +41868,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1506" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41891,7 +41894,7 @@
         <v>3.5</v>
       </c>
       <c r="G1507" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41917,7 +41920,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1508" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41943,7 +41946,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1509" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41969,7 +41972,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1510" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41995,7 +41998,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1511" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42021,7 +42024,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1512" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42047,7 +42050,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1513" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -42073,7 +42076,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1514" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -42099,7 +42102,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -42125,7 +42128,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1516" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -42151,7 +42154,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1517" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -42177,7 +42180,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1518" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -42203,7 +42206,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1519" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -42229,7 +42232,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1520" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -42255,7 +42258,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1521" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -42281,7 +42284,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1522" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -42307,7 +42310,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1523" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -42333,7 +42336,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1524" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -42359,7 +42362,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1525" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -42385,7 +42388,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1526" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -42411,7 +42414,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1527" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -42437,7 +42440,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1528" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -42463,7 +42466,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1529" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -42489,7 +42492,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1530" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -42515,7 +42518,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1531" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -42541,7 +42544,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1532" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -42567,7 +42570,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1533" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -42593,7 +42596,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1534" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -42619,7 +42622,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1535" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -42645,7 +42648,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1536" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -42671,7 +42674,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1537" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42697,7 +42700,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1538" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42723,7 +42726,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1539" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42749,7 +42752,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1540" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42775,7 +42778,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1541" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42801,7 +42804,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1542" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42827,7 +42830,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1543" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42853,7 +42856,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1544" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42879,7 +42882,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1545" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42905,7 +42908,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1546" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42931,7 +42934,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1547" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42957,7 +42960,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1548" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42983,7 +42986,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1549" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -43009,7 +43012,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1550" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43035,7 +43038,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1551" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -43061,7 +43064,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1552" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -43087,7 +43090,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1553" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -43113,7 +43116,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1554" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -43139,7 +43142,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1555" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -43165,7 +43168,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1556" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -43191,7 +43194,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1557" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -43217,7 +43220,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1558" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -43243,7 +43246,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1559" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -43269,7 +43272,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1560" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -43295,7 +43298,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1561" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -43321,7 +43324,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1562" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -43347,7 +43350,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1563" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -43373,7 +43376,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1564" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -43399,7 +43402,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1565" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -43425,7 +43428,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1566" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -43451,7 +43454,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1567" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -43477,7 +43480,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1568" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -43503,7 +43506,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1569" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -43529,7 +43532,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1570" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -43555,7 +43558,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1571" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -43581,7 +43584,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1572" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -43607,7 +43610,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1573" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -43633,7 +43636,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1574" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -43659,7 +43662,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1575" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43685,7 +43688,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1576" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43711,7 +43714,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1577" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43737,7 +43740,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1578" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43763,7 +43766,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1579" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43789,7 +43792,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1580" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43815,7 +43818,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1581" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43841,7 +43844,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1582" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43867,7 +43870,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1583" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43893,7 +43896,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1584" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43919,7 +43922,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1585" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43945,7 +43948,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1586" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43971,7 +43974,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1587" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43997,7 +44000,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G1588" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44023,7 +44026,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1589" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -44049,7 +44052,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1590" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -44075,7 +44078,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1591" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -44101,7 +44104,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1592" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -44127,7 +44130,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1593" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -44153,7 +44156,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1594" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -44179,7 +44182,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1595" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -44205,7 +44208,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1596" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -44231,7 +44234,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1597" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -44257,7 +44260,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1598" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -44283,7 +44286,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1599" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -44309,7 +44312,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G1600" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -44335,7 +44338,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1601" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -44361,7 +44364,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1602" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -44387,7 +44390,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1603" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -44413,7 +44416,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G1604" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -44439,7 +44442,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1605" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -44465,7 +44468,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1606" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -44491,7 +44494,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1607" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -44517,7 +44520,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1608" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -44543,7 +44546,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1609" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -44569,7 +44572,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1610" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -44595,7 +44598,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -44621,7 +44624,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1612" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -44647,7 +44650,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1613" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -44673,7 +44676,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1614" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44699,7 +44702,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1615" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44725,7 +44728,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1616" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44751,7 +44754,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1617" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44777,7 +44780,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1618" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44803,7 +44806,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1619" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44829,7 +44832,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1620" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44855,7 +44858,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1621" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44881,7 +44884,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1622" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44907,7 +44910,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1623" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44933,7 +44936,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1624" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44959,7 +44962,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1625" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44985,7 +44988,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1626" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45011,7 +45014,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1627" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45037,7 +45040,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1628" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45063,7 +45066,7 @@
         <v>4</v>
       </c>
       <c r="G1629" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -45089,7 +45092,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1630" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -45115,7 +45118,7 @@
         <v>4</v>
       </c>
       <c r="G1631" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -45141,7 +45144,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1632" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -45167,7 +45170,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1633" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -45193,7 +45196,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1634" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -45219,7 +45222,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1635" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -45245,7 +45248,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1636" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -45271,7 +45274,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1637" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -45297,7 +45300,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1638" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -45323,7 +45326,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1639" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -45349,7 +45352,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1640" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -45375,7 +45378,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1641" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -45401,7 +45404,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1642" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -45427,7 +45430,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1643" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -45453,7 +45456,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1644" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -45479,7 +45482,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1645" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -45505,7 +45508,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1646" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -45531,7 +45534,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1647" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -45557,7 +45560,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1648" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -45583,7 +45586,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1649" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45609,7 +45612,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1650" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -45635,7 +45638,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1651" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -45661,7 +45664,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1652" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45687,7 +45690,7 @@
         <v>4</v>
       </c>
       <c r="G1653" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45713,7 +45716,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1654" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45739,7 +45742,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1655" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45765,7 +45768,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1656" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45791,7 +45794,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1657" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45817,7 +45820,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1658" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45843,7 +45846,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1659" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45869,7 +45872,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1660" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45895,7 +45898,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1661" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45921,7 +45924,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1662" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45947,7 +45950,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1663" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45973,7 +45976,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1664" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45999,7 +46002,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1665" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46025,7 +46028,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1666" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -46051,7 +46054,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1667" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -46077,7 +46080,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1668" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -46103,7 +46106,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1669" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -46129,7 +46132,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1670" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -46155,7 +46158,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1671" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -46181,7 +46184,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1672" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -46207,7 +46210,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1673" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -46233,7 +46236,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1674" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -46259,7 +46262,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1675" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -46285,7 +46288,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1676" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -46311,7 +46314,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1677" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46337,7 +46340,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1678" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46363,7 +46366,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1679" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -46389,7 +46392,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1680" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46415,7 +46418,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1681" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -46441,7 +46444,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1682" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -46467,7 +46470,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1683" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -46493,7 +46496,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1684" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -46519,7 +46522,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1685" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -46545,7 +46548,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1686" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -46571,7 +46574,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1687" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -46597,7 +46600,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1688" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -46623,7 +46626,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1689" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -46649,7 +46652,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1690" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -46675,7 +46678,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1691" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46701,7 +46704,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1692" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46727,7 +46730,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1693" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46753,7 +46756,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1694" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46779,7 +46782,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1695" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46805,7 +46808,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1696" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46831,7 +46834,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1697" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46857,7 +46860,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1698" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46883,7 +46886,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1699" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46909,7 +46912,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1700" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46935,7 +46938,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1701" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46961,7 +46964,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1702" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46987,7 +46990,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1703" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47013,7 +47016,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1704" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47039,7 +47042,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1705" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47065,7 +47068,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1706" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -47091,7 +47094,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1707" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -47117,7 +47120,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1708" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -47143,7 +47146,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1709" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -47169,7 +47172,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1710" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47195,7 +47198,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1711" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -47221,7 +47224,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1712" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47247,7 +47250,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1713" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47273,7 +47276,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47299,7 +47302,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1715" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47325,7 +47328,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1716" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47351,7 +47354,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47377,7 +47380,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1718" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47403,7 +47406,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47429,7 +47432,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1720" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -47455,7 +47458,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -47481,7 +47484,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1722" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -47507,7 +47510,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1723" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -47533,7 +47536,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1724" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -47559,7 +47562,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1725" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -47585,7 +47588,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -47611,7 +47614,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1727" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -47637,7 +47640,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1728" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -47663,7 +47666,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1729" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47689,7 +47692,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1730" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47715,7 +47718,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1731" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47741,7 +47744,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1732" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47767,7 +47770,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1733" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47793,7 +47796,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1734" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47819,7 +47822,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1735" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47845,7 +47848,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1736" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47871,7 +47874,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1737" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47897,7 +47900,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1738" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47923,7 +47926,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1739" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47949,7 +47952,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G1740" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47975,7 +47978,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1741" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48001,7 +48004,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1742" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48027,7 +48030,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1743" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48053,7 +48056,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1744" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48079,7 +48082,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1745" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48105,7 +48108,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1746" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48131,7 +48134,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G1747" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48157,7 +48160,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1748" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48183,7 +48186,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1749" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48209,7 +48212,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1750" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48235,7 +48238,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1751" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48261,7 +48264,7 @@
         <v>4.25</v>
       </c>
       <c r="G1752" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48287,7 +48290,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1753" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48313,7 +48316,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1754" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48339,7 +48342,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1755" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48365,7 +48368,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1756" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48391,7 +48394,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1757" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48417,7 +48420,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1758" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -48443,7 +48446,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1759" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -48469,7 +48472,7 @@
         <v>4.25</v>
       </c>
       <c r="G1760" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -48495,7 +48498,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1761" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -48521,7 +48524,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1762" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -48547,7 +48550,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1763" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -48573,7 +48576,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1764" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -48599,7 +48602,7 @@
         <v>4.25</v>
       </c>
       <c r="G1765" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -48625,7 +48628,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1766" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -48651,7 +48654,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1767" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -48677,7 +48680,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1768" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48703,7 +48706,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1769" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48729,7 +48732,7 @@
         <v>4.25</v>
       </c>
       <c r="G1770" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48755,7 +48758,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1771" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48781,7 +48784,7 @@
         <v>4.25</v>
       </c>
       <c r="G1772" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48807,7 +48810,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1773" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48833,7 +48836,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1774" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48859,7 +48862,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1775" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48885,7 +48888,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1776" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48911,7 +48914,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1777" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48937,7 +48940,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1778" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48963,7 +48966,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1779" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48989,7 +48992,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1780" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49015,7 +49018,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1781" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49041,7 +49044,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1782" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49067,7 +49070,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1783" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49093,7 +49096,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1784" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49119,7 +49122,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1785" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49145,7 +49148,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1786" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49171,7 +49174,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1787" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49197,7 +49200,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1788" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49223,7 +49226,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1789" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49249,7 +49252,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1790" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49275,7 +49278,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1791" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49301,7 +49304,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1792" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49327,7 +49330,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1793" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49353,7 +49356,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1794" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49379,7 +49382,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1795" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49405,7 +49408,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -49431,7 +49434,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -49457,7 +49460,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -49483,7 +49486,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1799" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -49509,7 +49512,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1800" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -49535,7 +49538,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1801" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -49561,7 +49564,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1802" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -49587,7 +49590,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -49613,7 +49616,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1804" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -49639,7 +49642,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1805" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -49665,7 +49668,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1806" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49691,7 +49694,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1807" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49717,7 +49720,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1808" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49743,7 +49746,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G1809" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49769,7 +49772,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1810" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49795,7 +49798,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1811" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49821,7 +49824,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1812" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49847,7 +49850,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1813" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49873,7 +49876,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1814" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49899,7 +49902,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1815" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49925,7 +49928,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1816" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49951,7 +49954,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1817" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49977,7 +49980,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1818" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -50003,7 +50006,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1819" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50029,7 +50032,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1820" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50055,7 +50058,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1821" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -50081,7 +50084,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1822" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -50107,7 +50110,7 @@
         <v>4.25</v>
       </c>
       <c r="G1823" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -50133,7 +50136,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1824" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -50159,7 +50162,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1825" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -50185,7 +50188,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G1826" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50211,7 +50214,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1827" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50237,7 +50240,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1828" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50263,7 +50266,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1829" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -50289,7 +50292,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1830" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50315,7 +50318,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1831" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50341,7 +50344,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1832" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50367,7 +50370,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1833" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50393,7 +50396,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1834" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50419,7 +50422,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G1835" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -50445,7 +50448,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G1836" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -50471,7 +50474,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1837" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -50497,7 +50500,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1838" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -50523,7 +50526,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1839" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -50549,7 +50552,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G1840" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -50575,7 +50578,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1841" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -50601,7 +50604,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1842" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -50627,7 +50630,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1843" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -50653,7 +50656,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1844" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50679,7 +50682,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1845" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50705,7 +50708,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1846" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50731,7 +50734,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G1847" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50757,7 +50760,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1848" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50783,7 +50786,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1849" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50809,7 +50812,7 @@
         <v>4.25</v>
       </c>
       <c r="G1850" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50835,7 +50838,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1851" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50861,7 +50864,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G1852" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50887,7 +50890,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1853" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50913,7 +50916,7 @@
         <v>4.25</v>
       </c>
       <c r="G1854" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50939,7 +50942,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G1855" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50965,7 +50968,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1856" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50991,7 +50994,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G1857" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51017,7 +51020,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1858" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51043,7 +51046,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1859" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51069,7 +51072,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1860" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51095,7 +51098,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1861" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -51121,7 +51124,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51147,7 +51150,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1863" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -51173,7 +51176,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1864" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -51199,7 +51202,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1865" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -51225,7 +51228,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G1866" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51251,7 +51254,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1867" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51277,7 +51280,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1868" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -51303,7 +51306,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1869" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -51329,7 +51332,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1870" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -51355,7 +51358,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1871" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -51381,7 +51384,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1872" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -51407,7 +51410,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1873" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -51433,7 +51436,7 @@
         <v>3.95499992370605</v>
       </c>
       <c r="G1874" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -51459,7 +51462,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1875" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -51485,7 +51488,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G1876" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -51511,7 +51514,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1877" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -51537,7 +51540,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1878" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -51563,7 +51566,7 @@
         <v>4.21500015258789</v>
       </c>
       <c r="G1879" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -51589,7 +51592,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1880" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -51615,7 +51618,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G1881" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -51641,7 +51644,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1882" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -51667,7 +51670,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1883" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51693,7 +51696,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G1884" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51719,7 +51722,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G1885" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51745,7 +51748,7 @@
         <v>4.25</v>
       </c>
       <c r="G1886" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51771,7 +51774,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51797,7 +51800,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1888" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51823,7 +51826,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51849,7 +51852,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1890" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51875,7 +51878,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1891" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51901,7 +51904,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1892" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51927,7 +51930,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1893" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51953,7 +51956,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G1894" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51979,7 +51982,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1895" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52005,7 +52008,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1896" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52031,7 +52034,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1897" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52057,7 +52060,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G1898" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52083,7 +52086,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1899" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52109,7 +52112,7 @@
         <v>4.43499994277954</v>
       </c>
       <c r="G1900" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52135,7 +52138,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52161,7 +52164,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G1902" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52187,7 +52190,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1903" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52213,7 +52216,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G1904" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52239,7 +52242,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1905" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52265,7 +52268,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52291,7 +52294,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1907" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52317,7 +52320,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1908" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52343,7 +52346,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1909" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52369,7 +52372,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1910" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52395,7 +52398,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1911" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -52421,7 +52424,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1912" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -52447,7 +52450,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1913" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -52473,7 +52476,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1914" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -52499,7 +52502,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1915" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -52525,7 +52528,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1916" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -52551,7 +52554,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G1917" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -52577,7 +52580,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G1918" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -52603,7 +52606,7 @@
         <v>4.42500019073486</v>
       </c>
       <c r="G1919" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -52629,7 +52632,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G1920" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -52655,7 +52658,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1921" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52681,7 +52684,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G1922" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52707,7 +52710,7 @@
         <v>4.35500001907349</v>
       </c>
       <c r="G1923" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52733,7 +52736,7 @@
         <v>4.34999990463257</v>
       </c>
       <c r="G1924" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52759,7 +52762,7 @@
         <v>4.44500017166138</v>
       </c>
       <c r="G1925" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52785,7 +52788,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1926" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52811,7 +52814,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G1927" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52837,7 +52840,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G1928" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52863,7 +52866,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1929" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52889,7 +52892,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1930" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52915,7 +52918,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G1931" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52941,7 +52944,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G1932" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52967,7 +52970,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1933" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52993,7 +52996,7 @@
         <v>4.47499990463257</v>
       </c>
       <c r="G1934" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53019,7 +53022,7 @@
         <v>4.45499992370605</v>
       </c>
       <c r="G1935" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53045,7 +53048,7 @@
         <v>4.5</v>
       </c>
       <c r="G1936" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53071,7 +53074,7 @@
         <v>4.52500009536743</v>
       </c>
       <c r="G1937" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53097,7 +53100,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1938" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53123,7 +53126,7 @@
         <v>4.56500005722046</v>
       </c>
       <c r="G1939" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53149,7 +53152,7 @@
         <v>4.5</v>
       </c>
       <c r="G1940" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53175,7 +53178,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1941" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53201,7 +53204,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G1942" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53227,7 +53230,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1943" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53253,7 +53256,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G1944" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53279,7 +53282,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G1945" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53305,7 +53308,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G1946" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53331,7 +53334,7 @@
         <v>4.49499988555908</v>
       </c>
       <c r="G1947" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53357,7 +53360,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G1948" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53383,7 +53386,7 @@
         <v>4.54500007629395</v>
       </c>
       <c r="G1949" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53409,7 +53412,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G1950" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -53435,7 +53438,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1951" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -53461,7 +53464,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1952" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -53487,7 +53490,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G1953" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -53513,7 +53516,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G1954" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -53539,7 +53542,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G1955" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -53565,7 +53568,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1956" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -53591,7 +53594,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -53617,7 +53620,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G1958" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -53643,7 +53646,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G1959" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -53669,7 +53672,7 @@
         <v>4.83500003814697</v>
       </c>
       <c r="G1960" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53695,7 +53698,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G1961" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53721,7 +53724,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G1962" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53747,7 +53750,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1963" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53773,7 +53776,7 @@
         <v>4.85500001907349</v>
       </c>
       <c r="G1964" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53799,7 +53802,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G1965" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53825,7 +53828,7 @@
         <v>4.92500019073486</v>
       </c>
       <c r="G1966" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53851,7 +53854,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1967" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53877,7 +53880,7 @@
         <v>5</v>
       </c>
       <c r="G1968" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53903,7 +53906,7 @@
         <v>5</v>
       </c>
       <c r="G1969" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53929,7 +53932,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1970" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53955,7 +53958,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1971" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53981,7 +53984,7 @@
         <v>4.96500015258789</v>
       </c>
       <c r="G1972" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54007,7 +54010,7 @@
         <v>4.9850001335144</v>
       </c>
       <c r="G1973" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54033,7 +54036,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G1974" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54059,7 +54062,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54085,7 +54088,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1976" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54111,7 +54114,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G1977" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54137,7 +54140,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G1978" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54163,7 +54166,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1979" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54189,7 +54192,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1980" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54215,7 +54218,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1981" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54241,7 +54244,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1982" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54267,7 +54270,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1983" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54293,7 +54296,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1984" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54319,7 +54322,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1985" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54345,7 +54348,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1986" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54371,7 +54374,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1987" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54397,7 +54400,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1988" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -54423,7 +54426,7 @@
         <v>5.5</v>
       </c>
       <c r="G1989" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -54449,7 +54452,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1990" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -54475,7 +54478,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1991" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -54501,7 +54504,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -54527,7 +54530,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1993" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -54553,7 +54556,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1994" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -54579,7 +54582,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1995" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -54605,7 +54608,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1996" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -54631,7 +54634,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1997" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -54657,7 +54660,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1998" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54683,7 +54686,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1999" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54709,7 +54712,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2000" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54735,7 +54738,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2001" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54761,7 +54764,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G2002" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54787,7 +54790,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54813,7 +54816,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54839,7 +54842,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2005" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54865,7 +54868,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2006" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54891,7 +54894,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2007" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54917,7 +54920,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2008" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54943,7 +54946,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2009" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54969,7 +54972,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2010" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54995,7 +54998,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2011" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55021,7 +55024,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2012" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55047,7 +55050,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2013" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55073,7 +55076,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2014" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55099,7 +55102,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2015" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55125,7 +55128,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2016" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55151,7 +55154,7 @@
         <v>5.75</v>
       </c>
       <c r="G2017" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55177,7 +55180,7 @@
         <v>5.75</v>
       </c>
       <c r="G2018" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55203,7 +55206,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2019" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55229,7 +55232,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2020" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55255,7 +55258,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2021" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55281,7 +55284,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2022" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55307,7 +55310,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2023" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55333,7 +55336,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2024" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55359,7 +55362,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G2025" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55385,7 +55388,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2026" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55411,7 +55414,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G2027" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -55437,7 +55440,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2028" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -55463,7 +55466,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2029" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -55489,7 +55492,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2030" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -55515,7 +55518,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2031" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -55541,7 +55544,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2032" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -55567,7 +55570,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2033" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -55593,7 +55596,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2034" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -55619,7 +55622,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2035" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -55645,7 +55648,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G2036" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -55671,7 +55674,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2037" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55697,7 +55700,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G2038" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55723,7 +55726,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G2039" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55749,7 +55752,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55775,7 +55778,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2041" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55801,7 +55804,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G2042" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55827,7 +55830,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G2043" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55853,7 +55856,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G2044" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55879,7 +55882,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2045" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55905,7 +55908,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2046" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55931,7 +55934,7 @@
         <v>5.92999982833862</v>
       </c>
       <c r="G2047" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55957,7 +55960,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G2048" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55983,7 +55986,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G2049" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56009,7 +56012,7 @@
         <v>6</v>
       </c>
       <c r="G2050" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56035,7 +56038,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G2051" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56061,7 +56064,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G2052" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56087,7 +56090,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2053" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56113,7 +56116,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G2054" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56139,7 +56142,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G2055" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56165,7 +56168,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G2056" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56191,7 +56194,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2057" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56199,7 +56202,7 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>46027.6910532407</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2058" t="n">
         <v>153929</v>
@@ -56217,9 +56220,35 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2058" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H2058" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="1" t="n">
+        <v>46028.6869328704</v>
+      </c>
+      <c r="B2059" t="n">
+        <v>104163</v>
+      </c>
+      <c r="C2059" t="n">
+        <v>6.34000015258789</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>6.23000001907349</v>
+      </c>
+      <c r="E2059" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>6.26999998092651</v>
+      </c>
+      <c r="G2059" t="s">
+        <v>787</v>
+      </c>
+      <c r="H2059" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/EQUI.MI.xlsx
+++ b/data/EQUI.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="795">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61930727958679</t>
+    <t xml:space="preserve">1.61930751800537</t>
   </si>
   <si>
     <t xml:space="preserve">EQUI.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68691504001617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71744740009308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71417570114136</t>
+    <t xml:space="preserve">1.6869148015976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71744728088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71417582035065</t>
   </si>
   <si>
     <t xml:space="preserve">1.71090483665466</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70109057426453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67055833339691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67492008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69018590450287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67710065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65856337547302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6574729681015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65529179573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63784503936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64656829833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65311110019684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65420150756836</t>
+    <t xml:space="preserve">1.70109045505524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67055809497833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.674919962883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69018614292145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67710089683533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65856313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65747284889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65529203414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63784515857697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64656841754913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65311133861542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65420138835907</t>
   </si>
   <si>
     <t xml:space="preserve">1.64874935150146</t>
@@ -98,67 +98,67 @@
     <t xml:space="preserve">1.65965366363525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64002561569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64329719543457</t>
+    <t xml:space="preserve">1.64002573490143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64329695701599</t>
   </si>
   <si>
     <t xml:space="preserve">1.62585008144379</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64765894412994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67382943630219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68909597396851</t>
+    <t xml:space="preserve">1.64765882492065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67382955551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68909549713135</t>
   </si>
   <si>
     <t xml:space="preserve">1.67928171157837</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67819130420685</t>
+    <t xml:space="preserve">1.67819154262543</t>
   </si>
   <si>
     <t xml:space="preserve">1.67164838314056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67273938655853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70327186584473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69563794136047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66565132141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66837728023529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69836449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7038162946701</t>
+    <t xml:space="preserve">1.67273890972137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70327150821686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70654284954071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69563841819763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66565120220184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66837692260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6983642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70381653308868</t>
   </si>
   <si>
     <t xml:space="preserve">1.68745994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68473410606384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67110359668732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75016057491302</t>
+    <t xml:space="preserve">1.68473386764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67110311985016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75016033649445</t>
   </si>
   <si>
     <t xml:space="preserve">1.72289931774139</t>
@@ -167,157 +167,160 @@
     <t xml:space="preserve">1.72835159301758</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74470818042755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73107743263245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73925602436066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74198234081268</t>
+    <t xml:space="preserve">1.74470829963684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73107767105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73925614356995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74198198318481</t>
   </si>
   <si>
     <t xml:space="preserve">1.79923021793365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77742147445679</t>
+    <t xml:space="preserve">1.77742159366608</t>
   </si>
   <si>
     <t xml:space="preserve">1.7719691991806</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652982711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7965042591095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78832590579987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81831324100494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82376539707184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80468285083771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81558692455292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81286084651947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81013476848602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79377818107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84284806251526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88950252532959</t>
+    <t xml:space="preserve">1.73652970790863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79650437831879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78832578659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81831312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82376551628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80468273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81558680534363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81286072731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81013464927673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79377830028534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84284830093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8895024061203</t>
   </si>
   <si>
     <t xml:space="preserve">1.87200689315796</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88075459003448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84576380252838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81952106952667</t>
+    <t xml:space="preserve">1.88075482845306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84576392173767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81952083110809</t>
   </si>
   <si>
     <t xml:space="preserve">1.83118450641632</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86034369468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87492263317108</t>
+    <t xml:space="preserve">1.8603435754776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87492287158966</t>
   </si>
   <si>
     <t xml:space="preserve">1.87783896923065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86325943470001</t>
+    <t xml:space="preserve">1.86325919628143</t>
   </si>
   <si>
     <t xml:space="preserve">1.88367068767548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80785751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76703441143036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79619336128235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79910981655121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78161442279816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82243692874908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78453004360199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81660509109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83410012722015</t>
+    <t xml:space="preserve">1.80785727500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76703453063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79619371891022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79910957813263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78161430358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82243669033051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78452968597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81660485267639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83410024642944</t>
   </si>
   <si>
     <t xml:space="preserve">1.83701634407043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84868013858795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86909103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85159552097321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8574275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91282939910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89241826534271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88658666610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89533460140228</t>
+    <t xml:space="preserve">1.84867990016937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86909115314484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85159575939178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84284794330597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85742735862732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91282951831818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89241874217987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88658654689789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89533412456512</t>
   </si>
   <si>
     <t xml:space="preserve">1.83993220329285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85451209545135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86617541313171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81077361106873</t>
+    <t xml:space="preserve">1.85451185703278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86617529392242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81077337265015</t>
   </si>
   <si>
     <t xml:space="preserve">1.89825034141541</t>
@@ -326,13 +329,13 @@
     <t xml:space="preserve">1.91574549674988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95365190505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96239995956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92449343204498</t>
+    <t xml:space="preserve">1.95365238189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96239984035492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92449307441711</t>
   </si>
   <si>
     <t xml:space="preserve">1.96531569957733</t>
@@ -341,37 +344,37 @@
     <t xml:space="preserve">2.00613856315613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00905394554138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98281133174896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95948362350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9274092912674</t>
+    <t xml:space="preserve">2.00905442237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98281097412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95948398113251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92740869522095</t>
   </si>
   <si>
     <t xml:space="preserve">1.90991365909576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95656788349152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01197004318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00030660629272</t>
+    <t xml:space="preserve">1.95656847953796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01197052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00030636787415</t>
   </si>
   <si>
     <t xml:space="preserve">1.94490456581116</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94782030582428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90699779987335</t>
+    <t xml:space="preserve">1.94782042503357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90699756145477</t>
   </si>
   <si>
     <t xml:space="preserve">1.92157745361328</t>
@@ -383,265 +386,265 @@
     <t xml:space="preserve">2.06737232208252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98864305019379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9944748878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97406351566315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93907272815704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93032491207123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94198870658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90408205986023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82535302639008</t>
+    <t xml:space="preserve">1.9886429309845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99447476863861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97406363487244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93907248973846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93032515048981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94198834896088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90408194065094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8253527879715</t>
   </si>
   <si>
     <t xml:space="preserve">1.81368923187256</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79036176204681</t>
+    <t xml:space="preserve">1.79036200046539</t>
   </si>
   <si>
     <t xml:space="preserve">1.82826864719391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02852940559387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90331125259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89705038070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89078938961029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87826800346375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82192015647888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79061543941498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78435444831848</t>
+    <t xml:space="preserve">2.02852916717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90331161022186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8970502614975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89078962802887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87826764583588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8219199180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7906152009964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78435432910919</t>
   </si>
   <si>
     <t xml:space="preserve">1.75931107997894</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74678909778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73426759243011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72800660133362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65287590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69044101238251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64661490917206</t>
+    <t xml:space="preserve">1.74678885936737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73426735401154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72800636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65287601947784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69044137001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64661478996277</t>
   </si>
   <si>
     <t xml:space="preserve">1.60904943943024</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62783205509186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66539752483368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67791926860809</t>
+    <t xml:space="preserve">1.62783217430115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6653972864151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67791950702667</t>
   </si>
   <si>
     <t xml:space="preserve">1.63409304618835</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67165839672089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62157094478607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60278880596161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68418025970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70296287536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.696702003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70922386646271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71548449993134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65913653373718</t>
+    <t xml:space="preserve">1.67165887355804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62157106399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6027889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68418037891388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70296275615692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69670236110687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70922362804413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71548473834991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65913665294647</t>
   </si>
   <si>
     <t xml:space="preserve">1.64035379886627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61531007289886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59652757644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57148432731628</t>
+    <t xml:space="preserve">1.61531054973602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59652769565582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57148408889771</t>
   </si>
   <si>
     <t xml:space="preserve">1.56522345542908</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55896246433258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57774519920349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55270159244537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58400595188141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77183258533478</t>
+    <t xml:space="preserve">1.55896234512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57774496078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55270147323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58400583267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77183282375336</t>
   </si>
   <si>
     <t xml:space="preserve">1.81565916538239</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80939817428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80313742160797</t>
+    <t xml:space="preserve">1.8093980550766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80313694477081</t>
   </si>
   <si>
     <t xml:space="preserve">1.77809369564056</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74052798748016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76557159423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75305008888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59026682376862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47757077217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36487472057343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54644060134888</t>
+    <t xml:space="preserve">1.74052822589874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76557195186615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75305020809174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59026694297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47757089138031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36487460136414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54644048213959</t>
   </si>
   <si>
     <t xml:space="preserve">1.50261449813843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38365733623505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40244007110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32104849815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30226564407349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3273092508316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3335702419281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28348314762115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29600465297699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.28974390029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3398312330246</t>
+    <t xml:space="preserve">1.38365709781647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40243995189667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3210483789444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30226576328278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32730948925018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33357036113739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28348302841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.29600477218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.28974401950836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33983099460602</t>
   </si>
   <si>
     <t xml:space="preserve">1.35235297679901</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3147873878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3460921049118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43374419212341</t>
+    <t xml:space="preserve">1.31478750705719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34609198570251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43374466896057</t>
   </si>
   <si>
     <t xml:space="preserve">1.38991808891296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39617919921875</t>
+    <t xml:space="preserve">1.39617931842804</t>
   </si>
   <si>
     <t xml:space="preserve">1.45878803730011</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42122280597687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37739634513855</t>
+    <t xml:space="preserve">1.42122256755829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37739646434784</t>
   </si>
   <si>
     <t xml:space="preserve">1.41496193408966</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4400053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4462662935257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42748367786407</t>
+    <t xml:space="preserve">1.44000566005707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44626617431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4274834394455</t>
   </si>
   <si>
     <t xml:space="preserve">1.53391873836517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40870094299316</t>
+    <t xml:space="preserve">1.40870082378387</t>
   </si>
   <si>
     <t xml:space="preserve">1.4525271654129</t>
@@ -650,97 +653,94 @@
     <t xml:space="preserve">1.51513624191284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72174561023712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200677394867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85863530635834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8051495552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65806365013123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64469182491302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61126339435577</t>
+    <t xml:space="preserve">1.72174549102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85863554477692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80514991283417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65806341171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64469194412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61126315593719</t>
   </si>
   <si>
     <t xml:space="preserve">1.63800632953644</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61794912815094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60457742214203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57114863395691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65137779712677</t>
+    <t xml:space="preserve">1.61794900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60457766056061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5711487531662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65137767791748</t>
   </si>
   <si>
     <t xml:space="preserve">1.63132047653198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6647492647171</t>
+    <t xml:space="preserve">1.66474914550781</t>
   </si>
   <si>
     <t xml:space="preserve">1.62463486194611</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67143487930298</t>
+    <t xml:space="preserve">1.67143511772156</t>
   </si>
   <si>
     <t xml:space="preserve">1.68480634689331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69817781448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59120619297028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55777740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52434873580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51766300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53103411197662</t>
+    <t xml:space="preserve">1.69817793369293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59120607376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55777728557587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52434861660004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51766276359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53103458881378</t>
   </si>
   <si>
     <t xml:space="preserve">1.54440569877625</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55109143257141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53771984577179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57783436775208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58452022075653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56446301937103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49760556221008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51097702980042</t>
+    <t xml:space="preserve">1.5510915517807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53772032260895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57783448696136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58452010154724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56446266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49760544300079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5109771490097</t>
   </si>
   <si>
     <t xml:space="preserve">1.59789180755615</t>
@@ -749,142 +749,142 @@
     <t xml:space="preserve">1.50429129600525</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49091994762421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48423409461975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47754848003387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47086262702942</t>
+    <t xml:space="preserve">1.4909200668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48423397541046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4775482416153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47086274623871</t>
   </si>
   <si>
     <t xml:space="preserve">1.46417701244354</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44411969184875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4508056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43074834346771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41737675666809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36389088630676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33046209812164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34383380413055</t>
+    <t xml:space="preserve">1.44411981105804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45080542564392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43074822425842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41737687587738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36389064788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33046221733093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34383368492126</t>
   </si>
   <si>
     <t xml:space="preserve">1.3371479511261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32377660274506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32043349742889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67812073230743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73829197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77172100543976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75166392326355</t>
+    <t xml:space="preserve">1.32377648353577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.32043361663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67812049388885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73829221725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77172112464905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75166368484497</t>
   </si>
   <si>
     <t xml:space="preserve">1.7449779510498</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73160636425018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7650351524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78509247303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79177808761597</t>
+    <t xml:space="preserve">1.73160624504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76503539085388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78509294986725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79177820682526</t>
   </si>
   <si>
     <t xml:space="preserve">1.75834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79846429824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520687580109</t>
+    <t xml:space="preserve">1.79846394062042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520663738251</t>
   </si>
   <si>
     <t xml:space="preserve">1.85194981098175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86532115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87869298458099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89206409454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91212153434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92549300193787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89874994754791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87200701236725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83857858181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90543568134308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88537859916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91880714893341</t>
+    <t xml:space="preserve">1.86532127857208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8786928653717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89206421375275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91212141513824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92549276351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8987500667572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87200725078583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83857822418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90543556213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88537871837616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91880702972412</t>
   </si>
   <si>
     <t xml:space="preserve">1.96560740470886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99903583526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99235045909882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01240754127502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98566436767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97897863388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00572180747986</t>
+    <t xml:space="preserve">1.9990359544754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99235033988953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01240730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98566448688507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97897899150848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00572156906128</t>
   </si>
   <si>
     <t xml:space="preserve">2.01909327507019</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">2.03246474266052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04629111289978</t>
+    <t xml:space="preserve">2.0462908744812</t>
   </si>
   <si>
     <t xml:space="preserve">2.05320429801941</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">2.08085680007935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03937768936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08776998519897</t>
+    <t xml:space="preserve">2.03937816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0877697467804</t>
   </si>
   <si>
     <t xml:space="preserve">2.06011748313904</t>
@@ -917,28 +917,28 @@
     <t xml:space="preserve">2.06703042984009</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07394361495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10850954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12233543395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17072772979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14998817443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19838070869446</t>
+    <t xml:space="preserve">2.0739438533783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10850930213928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12233567237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17072749137878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14998841285706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19838047027588</t>
   </si>
   <si>
     <t xml:space="preserve">2.20529365539551</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19146704673767</t>
+    <t xml:space="preserve">2.19146728515625</t>
   </si>
   <si>
     <t xml:space="preserve">2.16381478309631</t>
@@ -947,34 +947,34 @@
     <t xml:space="preserve">2.14307498931885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764115333557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18455386161804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15690159797668</t>
+    <t xml:space="preserve">2.17764091491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18455410003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15690112113953</t>
   </si>
   <si>
     <t xml:space="preserve">2.22603273391724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21220660209656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23294615745544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23985910415649</t>
+    <t xml:space="preserve">2.21220636367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23294591903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23985958099365</t>
   </si>
   <si>
     <t xml:space="preserve">2.25368547439575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26059865951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26751160621643</t>
+    <t xml:space="preserve">2.2605984210968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26751136779785</t>
   </si>
   <si>
     <t xml:space="preserve">2.27442502975464</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">2.24677228927612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3089907169342</t>
+    <t xml:space="preserve">2.30899024009705</t>
   </si>
   <si>
     <t xml:space="preserve">2.32972979545593</t>
@@ -992,85 +992,85 @@
     <t xml:space="preserve">2.31590366363525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3228166103363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33664321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34355640411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38503527641296</t>
+    <t xml:space="preserve">2.32281684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33664345741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34355616569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38503503799438</t>
   </si>
   <si>
     <t xml:space="preserve">2.37120890617371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43342709541321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44725346565247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5163848400116</t>
+    <t xml:space="preserve">2.43342733383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44725370407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51638507843018</t>
   </si>
   <si>
     <t xml:space="preserve">2.48873257637024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49564576148987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56477689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55786371231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54403781890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57169008255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52329802513123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53021144866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55095100402832</t>
+    <t xml:space="preserve">2.49564528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.564777135849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55786395072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54403758049011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57169032096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52329850196838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53021121025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55095076560974</t>
   </si>
   <si>
     <t xml:space="preserve">2.58551645278931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59242963790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63390851020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62699508666992</t>
+    <t xml:space="preserve">2.59242939949036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63390874862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6269953250885</t>
   </si>
   <si>
     <t xml:space="preserve">2.65464758872986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64773440361023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62008213996887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64082169532776</t>
+    <t xml:space="preserve">2.64773464202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62008237838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64082145690918</t>
   </si>
   <si>
     <t xml:space="preserve">2.61316895484924</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66230630874634</t>
+    <t xml:space="preserve">2.66230654716492</t>
   </si>
   <si>
     <t xml:space="preserve">2.64100790023804</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">2.69780349731445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74040079116821</t>
+    <t xml:space="preserve">2.74040055274963</t>
   </si>
   <si>
     <t xml:space="preserve">2.79009699821472</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">2.768798828125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7475004196167</t>
+    <t xml:space="preserve">2.74750018119812</t>
   </si>
   <si>
     <t xml:space="preserve">2.73330116271973</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">2.76169919967651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71200275421143</t>
+    <t xml:space="preserve">2.71200251579285</t>
   </si>
   <si>
     <t xml:space="preserve">2.65520691871643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68360471725464</t>
+    <t xml:space="preserve">2.68360495567322</t>
   </si>
   <si>
     <t xml:space="preserve">2.62680888175964</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">2.67650532722473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66940569877625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70490336418152</t>
+    <t xml:space="preserve">2.66940593719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7049036026001</t>
   </si>
   <si>
     <t xml:space="preserve">2.75459957122803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71910262107849</t>
+    <t xml:space="preserve">2.71910238265991</t>
   </si>
   <si>
     <t xml:space="preserve">2.72620153427124</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">2.69070434570312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56291317939758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55581402778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59841132164001</t>
+    <t xml:space="preserve">2.56291365623474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55581426620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59841084480286</t>
   </si>
   <si>
     <t xml:space="preserve">2.79719686508179</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">2.54871439933777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49191880226135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47062039375305</t>
+    <t xml:space="preserve">2.49191856384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47062015533447</t>
   </si>
   <si>
     <t xml:space="preserve">2.37832689285278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25763583183289</t>
+    <t xml:space="preserve">2.25763607025146</t>
   </si>
   <si>
     <t xml:space="preserve">2.1724419593811</t>
@@ -1166,100 +1166,100 @@
     <t xml:space="preserve">2.21503877639771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34282970428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34992909431458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48481917381287</t>
+    <t xml:space="preserve">2.34282922744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34992933273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48481941223145</t>
   </si>
   <si>
     <t xml:space="preserve">2.59131169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47772002220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60551047325134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81139588356018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82559466362</t>
+    <t xml:space="preserve">2.47771978378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60551071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8113956451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82559442520142</t>
   </si>
   <si>
     <t xml:space="preserve">2.88239049911499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86819124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8965892791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87529134750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83979344367981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78299784660339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90368890762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88949036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81849551200867</t>
+    <t xml:space="preserve">2.8681914806366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89658951759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87529110908508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83979368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78299808502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90368914604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88949012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81849479675293</t>
   </si>
   <si>
     <t xml:space="preserve">2.8326940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8539924621582</t>
+    <t xml:space="preserve">2.85399270057678</t>
   </si>
   <si>
     <t xml:space="preserve">2.98100256919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95111799240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9735312461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94364666938782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91376185417175</t>
+    <t xml:space="preserve">2.95111775398254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97353148460388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9436469078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91376209259033</t>
   </si>
   <si>
     <t xml:space="preserve">2.87640595436096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81663656234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83905005455017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70456862449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59997200965881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61491465568542</t>
+    <t xml:space="preserve">2.81663680076599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83905029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70456838607788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59997224807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61491441726685</t>
   </si>
   <si>
     <t xml:space="preserve">2.60744333267212</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62238550186157</t>
+    <t xml:space="preserve">2.62238574028015</t>
   </si>
   <si>
     <t xml:space="preserve">2.65227007865906</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">2.62985682487488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65974140167236</t>
+    <t xml:space="preserve">2.65974187850952</t>
   </si>
   <si>
     <t xml:space="preserve">2.6373279094696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57008719444275</t>
+    <t xml:space="preserve">2.57008743286133</t>
   </si>
   <si>
     <t xml:space="preserve">2.58502960205078</t>
@@ -1283,88 +1283,88 @@
     <t xml:space="preserve">2.57755851745605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55514526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52526044845581</t>
+    <t xml:space="preserve">2.5551450252533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52526021003723</t>
   </si>
   <si>
     <t xml:space="preserve">2.59250116348267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54767394065857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50284695625305</t>
+    <t xml:space="preserve">2.54767370223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50284671783447</t>
   </si>
   <si>
     <t xml:space="preserve">2.47296190261841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45801949501038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49537563323975</t>
+    <t xml:space="preserve">2.45801973342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49537539482117</t>
   </si>
   <si>
     <t xml:space="preserve">2.4654905796051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48790454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48043322563171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53273153305054</t>
+    <t xml:space="preserve">2.48790431022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48043298721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53273177146912</t>
   </si>
   <si>
     <t xml:space="preserve">2.40572118759155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4356062412262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37583661079407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39077925682068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42813491821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44307732582092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41319227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39825034141541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42066407203674</t>
-  </si>
